--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1341,122 +1341,116 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8175</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>8175</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8250</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="H15" s="2" t="n">
+      <c r="D16" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>2.73</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="n">
-        <v>-0.058</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>-1165</v>
-      </c>
-      <c r="O15" s="2" t="n">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>-1130</v>
+      </c>
+      <c r="O16" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="P15" s="2" t="n">
-        <v>-370276</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>78145</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>-292130</v>
-      </c>
-      <c r="S15" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1415</v>
-      </c>
+      <c r="P16" s="2" t="n">
+        <v>-362101</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>78220</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-283880</v>
+      </c>
+      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1471,53 +1465,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I18" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N18" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O18" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q18" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R18" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S18" t="n">
         <v>1415</v>
@@ -1536,47 +1524,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J19" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L19" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N19" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P19" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q19" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R19" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S19" t="n">
         <v>1415</v>
@@ -1595,53 +1589,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N20" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q20" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R20" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
@@ -1660,53 +1648,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G21" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H21" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I21" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J21" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N21" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O21" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q21" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R21" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S21" t="n">
         <v>1415</v>
@@ -1725,43 +1713,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G22" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I22" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N22" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P22" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q22" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R22" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S22" t="n">
         <v>1415</v>
@@ -1780,53 +1778,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H23" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J23" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N23" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q23" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R23" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S23" t="n">
         <v>1415</v>
@@ -1845,46 +1833,56 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.21</v>
+      </c>
       <c r="G24" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9.42</v>
+      </c>
       <c r="I24" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>11.09</v>
+      </c>
+      <c r="J24" t="n">
+        <v>11.77</v>
+      </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M24" t="n">
-        <v>4.869</v>
+        <v>1.361</v>
       </c>
       <c r="N24" t="n">
-        <v>37762</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>11916</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.43</v>
+      </c>
       <c r="P24" t="n">
-        <v>37762</v>
+        <v>71497</v>
       </c>
       <c r="Q24" t="n">
-        <v>238</v>
+        <v>583</v>
       </c>
       <c r="R24" t="n">
-        <v>38000</v>
+        <v>72080</v>
       </c>
       <c r="S24" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="25">
@@ -1900,119 +1898,166 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="N25" t="n">
+        <v>37762</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>37762</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>238</v>
+      </c>
+      <c r="R25" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>0.23</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
         <v>0.23</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-0.23</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-1150</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>-1150</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>150</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>-1000</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>6178</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>321275</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>11269</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>332544</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8175</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>8175</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8250</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1353</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ROCKET</t>
+          <t>주도주</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2026,34 +2071,56 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1.58</v>
+      </c>
       <c r="P28" s="2" t="n">
-        <v>0</v>
+        <v>329450</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0</v>
+        <v>11344</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0</v>
+        <v>340794</v>
       </c>
       <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ABC-VCP</t>
+          <t>ROCKET</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2094,7 +2161,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TV알림</t>
+          <t>ABC-VCP</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2133,134 +2200,45 @@
       <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>27</v>
-      </c>
-      <c r="E34" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I34" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L34" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N34" t="n">
-        <v>507</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P34" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R34" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>45</v>
-      </c>
-      <c r="E35" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I35" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="K35" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>-0.703</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P35" t="n">
-        <v>-57188</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2829</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-54359</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1415</v>
-      </c>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TV알림</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2275,53 +2253,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
       <c r="F36" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="G36" t="n">
-        <v>3.14</v>
+        <v>5.47</v>
       </c>
       <c r="H36" t="n">
-        <v>2.76</v>
+        <v>3.29</v>
       </c>
       <c r="I36" t="n">
-        <v>8.68</v>
+        <v>17.35</v>
       </c>
       <c r="J36" t="n">
-        <v>9.01</v>
+        <v>20.1</v>
       </c>
       <c r="K36" t="n">
-        <v>247.7</v>
+        <v>185.95</v>
       </c>
       <c r="L36" t="n">
-        <v>174.67</v>
+        <v>187.46</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.288</v>
+        <v>0.274</v>
       </c>
       <c r="N36" t="n">
-        <v>1187</v>
+        <v>507</v>
       </c>
       <c r="O36" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="P36" t="n">
-        <v>36789</v>
+        <v>13680</v>
       </c>
       <c r="Q36" t="n">
-        <v>3306</v>
+        <v>1530</v>
       </c>
       <c r="R36" t="n">
-        <v>40095</v>
+        <v>15210</v>
       </c>
       <c r="S36" t="n">
         <v>1415</v>
@@ -2340,53 +2318,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="F37" t="n">
-        <v>3.53</v>
+        <v>1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="H37" t="n">
-        <v>4.11</v>
+        <v>2.96</v>
       </c>
       <c r="I37" t="n">
-        <v>11.14</v>
+        <v>13.15</v>
       </c>
       <c r="J37" t="n">
-        <v>9.65</v>
+        <v>5.82</v>
       </c>
       <c r="K37" t="n">
-        <v>533.86</v>
+        <v>313.5</v>
       </c>
       <c r="L37" t="n">
-        <v>403.59</v>
+        <v>175.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1.375</v>
+        <v>-0.703</v>
       </c>
       <c r="N37" t="n">
-        <v>8720</v>
+        <v>-1271</v>
       </c>
       <c r="O37" t="n">
-        <v>3.53</v>
+        <v>0.67</v>
       </c>
       <c r="P37" t="n">
-        <v>52321</v>
+        <v>-57188</v>
       </c>
       <c r="Q37" t="n">
-        <v>523</v>
+        <v>2829</v>
       </c>
       <c r="R37" t="n">
-        <v>52844</v>
+        <v>-54359</v>
       </c>
       <c r="S37" t="n">
         <v>1415</v>
@@ -2405,53 +2383,53 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>44.4</v>
+        <v>41.9</v>
       </c>
       <c r="F38" t="n">
-        <v>4.39</v>
+        <v>1.8</v>
       </c>
       <c r="G38" t="n">
-        <v>7.08</v>
+        <v>3.14</v>
       </c>
       <c r="H38" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="I38" t="n">
-        <v>7.95</v>
+        <v>8.68</v>
       </c>
       <c r="J38" t="n">
-        <v>2.19</v>
+        <v>9.01</v>
       </c>
       <c r="K38" t="n">
-        <v>800.2</v>
+        <v>247.7</v>
       </c>
       <c r="L38" t="n">
-        <v>60.03</v>
+        <v>174.67</v>
       </c>
       <c r="M38" t="n">
-        <v>2.446</v>
+        <v>-0.288</v>
       </c>
       <c r="N38" t="n">
-        <v>5075</v>
+        <v>1187</v>
       </c>
       <c r="O38" t="n">
-        <v>3.51</v>
+        <v>1.3</v>
       </c>
       <c r="P38" t="n">
-        <v>45679</v>
+        <v>36789</v>
       </c>
       <c r="Q38" t="n">
-        <v>661</v>
+        <v>3306</v>
       </c>
       <c r="R38" t="n">
-        <v>46340</v>
+        <v>40095</v>
       </c>
       <c r="S38" t="n">
         <v>1415</v>
@@ -2470,53 +2448,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
         <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="G39" t="n">
-        <v>6.04</v>
+        <v>6.86</v>
       </c>
       <c r="H39" t="n">
-        <v>2.52</v>
+        <v>4.11</v>
       </c>
       <c r="I39" t="n">
-        <v>13.51</v>
+        <v>11.14</v>
       </c>
       <c r="J39" t="n">
-        <v>4.74</v>
+        <v>9.65</v>
       </c>
       <c r="K39" t="n">
-        <v>2281.51</v>
+        <v>533.86</v>
       </c>
       <c r="L39" t="n">
-        <v>27.54</v>
+        <v>403.59</v>
       </c>
       <c r="M39" t="n">
-        <v>1.758</v>
+        <v>1.375</v>
       </c>
       <c r="N39" t="n">
-        <v>851</v>
+        <v>8720</v>
       </c>
       <c r="O39" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="P39" t="n">
-        <v>13616</v>
+        <v>52321</v>
       </c>
       <c r="Q39" t="n">
-        <v>1561</v>
+        <v>523</v>
       </c>
       <c r="R39" t="n">
-        <v>15177</v>
+        <v>52844</v>
       </c>
       <c r="S39" t="n">
         <v>1415</v>
@@ -2535,46 +2513,56 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>44.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.39</v>
+      </c>
       <c r="G40" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>7.08</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.26</v>
+      </c>
       <c r="I40" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
+        <v>7.95</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.19</v>
+      </c>
       <c r="K40" t="n">
-        <v>1659.27</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+        <v>800.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>60.03</v>
+      </c>
       <c r="M40" t="n">
-        <v>15.576</v>
+        <v>2.446</v>
       </c>
       <c r="N40" t="n">
-        <v>88875</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>5075</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.51</v>
+      </c>
       <c r="P40" t="n">
-        <v>88875</v>
+        <v>45679</v>
       </c>
       <c r="Q40" t="n">
-        <v>185</v>
+        <v>661</v>
       </c>
       <c r="R40" t="n">
-        <v>89060</v>
+        <v>46340</v>
       </c>
       <c r="S40" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="41">
@@ -2590,34 +2578,56 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L41" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N41" t="n">
+        <v>851</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.14</v>
+      </c>
       <c r="P41" t="n">
-        <v>-1537</v>
+        <v>13616</v>
       </c>
       <c r="Q41" t="n">
-        <v>95</v>
+        <v>1561</v>
       </c>
       <c r="R41" t="n">
-        <v>-1442</v>
+        <v>15177</v>
       </c>
       <c r="S41" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="42">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2644,333 +2654,313 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>1.54</v>
+        <v>15.58</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>1.54</v>
+        <v>15.58</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>16147.65</v>
+        <v>1659.27</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>1.542</v>
+        <v>15.576</v>
       </c>
       <c r="N42" t="n">
-        <v>60798</v>
+        <v>88875</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
+        <v>88875</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>185</v>
+      </c>
+      <c r="R42" t="n">
+        <v>89060</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>-1537</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>95</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-1442</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>16147.65</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="N44" t="n">
+        <v>60798</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
         <v>49448</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q44" t="n">
         <v>1099</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R44" t="n">
         <v>50548</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S44" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D45" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E45" s="2" t="n">
         <v>42.6</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>4.59</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>887.1799999999999</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>0.312</v>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N45" s="2" t="n">
         <v>1872</v>
       </c>
-      <c r="O43" s="2" t="n">
+      <c r="O45" s="2" t="n">
         <v>1.47</v>
       </c>
-      <c r="P43" s="2" t="n">
+      <c r="P45" s="2" t="n">
         <v>241683</v>
       </c>
-      <c r="Q43" s="2" t="n">
+      <c r="Q45" s="2" t="n">
         <v>11789</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R45" s="2" t="n">
         <v>253473</v>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D47" t="n">
         <v>3</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
         <v>0.34</v>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
         <v>0.49</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
         <v>13.35</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M47" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N47" t="n">
         <v>-4880</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q47" t="n">
         <v>1291</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R47" t="n">
         <v>-13350</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S47" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="n">
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="n">
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="Q48" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="M49" t="n">
-        <v>-0.486</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-7995</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>-15989</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>989</v>
-      </c>
-      <c r="R49" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2985,253 +2975,308 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-0.486</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-7995</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-15989</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>989</v>
+      </c>
+      <c r="R51" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D52" t="n">
         <v>4</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E52" t="n">
         <v>75</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F52" t="n">
         <v>2.87</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G52" t="n">
         <v>0.23</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H52" t="n">
         <v>0.08</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I52" t="n">
         <v>0.58</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J52" t="n">
         <v>0.08</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K52" t="n">
         <v>50.06</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L52" t="n">
         <v>55.1</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M52" t="n">
         <v>0.15</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N52" t="n">
         <v>2446</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O52" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P52" t="n">
         <v>9783</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q52" t="n">
         <v>1867</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R52" t="n">
         <v>11650</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S52" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D53" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E53" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F53" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>0.58</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K53" s="2" t="n">
         <v>50.06</v>
       </c>
-      <c r="L51" s="2" t="n">
+      <c r="L53" s="2" t="n">
         <v>31.53</v>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="M53" s="2" t="n">
         <v>-0.593</v>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N53" s="2" t="n">
         <v>-9037</v>
       </c>
-      <c r="O51" s="2" t="n">
+      <c r="O53" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>-144600</v>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="Q53" s="2" t="n">
         <v>7375</v>
       </c>
-      <c r="R51" s="2" t="n">
+      <c r="R53" s="2" t="n">
         <v>-137225</v>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D55" t="n">
         <v>12</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>16.7</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>0.72</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>0.44</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>0.64</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I55" t="n">
         <v>0.84</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J55" t="n">
         <v>1.81</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>14.12</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L55" t="n">
         <v>26.24</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M55" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N55" t="n">
         <v>-6941</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O55" t="n">
         <v>0.14</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P55" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q55" t="n">
         <v>5515</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R55" t="n">
         <v>-77775</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S55" t="n">
         <v>1415</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>-0.461</v>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>-6941</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>-83290</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>5515</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>-77775</v>
-      </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>삼닉v3_미분류</t>
+          <t>삼닉v3_MA</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3245,34 +3290,56 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0.14</v>
+      </c>
       <c r="P56" s="2" t="n">
-        <v>0</v>
+        <v>-83290</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>0</v>
+        <v>5515</v>
       </c>
       <c r="R56" s="2" t="n">
-        <v>0</v>
+        <v>-77775</v>
       </c>
       <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>5minHL</t>
+          <t>삼닉v3_미분류</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3313,7 +3380,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>5minHL2</t>
+          <t>5minHL</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3354,7 +3421,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>5minHL_동시</t>
+          <t>5minHL2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3393,128 +3460,45 @@
       <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M64" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N64" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>26</v>
-      </c>
-      <c r="R64" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>50</v>
-      </c>
-      <c r="F65" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G65" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1279.97</v>
-      </c>
-      <c r="L65" t="n">
-        <v>875.09</v>
-      </c>
-      <c r="M65" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="N65" t="n">
-        <v>4951</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P65" t="n">
-        <v>29704</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>756</v>
-      </c>
-      <c r="R65" t="n">
-        <v>30460</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3529,53 +3513,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K66" t="n">
-        <v>4319.93</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>1351.81</v>
+        <v>49.85</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.059</v>
+        <v>-2.747</v>
       </c>
       <c r="N66" t="n">
-        <v>-3794</v>
+        <v>-2426</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-11383</v>
+        <v>-2426</v>
       </c>
       <c r="Q66" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="R66" t="n">
-        <v>-11230</v>
+        <v>-2400</v>
       </c>
       <c r="S66" t="n">
         <v>1415</v>
@@ -3594,43 +3572,53 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>100</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.93</v>
+      </c>
       <c r="G67" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I67" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K67" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
+        <v>1279.97</v>
+      </c>
+      <c r="L67" t="n">
+        <v>875.09</v>
+      </c>
       <c r="M67" t="n">
-        <v>1.678</v>
+        <v>-0.191</v>
       </c>
       <c r="N67" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O67" t="inlineStr"/>
+        <v>4951</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.93</v>
+      </c>
       <c r="P67" t="n">
-        <v>1670</v>
+        <v>29704</v>
       </c>
       <c r="Q67" t="n">
-        <v>30</v>
+        <v>756</v>
       </c>
       <c r="R67" t="n">
-        <v>1700</v>
+        <v>30460</v>
       </c>
       <c r="S67" t="n">
         <v>1415</v>
@@ -3649,124 +3637,181 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.08</v>
+      </c>
       <c r="H68" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
+        <v>3.13</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.08</v>
+      </c>
       <c r="J68" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K68" t="inlineStr"/>
+        <v>3.61</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4319.93</v>
+      </c>
       <c r="L68" t="n">
-        <v>5756.96</v>
+        <v>1351.81</v>
       </c>
       <c r="M68" t="n">
-        <v>-6.785</v>
+        <v>-2.059</v>
       </c>
       <c r="N68" t="n">
-        <v>-7272</v>
+        <v>-3794</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P68" t="n">
-        <v>-14543</v>
+        <v>-11383</v>
       </c>
       <c r="Q68" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="R68" t="n">
-        <v>-14485</v>
+        <v>-11230</v>
       </c>
       <c r="S68" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J69" s="2" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>30</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
         <v>7.52</v>
       </c>
-      <c r="K69" s="2" t="n">
-        <v>1633.99</v>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>2111.58</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>-1.689</v>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>4045</v>
-      </c>
-      <c r="S69" s="2" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>58</v>
+      </c>
+      <c r="R70" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_B</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3775,34 +3820,56 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>1.07</v>
+      </c>
       <c r="P71" s="2" t="n">
-        <v>0</v>
+        <v>3022</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>0</v>
+        <v>4045</v>
       </c>
       <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_1A0</t>
+          <t>KR_TR_ORD_B</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3841,117 +3908,105 @@
       <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E77" t="n">
         <v>100</v>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="n">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
         <v>1.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="n">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
         <v>1.3</v>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
         <v>7</v>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="n">
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="n">
         <v>1.299</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N77" t="n">
         <v>6421</v>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="n">
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
         <v>6421</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q77" t="n">
         <v>149</v>
       </c>
-      <c r="R75" t="n">
+      <c r="R77" t="n">
         <v>6570</v>
       </c>
-      <c r="S75" t="n">
+      <c r="S77" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="n">
-        <v>1.299</v>
-      </c>
-      <c r="N76" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>6570</v>
-      </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3965,34 +4020,46 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>6421</v>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R78" s="2" t="n">
-        <v>0</v>
+        <v>6570</v>
       </c>
       <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4033,7 +4100,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_BASE</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4074,7 +4141,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_BASE</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4115,7 +4182,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4156,7 +4223,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ADD1</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4197,7 +4264,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_ADD1</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4236,128 +4303,45 @@
       <c r="S90" s="2" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="n">
-        <v>3</v>
-      </c>
-      <c r="M92" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N92" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>949</v>
-      </c>
-      <c r="R92" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S92" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
-        <v>50</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G93" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H93" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="I93" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J93" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="K93" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L93" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M93" t="n">
-        <v>-0.896</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-471</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P93" t="n">
-        <v>9429</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>6892</v>
-      </c>
-      <c r="R93" t="n">
-        <v>16322</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1373</v>
-      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4372,56 +4356,50 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2.69</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I94" t="n">
-        <v>4.37</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="K94" t="n">
-        <v>18</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.787</v>
+        <v>-10.012</v>
       </c>
       <c r="N94" t="n">
-        <v>-62797</v>
+        <v>-71414</v>
       </c>
       <c r="O94" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>-340821</v>
+        <v>-71414</v>
       </c>
       <c r="Q94" t="n">
-        <v>9807</v>
+        <v>949</v>
       </c>
       <c r="R94" t="n">
-        <v>-331014</v>
+        <v>-70465</v>
       </c>
       <c r="S94" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="95">
@@ -4437,125 +4415,192 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J95" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K95" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-471</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P95" t="n">
+        <v>9429</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>6892</v>
+      </c>
+      <c r="R95" t="n">
+        <v>16322</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>40</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="J96" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="K96" t="n">
+        <v>18</v>
+      </c>
+      <c r="L96" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-0.787</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-62797</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-340821</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>9807</v>
+      </c>
+      <c r="R96" t="n">
+        <v>-331014</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D97" t="n">
         <v>6</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E97" t="n">
         <v>33.3</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F97" t="n">
         <v>0.95</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G97" t="n">
         <v>2.18</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H97" t="n">
         <v>2.6</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I97" t="n">
         <v>3.21</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J97" t="n">
         <v>3.37</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K97" t="n">
         <v>14</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L97" t="n">
         <v>13.25</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M97" t="n">
         <v>-1.004</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N97" t="n">
         <v>-6626</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O97" t="n">
         <v>0.48</v>
       </c>
-      <c r="P95" t="n">
+      <c r="P97" t="n">
         <v>-71076</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q97" t="n">
         <v>8465</v>
       </c>
-      <c r="R95" t="n">
+      <c r="R97" t="n">
         <v>-62611</v>
       </c>
-      <c r="S95" t="n">
+      <c r="S97" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1.315</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-19540</v>
-      </c>
-      <c r="O96" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>-473882</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>26113</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>-447768</v>
-      </c>
-      <c r="S96" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ORD_1A0</t>
+          <t>US_TR_ORD_B</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4569,34 +4614,56 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1.315</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-19540</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0.23</v>
+      </c>
       <c r="P98" s="2" t="n">
-        <v>0</v>
+        <v>-473882</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>0</v>
+        <v>26113</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>0</v>
+        <v>-447768</v>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4637,7 +4704,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4678,7 +4745,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -4719,7 +4786,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>US_TR_BASE</t>
+          <t>US_TR_VCP1</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4758,244 +4825,161 @@
       <c r="S106" s="2" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="n">
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
         <v>2.13</v>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="n">
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="n">
         <v>2.13</v>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="n">
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
         <v>1</v>
       </c>
-      <c r="M108" t="n">
+      <c r="M110" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N108" t="n">
+      <c r="N110" t="n">
         <v>-41586</v>
       </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="Q110" t="n">
         <v>2702</v>
       </c>
-      <c r="R108" t="n">
+      <c r="R110" t="n">
         <v>-38883</v>
       </c>
-      <c r="S108" t="n">
+      <c r="S110" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="n">
+      <c r="E111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="n">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="n">
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M109" s="2" t="n">
+      <c r="M111" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N111" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="2" t="n">
+      <c r="O111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q109" s="2" t="n">
+      <c r="Q111" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R109" s="2" t="n">
+      <c r="R111" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S109" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>7</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
-        <v>8</v>
-      </c>
-      <c r="M111" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R111" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S111" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>3</v>
-      </c>
-      <c r="E112" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H112" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I112" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J112" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K112" t="n">
-        <v>18</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-18508</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P112" t="n">
-        <v>-52375</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>4226</v>
-      </c>
-      <c r="R112" t="n">
-        <v>-48149</v>
-      </c>
-      <c r="S112" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5010,11 +4994,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5024,377 +5008,381 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>2.68</v>
+        <v>6.17</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
+        <v>8</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R113" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I114" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J114" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K114" t="n">
+        <v>18</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
         <v>7.5</v>
       </c>
-      <c r="M113" t="n">
+      <c r="M115" t="n">
         <v>-1.87</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N115" t="n">
         <v>-38258</v>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
         <v>-79635</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="Q115" t="n">
         <v>4778</v>
       </c>
-      <c r="R113" t="n">
+      <c r="R115" t="n">
         <v>-74857</v>
       </c>
-      <c r="S113" t="n">
+      <c r="S115" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-2.042</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>-15588</v>
-      </c>
-      <c r="O114" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P114" s="2" t="n">
-        <v>-187023</v>
-      </c>
-      <c r="Q114" s="2" t="n">
-        <v>10888</v>
-      </c>
-      <c r="R114" s="2" t="n">
-        <v>-176134</v>
-      </c>
-      <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-2.042</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-15588</v>
+      </c>
+      <c r="O116" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>-187023</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>10888</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>-176134</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="D118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D120" t="n">
         <v>2</v>
       </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
         <v>7.15</v>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
         <v>10.49</v>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
         <v>1</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M120" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N120" t="n">
         <v>-27445</v>
       </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q120" t="n">
         <v>1054</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R120" t="n">
         <v>-53835</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S120" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D121" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="n">
+      <c r="E121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="n">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="n">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M119" s="2" t="n">
+      <c r="M121" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N121" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" s="2" t="n">
+      <c r="O121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q119" s="2" t="n">
+      <c r="Q121" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R119" s="2" t="n">
+      <c r="R121" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S119" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>17</v>
-      </c>
-      <c r="E121" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G121" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H121" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I121" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J121" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M121" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N121" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O121" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P121" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R121" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>7</v>
-      </c>
-      <c r="E122" t="n">
-        <v>100</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N122" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R122" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S121" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5409,241 +5397,304 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>17</v>
+      </c>
+      <c r="E123" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G123" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I123" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O123" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P123" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>7</v>
+      </c>
+      <c r="E124" t="n">
+        <v>100</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N124" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R124" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D125" t="n">
         <v>4</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E125" t="n">
         <v>50</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F125" t="n">
         <v>2.51</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G125" t="n">
         <v>11.43</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H125" t="n">
         <v>2.87</v>
       </c>
-      <c r="I123" t="n">
+      <c r="I125" t="n">
         <v>12</v>
       </c>
-      <c r="J123" t="n">
+      <c r="J125" t="n">
         <v>4.94</v>
       </c>
-      <c r="K123" t="n">
+      <c r="K125" t="n">
         <v>14</v>
       </c>
-      <c r="L123" t="n">
+      <c r="L125" t="n">
         <v>14</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M125" t="n">
         <v>4.282</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N125" t="n">
         <v>7910</v>
       </c>
-      <c r="O123" t="n">
+      <c r="O125" t="n">
         <v>2.51</v>
       </c>
-      <c r="P123" t="n">
+      <c r="P125" t="n">
         <v>-912</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q125" t="n">
         <v>635</v>
       </c>
-      <c r="R123" t="n">
+      <c r="R125" t="n">
         <v>-278</v>
       </c>
-      <c r="S123" t="n">
+      <c r="S125" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D126" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F124" s="2" t="n">
+      <c r="F126" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G124" s="2" t="n">
+      <c r="G126" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H126" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K124" s="2" t="n">
+      <c r="K126" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L124" s="2" t="n">
+      <c r="L126" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M124" s="2" t="n">
+      <c r="M126" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N126" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O124" s="2" t="n">
+      <c r="O126" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P124" s="2" t="n">
+      <c r="P126" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q124" s="2" t="n">
+      <c r="Q126" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R126" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S124" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="n">
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
         <v>0.54</v>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="n">
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
         <v>0.54</v>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="n">
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
         <v>12</v>
       </c>
-      <c r="M126" t="n">
+      <c r="M128" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N128" t="n">
         <v>-1280</v>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="Q128" t="n">
         <v>208</v>
       </c>
-      <c r="R126" t="n">
+      <c r="R128" t="n">
         <v>-1072</v>
       </c>
-      <c r="S126" t="n">
+      <c r="S128" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q127" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -5657,34 +5708,50 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr"/>
-      <c r="N129" s="2" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P129" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q129" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R129" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S129" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5723,236 +5790,153 @@
       <c r="S131" s="2" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D133" t="n">
+      <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E135" t="n">
         <v>100</v>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="n">
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="n">
         <v>2.1</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="n">
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="n">
         <v>2.1</v>
       </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="n">
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="n">
         <v>52.73</v>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="n">
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
         <v>2.102</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N135" t="n">
         <v>2341</v>
       </c>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="n">
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
         <v>2341</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q135" t="n">
         <v>34</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R135" t="n">
         <v>2375</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S135" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D136" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E136" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="n">
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="n">
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="n">
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="n">
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N136" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" s="2" t="n">
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q134" s="2" t="n">
+      <c r="Q136" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R134" s="2" t="n">
+      <c r="R136" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S134" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>2</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M136" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>513</v>
-      </c>
-      <c r="R136" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S136" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>4</v>
-      </c>
-      <c r="E137" t="n">
-        <v>25</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I137" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J137" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M137" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N137" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P137" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R137" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S137" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5967,7 +5951,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5981,33 +5965,33 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N138" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q138" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R138" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S138" t="n">
         <v>1415</v>
@@ -6026,43 +6010,53 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
-        <v>100</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G139" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I139" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J139" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K139" t="n">
-        <v>14</v>
-      </c>
-      <c r="L139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M139" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N139" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O139" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P139" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q139" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R139" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S139" t="n">
         <v>1415</v>
@@ -6081,11 +6075,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -6095,36 +6089,36 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N140" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q140" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R140" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S140" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="141">
@@ -6140,50 +6134,46 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>14</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N141" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
-        <v>-68185</v>
+        <v>48540</v>
       </c>
       <c r="Q141" t="n">
-        <v>5784</v>
+        <v>4254</v>
       </c>
       <c r="R141" t="n">
-        <v>-62401</v>
+        <v>52794</v>
       </c>
       <c r="S141" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="142">
@@ -6199,7 +6189,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6213,214 +6203,218 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R142" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>4</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="n">
         <v>20</v>
       </c>
-      <c r="M142" t="n">
+      <c r="M144" t="n">
         <v>-3.417</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N144" t="n">
         <v>-120621</v>
       </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
         <v>-324235</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="Q144" t="n">
         <v>7584</v>
       </c>
-      <c r="R142" t="n">
+      <c r="R144" t="n">
         <v>-316651</v>
       </c>
-      <c r="S142" t="n">
+      <c r="S144" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D145" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E145" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="F143" s="2" t="n">
+      <c r="F145" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="G143" s="2" t="n">
+      <c r="G145" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H143" s="2" t="n">
+      <c r="H145" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I143" s="2" t="n">
+      <c r="I145" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J145" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K143" s="2" t="n">
+      <c r="K145" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L143" s="2" t="n">
+      <c r="L145" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M143" s="2" t="n">
+      <c r="M145" s="2" t="n">
         <v>-0.9419999999999999</v>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N145" s="2" t="n">
         <v>-26899</v>
       </c>
-      <c r="O143" s="2" t="n">
+      <c r="O145" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="P143" s="2" t="n">
+      <c r="P145" s="2" t="n">
         <v>-504757</v>
       </c>
-      <c r="Q143" s="2" t="n">
+      <c r="Q145" s="2" t="n">
         <v>40759</v>
       </c>
-      <c r="R143" s="2" t="n">
+      <c r="R145" s="2" t="n">
         <v>-463999</v>
       </c>
-      <c r="S143" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>9</v>
-      </c>
-      <c r="E145" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G145" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H145" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I145" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J145" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P145" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R145" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S145" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>2</v>
-      </c>
-      <c r="E146" t="n">
-        <v>100</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N146" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>667</v>
-      </c>
-      <c r="R146" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S146" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S145" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6435,44 +6429,52 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E147" t="n">
-        <v>100</v>
-      </c>
-      <c r="F147" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G147" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H147" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I147" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J147" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J147" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N147" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O147" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P147" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q147" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R147" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S147" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="148">
@@ -6488,228 +6490,214 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D148" t="n">
         <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N148" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>667</v>
+      </c>
+      <c r="R148" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>100</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N149" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>269</v>
+      </c>
+      <c r="R149" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N150" t="n">
         <v>-21127</v>
       </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q148" t="n">
+      <c r="Q150" t="n">
         <v>756</v>
       </c>
-      <c r="R148" t="n">
+      <c r="R150" t="n">
         <v>-58400</v>
       </c>
-      <c r="S148" t="n">
+      <c r="S150" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D151" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E151" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F149" s="2" t="n">
+      <c r="F151" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G149" s="2" t="n">
+      <c r="G151" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H149" s="2" t="n">
+      <c r="H151" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I149" s="2" t="n">
+      <c r="I151" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J151" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="2" t="n">
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N151" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O149" s="2" t="n">
+      <c r="O151" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P149" s="2" t="n">
+      <c r="P151" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q149" s="2" t="n">
+      <c r="Q151" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R149" s="2" t="n">
+      <c r="R151" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S149" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>9</v>
-      </c>
-      <c r="E151" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H151" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I151" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J151" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K151" t="n">
-        <v>3</v>
-      </c>
-      <c r="L151" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P151" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R151" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S151" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" t="n">
-        <v>100</v>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N152" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>667</v>
-      </c>
-      <c r="R152" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S152" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S151" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6724,46 +6712,56 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G153" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I153" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J153" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K153" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M153" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N153" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O153" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P153" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q153" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R153" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S153" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="154">
@@ -6779,119 +6777,166 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="n">
+        <v>100</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N154" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>667</v>
+      </c>
+      <c r="R154" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>100</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N155" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>269</v>
+      </c>
+      <c r="R155" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
         <v>2.19</v>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="n">
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
         <v>2.96</v>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="n">
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="n">
         <v>6.5</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M156" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N156" t="n">
         <v>-21127</v>
       </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="Q156" t="n">
         <v>756</v>
       </c>
-      <c r="R154" t="n">
+      <c r="R156" t="n">
         <v>-58400</v>
       </c>
-      <c r="S154" t="n">
+      <c r="S156" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M155" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O155" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P155" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q155" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R155" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S155" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -6905,39 +6950,61 @@
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="2" t="inlineStr"/>
-      <c r="N157" s="2" t="inlineStr"/>
-      <c r="O157" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O157" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P157" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R157" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S157" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -6971,90 +7038,45 @@
       <c r="S159" s="2" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R161" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S161" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>262</v>
-      </c>
-      <c r="R162" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S162" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr"/>
+      <c r="P161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7069,456 +7091,542 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R163" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>262</v>
+      </c>
+      <c r="R164" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="n">
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="n">
         <v>0.61</v>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="n">
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="n">
         <v>0.61</v>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="n">
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="n">
         <v>21</v>
       </c>
-      <c r="M163" t="n">
+      <c r="M165" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N163" t="n">
+      <c r="N165" t="n">
         <v>-37549</v>
       </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" t="n">
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q163" t="n">
+      <c r="Q165" t="n">
         <v>201</v>
       </c>
-      <c r="R163" t="n">
+      <c r="R165" t="n">
         <v>-18985</v>
       </c>
-      <c r="S163" t="n">
+      <c r="S165" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
+      <c r="D166" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="n">
+      <c r="E166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="n">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="n">
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M164" s="2" t="n">
+      <c r="M166" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N166" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="2" t="n">
+      <c r="O166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q164" s="2" t="n">
+      <c r="Q166" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R164" s="2" t="n">
+      <c r="R166" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S164" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="S166" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D166" t="n">
+      <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="n">
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="n">
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="n">
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="n">
         <v>3</v>
       </c>
-      <c r="M166" t="n">
+      <c r="M168" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N166" t="n">
+      <c r="N168" t="n">
         <v>-74087</v>
       </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="n">
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q166" t="n">
+      <c r="Q168" t="n">
         <v>257</v>
       </c>
-      <c r="R166" t="n">
+      <c r="R168" t="n">
         <v>-73830</v>
       </c>
-      <c r="S166" t="n">
+      <c r="S168" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="n">
+      <c r="E169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="n">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="n">
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M167" s="2" t="n">
+      <c r="M169" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N169" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="2" t="n">
+      <c r="O169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q167" s="2" t="n">
+      <c r="Q169" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R167" s="2" t="n">
+      <c r="R169" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S167" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="S169" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D169" t="n">
+      <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="n">
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="n">
         <v>4.6</v>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="n">
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="n">
         <v>4.6</v>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="n">
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="n">
         <v>3</v>
       </c>
-      <c r="M169" t="n">
+      <c r="M171" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N169" t="n">
+      <c r="N171" t="n">
         <v>-29689</v>
       </c>
-      <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" t="n">
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q169" t="n">
+      <c r="Q171" t="n">
         <v>189</v>
       </c>
-      <c r="R169" t="n">
+      <c r="R171" t="n">
         <v>-29500</v>
       </c>
-      <c r="S169" t="n">
+      <c r="S171" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="n">
+      <c r="E172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="n">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="n">
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M170" s="2" t="n">
+      <c r="M172" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N172" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="2" t="n">
+      <c r="O172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q170" s="2" t="n">
+      <c r="Q172" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R170" s="2" t="n">
+      <c r="R172" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S170" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="S172" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D172" t="n">
+      <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="n">
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
         <v>0.87</v>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="n">
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
         <v>0.87</v>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="n">
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
         <v>3</v>
       </c>
-      <c r="M172" t="n">
+      <c r="M174" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N172" t="n">
+      <c r="N174" t="n">
         <v>-29188</v>
       </c>
-      <c r="O172" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" t="n">
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q172" t="n">
+      <c r="Q174" t="n">
         <v>2950</v>
       </c>
-      <c r="R172" t="n">
+      <c r="R174" t="n">
         <v>-26238</v>
       </c>
-      <c r="S172" t="n">
+      <c r="S174" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n">
+      <c r="D175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="n">
+      <c r="E175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="n">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="n">
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M173" s="2" t="n">
+      <c r="M175" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N175" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P173" s="2" t="n">
+      <c r="O175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q173" s="2" t="n">
+      <c r="Q175" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R173" s="2" t="n">
+      <c r="R175" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S173" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S175"/>
+  <dimension ref="A1:S178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1353,163 +1353,169 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09/14~09/18</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>4.86</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>3.316</v>
+        <v>-4.859</v>
       </c>
       <c r="N15" t="n">
-        <v>8175</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+        <v>-74342</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" t="n">
-        <v>8175</v>
+        <v>-15947</v>
       </c>
       <c r="Q15" t="n">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="R15" t="n">
-        <v>8250</v>
+        <v>-15601</v>
       </c>
       <c r="S15" t="n">
-        <v>1353</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10808</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P16" t="n">
+        <v>27162</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3889</v>
+      </c>
+      <c r="R16" t="n">
+        <v>31050</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>270</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="D17" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="I16" s="2" t="n">
+      <c r="G17" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="n">
-        <v>-0.046</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>-1130</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>-362101</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>78220</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>-283880</v>
-      </c>
-      <c r="S16" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1415</v>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>-1257</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>-359061</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>82380</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>-276681</v>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1524,53 +1530,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N19" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O19" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q19" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R19" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S19" t="n">
         <v>1415</v>
@@ -1589,47 +1589,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J20" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L20" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N20" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P20" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q20" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R20" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
@@ -1648,53 +1654,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N21" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q21" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R21" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S21" t="n">
         <v>1415</v>
@@ -1713,53 +1713,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G22" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H22" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J22" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N22" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q22" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R22" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S22" t="n">
         <v>1415</v>
@@ -1778,43 +1778,53 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G23" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I23" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N23" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P23" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q23" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R23" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S23" t="n">
         <v>1415</v>
@@ -1833,53 +1843,43 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J24" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N24" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q24" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R24" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S24" t="n">
         <v>1415</v>
@@ -1898,46 +1898,56 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.21</v>
+      </c>
       <c r="G25" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9.42</v>
+      </c>
       <c r="I25" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>11.09</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11.77</v>
+      </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M25" t="n">
-        <v>4.869</v>
+        <v>1.361</v>
       </c>
       <c r="N25" t="n">
-        <v>37762</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>11916</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.43</v>
+      </c>
       <c r="P25" t="n">
-        <v>37762</v>
+        <v>71497</v>
       </c>
       <c r="Q25" t="n">
-        <v>238</v>
+        <v>583</v>
       </c>
       <c r="R25" t="n">
-        <v>38000</v>
+        <v>72080</v>
       </c>
       <c r="S25" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="26">
@@ -1953,50 +1963,46 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>-0.23</v>
+        <v>4.869</v>
       </c>
       <c r="N26" t="n">
-        <v>-1150</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
+        <v>37762</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>-1150</v>
+        <v>37762</v>
       </c>
       <c r="Q26" t="n">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="R26" t="n">
-        <v>-1000</v>
+        <v>38000</v>
       </c>
       <c r="S26" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="27">
@@ -2012,298 +2018,292 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>09/14~09/18</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>150</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
         <v>100</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>3.32</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>3.32</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>3.316</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N28" t="n">
         <v>8175</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>8175</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q28" t="n">
         <v>75</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>8250</v>
       </c>
-      <c r="S27" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="S28" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D29" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E29" s="2" t="n">
         <v>41.5</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>6.14</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>3.21</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>1.45</v>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="M29" s="2" t="n">
         <v>0.67</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="N29" s="2" t="n">
         <v>6216</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="O29" s="2" t="n">
         <v>1.58</v>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>329450</v>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>11344</v>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="R29" s="2" t="n">
         <v>340794</v>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I36" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L36" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N36" t="n">
-        <v>507</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P36" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R36" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2318,53 +2318,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F37" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G37" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H37" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I37" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J37" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K37" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L37" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N37" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O37" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P37" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q37" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R37" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S37" t="n">
         <v>1415</v>
@@ -2383,53 +2383,53 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E38" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G38" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H38" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I38" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J38" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K38" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L38" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N38" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O38" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P38" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q38" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R38" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S38" t="n">
         <v>1415</v>
@@ -2448,53 +2448,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F39" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H39" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I39" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J39" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K39" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L39" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M39" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N39" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O39" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P39" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q39" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R39" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S39" t="n">
         <v>1415</v>
@@ -2513,53 +2513,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G40" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H40" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I40" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J40" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K40" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L40" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M40" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N40" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O40" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P40" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q40" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R40" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S40" t="n">
         <v>1415</v>
@@ -2578,53 +2578,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G41" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H41" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I41" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J41" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K41" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L41" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M41" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N41" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P41" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q41" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R41" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S41" t="n">
         <v>1415</v>
@@ -2643,46 +2643,56 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.14</v>
+      </c>
       <c r="G42" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>6.04</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.52</v>
+      </c>
       <c r="I42" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="J42" t="inlineStr"/>
+        <v>13.51</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.74</v>
+      </c>
       <c r="K42" t="n">
-        <v>1659.27</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>2281.51</v>
+      </c>
+      <c r="L42" t="n">
+        <v>27.54</v>
+      </c>
       <c r="M42" t="n">
-        <v>15.576</v>
+        <v>1.758</v>
       </c>
       <c r="N42" t="n">
-        <v>88875</v>
-      </c>
-      <c r="O42" t="inlineStr"/>
+        <v>851</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.14</v>
+      </c>
       <c r="P42" t="n">
-        <v>88875</v>
+        <v>13616</v>
       </c>
       <c r="Q42" t="n">
-        <v>185</v>
+        <v>1561</v>
       </c>
       <c r="R42" t="n">
-        <v>89060</v>
+        <v>15177</v>
       </c>
       <c r="S42" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="43">
@@ -2698,34 +2708,46 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>15.58</v>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>15.58</v>
+      </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>1659.27</v>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>15.576</v>
+      </c>
+      <c r="N43" t="n">
+        <v>88875</v>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>-1537</v>
+        <v>88875</v>
       </c>
       <c r="Q43" t="n">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="R43" t="n">
-        <v>-1442</v>
+        <v>89060</v>
       </c>
       <c r="S43" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="44">
@@ -2741,285 +2763,269 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>1.54</v>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>1.54</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>16147.65</v>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="N44" t="n">
-        <v>60798</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
+        <v>-1537</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>95</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-1442</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>16147.65</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="N45" t="n">
+        <v>60798</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
         <v>49448</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q45" t="n">
         <v>1099</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>50548</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S45" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D46" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E46" s="2" t="n">
         <v>42.6</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F46" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>4.59</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>887.1799999999999</v>
       </c>
-      <c r="L45" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>0.312</v>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N46" s="2" t="n">
         <v>1872</v>
       </c>
-      <c r="O45" s="2" t="n">
+      <c r="O46" s="2" t="n">
         <v>1.47</v>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P46" s="2" t="n">
         <v>241683</v>
       </c>
-      <c r="Q45" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>11789</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="R46" s="2" t="n">
         <v>253473</v>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
         <v>0.34</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
         <v>0.49</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
         <v>13.35</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>-4880</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q48" t="n">
         <v>1291</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>-13350</v>
       </c>
-      <c r="S47" t="n">
+      <c r="S48" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="M49" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N49" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q48" s="2" t="n">
+      <c r="Q49" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M50" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R50" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3034,11 +3040,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -3048,36 +3054,36 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>0.59</v>
+        <v>2.28</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>27.47</v>
+        <v>29.99</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.486</v>
+        <v>-0.912</v>
       </c>
       <c r="N51" t="n">
-        <v>-7995</v>
+        <v>-13839</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-15989</v>
+        <v>-138394</v>
       </c>
       <c r="Q51" t="n">
-        <v>989</v>
+        <v>4519</v>
       </c>
       <c r="R51" t="n">
-        <v>-15000</v>
+        <v>-133875</v>
       </c>
       <c r="S51" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="52">
@@ -3093,471 +3099,471 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-0.486</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-7995</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-15989</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>989</v>
+      </c>
+      <c r="R52" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E53" t="n">
         <v>75</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F53" t="n">
         <v>2.87</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G53" t="n">
         <v>0.23</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H53" t="n">
         <v>0.08</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I53" t="n">
         <v>0.58</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J53" t="n">
         <v>0.08</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K53" t="n">
         <v>50.06</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L53" t="n">
         <v>55.1</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M53" t="n">
         <v>0.15</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N53" t="n">
         <v>2446</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O53" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P53" t="n">
         <v>9783</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q53" t="n">
         <v>1867</v>
       </c>
-      <c r="R52" t="n">
+      <c r="R53" t="n">
         <v>11650</v>
       </c>
-      <c r="S52" t="n">
+      <c r="S53" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E54" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F54" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>0.58</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K54" s="2" t="n">
         <v>50.06</v>
       </c>
-      <c r="L53" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>31.53</v>
       </c>
-      <c r="M53" s="2" t="n">
+      <c r="M54" s="2" t="n">
         <v>-0.593</v>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N54" s="2" t="n">
         <v>-9037</v>
       </c>
-      <c r="O53" s="2" t="n">
+      <c r="O54" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>-144600</v>
       </c>
-      <c r="Q53" s="2" t="n">
+      <c r="Q54" s="2" t="n">
         <v>7375</v>
       </c>
-      <c r="R53" s="2" t="n">
+      <c r="R54" s="2" t="n">
         <v>-137225</v>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D56" t="n">
         <v>12</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E56" t="n">
         <v>16.7</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F56" t="n">
         <v>0.72</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G56" t="n">
         <v>0.44</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H56" t="n">
         <v>0.64</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I56" t="n">
         <v>0.84</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J56" t="n">
         <v>1.81</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K56" t="n">
         <v>14.12</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L56" t="n">
         <v>26.24</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M56" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N56" t="n">
         <v>-6941</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O56" t="n">
         <v>0.14</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P56" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q56" t="n">
         <v>5515</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>-77775</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S56" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D57" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E57" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F57" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J57" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="K57" s="2" t="n">
         <v>14.12</v>
       </c>
-      <c r="L56" s="2" t="n">
+      <c r="L57" s="2" t="n">
         <v>26.24</v>
       </c>
-      <c r="M56" s="2" t="n">
+      <c r="M57" s="2" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="N57" s="2" t="n">
         <v>-6941</v>
       </c>
-      <c r="O56" s="2" t="n">
+      <c r="O57" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="P56" s="2" t="n">
+      <c r="P57" s="2" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q56" s="2" t="n">
+      <c r="Q57" s="2" t="n">
         <v>5515</v>
       </c>
-      <c r="R56" s="2" t="n">
+      <c r="R57" s="2" t="n">
         <v>-77775</v>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="S57" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_미분류</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="D61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>26</v>
-      </c>
-      <c r="R66" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3572,53 +3578,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I67" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K67" t="n">
-        <v>1279.97</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>875.09</v>
+        <v>49.85</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.191</v>
+        <v>-2.747</v>
       </c>
       <c r="N67" t="n">
-        <v>4951</v>
+        <v>-2426</v>
       </c>
       <c r="O67" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>29704</v>
+        <v>-2426</v>
       </c>
       <c r="Q67" t="n">
-        <v>756</v>
+        <v>26</v>
       </c>
       <c r="R67" t="n">
-        <v>30460</v>
+        <v>-2400</v>
       </c>
       <c r="S67" t="n">
         <v>1415</v>
@@ -3637,53 +3637,53 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G68" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H68" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K68" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L68" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M68" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N68" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O68" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P68" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q68" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R68" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
       <c r="S68" t="n">
         <v>1415</v>
@@ -3702,43 +3702,53 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>100</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G69" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I69" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K69" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L69" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M69" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N69" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O69" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P69" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q69" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R69" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
       <c r="S69" t="n">
         <v>1415</v>
@@ -3757,650 +3767,646 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
-        <v>5756.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>-6.785</v>
+        <v>1.678</v>
       </c>
       <c r="N70" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>-14543</v>
+        <v>1670</v>
       </c>
       <c r="Q70" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R70" t="n">
-        <v>-14485</v>
+        <v>1700</v>
       </c>
       <c r="S70" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>58</v>
+      </c>
+      <c r="R71" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D72" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E72" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F72" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I72" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J72" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="K72" s="2" t="n">
         <v>1633.99</v>
       </c>
-      <c r="L71" s="2" t="n">
+      <c r="L72" s="2" t="n">
         <v>2111.58</v>
       </c>
-      <c r="M71" s="2" t="n">
+      <c r="M72" s="2" t="n">
         <v>-1.689</v>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N72" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="O71" s="2" t="n">
+      <c r="O72" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P72" s="2" t="n">
         <v>3022</v>
       </c>
-      <c r="Q71" s="2" t="n">
+      <c r="Q72" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="R71" s="2" t="n">
+      <c r="R72" s="2" t="n">
         <v>4045</v>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="S72" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="D76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E78" t="n">
         <v>100</v>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
         <v>1.3</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="n">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
         <v>1.3</v>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="n">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
         <v>7</v>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="n">
         <v>1.299</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N78" t="n">
         <v>6421</v>
       </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="n">
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
         <v>6421</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q78" t="n">
         <v>149</v>
       </c>
-      <c r="R77" t="n">
+      <c r="R78" t="n">
         <v>6570</v>
       </c>
-      <c r="S77" t="n">
+      <c r="S78" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E79" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="n">
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="n">
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="n">
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="n">
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="n">
         <v>1.299</v>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N79" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="Q78" s="2" t="n">
+      <c r="Q79" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="R78" s="2" t="n">
+      <c r="R79" s="2" t="n">
         <v>6570</v>
       </c>
-      <c r="S78" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="S79" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>KR_TR_BASE</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ADD1</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="n">
-        <v>3</v>
-      </c>
-      <c r="M94" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N94" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>949</v>
-      </c>
-      <c r="R94" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S94" t="n">
-        <v>1411</v>
-      </c>
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4415,56 +4421,50 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G95" t="n">
-        <v>2.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="I95" t="n">
-        <v>7.7</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="K95" t="n">
-        <v>14.2</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.896</v>
+        <v>-10.012</v>
       </c>
       <c r="N95" t="n">
-        <v>-471</v>
+        <v>-71414</v>
       </c>
       <c r="O95" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>9429</v>
+        <v>-71414</v>
       </c>
       <c r="Q95" t="n">
-        <v>6892</v>
+        <v>949</v>
       </c>
       <c r="R95" t="n">
-        <v>16322</v>
+        <v>-70465</v>
       </c>
       <c r="S95" t="n">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="96">
@@ -4480,56 +4480,56 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>0.14</v>
+        <v>0.93</v>
       </c>
       <c r="G96" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="H96" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="I96" t="n">
-        <v>4.37</v>
+        <v>7.7</v>
       </c>
       <c r="J96" t="n">
-        <v>6.38</v>
+        <v>5.74</v>
       </c>
       <c r="K96" t="n">
-        <v>18</v>
+        <v>14.2</v>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.787</v>
+        <v>-0.896</v>
       </c>
       <c r="N96" t="n">
-        <v>-62797</v>
+        <v>-471</v>
       </c>
       <c r="O96" t="n">
-        <v>0.09</v>
+        <v>0.93</v>
       </c>
       <c r="P96" t="n">
-        <v>-340821</v>
+        <v>9429</v>
       </c>
       <c r="Q96" t="n">
-        <v>9807</v>
+        <v>6892</v>
       </c>
       <c r="R96" t="n">
-        <v>-331014</v>
+        <v>16322</v>
       </c>
       <c r="S96" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="97">
@@ -4545,389 +4545,478 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>40</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="J97" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="K97" t="n">
+        <v>18</v>
+      </c>
+      <c r="L97" t="n">
+        <v>9</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-0.787</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-62797</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P97" t="n">
+        <v>-340821</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>9807</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-331014</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D98" t="n">
         <v>6</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E98" t="n">
         <v>33.3</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F98" t="n">
         <v>0.95</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G98" t="n">
         <v>2.18</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H98" t="n">
         <v>2.6</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I98" t="n">
         <v>3.21</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J98" t="n">
         <v>3.37</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K98" t="n">
         <v>14</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L98" t="n">
         <v>13.25</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M98" t="n">
         <v>-1.004</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N98" t="n">
         <v>-6626</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O98" t="n">
         <v>0.48</v>
       </c>
-      <c r="P97" t="n">
+      <c r="P98" t="n">
         <v>-71076</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q98" t="n">
         <v>8465</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R98" t="n">
         <v>-62611</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S98" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>10</v>
+      </c>
+      <c r="M99" t="n">
+        <v>-4.859</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-74342</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>-15947</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>346</v>
+      </c>
+      <c r="R99" t="n">
+        <v>-15601</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K100" t="n">
+        <v>19</v>
+      </c>
+      <c r="L100" t="n">
+        <v>19</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N100" t="n">
+        <v>11686</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P100" t="n">
+        <v>18987</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3814</v>
+      </c>
+      <c r="R100" t="n">
+        <v>22800</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F98" s="2" t="n">
+      <c r="D101" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-18044</v>
+      </c>
+      <c r="O101" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="G98" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1.315</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-19540</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>-473882</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>26113</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>-447768</v>
-      </c>
-      <c r="S98" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="P101" s="2" t="n">
+        <v>-470842</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>30273</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>-440569</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_BASE</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="n">
-        <v>1</v>
-      </c>
-      <c r="M110" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N110" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R110" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>US_TR_JEO2</t>
+          <t>US_TR_BASE</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -4941,50 +5030,34 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="n">
-        <v>2.13</v>
-      </c>
+      <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="n">
-        <v>2.13</v>
-      </c>
+      <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O111" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="n">
-        <v>-41586</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>2702</v>
+        <v>0</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>-38883</v>
+        <v>0</v>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4998,7 +5071,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5008,329 +5081,345 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>3.34</v>
+        <v>2.13</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>6.17</v>
+        <v>2.13</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-3.337</v>
+        <v>-2.131</v>
       </c>
       <c r="N113" t="n">
-        <v>-7859</v>
+        <v>-41586</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-55013</v>
+        <v>-41586</v>
       </c>
       <c r="Q113" t="n">
-        <v>1884</v>
+        <v>2702</v>
       </c>
       <c r="R113" t="n">
-        <v>-53128</v>
+        <v>-38883</v>
       </c>
       <c r="S113" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>2702</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>-38883</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D117" t="n">
         <v>3</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E117" t="n">
         <v>66.7</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F117" t="n">
         <v>0.08</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G117" t="n">
         <v>2.89</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H117" t="n">
         <v>3.18</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I117" t="n">
         <v>3.32</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J117" t="n">
         <v>3.18</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K117" t="n">
         <v>18</v>
       </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
         <v>0.864</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N117" t="n">
         <v>-18508</v>
       </c>
-      <c r="O114" t="n">
+      <c r="O117" t="n">
         <v>0.16</v>
       </c>
-      <c r="P114" t="n">
+      <c r="P117" t="n">
         <v>-52375</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q117" t="n">
         <v>4226</v>
       </c>
-      <c r="R114" t="n">
+      <c r="R117" t="n">
         <v>-48149</v>
       </c>
-      <c r="S114" t="n">
+      <c r="S117" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D118" t="n">
         <v>2</v>
       </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
         <v>1.87</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="n">
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
         <v>2.68</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
         <v>7.5</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M118" t="n">
         <v>-1.87</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N118" t="n">
         <v>-38258</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
         <v>-79635</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="Q118" t="n">
         <v>4778</v>
       </c>
-      <c r="R115" t="n">
+      <c r="R118" t="n">
         <v>-74857</v>
       </c>
-      <c r="S115" t="n">
+      <c r="S118" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D119" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E119" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F119" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="G116" s="2" t="n">
+      <c r="G119" s="2" t="n">
         <v>2.89</v>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H119" s="2" t="n">
         <v>3.03</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I119" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J119" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K116" s="2" t="n">
+      <c r="K119" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L116" s="2" t="n">
+      <c r="L119" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="M116" s="2" t="n">
+      <c r="M119" s="2" t="n">
         <v>-2.042</v>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N119" s="2" t="n">
         <v>-15588</v>
       </c>
-      <c r="O116" s="2" t="n">
+      <c r="O119" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="P116" s="2" t="n">
+      <c r="P119" s="2" t="n">
         <v>-187023</v>
       </c>
-      <c r="Q116" s="2" t="n">
+      <c r="Q119" s="2" t="n">
         <v>10888</v>
       </c>
-      <c r="R116" s="2" t="n">
+      <c r="R119" s="2" t="n">
         <v>-176134</v>
       </c>
-      <c r="S116" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ADD1</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
-        <v>1</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>-54889</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>1054</v>
-      </c>
-      <c r="R120" t="n">
-        <v>-53835</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S119" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5344,50 +5433,34 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="n">
-        <v>7.15</v>
-      </c>
+      <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="n">
-        <v>10.49</v>
-      </c>
+      <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O121" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="n">
-        <v>-54889</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>1054</v>
+        <v>0</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>-53835</v>
+        <v>0</v>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5401,241 +5474,229 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G123" t="n">
-        <v>7.27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I123" t="n">
-        <v>16.31</v>
-      </c>
+        <v>7.15</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0.78</v>
-      </c>
+        <v>10.49</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>2.681</v>
+        <v>-7.145</v>
       </c>
       <c r="N123" t="n">
-        <v>3410</v>
+        <v>-27445</v>
       </c>
       <c r="O123" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>134658</v>
+        <v>-54889</v>
       </c>
       <c r="Q123" t="n">
-        <v>7271</v>
+        <v>1054</v>
       </c>
       <c r="R123" t="n">
-        <v>141929</v>
+        <v>-53835</v>
       </c>
       <c r="S123" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E126" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G126" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I126" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J126" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O126" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P126" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R126" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D127" t="n">
         <v>7</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E127" t="n">
         <v>100</v>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="n">
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="n">
         <v>6.16</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="n">
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="n">
         <v>11.46</v>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="n">
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
         <v>10.43</v>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="n">
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
         <v>6.16</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N127" t="n">
         <v>18699</v>
       </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="n">
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
         <v>86535</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="Q127" t="n">
         <v>1828</v>
       </c>
-      <c r="R124" t="n">
+      <c r="R127" t="n">
         <v>88363</v>
       </c>
-      <c r="S124" t="n">
+      <c r="S127" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>4</v>
-      </c>
-      <c r="E125" t="n">
-        <v>50</v>
-      </c>
-      <c r="F125" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G125" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="H125" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I125" t="n">
-        <v>12</v>
-      </c>
-      <c r="J125" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K125" t="n">
-        <v>14</v>
-      </c>
-      <c r="L125" t="n">
-        <v>14</v>
-      </c>
-      <c r="M125" t="n">
-        <v>4.282</v>
-      </c>
-      <c r="N125" t="n">
-        <v>7910</v>
-      </c>
-      <c r="O125" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P125" t="n">
-        <v>-912</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>635</v>
-      </c>
-      <c r="R125" t="n">
-        <v>-278</v>
-      </c>
-      <c r="S125" t="n">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>3.779</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>7875</v>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P126" s="2" t="n">
-        <v>220281</v>
-      </c>
-      <c r="Q126" s="2" t="n">
-        <v>9734</v>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>230014</v>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5645,255 +5706,287 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="G128" t="n">
+        <v>11.43</v>
+      </c>
       <c r="H128" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
+        <v>2.87</v>
+      </c>
+      <c r="I128" t="n">
+        <v>12</v>
+      </c>
       <c r="J128" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K128" t="inlineStr"/>
+        <v>4.94</v>
+      </c>
+      <c r="K128" t="n">
+        <v>14</v>
+      </c>
       <c r="L128" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.54</v>
+        <v>4.282</v>
       </c>
       <c r="N128" t="n">
-        <v>-1280</v>
+        <v>7910</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P128" t="n">
-        <v>-1280</v>
+        <v>-912</v>
       </c>
       <c r="Q128" t="n">
-        <v>208</v>
+        <v>635</v>
       </c>
       <c r="R128" t="n">
-        <v>-1072</v>
+        <v>-278</v>
       </c>
       <c r="S128" t="n">
-        <v>1383</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>3.779</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>7875</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>220281</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>9734</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>230014</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>12</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>208</v>
+      </c>
+      <c r="R131" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="n">
+      <c r="E132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="n">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="n">
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M129" s="2" t="n">
+      <c r="M132" s="2" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N132" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="O129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" s="2" t="n">
+      <c r="O132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q129" s="2" t="n">
+      <c r="Q132" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="R129" s="2" t="n">
+      <c r="R132" s="2" t="n">
         <v>-1072</v>
       </c>
-      <c r="S129" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="S132" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr"/>
-      <c r="O131" s="2" t="inlineStr"/>
-      <c r="P131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr"/>
-      <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr"/>
-      <c r="P133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>100</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>34</v>
-      </c>
-      <c r="R135" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S135" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5902,224 +5995,137 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="n">
-        <v>52.73</v>
-      </c>
+      <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N136" s="2" t="n">
-        <v>2341</v>
-      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr"/>
       <c r="P136" s="2" t="n">
-        <v>2341</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R136" s="2" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="n">
+        <v>100</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>34</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M138" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>513</v>
-      </c>
-      <c r="R138" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S138" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>4</v>
-      </c>
-      <c r="E139" t="n">
-        <v>25</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I139" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M139" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N139" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P139" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R139" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S139" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M140" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N140" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R140" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S140" t="n">
-        <v>1415</v>
-      </c>
+      <c r="E139" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6134,43 +6140,47 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>100</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="n">
-        <v>14</v>
-      </c>
-      <c r="L141" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
       <c r="M141" t="n">
-        <v>1.042</v>
+        <v>-2.607</v>
       </c>
       <c r="N141" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O141" t="inlineStr"/>
+        <v>-8011</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
       <c r="P141" t="n">
-        <v>48540</v>
+        <v>-16021</v>
       </c>
       <c r="Q141" t="n">
-        <v>4254</v>
+        <v>513</v>
       </c>
       <c r="R141" t="n">
-        <v>52794</v>
+        <v>-15508</v>
       </c>
       <c r="S141" t="n">
         <v>1415</v>
@@ -6189,50 +6199,56 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H142" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I142" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J142" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K142" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
       <c r="L142" t="n">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.864</v>
+        <v>-0.217</v>
       </c>
       <c r="N142" t="n">
-        <v>-28997</v>
+        <v>-13272</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P142" t="n">
-        <v>-86990</v>
+        <v>-53089</v>
       </c>
       <c r="Q142" t="n">
-        <v>13787</v>
+        <v>5913</v>
       </c>
       <c r="R142" t="n">
-        <v>-73203</v>
+        <v>-47176</v>
       </c>
       <c r="S142" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="143">
@@ -6248,7 +6264,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6262,36 +6278,36 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>0.92</v>
+        <v>0.14</v>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>1.07</v>
+        <v>0.16</v>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.918</v>
+        <v>-0.136</v>
       </c>
       <c r="N143" t="n">
-        <v>-18443</v>
+        <v>-2389</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>-68185</v>
+        <v>-4777</v>
       </c>
       <c r="Q143" t="n">
-        <v>5784</v>
+        <v>2924</v>
       </c>
       <c r="R143" t="n">
-        <v>-62401</v>
+        <v>-1854</v>
       </c>
       <c r="S143" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="144">
@@ -6307,281 +6323,287 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>14</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>-3.417</v>
+        <v>1.042</v>
       </c>
       <c r="N144" t="n">
-        <v>-120621</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O144" t="inlineStr"/>
       <c r="P144" t="n">
-        <v>-324235</v>
+        <v>48540</v>
       </c>
       <c r="Q144" t="n">
-        <v>7584</v>
+        <v>4254</v>
       </c>
       <c r="R144" t="n">
-        <v>-316651</v>
+        <v>52794</v>
       </c>
       <c r="S144" t="n">
-        <v>1338</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="M145" s="2" t="n">
-        <v>-0.9419999999999999</v>
-      </c>
-      <c r="N145" s="2" t="n">
-        <v>-26899</v>
-      </c>
-      <c r="O145" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P145" s="2" t="n">
-        <v>-504757</v>
-      </c>
-      <c r="Q145" s="2" t="n">
-        <v>40759</v>
-      </c>
-      <c r="R145" s="2" t="n">
-        <v>-463999</v>
-      </c>
-      <c r="S145" s="2" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R145" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>4</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R146" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1383</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E147" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I147" t="n">
-        <v>3.38</v>
-      </c>
+        <v>3.42</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>7.04</v>
+        <v>4.05</v>
       </c>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>20</v>
+      </c>
       <c r="M147" t="n">
-        <v>-1.213</v>
+        <v>-3.417</v>
       </c>
       <c r="N147" t="n">
-        <v>-744</v>
+        <v>-120621</v>
       </c>
       <c r="O147" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>-6692</v>
+        <v>-324235</v>
       </c>
       <c r="Q147" t="n">
-        <v>2139</v>
+        <v>7584</v>
       </c>
       <c r="R147" t="n">
-        <v>-4553</v>
+        <v>-316651</v>
       </c>
       <c r="S147" t="n">
-        <v>1415</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>2</v>
-      </c>
-      <c r="E148" t="n">
-        <v>100</v>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N148" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>667</v>
-      </c>
-      <c r="R148" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S148" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>100</v>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N149" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>269</v>
-      </c>
-      <c r="R149" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S149" t="n">
-        <v>1383</v>
-      </c>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-0.9419999999999999</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-26899</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>-504757</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>40759</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>-463999</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6596,283 +6618,275 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1.17</v>
+      </c>
       <c r="H150" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I150" t="inlineStr"/>
+        <v>4.19</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3.38</v>
+      </c>
       <c r="J150" t="n">
-        <v>2.96</v>
+        <v>7.04</v>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>-2.191</v>
+        <v>-1.213</v>
       </c>
       <c r="N150" t="n">
-        <v>-21127</v>
+        <v>-744</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="P150" t="n">
-        <v>-59156</v>
+        <v>-6692</v>
       </c>
       <c r="Q150" t="n">
-        <v>756</v>
+        <v>2139</v>
       </c>
       <c r="R150" t="n">
-        <v>-58400</v>
+        <v>-4553</v>
       </c>
       <c r="S150" t="n">
-        <v>1369</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I151" s="2" t="n">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>100</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="n">
         <v>12.69</v>
       </c>
-      <c r="J151" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N151" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O151" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P151" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q151" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R151" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S151" s="2" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N151" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>667</v>
+      </c>
+      <c r="R151" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>100</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N152" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>269</v>
+      </c>
+      <c r="R152" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1383</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I153" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>-2.191</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-21127</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>-59156</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>756</v>
+      </c>
+      <c r="R153" t="n">
+        <v>-58400</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G154" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="J153" t="n">
+      <c r="H154" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J154" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K153" t="n">
-        <v>3</v>
-      </c>
-      <c r="L153" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P153" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R153" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S153" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>2</v>
-      </c>
-      <c r="E154" t="n">
-        <v>100</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N154" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>667</v>
-      </c>
-      <c r="R154" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S154" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>100</v>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="n">
-        <v>1</v>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N155" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>269</v>
-      </c>
-      <c r="R155" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S155" t="n">
-        <v>1383</v>
-      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O154" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>84466</v>
+      </c>
+      <c r="Q154" s="2" t="n">
+        <v>3831</v>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>88297</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6887,403 +6901,462 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>9</v>
+      </c>
+      <c r="E156" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H156" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J156" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K156" t="n">
+        <v>3</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M156" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P156" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R156" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>100</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N157" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>667</v>
+      </c>
+      <c r="R157" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>100</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N158" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>269</v>
+      </c>
+      <c r="R158" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D159" t="n">
         <v>2</v>
       </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="n">
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
         <v>2.19</v>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="n">
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
         <v>2.96</v>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="n">
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="n">
         <v>6.5</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M159" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N159" t="n">
         <v>-21127</v>
       </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="Q159" t="n">
         <v>756</v>
       </c>
-      <c r="R156" t="n">
+      <c r="R159" t="n">
         <v>-58400</v>
       </c>
-      <c r="S156" t="n">
+      <c r="S159" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D160" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F157" s="2" t="n">
+      <c r="F160" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G157" s="2" t="n">
+      <c r="G160" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H160" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I157" s="2" t="n">
+      <c r="I160" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J160" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K157" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L157" s="2" t="n">
+      <c r="L160" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="M157" s="2" t="n">
+      <c r="M160" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N160" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O157" s="2" t="n">
+      <c r="O160" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P157" s="2" t="n">
+      <c r="P160" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q157" s="2" t="n">
+      <c r="Q160" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R157" s="2" t="n">
+      <c r="R160" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S157" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="S160" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="2" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr"/>
-      <c r="O159" s="2" t="inlineStr"/>
-      <c r="P159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="D162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-      <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="2" t="inlineStr"/>
-      <c r="M161" s="2" t="inlineStr"/>
-      <c r="N161" s="2" t="inlineStr"/>
-      <c r="O161" s="2" t="inlineStr"/>
-      <c r="P161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="D164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="n">
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
         <v>51315</v>
       </c>
-      <c r="Q163" t="n">
+      <c r="Q166" t="n">
         <v>1370</v>
       </c>
-      <c r="R163" t="n">
+      <c r="R166" t="n">
         <v>52685</v>
       </c>
-      <c r="S163" t="n">
+      <c r="S166" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="n">
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
         <v>-69677</v>
       </c>
-      <c r="Q164" t="n">
+      <c r="Q167" t="n">
         <v>262</v>
       </c>
-      <c r="R164" t="n">
+      <c r="R167" t="n">
         <v>-69415</v>
       </c>
-      <c r="S164" t="n">
+      <c r="S167" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="n">
-        <v>21</v>
-      </c>
-      <c r="M165" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="N165" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="n">
-        <v>-19186</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>201</v>
-      </c>
-      <c r="R165" t="n">
-        <v>-18985</v>
-      </c>
-      <c r="S165" t="n">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="M166" s="2" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="N166" s="2" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" s="2" t="n">
-        <v>-37548</v>
-      </c>
-      <c r="Q166" s="2" t="n">
-        <v>1833</v>
-      </c>
-      <c r="R166" s="2" t="n">
-        <v>-35715</v>
-      </c>
-      <c r="S166" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>수동매매_시딩</t>
+          <t>2X단타_시딩</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7293,7 +7366,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7307,42 +7380,42 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>8.300000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
-        <v>8.300000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="M168" t="n">
-        <v>-8.304</v>
+        <v>-0.612</v>
       </c>
       <c r="N168" t="n">
-        <v>-74087</v>
+        <v>-37549</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="P168" t="n">
-        <v>-74087</v>
+        <v>-19186</v>
       </c>
       <c r="Q168" t="n">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="R168" t="n">
-        <v>-73830</v>
+        <v>-18985</v>
       </c>
       <c r="S168" t="n">
-        <v>1373</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>수동매매_시딩</t>
+          <t>2X단타_시딩</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -7366,40 +7439,40 @@
       </c>
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>-8.304</v>
+        <v>-0.612</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-74087</v>
+        <v>-37549</v>
       </c>
       <c r="O169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P169" s="2" t="n">
-        <v>-74087</v>
+        <v>-37548</v>
       </c>
       <c r="Q169" s="2" t="n">
-        <v>257</v>
+        <v>1833</v>
       </c>
       <c r="R169" s="2" t="n">
-        <v>-73830</v>
+        <v>-35715</v>
       </c>
       <c r="S169" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7423,33 +7496,33 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
         <v>3</v>
       </c>
       <c r="M171" t="n">
-        <v>-4.602</v>
+        <v>-8.304</v>
       </c>
       <c r="N171" t="n">
-        <v>-29689</v>
+        <v>-74087</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>-29689</v>
+        <v>-74087</v>
       </c>
       <c r="Q171" t="n">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="R171" t="n">
-        <v>-29500</v>
+        <v>-73830</v>
       </c>
       <c r="S171" t="n">
         <v>1373</v>
@@ -7458,7 +7531,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7482,40 +7555,40 @@
       </c>
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>-4.602</v>
+        <v>-8.304</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-29689</v>
+        <v>-74087</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>-29689</v>
+        <v>-74087</v>
       </c>
       <c r="Q172" s="2" t="n">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="R172" s="2" t="n">
-        <v>-29500</v>
+        <v>-73830</v>
       </c>
       <c r="S172" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>주도주_시딩</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7539,33 +7612,33 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>0.87</v>
+        <v>4.6</v>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>0.87</v>
+        <v>4.6</v>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>3</v>
       </c>
       <c r="M174" t="n">
-        <v>-0.867</v>
+        <v>-4.602</v>
       </c>
       <c r="N174" t="n">
-        <v>-29188</v>
+        <v>-29689</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>-29188</v>
+        <v>-29689</v>
       </c>
       <c r="Q174" t="n">
-        <v>2950</v>
+        <v>189</v>
       </c>
       <c r="R174" t="n">
-        <v>-26238</v>
+        <v>-29500</v>
       </c>
       <c r="S174" t="n">
         <v>1373</v>
@@ -7574,7 +7647,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>주도주_시딩</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7598,35 +7671,151 @@
       </c>
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="n">
-        <v>0.87</v>
+        <v>4.6</v>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="n">
-        <v>0.87</v>
+        <v>4.6</v>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M175" s="2" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q175" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="n">
+        <v>3</v>
+      </c>
+      <c r="M177" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N177" t="n">
         <v>-29188</v>
       </c>
-      <c r="O175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="2" t="n">
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q175" s="2" t="n">
+      <c r="Q177" t="n">
         <v>2950</v>
       </c>
-      <c r="R175" s="2" t="n">
+      <c r="R177" t="n">
         <v>-26238</v>
       </c>
-      <c r="S175" s="2" t="inlineStr"/>
+      <c r="S177" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q178" s="2" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S178" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S178"/>
+  <dimension ref="A1:S179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6543,128 +6543,122 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>100</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>28</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="N148" t="n">
+        <v>37246</v>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>-106352</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>4918</v>
+      </c>
+      <c r="R148" t="n">
+        <v>-101433</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H148" s="2" t="n">
+      <c r="D149" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H149" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I148" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J148" s="2" t="n">
+      <c r="I149" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J149" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K148" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L148" s="2" t="n">
+      <c r="K149" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L149" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M148" s="2" t="n">
-        <v>-0.9419999999999999</v>
-      </c>
-      <c r="N148" s="2" t="n">
-        <v>-26899</v>
-      </c>
-      <c r="O148" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P148" s="2" t="n">
-        <v>-504757</v>
-      </c>
-      <c r="Q148" s="2" t="n">
-        <v>40759</v>
-      </c>
-      <c r="R148" s="2" t="n">
-        <v>-463999</v>
-      </c>
-      <c r="S148" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>9</v>
-      </c>
-      <c r="E150" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H150" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I150" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J150" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P150" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R150" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S150" t="n">
-        <v>1415</v>
-      </c>
+      <c r="M149" s="2" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-23692</v>
+      </c>
+      <c r="O149" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>-611109</v>
+      </c>
+      <c r="Q149" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>-565432</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6679,44 +6673,52 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E151" t="n">
-        <v>100</v>
-      </c>
-      <c r="F151" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G151" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I151" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J151" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J151" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N151" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O151" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P151" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q151" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R151" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S151" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="152">
@@ -6732,44 +6734,44 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
         <v>100</v>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N152" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q152" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R152" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S152" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="153">
@@ -6785,173 +6787,161 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N153" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>269</v>
+      </c>
+      <c r="R153" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N153" t="n">
+      <c r="N154" t="n">
         <v>-21127</v>
       </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="Q154" t="n">
         <v>756</v>
       </c>
-      <c r="R153" t="n">
+      <c r="R154" t="n">
         <v>-58400</v>
       </c>
-      <c r="S153" t="n">
+      <c r="S154" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D155" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E155" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F154" s="2" t="n">
+      <c r="F155" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G154" s="2" t="n">
+      <c r="G155" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H154" s="2" t="n">
+      <c r="H155" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I154" s="2" t="n">
+      <c r="I155" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J154" s="2" t="n">
+      <c r="J155" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="n">
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N155" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O154" s="2" t="n">
+      <c r="O155" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P154" s="2" t="n">
+      <c r="P155" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q154" s="2" t="n">
+      <c r="Q155" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R154" s="2" t="n">
+      <c r="R155" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S154" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>9</v>
-      </c>
-      <c r="E156" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H156" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I156" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J156" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K156" t="n">
-        <v>3</v>
-      </c>
-      <c r="L156" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M156" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N156" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O156" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P156" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R156" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S156" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S155" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6966,46 +6956,56 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E157" t="n">
-        <v>100</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G157" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H157" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I157" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K157" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M157" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N157" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O157" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P157" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q157" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R157" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S157" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="158">
@@ -7021,46 +7021,46 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>100</v>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N158" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q158" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R158" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S158" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="159">
@@ -7076,239 +7076,251 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>100</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N159" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>269</v>
+      </c>
+      <c r="R159" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D159" t="n">
+      <c r="D160" t="n">
         <v>2</v>
       </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="n">
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
         <v>2.19</v>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="n">
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
         <v>2.96</v>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="n">
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="n">
         <v>6.5</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M160" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N160" t="n">
         <v>-21127</v>
       </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q159" t="n">
+      <c r="Q160" t="n">
         <v>756</v>
       </c>
-      <c r="R159" t="n">
+      <c r="R160" t="n">
         <v>-58400</v>
       </c>
-      <c r="S159" t="n">
+      <c r="S160" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D160" s="2" t="n">
+      <c r="D161" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E161" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F160" s="2" t="n">
+      <c r="F161" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G160" s="2" t="n">
+      <c r="G161" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H160" s="2" t="n">
+      <c r="H161" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I160" s="2" t="n">
+      <c r="I161" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J161" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K160" s="2" t="n">
+      <c r="K161" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L160" s="2" t="n">
+      <c r="L161" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="M160" s="2" t="n">
+      <c r="M161" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N160" s="2" t="n">
+      <c r="N161" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O160" s="2" t="n">
+      <c r="O161" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P160" s="2" t="n">
+      <c r="P161" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q160" s="2" t="n">
+      <c r="Q161" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R160" s="2" t="n">
+      <c r="R161" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S160" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="S161" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="2" t="inlineStr"/>
-      <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr"/>
-      <c r="P162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="D163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr"/>
+      <c r="P163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr"/>
-      <c r="P164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R166" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S166" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7323,7 +7335,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7341,16 +7353,16 @@
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="n">
-        <v>-69677</v>
+        <v>51315</v>
       </c>
       <c r="Q167" t="n">
-        <v>262</v>
+        <v>1370</v>
       </c>
       <c r="R167" t="n">
-        <v>-69415</v>
+        <v>52685</v>
       </c>
       <c r="S167" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="168">
@@ -7366,456 +7378,499 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>262</v>
+      </c>
+      <c r="R168" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S168" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D168" t="n">
+      <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="n">
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="n">
         <v>0.61</v>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="n">
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="n">
         <v>0.61</v>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="n">
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="n">
         <v>21</v>
       </c>
-      <c r="M168" t="n">
+      <c r="M169" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N168" t="n">
+      <c r="N169" t="n">
         <v>-37549</v>
       </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q168" t="n">
+      <c r="Q169" t="n">
         <v>201</v>
       </c>
-      <c r="R168" t="n">
+      <c r="R169" t="n">
         <v>-18985</v>
       </c>
-      <c r="S168" t="n">
+      <c r="S169" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D169" s="2" t="n">
+      <c r="D170" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="n">
+      <c r="E170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="n">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="n">
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M169" s="2" t="n">
+      <c r="M170" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N170" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" s="2" t="n">
+      <c r="O170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q169" s="2" t="n">
+      <c r="Q170" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R169" s="2" t="n">
+      <c r="R170" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S169" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="S170" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D171" t="n">
+      <c r="D172" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="n">
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="n">
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="n">
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="n">
         <v>3</v>
       </c>
-      <c r="M171" t="n">
+      <c r="M172" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N171" t="n">
+      <c r="N172" t="n">
         <v>-74087</v>
       </c>
-      <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" t="n">
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q171" t="n">
+      <c r="Q172" t="n">
         <v>257</v>
       </c>
-      <c r="R171" t="n">
+      <c r="R172" t="n">
         <v>-73830</v>
       </c>
-      <c r="S171" t="n">
+      <c r="S172" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="n">
+      <c r="E173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="n">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="n">
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M172" s="2" t="n">
+      <c r="M173" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N173" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" s="2" t="n">
+      <c r="O173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q172" s="2" t="n">
+      <c r="Q173" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R172" s="2" t="n">
+      <c r="R173" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S172" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="S173" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D174" t="n">
+      <c r="D175" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="n">
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="n">
         <v>4.6</v>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="n">
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="n">
         <v>4.6</v>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="n">
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="n">
         <v>3</v>
       </c>
-      <c r="M174" t="n">
+      <c r="M175" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N174" t="n">
+      <c r="N175" t="n">
         <v>-29689</v>
       </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" t="n">
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q174" t="n">
+      <c r="Q175" t="n">
         <v>189</v>
       </c>
-      <c r="R174" t="n">
+      <c r="R175" t="n">
         <v>-29500</v>
       </c>
-      <c r="S174" t="n">
+      <c r="S175" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n">
+      <c r="D176" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="n">
+      <c r="E176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="n">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="n">
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M175" s="2" t="n">
+      <c r="M176" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N176" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="2" t="n">
+      <c r="O176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q175" s="2" t="n">
+      <c r="Q176" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R175" s="2" t="n">
+      <c r="R176" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S175" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="S176" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D177" t="n">
+      <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="n">
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="n">
         <v>0.87</v>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="n">
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="n">
         <v>0.87</v>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="n">
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="n">
         <v>3</v>
       </c>
-      <c r="M177" t="n">
+      <c r="M178" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N177" t="n">
+      <c r="N178" t="n">
         <v>-29188</v>
       </c>
-      <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="n">
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q177" t="n">
+      <c r="Q178" t="n">
         <v>2950</v>
       </c>
-      <c r="R177" t="n">
+      <c r="R178" t="n">
         <v>-26238</v>
       </c>
-      <c r="S177" t="n">
+      <c r="S178" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D179" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="n">
+      <c r="E179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="n">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="n">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M178" s="2" t="n">
+      <c r="M179" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N179" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" s="2" t="n">
+      <c r="O179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q178" s="2" t="n">
+      <c r="Q179" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R178" s="2" t="n">
+      <c r="R179" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S178" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:S181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1459,122 +1459,116 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>9.462999999999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24419</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>24419</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>24500</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="D18" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="H17" s="2" t="n">
+      <c r="G18" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H18" s="2" t="n">
         <v>2.74</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>-1257</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>-359061</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>82380</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>-276681</v>
-      </c>
-      <c r="S17" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1415</v>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>-1164</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>-334642</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>82461</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-252181</v>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1589,53 +1583,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I20" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N20" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O20" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q20" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R20" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
@@ -1654,47 +1642,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H21" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J21" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L21" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N21" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P21" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q21" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R21" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S21" t="n">
         <v>1415</v>
@@ -1713,53 +1707,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N22" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q22" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R22" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S22" t="n">
         <v>1415</v>
@@ -1778,53 +1766,53 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H23" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J23" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N23" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q23" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R23" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S23" t="n">
         <v>1415</v>
@@ -1843,43 +1831,53 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G24" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I24" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N24" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P24" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q24" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R24" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S24" t="n">
         <v>1415</v>
@@ -1898,53 +1896,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N25" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q25" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R25" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S25" t="n">
         <v>1415</v>
@@ -1963,46 +1951,56 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.21</v>
+      </c>
       <c r="G26" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.42</v>
+      </c>
       <c r="I26" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>11.09</v>
+      </c>
+      <c r="J26" t="n">
+        <v>11.77</v>
+      </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M26" t="n">
-        <v>4.869</v>
+        <v>1.361</v>
       </c>
       <c r="N26" t="n">
-        <v>37762</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
+        <v>11916</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.43</v>
+      </c>
       <c r="P26" t="n">
-        <v>37762</v>
+        <v>71497</v>
       </c>
       <c r="Q26" t="n">
-        <v>238</v>
+        <v>583</v>
       </c>
       <c r="R26" t="n">
-        <v>38000</v>
+        <v>72080</v>
       </c>
       <c r="S26" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="27">
@@ -2018,50 +2016,46 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>-0.23</v>
+        <v>4.869</v>
       </c>
       <c r="N27" t="n">
-        <v>-1150</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
+        <v>37762</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>-1150</v>
+        <v>37762</v>
       </c>
       <c r="Q27" t="n">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="R27" t="n">
-        <v>-1000</v>
+        <v>38000</v>
       </c>
       <c r="S27" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="28">
@@ -2077,115 +2071,166 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>09/14~09/18</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>150</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
         <v>100</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>3.32</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>3.32</v>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>3.316</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N29" t="n">
         <v>8175</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>8175</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q29" t="n">
         <v>75</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>8250</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>1378</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>6216</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>329450</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>11344</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>340794</v>
-      </c>
-      <c r="S29" s="2" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>9.462999999999999</v>
+      </c>
+      <c r="N30" t="n">
+        <v>24419</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>24419</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>81</v>
+      </c>
+      <c r="R30" t="n">
+        <v>24500</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ROCKET</t>
+          <t>주도주</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2199,34 +2244,56 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>6553</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>1.62</v>
+      </c>
       <c r="P31" s="2" t="n">
-        <v>0</v>
+        <v>353869</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
+        <v>11425</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0</v>
+        <v>365294</v>
       </c>
       <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ABC-VCP</t>
+          <t>ROCKET</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2267,7 +2334,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TV알림</t>
+          <t>ABC-VCP</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2306,134 +2373,45 @@
       <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>27</v>
-      </c>
-      <c r="E37" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I37" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L37" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N37" t="n">
-        <v>507</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P37" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R37" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>45</v>
-      </c>
-      <c r="E38" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I38" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="J38" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="K38" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>-0.703</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-57188</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2829</v>
-      </c>
-      <c r="R38" t="n">
-        <v>-54359</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1415</v>
-      </c>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TV알림</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2448,53 +2426,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E39" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="G39" t="n">
-        <v>3.14</v>
+        <v>5.47</v>
       </c>
       <c r="H39" t="n">
-        <v>2.76</v>
+        <v>3.29</v>
       </c>
       <c r="I39" t="n">
-        <v>8.68</v>
+        <v>17.35</v>
       </c>
       <c r="J39" t="n">
-        <v>9.01</v>
+        <v>20.1</v>
       </c>
       <c r="K39" t="n">
-        <v>247.7</v>
+        <v>185.95</v>
       </c>
       <c r="L39" t="n">
-        <v>174.67</v>
+        <v>187.46</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.288</v>
+        <v>0.274</v>
       </c>
       <c r="N39" t="n">
-        <v>1187</v>
+        <v>507</v>
       </c>
       <c r="O39" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="P39" t="n">
-        <v>36789</v>
+        <v>13680</v>
       </c>
       <c r="Q39" t="n">
-        <v>3306</v>
+        <v>1530</v>
       </c>
       <c r="R39" t="n">
-        <v>40095</v>
+        <v>15210</v>
       </c>
       <c r="S39" t="n">
         <v>1415</v>
@@ -2513,53 +2491,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="F40" t="n">
-        <v>3.53</v>
+        <v>1.11</v>
       </c>
       <c r="G40" t="n">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="H40" t="n">
-        <v>4.11</v>
+        <v>2.96</v>
       </c>
       <c r="I40" t="n">
-        <v>11.14</v>
+        <v>13.15</v>
       </c>
       <c r="J40" t="n">
-        <v>9.65</v>
+        <v>5.82</v>
       </c>
       <c r="K40" t="n">
-        <v>533.86</v>
+        <v>313.5</v>
       </c>
       <c r="L40" t="n">
-        <v>403.59</v>
+        <v>175.2</v>
       </c>
       <c r="M40" t="n">
-        <v>1.375</v>
+        <v>-0.703</v>
       </c>
       <c r="N40" t="n">
-        <v>8720</v>
+        <v>-1271</v>
       </c>
       <c r="O40" t="n">
-        <v>3.53</v>
+        <v>0.67</v>
       </c>
       <c r="P40" t="n">
-        <v>52321</v>
+        <v>-57188</v>
       </c>
       <c r="Q40" t="n">
-        <v>523</v>
+        <v>2829</v>
       </c>
       <c r="R40" t="n">
-        <v>52844</v>
+        <v>-54359</v>
       </c>
       <c r="S40" t="n">
         <v>1415</v>
@@ -2578,53 +2556,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E41" t="n">
-        <v>44.4</v>
+        <v>41.9</v>
       </c>
       <c r="F41" t="n">
-        <v>4.39</v>
+        <v>1.8</v>
       </c>
       <c r="G41" t="n">
-        <v>7.08</v>
+        <v>3.14</v>
       </c>
       <c r="H41" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="I41" t="n">
-        <v>7.95</v>
+        <v>8.68</v>
       </c>
       <c r="J41" t="n">
-        <v>2.19</v>
+        <v>9.01</v>
       </c>
       <c r="K41" t="n">
-        <v>800.2</v>
+        <v>247.7</v>
       </c>
       <c r="L41" t="n">
-        <v>60.03</v>
+        <v>174.67</v>
       </c>
       <c r="M41" t="n">
-        <v>2.446</v>
+        <v>-0.288</v>
       </c>
       <c r="N41" t="n">
-        <v>5075</v>
+        <v>1187</v>
       </c>
       <c r="O41" t="n">
-        <v>3.51</v>
+        <v>1.3</v>
       </c>
       <c r="P41" t="n">
-        <v>45679</v>
+        <v>36789</v>
       </c>
       <c r="Q41" t="n">
-        <v>661</v>
+        <v>3306</v>
       </c>
       <c r="R41" t="n">
-        <v>46340</v>
+        <v>40095</v>
       </c>
       <c r="S41" t="n">
         <v>1415</v>
@@ -2643,53 +2621,53 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
         <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="G42" t="n">
-        <v>6.04</v>
+        <v>6.86</v>
       </c>
       <c r="H42" t="n">
-        <v>2.52</v>
+        <v>4.11</v>
       </c>
       <c r="I42" t="n">
-        <v>13.51</v>
+        <v>11.14</v>
       </c>
       <c r="J42" t="n">
-        <v>4.74</v>
+        <v>9.65</v>
       </c>
       <c r="K42" t="n">
-        <v>2281.51</v>
+        <v>533.86</v>
       </c>
       <c r="L42" t="n">
-        <v>27.54</v>
+        <v>403.59</v>
       </c>
       <c r="M42" t="n">
-        <v>1.758</v>
+        <v>1.375</v>
       </c>
       <c r="N42" t="n">
-        <v>851</v>
+        <v>8720</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="P42" t="n">
-        <v>13616</v>
+        <v>52321</v>
       </c>
       <c r="Q42" t="n">
-        <v>1561</v>
+        <v>523</v>
       </c>
       <c r="R42" t="n">
-        <v>15177</v>
+        <v>52844</v>
       </c>
       <c r="S42" t="n">
         <v>1415</v>
@@ -2708,46 +2686,56 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
+        <v>44.4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.39</v>
+      </c>
       <c r="G43" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>7.08</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.26</v>
+      </c>
       <c r="I43" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>7.95</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.19</v>
+      </c>
       <c r="K43" t="n">
-        <v>1659.27</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>800.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>60.03</v>
+      </c>
       <c r="M43" t="n">
-        <v>15.576</v>
+        <v>2.446</v>
       </c>
       <c r="N43" t="n">
-        <v>88875</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>5075</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.51</v>
+      </c>
       <c r="P43" t="n">
-        <v>88875</v>
+        <v>45679</v>
       </c>
       <c r="Q43" t="n">
-        <v>185</v>
+        <v>661</v>
       </c>
       <c r="R43" t="n">
-        <v>89060</v>
+        <v>46340</v>
       </c>
       <c r="S43" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="44">
@@ -2763,34 +2751,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="E44" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L44" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N44" t="n">
+        <v>851</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.14</v>
+      </c>
       <c r="P44" t="n">
-        <v>-1537</v>
+        <v>13616</v>
       </c>
       <c r="Q44" t="n">
-        <v>95</v>
+        <v>1561</v>
       </c>
       <c r="R44" t="n">
-        <v>-1442</v>
+        <v>15177</v>
       </c>
       <c r="S44" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="45">
@@ -2806,7 +2816,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2817,333 +2827,313 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>1.54</v>
+        <v>15.58</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>1.54</v>
+        <v>15.58</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
-        <v>16147.65</v>
+        <v>1659.27</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>1.542</v>
+        <v>15.576</v>
       </c>
       <c r="N45" t="n">
-        <v>60798</v>
+        <v>88875</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
+        <v>88875</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>185</v>
+      </c>
+      <c r="R45" t="n">
+        <v>89060</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>-1537</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>95</v>
+      </c>
+      <c r="R46" t="n">
+        <v>-1442</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>16147.65</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="N47" t="n">
+        <v>60798</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
         <v>49448</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q47" t="n">
         <v>1099</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R47" t="n">
         <v>50548</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S47" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D48" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>42.6</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F48" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>4.59</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K48" s="2" t="n">
         <v>887.1799999999999</v>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>0.312</v>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>1872</v>
       </c>
-      <c r="O46" s="2" t="n">
+      <c r="O48" s="2" t="n">
         <v>1.47</v>
       </c>
-      <c r="P46" s="2" t="n">
+      <c r="P48" s="2" t="n">
         <v>241683</v>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="Q48" s="2" t="n">
         <v>11789</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>253473</v>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D50" t="n">
         <v>3</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>0.34</v>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
         <v>0.49</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
         <v>13.35</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M50" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N50" t="n">
         <v>-4880</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q50" t="n">
         <v>1291</v>
       </c>
-      <c r="R48" t="n">
+      <c r="R50" t="n">
         <v>-13350</v>
       </c>
-      <c r="S48" t="n">
+      <c r="S50" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="n">
+      <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M49" s="2" t="n">
+      <c r="M51" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="N51" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="n">
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q49" s="2" t="n">
+      <c r="Q51" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="R51" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M51" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R51" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="M52" t="n">
-        <v>-0.486</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-7995</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>-15989</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>989</v>
-      </c>
-      <c r="R52" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3158,253 +3148,308 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-0.486</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-7995</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-15989</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>989</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D55" t="n">
         <v>4</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>75</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>2.87</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>0.23</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>0.08</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I55" t="n">
         <v>0.58</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J55" t="n">
         <v>0.08</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>50.06</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L55" t="n">
         <v>55.1</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M55" t="n">
         <v>0.15</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N55" t="n">
         <v>2446</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O55" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P55" t="n">
         <v>9783</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q55" t="n">
         <v>1867</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R55" t="n">
         <v>11650</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S55" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D56" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E56" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F56" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>0.58</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="K56" s="2" t="n">
         <v>50.06</v>
       </c>
-      <c r="L54" s="2" t="n">
+      <c r="L56" s="2" t="n">
         <v>31.53</v>
       </c>
-      <c r="M54" s="2" t="n">
+      <c r="M56" s="2" t="n">
         <v>-0.593</v>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="N56" s="2" t="n">
         <v>-9037</v>
       </c>
-      <c r="O54" s="2" t="n">
+      <c r="O56" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P56" s="2" t="n">
         <v>-144600</v>
       </c>
-      <c r="Q54" s="2" t="n">
+      <c r="Q56" s="2" t="n">
         <v>7375</v>
       </c>
-      <c r="R54" s="2" t="n">
+      <c r="R56" s="2" t="n">
         <v>-137225</v>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D58" t="n">
         <v>12</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E58" t="n">
         <v>16.7</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F58" t="n">
         <v>0.72</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G58" t="n">
         <v>0.44</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H58" t="n">
         <v>0.64</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I58" t="n">
         <v>0.84</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J58" t="n">
         <v>1.81</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K58" t="n">
         <v>14.12</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L58" t="n">
         <v>26.24</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M58" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N58" t="n">
         <v>-6941</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O58" t="n">
         <v>0.14</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P58" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q58" t="n">
         <v>5515</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R58" t="n">
         <v>-77775</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S58" t="n">
         <v>1415</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>-0.461</v>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>-6941</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>-83290</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>5515</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>-77775</v>
-      </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>삼닉v3_미분류</t>
+          <t>삼닉v3_MA</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3418,34 +3463,56 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0.14</v>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>0</v>
+        <v>-83290</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0</v>
+        <v>5515</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0</v>
+        <v>-77775</v>
       </c>
       <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>5minHL</t>
+          <t>삼닉v3_미분류</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3486,7 +3553,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>5minHL2</t>
+          <t>5minHL</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3527,7 +3594,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>5minHL_동시</t>
+          <t>5minHL2</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3566,128 +3633,45 @@
       <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>26</v>
-      </c>
-      <c r="R67" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>6</v>
-      </c>
-      <c r="E68" t="n">
-        <v>50</v>
-      </c>
-      <c r="F68" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I68" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1279.97</v>
-      </c>
-      <c r="L68" t="n">
-        <v>875.09</v>
-      </c>
-      <c r="M68" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="N68" t="n">
-        <v>4951</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P68" t="n">
-        <v>29704</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>756</v>
-      </c>
-      <c r="R68" t="n">
-        <v>30460</v>
-      </c>
-      <c r="S68" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3702,53 +3686,47 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K69" t="n">
-        <v>4319.93</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>1351.81</v>
+        <v>49.85</v>
       </c>
       <c r="M69" t="n">
-        <v>-2.059</v>
+        <v>-2.747</v>
       </c>
       <c r="N69" t="n">
-        <v>-3794</v>
+        <v>-2426</v>
       </c>
       <c r="O69" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-11383</v>
+        <v>-2426</v>
       </c>
       <c r="Q69" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="R69" t="n">
-        <v>-11230</v>
+        <v>-2400</v>
       </c>
       <c r="S69" t="n">
         <v>1415</v>
@@ -3767,43 +3745,53 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>100</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.93</v>
+      </c>
       <c r="G70" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I70" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K70" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
+        <v>1279.97</v>
+      </c>
+      <c r="L70" t="n">
+        <v>875.09</v>
+      </c>
       <c r="M70" t="n">
-        <v>1.678</v>
+        <v>-0.191</v>
       </c>
       <c r="N70" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O70" t="inlineStr"/>
+        <v>4951</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.93</v>
+      </c>
       <c r="P70" t="n">
-        <v>1670</v>
+        <v>29704</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>756</v>
       </c>
       <c r="R70" t="n">
-        <v>1700</v>
+        <v>30460</v>
       </c>
       <c r="S70" t="n">
         <v>1415</v>
@@ -3822,124 +3810,181 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.08</v>
+      </c>
       <c r="H71" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
+        <v>3.13</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.08</v>
+      </c>
       <c r="J71" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
+        <v>3.61</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4319.93</v>
+      </c>
       <c r="L71" t="n">
-        <v>5756.96</v>
+        <v>1351.81</v>
       </c>
       <c r="M71" t="n">
-        <v>-6.785</v>
+        <v>-2.059</v>
       </c>
       <c r="N71" t="n">
-        <v>-7272</v>
+        <v>-3794</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P71" t="n">
-        <v>-14543</v>
+        <v>-11383</v>
       </c>
       <c r="Q71" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="R71" t="n">
-        <v>-14485</v>
+        <v>-11230</v>
       </c>
       <c r="S71" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>100</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>30</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="n">
         <v>7.52</v>
       </c>
-      <c r="K72" s="2" t="n">
-        <v>1633.99</v>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>2111.58</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>-1.689</v>
-      </c>
-      <c r="N72" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="O72" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P72" s="2" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>4045</v>
-      </c>
-      <c r="S72" s="2" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>58</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_B</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3948,34 +3993,56 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>1.07</v>
+      </c>
       <c r="P74" s="2" t="n">
-        <v>0</v>
+        <v>3022</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0</v>
+        <v>4045</v>
       </c>
       <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_1A0</t>
+          <t>KR_TR_ORD_B</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4014,117 +4081,105 @@
       <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E80" t="n">
         <v>100</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="n">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
         <v>1.3</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
         <v>1.3</v>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="n">
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
         <v>7</v>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="n">
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
         <v>1.299</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N80" t="n">
         <v>6421</v>
       </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="n">
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
         <v>6421</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q80" t="n">
         <v>149</v>
       </c>
-      <c r="R78" t="n">
+      <c r="R80" t="n">
         <v>6570</v>
       </c>
-      <c r="S78" t="n">
+      <c r="S80" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="n">
-        <v>1.299</v>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="Q79" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="R79" s="2" t="n">
-        <v>6570</v>
-      </c>
-      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4138,34 +4193,46 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>6421</v>
+      </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R81" s="2" t="n">
-        <v>0</v>
+        <v>6570</v>
       </c>
       <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4206,7 +4273,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_BASE</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4247,7 +4314,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_BASE</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4288,7 +4355,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4329,7 +4396,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ADD1</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4370,7 +4437,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_ADD1</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4409,128 +4476,45 @@
       <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="n">
-        <v>3</v>
-      </c>
-      <c r="M95" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>949</v>
-      </c>
-      <c r="R95" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S95" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10</v>
-      </c>
-      <c r="E96" t="n">
-        <v>50</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G96" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H96" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="I96" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J96" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="K96" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L96" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M96" t="n">
-        <v>-0.896</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-471</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P96" t="n">
-        <v>9429</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>6892</v>
-      </c>
-      <c r="R96" t="n">
-        <v>16322</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1373</v>
-      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4545,56 +4529,50 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2.69</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>4.37</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="K97" t="n">
-        <v>18</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.787</v>
+        <v>-10.012</v>
       </c>
       <c r="N97" t="n">
-        <v>-62797</v>
+        <v>-71414</v>
       </c>
       <c r="O97" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-340821</v>
+        <v>-71414</v>
       </c>
       <c r="Q97" t="n">
-        <v>9807</v>
+        <v>949</v>
       </c>
       <c r="R97" t="n">
-        <v>-331014</v>
+        <v>-70465</v>
       </c>
       <c r="S97" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="98">
@@ -4610,56 +4588,56 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="G98" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="H98" t="n">
-        <v>2.6</v>
+        <v>4.28</v>
       </c>
       <c r="I98" t="n">
-        <v>3.21</v>
+        <v>7.7</v>
       </c>
       <c r="J98" t="n">
-        <v>3.37</v>
+        <v>5.74</v>
       </c>
       <c r="K98" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="L98" t="n">
-        <v>13.25</v>
+        <v>5.6</v>
       </c>
       <c r="M98" t="n">
-        <v>-1.004</v>
+        <v>-0.896</v>
       </c>
       <c r="N98" t="n">
-        <v>-6626</v>
+        <v>-471</v>
       </c>
       <c r="O98" t="n">
-        <v>0.48</v>
+        <v>0.93</v>
       </c>
       <c r="P98" t="n">
-        <v>-71076</v>
+        <v>9429</v>
       </c>
       <c r="Q98" t="n">
-        <v>8465</v>
+        <v>6892</v>
       </c>
       <c r="R98" t="n">
-        <v>-62611</v>
+        <v>16322</v>
       </c>
       <c r="S98" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="99">
@@ -4675,50 +4653,56 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
+        <v>0.14</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.69</v>
+      </c>
       <c r="H99" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4.37</v>
+      </c>
       <c r="J99" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="K99" t="inlineStr"/>
+        <v>6.38</v>
+      </c>
+      <c r="K99" t="n">
+        <v>18</v>
+      </c>
       <c r="L99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M99" t="n">
-        <v>-4.859</v>
+        <v>-0.787</v>
       </c>
       <c r="N99" t="n">
-        <v>-74342</v>
+        <v>-62797</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="P99" t="n">
-        <v>-15947</v>
+        <v>-340821</v>
       </c>
       <c r="Q99" t="n">
-        <v>346</v>
+        <v>9807</v>
       </c>
       <c r="R99" t="n">
-        <v>-15601</v>
+        <v>-331014</v>
       </c>
       <c r="S99" t="n">
-        <v>1338</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="100">
@@ -4734,125 +4718,186 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/14~09/18</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
         <v>33.3</v>
       </c>
       <c r="F100" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J100" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K100" t="n">
+        <v>14</v>
+      </c>
+      <c r="L100" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="M100" t="n">
+        <v>-1.004</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-6626</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P100" t="n">
+        <v>-71076</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>8465</v>
+      </c>
+      <c r="R100" t="n">
+        <v>-62611</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>10</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-4.859</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-74342</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-15947</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>346</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-15601</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F102" t="n">
         <v>2.96</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G102" t="n">
         <v>6.38</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H102" t="n">
         <v>2.16</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I102" t="n">
         <v>6.38</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J102" t="n">
         <v>2.22</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K102" t="n">
         <v>19</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L102" t="n">
         <v>19</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M102" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>11686</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O102" t="n">
         <v>1.48</v>
       </c>
-      <c r="P100" t="n">
+      <c r="P102" t="n">
         <v>18987</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q102" t="n">
         <v>3814</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R102" t="n">
         <v>22800</v>
       </c>
-      <c r="S100" t="n">
+      <c r="S102" t="n">
         <v>1378</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-18044</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>-470842</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>30273</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>-440569</v>
-      </c>
-      <c r="S101" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ORD_1A0</t>
+          <t>US_TR_ORD_B</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4866,34 +4911,56 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-18044</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>0.34</v>
+      </c>
       <c r="P103" s="2" t="n">
-        <v>0</v>
+        <v>-470842</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>0</v>
+        <v>30273</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>0</v>
+        <v>-440569</v>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4934,7 +5001,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4975,7 +5042,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5016,7 +5083,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>US_TR_BASE</t>
+          <t>US_TR_VCP1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5055,244 +5122,161 @@
       <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
         <v>2.13</v>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="n">
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
         <v>2.13</v>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="n">
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
         <v>1</v>
       </c>
-      <c r="M113" t="n">
+      <c r="M115" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N115" t="n">
         <v>-41586</v>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="Q115" t="n">
         <v>2702</v>
       </c>
-      <c r="R113" t="n">
+      <c r="R115" t="n">
         <v>-38883</v>
       </c>
-      <c r="S113" t="n">
+      <c r="S115" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="n">
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="n">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="n">
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M114" s="2" t="n">
+      <c r="M116" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N116" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="2" t="n">
+      <c r="O116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q114" s="2" t="n">
+      <c r="Q116" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R116" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>7</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R116" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S116" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G117" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H117" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I117" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J117" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K117" t="n">
-        <v>18</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-18508</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P117" t="n">
-        <v>-52375</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>4226</v>
-      </c>
-      <c r="R117" t="n">
-        <v>-48149</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5307,11 +5291,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -5321,377 +5305,381 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
-        <v>2.68</v>
+        <v>6.17</v>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
+        <v>8</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J119" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K119" t="n">
+        <v>18</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P119" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R119" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
         <v>7.5</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M120" t="n">
         <v>-1.87</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N120" t="n">
         <v>-38258</v>
       </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
         <v>-79635</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q120" t="n">
         <v>4778</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R120" t="n">
         <v>-74857</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S120" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-2.042</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-15588</v>
-      </c>
-      <c r="O119" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P119" s="2" t="n">
-        <v>-187023</v>
-      </c>
-      <c r="Q119" s="2" t="n">
-        <v>10888</v>
-      </c>
-      <c r="R119" s="2" t="n">
-        <v>-176134</v>
-      </c>
-      <c r="S119" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-2.042</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-15588</v>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>-187023</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>10888</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>-176134</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr"/>
-      <c r="N121" s="2" t="inlineStr"/>
-      <c r="O121" s="2" t="inlineStr"/>
-      <c r="P121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="D123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D125" t="n">
         <v>2</v>
       </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="n">
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
         <v>7.15</v>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="n">
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
         <v>10.49</v>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="n">
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
         <v>1</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M125" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N125" t="n">
         <v>-27445</v>
       </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q125" t="n">
         <v>1054</v>
       </c>
-      <c r="R123" t="n">
+      <c r="R125" t="n">
         <v>-53835</v>
       </c>
-      <c r="S123" t="n">
+      <c r="S125" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D126" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="n">
+      <c r="E126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="n">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="n">
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M124" s="2" t="n">
+      <c r="M126" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N126" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="2" t="n">
+      <c r="O126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q124" s="2" t="n">
+      <c r="Q126" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R126" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S124" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E126" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G126" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H126" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I126" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J126" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M126" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N126" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O126" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P126" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R126" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>7</v>
-      </c>
-      <c r="E127" t="n">
-        <v>100</v>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N127" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R127" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S127" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S126" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5706,241 +5694,304 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>17</v>
+      </c>
+      <c r="E128" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G128" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I128" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O128" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P128" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R128" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>7</v>
+      </c>
+      <c r="E129" t="n">
+        <v>100</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N129" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R129" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D130" t="n">
         <v>4</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E130" t="n">
         <v>50</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F130" t="n">
         <v>2.51</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G130" t="n">
         <v>11.43</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H130" t="n">
         <v>2.87</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I130" t="n">
         <v>12</v>
       </c>
-      <c r="J128" t="n">
+      <c r="J130" t="n">
         <v>4.94</v>
       </c>
-      <c r="K128" t="n">
+      <c r="K130" t="n">
         <v>14</v>
       </c>
-      <c r="L128" t="n">
+      <c r="L130" t="n">
         <v>14</v>
       </c>
-      <c r="M128" t="n">
+      <c r="M130" t="n">
         <v>4.282</v>
       </c>
-      <c r="N128" t="n">
+      <c r="N130" t="n">
         <v>7910</v>
       </c>
-      <c r="O128" t="n">
+      <c r="O130" t="n">
         <v>2.51</v>
       </c>
-      <c r="P128" t="n">
+      <c r="P130" t="n">
         <v>-912</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="Q130" t="n">
         <v>635</v>
       </c>
-      <c r="R128" t="n">
+      <c r="R130" t="n">
         <v>-278</v>
       </c>
-      <c r="S128" t="n">
+      <c r="S130" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D131" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E131" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F129" s="2" t="n">
+      <c r="F131" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G129" s="2" t="n">
+      <c r="G131" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H131" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I129" s="2" t="n">
+      <c r="I131" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J131" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K129" s="2" t="n">
+      <c r="K131" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L129" s="2" t="n">
+      <c r="L131" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M129" s="2" t="n">
+      <c r="M131" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N131" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O129" s="2" t="n">
+      <c r="O131" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P129" s="2" t="n">
+      <c r="P131" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q129" s="2" t="n">
+      <c r="Q131" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R129" s="2" t="n">
+      <c r="R131" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S129" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="S131" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="n">
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
         <v>0.54</v>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="n">
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
         <v>0.54</v>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="n">
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="n">
         <v>12</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M133" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N133" t="n">
         <v>-1280</v>
       </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q131" t="n">
+      <c r="Q133" t="n">
         <v>208</v>
       </c>
-      <c r="R131" t="n">
+      <c r="R133" t="n">
         <v>-1072</v>
       </c>
-      <c r="S131" t="n">
+      <c r="S133" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q132" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R132" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S132" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5954,34 +6005,50 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P134" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q134" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R134" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S134" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6020,236 +6087,153 @@
       <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D138" t="n">
+      <c r="D140" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E140" t="n">
         <v>100</v>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="n">
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
         <v>2.1</v>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="n">
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="n">
         <v>2.1</v>
       </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="n">
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
         <v>52.73</v>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="n">
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
         <v>2.102</v>
       </c>
-      <c r="N138" t="n">
+      <c r="N140" t="n">
         <v>2341</v>
       </c>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
         <v>2341</v>
       </c>
-      <c r="Q138" t="n">
+      <c r="Q140" t="n">
         <v>34</v>
       </c>
-      <c r="R138" t="n">
+      <c r="R140" t="n">
         <v>2375</v>
       </c>
-      <c r="S138" t="n">
+      <c r="S140" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n">
+      <c r="D141" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E141" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="n">
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="n">
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="n">
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="n">
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N139" s="2" t="n">
+      <c r="N141" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O139" s="2" t="inlineStr"/>
-      <c r="P139" s="2" t="n">
+      <c r="O141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q139" s="2" t="n">
+      <c r="Q141" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R139" s="2" t="n">
+      <c r="R141" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S139" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>2</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="n">
-        <v>1</v>
-      </c>
-      <c r="M141" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>513</v>
-      </c>
-      <c r="R141" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S141" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>4</v>
-      </c>
-      <c r="E142" t="n">
-        <v>25</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G142" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I142" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J142" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M142" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N142" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P142" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R142" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S142" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S141" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6264,7 +6248,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6278,33 +6262,33 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N143" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q143" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R143" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S143" t="n">
         <v>1415</v>
@@ -6323,43 +6307,53 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
-        <v>100</v>
-      </c>
-      <c r="F144" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G144" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I144" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J144" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K144" t="n">
-        <v>14</v>
-      </c>
-      <c r="L144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M144" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N144" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O144" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P144" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q144" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R144" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S144" t="n">
         <v>1415</v>
@@ -6378,11 +6372,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -6392,36 +6386,36 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M145" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N145" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q145" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R145" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S145" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="146">
@@ -6437,50 +6431,46 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>14</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N146" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O146" t="inlineStr"/>
       <c r="P146" t="n">
-        <v>-68185</v>
+        <v>48540</v>
       </c>
       <c r="Q146" t="n">
-        <v>5784</v>
+        <v>4254</v>
       </c>
       <c r="R146" t="n">
-        <v>-62401</v>
+        <v>52794</v>
       </c>
       <c r="S146" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="147">
@@ -6496,7 +6486,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6510,36 +6500,36 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>20</v>
+        <v>4.67</v>
       </c>
       <c r="M147" t="n">
-        <v>-3.417</v>
+        <v>-0.864</v>
       </c>
       <c r="N147" t="n">
-        <v>-120621</v>
+        <v>-28997</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>-324235</v>
+        <v>-86990</v>
       </c>
       <c r="Q147" t="n">
-        <v>7584</v>
+        <v>13787</v>
       </c>
       <c r="R147" t="n">
-        <v>-316651</v>
+        <v>-73203</v>
       </c>
       <c r="S147" t="n">
-        <v>1338</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="148">
@@ -6555,224 +6545,228 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>4</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R148" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>3</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>20</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R149" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D148" t="n">
+      <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E150" t="n">
         <v>100</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
         <v>2.42</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="n">
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="n">
         <v>2.42</v>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="n">
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
         <v>28</v>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="n">
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
         <v>2.425</v>
       </c>
-      <c r="N148" t="n">
-        <v>37246</v>
-      </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
-        <v>-106352</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>4918</v>
-      </c>
-      <c r="R148" t="n">
-        <v>-101433</v>
-      </c>
-      <c r="S148" t="n">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="N150" t="n">
+        <v>36357</v>
+      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>-103816</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>4801</v>
+      </c>
+      <c r="R150" t="n">
+        <v>-99015</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D151" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E151" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F149" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G149" s="2" t="n">
+      <c r="F151" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G151" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H149" s="2" t="n">
+      <c r="H151" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I149" s="2" t="n">
+      <c r="I151" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J151" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K149" s="2" t="n">
+      <c r="K151" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L149" s="2" t="n">
+      <c r="L151" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M149" s="2" t="n">
+      <c r="M151" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N149" s="2" t="n">
-        <v>-23692</v>
-      </c>
-      <c r="O149" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P149" s="2" t="n">
-        <v>-611109</v>
-      </c>
-      <c r="Q149" s="2" t="n">
-        <v>45677</v>
-      </c>
-      <c r="R149" s="2" t="n">
-        <v>-565432</v>
-      </c>
-      <c r="S149" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>9</v>
-      </c>
-      <c r="E151" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H151" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I151" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J151" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P151" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R151" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S151" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" t="n">
-        <v>100</v>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N152" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>667</v>
-      </c>
-      <c r="R152" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S152" t="n">
-        <v>1411</v>
-      </c>
+      <c r="N151" s="2" t="n">
+        <v>-23737</v>
+      </c>
+      <c r="O151" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>-608573</v>
+      </c>
+      <c r="Q151" s="2" t="n">
+        <v>45560</v>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>-563014</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6787,44 +6781,52 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G153" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I153" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J153" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N153" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O153" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P153" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q153" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R153" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S153" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="154">
@@ -6840,228 +6842,214 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N154" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>667</v>
+      </c>
+      <c r="R154" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>100</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N155" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>269</v>
+      </c>
+      <c r="R155" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N156" t="n">
         <v>-21127</v>
       </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="Q156" t="n">
         <v>756</v>
       </c>
-      <c r="R154" t="n">
+      <c r="R156" t="n">
         <v>-58400</v>
       </c>
-      <c r="S154" t="n">
+      <c r="S156" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D157" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E157" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F155" s="2" t="n">
+      <c r="F157" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G155" s="2" t="n">
+      <c r="G157" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H155" s="2" t="n">
+      <c r="H157" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I155" s="2" t="n">
+      <c r="I157" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J157" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="2" t="n">
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N157" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O155" s="2" t="n">
+      <c r="O157" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P155" s="2" t="n">
+      <c r="P157" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q155" s="2" t="n">
+      <c r="Q157" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R155" s="2" t="n">
+      <c r="R157" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S155" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>9</v>
-      </c>
-      <c r="E157" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H157" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I157" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J157" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K157" t="n">
-        <v>3</v>
-      </c>
-      <c r="L157" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M157" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N157" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P157" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R157" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S157" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>2</v>
-      </c>
-      <c r="E158" t="n">
-        <v>100</v>
-      </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N158" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>667</v>
-      </c>
-      <c r="R158" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S158" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S157" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7076,46 +7064,56 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E159" t="n">
-        <v>100</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G159" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H159" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I159" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J159" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J159" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K159" t="n">
-        <v>1</v>
-      </c>
-      <c r="L159" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M159" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N159" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O159" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P159" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q159" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R159" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S159" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="160">
@@ -7131,119 +7129,166 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="n">
+        <v>100</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N160" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>667</v>
+      </c>
+      <c r="R160" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>100</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N161" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>269</v>
+      </c>
+      <c r="R161" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
         <v>2.19</v>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="n">
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
         <v>2.96</v>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="n">
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="n">
         <v>6.5</v>
       </c>
-      <c r="M160" t="n">
+      <c r="M162" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N160" t="n">
+      <c r="N162" t="n">
         <v>-21127</v>
       </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q160" t="n">
+      <c r="Q162" t="n">
         <v>756</v>
       </c>
-      <c r="R160" t="n">
+      <c r="R162" t="n">
         <v>-58400</v>
       </c>
-      <c r="S160" t="n">
+      <c r="S162" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E161" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M161" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N161" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O161" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P161" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q161" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R161" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S161" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -7257,39 +7302,61 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="inlineStr"/>
-      <c r="M163" s="2" t="inlineStr"/>
-      <c r="N163" s="2" t="inlineStr"/>
-      <c r="O163" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O163" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P163" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R163" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S163" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7323,90 +7390,45 @@
       <c r="S165" s="2" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R167" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S167" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>262</v>
-      </c>
-      <c r="R168" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S168" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7421,456 +7443,542 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R169" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>262</v>
+      </c>
+      <c r="R170" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S170" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D169" t="n">
+      <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="n">
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="n">
         <v>0.61</v>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="n">
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="n">
         <v>0.61</v>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="n">
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="n">
         <v>21</v>
       </c>
-      <c r="M169" t="n">
+      <c r="M171" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N169" t="n">
+      <c r="N171" t="n">
         <v>-37549</v>
       </c>
-      <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" t="n">
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q169" t="n">
+      <c r="Q171" t="n">
         <v>201</v>
       </c>
-      <c r="R169" t="n">
+      <c r="R171" t="n">
         <v>-18985</v>
       </c>
-      <c r="S169" t="n">
+      <c r="S171" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="n">
+      <c r="E172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="n">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="n">
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M170" s="2" t="n">
+      <c r="M172" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N172" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="2" t="n">
+      <c r="O172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q170" s="2" t="n">
+      <c r="Q172" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R170" s="2" t="n">
+      <c r="R172" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S170" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="S172" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D172" t="n">
+      <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="n">
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="n">
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="n">
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
         <v>3</v>
       </c>
-      <c r="M172" t="n">
+      <c r="M174" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N172" t="n">
+      <c r="N174" t="n">
         <v>-74087</v>
       </c>
-      <c r="O172" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" t="n">
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q172" t="n">
+      <c r="Q174" t="n">
         <v>257</v>
       </c>
-      <c r="R172" t="n">
+      <c r="R174" t="n">
         <v>-73830</v>
       </c>
-      <c r="S172" t="n">
+      <c r="S174" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n">
+      <c r="D175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="n">
+      <c r="E175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="n">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="n">
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M173" s="2" t="n">
+      <c r="M175" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N175" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P173" s="2" t="n">
+      <c r="O175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q173" s="2" t="n">
+      <c r="Q175" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R173" s="2" t="n">
+      <c r="R175" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S173" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="S175" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D177" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="n">
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="n">
         <v>4.6</v>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="n">
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="n">
         <v>4.6</v>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="n">
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="n">
         <v>3</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M177" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N175" t="n">
+      <c r="N177" t="n">
         <v>-29689</v>
       </c>
-      <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" t="n">
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q175" t="n">
+      <c r="Q177" t="n">
         <v>189</v>
       </c>
-      <c r="R175" t="n">
+      <c r="R177" t="n">
         <v>-29500</v>
       </c>
-      <c r="S175" t="n">
+      <c r="S177" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D178" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="n">
+      <c r="E178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="n">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="n">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M176" s="2" t="n">
+      <c r="M178" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N178" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P176" s="2" t="n">
+      <c r="O178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q176" s="2" t="n">
+      <c r="Q178" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R176" s="2" t="n">
+      <c r="R178" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S176" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="S178" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="n">
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
         <v>0.87</v>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="n">
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="n">
         <v>0.87</v>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="n">
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="n">
         <v>3</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M180" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N178" t="n">
+      <c r="N180" t="n">
         <v>-29188</v>
       </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q178" t="n">
+      <c r="Q180" t="n">
         <v>2950</v>
       </c>
-      <c r="R178" t="n">
+      <c r="R180" t="n">
         <v>-26238</v>
       </c>
-      <c r="S178" t="n">
+      <c r="S180" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D179" s="2" t="n">
+      <c r="D181" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="n">
+      <c r="E181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="n">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="n">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M179" s="2" t="n">
+      <c r="M181" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N179" s="2" t="n">
+      <c r="N181" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" s="2" t="n">
+      <c r="O181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q179" s="2" t="n">
+      <c r="Q181" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R179" s="2" t="n">
+      <c r="R181" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S179" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S181"/>
+  <dimension ref="A1:S183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1475,37 +1475,45 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.71</v>
+      </c>
       <c r="G17" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>6.05</v>
+      </c>
       <c r="I17" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>6.05</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>9.462999999999999</v>
+        <v>1.707</v>
       </c>
       <c r="N17" t="n">
-        <v>24419</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>-5038</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.71</v>
+      </c>
       <c r="P17" t="n">
-        <v>24419</v>
+        <v>23912</v>
       </c>
       <c r="Q17" t="n">
-        <v>81</v>
+        <v>1520</v>
       </c>
       <c r="R17" t="n">
-        <v>24500</v>
+        <v>25432</v>
       </c>
       <c r="S17" t="n">
         <v>1351</v>
@@ -1528,19 +1536,19 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4.38</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>19.29</v>
@@ -1551,22 +1559,22 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="n">
-        <v>-0.021</v>
+        <v>-0.042</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1164</v>
+        <v>-1285</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>-334642</v>
+        <v>-335149</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>82461</v>
+        <v>83900</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>-252181</v>
+        <v>-251249</v>
       </c>
       <c r="S18" s="2" t="inlineStr"/>
     </row>
@@ -4895,447 +4903,431 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>US_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>33988</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>665</v>
+      </c>
+      <c r="R103" t="n">
+        <v>34653</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D104" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E104" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F104" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="G103" s="2" t="n">
+      <c r="G104" s="2" t="n">
         <v>2.85</v>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H104" s="2" t="n">
         <v>3.77</v>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="I104" s="2" t="n">
         <v>7.7</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J104" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K103" s="2" t="n">
+      <c r="K104" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L104" s="2" t="n">
         <v>9.94</v>
       </c>
-      <c r="M103" s="2" t="n">
+      <c r="M104" s="2" t="n">
         <v>-1.22</v>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N104" s="2" t="n">
         <v>-18044</v>
       </c>
-      <c r="O103" s="2" t="n">
+      <c r="O104" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="P103" s="2" t="n">
-        <v>-470842</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>30273</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>-440569</v>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="P104" s="2" t="n">
+        <v>-436854</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>30938</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>-405916</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="D112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="D114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
         <v>2.13</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="n">
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
         <v>2.13</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M116" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N116" t="n">
         <v>-41586</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="Q116" t="n">
         <v>2702</v>
       </c>
-      <c r="R115" t="n">
+      <c r="R116" t="n">
         <v>-38883</v>
       </c>
-      <c r="S115" t="n">
+      <c r="S116" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="n">
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="n">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="n">
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M116" s="2" t="n">
+      <c r="M117" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N117" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" s="2" t="n">
+      <c r="O117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q116" s="2" t="n">
+      <c r="Q117" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R116" s="2" t="n">
+      <c r="R117" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S116" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>7</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
-        <v>8</v>
-      </c>
-      <c r="M118" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R118" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S118" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S117" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5350,56 +5342,50 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E119" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I119" t="n">
-        <v>3.32</v>
-      </c>
+        <v>3.34</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K119" t="n">
-        <v>18</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M119" t="n">
-        <v>0.864</v>
+        <v>-3.337</v>
       </c>
       <c r="N119" t="n">
-        <v>-18508</v>
+        <v>-7859</v>
       </c>
       <c r="O119" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>-52375</v>
+        <v>-55013</v>
       </c>
       <c r="Q119" t="n">
-        <v>4226</v>
+        <v>1884</v>
       </c>
       <c r="R119" t="n">
-        <v>-48149</v>
+        <v>-53128</v>
       </c>
       <c r="S119" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="120">
@@ -5415,391 +5401,395 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J120" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K120" t="n">
+        <v>18</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D121" t="n">
         <v>2</v>
       </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
         <v>1.87</v>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
         <v>2.68</v>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
         <v>7.5</v>
       </c>
-      <c r="M120" t="n">
+      <c r="M121" t="n">
         <v>-1.87</v>
       </c>
-      <c r="N120" t="n">
+      <c r="N121" t="n">
         <v>-38258</v>
       </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
         <v>-79635</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="Q121" t="n">
         <v>4778</v>
       </c>
-      <c r="R120" t="n">
+      <c r="R121" t="n">
         <v>-74857</v>
       </c>
-      <c r="S120" t="n">
+      <c r="S121" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-2.042</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>-15588</v>
-      </c>
-      <c r="O121" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P121" s="2" t="n">
-        <v>-187023</v>
-      </c>
-      <c r="Q121" s="2" t="n">
-        <v>10888</v>
-      </c>
-      <c r="R121" s="2" t="n">
-        <v>-176134</v>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-34495</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-34495</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>774</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-33721</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-17042</v>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>-221518</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>11662</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>-209855</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="inlineStr"/>
-      <c r="N123" s="2" t="inlineStr"/>
-      <c r="O123" s="2" t="inlineStr"/>
-      <c r="P123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="D125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D127" t="n">
         <v>2</v>
       </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="n">
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
         <v>7.15</v>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
         <v>10.49</v>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="n">
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
         <v>1</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M127" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N127" t="n">
         <v>-27445</v>
       </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q127" t="n">
         <v>1054</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R127" t="n">
         <v>-53835</v>
       </c>
-      <c r="S125" t="n">
+      <c r="S127" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D128" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="n">
+      <c r="E128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="n">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="n">
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M126" s="2" t="n">
+      <c r="M128" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N128" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="2" t="n">
+      <c r="O128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q126" s="2" t="n">
+      <c r="Q128" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R126" s="2" t="n">
+      <c r="R128" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S126" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>17</v>
-      </c>
-      <c r="E128" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G128" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H128" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I128" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J128" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M128" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N128" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O128" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P128" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R128" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S128" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>7</v>
-      </c>
-      <c r="E129" t="n">
-        <v>100</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N129" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R129" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S129" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S128" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5814,241 +5804,304 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>17</v>
+      </c>
+      <c r="E130" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I130" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J130" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N130" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O130" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P130" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R130" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+      <c r="E131" t="n">
+        <v>100</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N131" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R131" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D132" t="n">
         <v>4</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E132" t="n">
         <v>50</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F132" t="n">
         <v>2.51</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G132" t="n">
         <v>11.43</v>
       </c>
-      <c r="H130" t="n">
+      <c r="H132" t="n">
         <v>2.87</v>
       </c>
-      <c r="I130" t="n">
+      <c r="I132" t="n">
         <v>12</v>
       </c>
-      <c r="J130" t="n">
+      <c r="J132" t="n">
         <v>4.94</v>
       </c>
-      <c r="K130" t="n">
+      <c r="K132" t="n">
         <v>14</v>
       </c>
-      <c r="L130" t="n">
+      <c r="L132" t="n">
         <v>14</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M132" t="n">
         <v>4.282</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N132" t="n">
         <v>7910</v>
       </c>
-      <c r="O130" t="n">
+      <c r="O132" t="n">
         <v>2.51</v>
       </c>
-      <c r="P130" t="n">
+      <c r="P132" t="n">
         <v>-912</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q132" t="n">
         <v>635</v>
       </c>
-      <c r="R130" t="n">
+      <c r="R132" t="n">
         <v>-278</v>
       </c>
-      <c r="S130" t="n">
+      <c r="S132" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D133" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F133" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G131" s="2" t="n">
+      <c r="G133" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H133" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I131" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K131" s="2" t="n">
+      <c r="K133" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L131" s="2" t="n">
+      <c r="L133" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M131" s="2" t="n">
+      <c r="M133" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N133" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O131" s="2" t="n">
+      <c r="O133" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P131" s="2" t="n">
+      <c r="P133" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q131" s="2" t="n">
+      <c r="Q133" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R133" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S131" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="S133" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D133" t="n">
+      <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="n">
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
         <v>0.54</v>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="n">
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
         <v>0.54</v>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="n">
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
         <v>12</v>
       </c>
-      <c r="M133" t="n">
+      <c r="M135" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N135" t="n">
         <v>-1280</v>
       </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q135" t="n">
         <v>208</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R135" t="n">
         <v>-1072</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S135" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M134" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N134" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q134" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R134" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S134" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6062,34 +6115,50 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P136" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R136" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6128,236 +6197,153 @@
       <c r="S138" s="2" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D140" t="n">
+      <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E142" t="n">
         <v>100</v>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="n">
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
         <v>2.1</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="n">
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="n">
         <v>2.1</v>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="n">
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
         <v>52.73</v>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="n">
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
         <v>2.102</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N142" t="n">
         <v>2341</v>
       </c>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="n">
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="n">
         <v>2341</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="Q142" t="n">
         <v>34</v>
       </c>
-      <c r="R140" t="n">
+      <c r="R142" t="n">
         <v>2375</v>
       </c>
-      <c r="S140" t="n">
+      <c r="S142" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
+      <c r="D143" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="E143" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="n">
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="n">
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="n">
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="n">
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N141" s="2" t="n">
+      <c r="N143" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O141" s="2" t="inlineStr"/>
-      <c r="P141" s="2" t="n">
+      <c r="O143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q141" s="2" t="n">
+      <c r="Q143" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R141" s="2" t="n">
+      <c r="R143" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S141" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>2</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M143" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N143" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>513</v>
-      </c>
-      <c r="R143" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S143" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>4</v>
-      </c>
-      <c r="E144" t="n">
-        <v>25</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G144" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J144" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M144" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N144" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P144" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R144" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S144" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S143" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6372,7 +6358,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6386,33 +6372,33 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N145" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q145" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R145" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S145" t="n">
         <v>1415</v>
@@ -6431,43 +6417,53 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E146" t="n">
-        <v>100</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G146" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I146" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J146" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K146" t="n">
-        <v>14</v>
-      </c>
-      <c r="L146" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M146" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N146" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O146" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P146" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q146" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R146" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S146" t="n">
         <v>1415</v>
@@ -6486,11 +6482,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -6500,36 +6496,36 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M147" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N147" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q147" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R147" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S147" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="148">
@@ -6545,50 +6541,46 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>14</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N148" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O148" t="inlineStr"/>
       <c r="P148" t="n">
-        <v>-68185</v>
+        <v>48540</v>
       </c>
       <c r="Q148" t="n">
-        <v>5784</v>
+        <v>4254</v>
       </c>
       <c r="R148" t="n">
-        <v>-62401</v>
+        <v>52794</v>
       </c>
       <c r="S148" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="149">
@@ -6604,7 +6596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6618,36 +6610,36 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
-        <v>20</v>
+        <v>4.67</v>
       </c>
       <c r="M149" t="n">
-        <v>-3.417</v>
+        <v>-0.864</v>
       </c>
       <c r="N149" t="n">
-        <v>-120621</v>
+        <v>-28997</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>-324235</v>
+        <v>-86990</v>
       </c>
       <c r="Q149" t="n">
-        <v>7584</v>
+        <v>13787</v>
       </c>
       <c r="R149" t="n">
-        <v>-316651</v>
+        <v>-73203</v>
       </c>
       <c r="S149" t="n">
-        <v>1338</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="150">
@@ -6663,224 +6655,228 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>4</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R150" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>20</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R151" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D150" t="n">
+      <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E152" t="n">
         <v>100</v>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="n">
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
         <v>2.42</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="n">
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="n">
         <v>2.42</v>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="n">
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="n">
         <v>28</v>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="n">
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
         <v>2.425</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N152" t="n">
         <v>36357</v>
       </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="n">
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="n">
         <v>-103816</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q152" t="n">
         <v>4801</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R152" t="n">
         <v>-99015</v>
       </c>
-      <c r="S150" t="n">
+      <c r="S152" t="n">
         <v>1351</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n">
+      <c r="D153" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E153" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F151" s="2" t="n">
+      <c r="F153" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="G151" s="2" t="n">
+      <c r="G153" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H151" s="2" t="n">
+      <c r="H153" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I151" s="2" t="n">
+      <c r="I153" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J151" s="2" t="n">
+      <c r="J153" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K151" s="2" t="n">
+      <c r="K153" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L151" s="2" t="n">
+      <c r="L153" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M151" s="2" t="n">
+      <c r="M153" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N153" s="2" t="n">
         <v>-23737</v>
       </c>
-      <c r="O151" s="2" t="n">
+      <c r="O153" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="P151" s="2" t="n">
+      <c r="P153" s="2" t="n">
         <v>-608573</v>
       </c>
-      <c r="Q151" s="2" t="n">
+      <c r="Q153" s="2" t="n">
         <v>45560</v>
       </c>
-      <c r="R151" s="2" t="n">
+      <c r="R153" s="2" t="n">
         <v>-563014</v>
       </c>
-      <c r="S151" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>9</v>
-      </c>
-      <c r="E153" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H153" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I153" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J153" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P153" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R153" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S153" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>2</v>
-      </c>
-      <c r="E154" t="n">
-        <v>100</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N154" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>667</v>
-      </c>
-      <c r="R154" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S154" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S153" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6895,44 +6891,52 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E155" t="n">
-        <v>100</v>
-      </c>
-      <c r="F155" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G155" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H155" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I155" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J155" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J155" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N155" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O155" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P155" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q155" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R155" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S155" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="156">
@@ -6948,228 +6952,214 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D156" t="n">
         <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N156" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>667</v>
+      </c>
+      <c r="R156" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>100</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N157" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>269</v>
+      </c>
+      <c r="R157" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N158" t="n">
         <v>-21127</v>
       </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="Q158" t="n">
         <v>756</v>
       </c>
-      <c r="R156" t="n">
+      <c r="R158" t="n">
         <v>-58400</v>
       </c>
-      <c r="S156" t="n">
+      <c r="S158" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D159" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E159" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F157" s="2" t="n">
+      <c r="F159" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G157" s="2" t="n">
+      <c r="G159" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H159" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I157" s="2" t="n">
+      <c r="I159" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J159" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="2" t="n">
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N159" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O157" s="2" t="n">
+      <c r="O159" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P157" s="2" t="n">
+      <c r="P159" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q157" s="2" t="n">
+      <c r="Q159" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R157" s="2" t="n">
+      <c r="R159" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S157" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>9</v>
-      </c>
-      <c r="E159" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H159" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I159" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J159" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K159" t="n">
-        <v>3</v>
-      </c>
-      <c r="L159" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M159" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P159" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R159" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S159" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>2</v>
-      </c>
-      <c r="E160" t="n">
-        <v>100</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N160" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>667</v>
-      </c>
-      <c r="R160" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S160" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S159" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7184,46 +7174,56 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E161" t="n">
-        <v>100</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G161" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H161" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I161" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J161" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J161" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M161" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N161" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O161" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P161" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q161" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R161" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S161" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="162">
@@ -7239,119 +7239,166 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>2</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="n">
+        <v>100</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N162" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>667</v>
+      </c>
+      <c r="R162" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S162" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>100</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N163" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>269</v>
+      </c>
+      <c r="R163" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="n">
         <v>2.19</v>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="n">
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="n">
         <v>2.96</v>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="n">
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="n">
         <v>6.5</v>
       </c>
-      <c r="M162" t="n">
+      <c r="M164" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N162" t="n">
+      <c r="N164" t="n">
         <v>-21127</v>
       </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" t="n">
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q162" t="n">
+      <c r="Q164" t="n">
         <v>756</v>
       </c>
-      <c r="R162" t="n">
+      <c r="R164" t="n">
         <v>-58400</v>
       </c>
-      <c r="S162" t="n">
+      <c r="S164" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M163" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N163" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O163" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P163" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q163" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R163" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S163" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7365,39 +7412,61 @@
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="inlineStr"/>
-      <c r="N165" s="2" t="inlineStr"/>
-      <c r="O165" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P165" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R165" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S165" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7431,90 +7500,45 @@
       <c r="S167" s="2" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R169" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S169" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>262</v>
-      </c>
-      <c r="R170" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S170" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7529,456 +7553,542 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R171" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>262</v>
+      </c>
+      <c r="R172" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D171" t="n">
+      <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="n">
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="n">
         <v>0.61</v>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="n">
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="n">
         <v>0.61</v>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="n">
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="n">
         <v>21</v>
       </c>
-      <c r="M171" t="n">
+      <c r="M173" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N171" t="n">
+      <c r="N173" t="n">
         <v>-37549</v>
       </c>
-      <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" t="n">
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q171" t="n">
+      <c r="Q173" t="n">
         <v>201</v>
       </c>
-      <c r="R171" t="n">
+      <c r="R173" t="n">
         <v>-18985</v>
       </c>
-      <c r="S171" t="n">
+      <c r="S173" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D174" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="n">
+      <c r="E174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="n">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="n">
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M172" s="2" t="n">
+      <c r="M174" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N174" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" s="2" t="n">
+      <c r="O174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q172" s="2" t="n">
+      <c r="Q174" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R172" s="2" t="n">
+      <c r="R174" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S172" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="S174" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D174" t="n">
+      <c r="D176" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="n">
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="n">
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="n">
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="n">
         <v>3</v>
       </c>
-      <c r="M174" t="n">
+      <c r="M176" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N174" t="n">
+      <c r="N176" t="n">
         <v>-74087</v>
       </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" t="n">
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q174" t="n">
+      <c r="Q176" t="n">
         <v>257</v>
       </c>
-      <c r="R174" t="n">
+      <c r="R176" t="n">
         <v>-73830</v>
       </c>
-      <c r="S174" t="n">
+      <c r="S176" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n">
+      <c r="D177" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="n">
+      <c r="E177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="n">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="n">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M175" s="2" t="n">
+      <c r="M177" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N177" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="2" t="n">
+      <c r="O177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q175" s="2" t="n">
+      <c r="Q177" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R175" s="2" t="n">
+      <c r="R177" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S175" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="S177" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D177" t="n">
+      <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="n">
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="n">
         <v>4.6</v>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="n">
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="n">
         <v>4.6</v>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="n">
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="n">
         <v>3</v>
       </c>
-      <c r="M177" t="n">
+      <c r="M179" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N177" t="n">
+      <c r="N179" t="n">
         <v>-29689</v>
       </c>
-      <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="n">
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q177" t="n">
+      <c r="Q179" t="n">
         <v>189</v>
       </c>
-      <c r="R177" t="n">
+      <c r="R179" t="n">
         <v>-29500</v>
       </c>
-      <c r="S177" t="n">
+      <c r="S179" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D180" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="n">
+      <c r="E180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="n">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="n">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M178" s="2" t="n">
+      <c r="M180" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N180" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" s="2" t="n">
+      <c r="O180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q178" s="2" t="n">
+      <c r="Q180" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R178" s="2" t="n">
+      <c r="R180" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S178" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="S180" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D180" t="n">
+      <c r="D182" t="n">
         <v>1</v>
       </c>
-      <c r="E180" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="n">
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="n">
         <v>0.87</v>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="n">
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="n">
         <v>0.87</v>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="n">
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="n">
         <v>3</v>
       </c>
-      <c r="M180" t="n">
+      <c r="M182" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N180" t="n">
+      <c r="N182" t="n">
         <v>-29188</v>
       </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q180" t="n">
+      <c r="Q182" t="n">
         <v>2950</v>
       </c>
-      <c r="R180" t="n">
+      <c r="R182" t="n">
         <v>-26238</v>
       </c>
-      <c r="S180" t="n">
+      <c r="S182" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n">
+      <c r="D183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="n">
+      <c r="E183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="n">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="n">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M181" s="2" t="n">
+      <c r="M183" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N181" s="2" t="n">
+      <c r="N183" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="2" t="n">
+      <c r="O183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q181" s="2" t="n">
+      <c r="Q183" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R181" s="2" t="n">
+      <c r="R183" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S181" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S183"/>
+  <dimension ref="A1:S204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>4.86</v>
+        <v>3.05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
@@ -1376,22 +1376,22 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>-4.859</v>
+        <v>-3.054</v>
       </c>
       <c r="N15" t="n">
-        <v>-74342</v>
+        <v>-38107</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-15947</v>
+        <v>-17820</v>
       </c>
       <c r="Q15" t="n">
-        <v>346</v>
+        <v>495</v>
       </c>
       <c r="R15" t="n">
-        <v>-15601</v>
+        <v>-17325</v>
       </c>
       <c r="S15" t="n">
         <v>1338</v>
@@ -1446,13 +1446,13 @@
         <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>27162</v>
+        <v>81557</v>
       </c>
       <c r="Q16" t="n">
-        <v>3889</v>
+        <v>4127</v>
       </c>
       <c r="R16" t="n">
-        <v>31050</v>
+        <v>85684</v>
       </c>
       <c r="S16" t="n">
         <v>1378</v>
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.71</v>
+        <v>2.97</v>
       </c>
       <c r="G17" t="n">
-        <v>9.460000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="H17" t="n">
-        <v>6.05</v>
+        <v>1.45</v>
       </c>
       <c r="I17" t="n">
-        <v>9.460000000000001</v>
+        <v>29.58</v>
       </c>
       <c r="J17" t="n">
         <v>6.05</v>
@@ -1498,25 +1498,25 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>1.707</v>
+        <v>3.717</v>
       </c>
       <c r="N17" t="n">
-        <v>-5038</v>
+        <v>6290</v>
       </c>
       <c r="O17" t="n">
-        <v>0.71</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>23912</v>
+        <v>115348</v>
       </c>
       <c r="Q17" t="n">
-        <v>1520</v>
+        <v>6809</v>
       </c>
       <c r="R17" t="n">
-        <v>25432</v>
+        <v>122157</v>
       </c>
       <c r="S17" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="18">
@@ -1536,22 +1536,22 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38</v>
+        <v>38.7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19.29</v>
+        <v>29.58</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>20.1</v>
@@ -1559,22 +1559,22 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="n">
-        <v>-0.042</v>
+        <v>0.16</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1285</v>
+        <v>-820</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>-335149</v>
+        <v>-191191</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>83900</v>
+        <v>89576</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>-251249</v>
+        <v>-101614</v>
       </c>
       <c r="S18" s="2" t="inlineStr"/>
     </row>
@@ -2232,7 +2232,7 @@
         <v>24500</v>
       </c>
       <c r="S30" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="31">
@@ -4933,16 +4933,16 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>33988</v>
+        <v>46530</v>
       </c>
       <c r="Q103" t="n">
-        <v>665</v>
+        <v>2909</v>
       </c>
       <c r="R103" t="n">
-        <v>34653</v>
+        <v>49439</v>
       </c>
       <c r="S103" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="104">
@@ -4998,13 +4998,13 @@
         <v>0.34</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>-436854</v>
+        <v>-424312</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>30938</v>
+        <v>33182</v>
       </c>
       <c r="R104" s="2" t="n">
-        <v>-405916</v>
+        <v>-391130</v>
       </c>
       <c r="S104" s="2" t="inlineStr"/>
     </row>
@@ -5173,220 +5173,204 @@
       <c r="S112" s="2" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>-298</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>217</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-81</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="D115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="n">
+        <v>-298</v>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>-81</v>
+      </c>
+      <c r="S115" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
         <v>2.13</v>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
         <v>2.13</v>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
         <v>1</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M117" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N117" t="n">
         <v>-41586</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q117" t="n">
         <v>2702</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R117" t="n">
         <v>-38883</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S117" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="n">
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="n">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="n">
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M117" s="2" t="n">
+      <c r="M118" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N118" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="2" t="n">
+      <c r="O118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q117" s="2" t="n">
+      <c r="Q118" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R117" s="2" t="n">
+      <c r="R118" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S117" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>7</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>8</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R119" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S118" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5401,56 +5385,50 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E120" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G120" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I120" t="n">
-        <v>3.32</v>
-      </c>
+        <v>3.34</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K120" t="n">
-        <v>18</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M120" t="n">
-        <v>0.864</v>
+        <v>-3.337</v>
       </c>
       <c r="N120" t="n">
-        <v>-18508</v>
+        <v>-7859</v>
       </c>
       <c r="O120" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-52375</v>
+        <v>-55013</v>
       </c>
       <c r="Q120" t="n">
-        <v>4226</v>
+        <v>1884</v>
       </c>
       <c r="R120" t="n">
-        <v>-48149</v>
+        <v>-53128</v>
       </c>
       <c r="S120" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="121">
@@ -5466,50 +5444,56 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H121" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3.32</v>
+      </c>
       <c r="J121" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="K121" t="n">
+        <v>18</v>
+      </c>
       <c r="L121" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>-1.87</v>
+        <v>0.864</v>
       </c>
       <c r="N121" t="n">
-        <v>-38258</v>
+        <v>-18508</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P121" t="n">
-        <v>-79635</v>
+        <v>-52375</v>
       </c>
       <c r="Q121" t="n">
-        <v>4778</v>
+        <v>4226</v>
       </c>
       <c r="R121" t="n">
-        <v>-74857</v>
+        <v>-48149</v>
       </c>
       <c r="S121" t="n">
-        <v>1369</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="122">
@@ -5525,11 +5509,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -5539,322 +5523,316 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>6.05</v>
+        <v>1.87</v>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>6.05</v>
+        <v>2.68</v>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-38258</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-79635</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>4778</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-74857</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="M122" t="n">
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="n">
         <v>-6.05</v>
       </c>
-      <c r="N122" t="n">
-        <v>-34495</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>-34495</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>774</v>
-      </c>
-      <c r="R122" t="n">
-        <v>-33721</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="N123" t="n">
+        <v>-34546</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-34546</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>775</v>
+      </c>
+      <c r="R123" t="n">
+        <v>-33771</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D124" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="F123" s="2" t="n">
+      <c r="F124" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="G123" s="2" t="n">
+      <c r="G124" s="2" t="n">
         <v>2.89</v>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H124" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="I123" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K123" s="2" t="n">
+      <c r="K124" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L123" s="2" t="n">
+      <c r="L124" s="2" t="n">
         <v>6.55</v>
       </c>
-      <c r="M123" s="2" t="n">
+      <c r="M124" s="2" t="n">
         <v>-2.35</v>
       </c>
-      <c r="N123" s="2" t="n">
-        <v>-17042</v>
-      </c>
-      <c r="O123" s="2" t="n">
+      <c r="N124" s="2" t="n">
+        <v>-17046</v>
+      </c>
+      <c r="O124" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="P123" s="2" t="n">
-        <v>-221518</v>
-      </c>
-      <c r="Q123" s="2" t="n">
-        <v>11662</v>
-      </c>
-      <c r="R123" s="2" t="n">
-        <v>-209855</v>
-      </c>
-      <c r="S123" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="P124" s="2" t="n">
+        <v>-221569</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>11663</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>-209905</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="D126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D128" t="n">
         <v>2</v>
       </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="n">
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
         <v>7.15</v>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="n">
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
         <v>10.49</v>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="n">
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
         <v>1</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M128" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N128" t="n">
         <v>-27445</v>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q128" t="n">
         <v>1054</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R128" t="n">
         <v>-53835</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S128" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D129" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="n">
+      <c r="E129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="n">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="n">
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M128" s="2" t="n">
+      <c r="M129" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N129" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="2" t="n">
+      <c r="O129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q128" s="2" t="n">
+      <c r="Q129" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R129" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S128" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>17</v>
-      </c>
-      <c r="E130" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F130" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G130" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H130" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I130" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J130" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M130" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N130" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O130" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P130" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R130" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S130" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S129" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5869,46 +5847,56 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E131" t="n">
-        <v>100</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
+        <v>52.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.87</v>
+      </c>
       <c r="G131" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>7.27</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.48</v>
+      </c>
       <c r="I131" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
+        <v>16.31</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5.68</v>
+      </c>
       <c r="K131" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
+        <v>0.78</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M131" t="n">
-        <v>6.16</v>
+        <v>2.681</v>
       </c>
       <c r="N131" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O131" t="inlineStr"/>
+        <v>3410</v>
+      </c>
+      <c r="O131" t="n">
+        <v>2.11</v>
+      </c>
       <c r="P131" t="n">
-        <v>86535</v>
+        <v>134658</v>
       </c>
       <c r="Q131" t="n">
-        <v>1828</v>
+        <v>7271</v>
       </c>
       <c r="R131" t="n">
-        <v>88363</v>
+        <v>141929</v>
       </c>
       <c r="S131" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="132">
@@ -5924,490 +5912,486 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>100</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N132" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R132" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D133" t="n">
         <v>4</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E133" t="n">
         <v>50</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F133" t="n">
         <v>2.51</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G133" t="n">
         <v>11.43</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H133" t="n">
         <v>2.87</v>
       </c>
-      <c r="I132" t="n">
+      <c r="I133" t="n">
         <v>12</v>
       </c>
-      <c r="J132" t="n">
+      <c r="J133" t="n">
         <v>4.94</v>
       </c>
-      <c r="K132" t="n">
+      <c r="K133" t="n">
         <v>14</v>
       </c>
-      <c r="L132" t="n">
+      <c r="L133" t="n">
         <v>14</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M133" t="n">
         <v>4.282</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>7910</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O133" t="n">
         <v>2.51</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P133" t="n">
         <v>-912</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>635</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>-278</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D134" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E133" s="2" t="n">
+      <c r="E134" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F133" s="2" t="n">
+      <c r="F134" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G133" s="2" t="n">
+      <c r="G134" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H133" s="2" t="n">
+      <c r="H134" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I133" s="2" t="n">
+      <c r="I134" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J134" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K133" s="2" t="n">
+      <c r="K134" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L133" s="2" t="n">
+      <c r="L134" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M133" s="2" t="n">
+      <c r="M134" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N133" s="2" t="n">
+      <c r="N134" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O133" s="2" t="n">
+      <c r="O134" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P133" s="2" t="n">
+      <c r="P134" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q133" s="2" t="n">
+      <c r="Q134" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R133" s="2" t="n">
+      <c r="R134" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S133" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="S134" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="n">
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
         <v>0.54</v>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="n">
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
         <v>0.54</v>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="n">
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
         <v>12</v>
       </c>
-      <c r="M135" t="n">
+      <c r="M136" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N135" t="n">
+      <c r="N136" t="n">
         <v>-1280</v>
       </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q135" t="n">
+      <c r="Q136" t="n">
         <v>208</v>
       </c>
-      <c r="R135" t="n">
+      <c r="R136" t="n">
         <v>-1072</v>
       </c>
-      <c r="S135" t="n">
+      <c r="S136" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
+      <c r="D137" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="n">
+      <c r="E137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="n">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="n">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="M137" s="2" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N136" s="2" t="n">
+      <c r="N137" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="O136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="2" t="n">
+      <c r="O137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q136" s="2" t="n">
+      <c r="Q137" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="R136" s="2" t="n">
+      <c r="R137" s="2" t="n">
         <v>-1072</v>
       </c>
-      <c r="S136" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="S137" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr"/>
-      <c r="P138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr"/>
-      <c r="P140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D142" t="n">
+      <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E143" t="n">
         <v>100</v>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="n">
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
         <v>2.1</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="n">
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="n">
         <v>2.1</v>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="n">
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
         <v>52.73</v>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="n">
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
         <v>2.102</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N143" t="n">
         <v>2341</v>
       </c>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="n">
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="n">
         <v>2341</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="Q143" t="n">
         <v>34</v>
       </c>
-      <c r="R142" t="n">
+      <c r="R143" t="n">
         <v>2375</v>
       </c>
-      <c r="S142" t="n">
+      <c r="S143" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D144" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E144" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="n">
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="n">
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="n">
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="n">
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N144" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O143" s="2" t="inlineStr"/>
-      <c r="P143" s="2" t="n">
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q143" s="2" t="n">
+      <c r="Q144" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R143" s="2" t="n">
+      <c r="R144" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S143" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="n">
-        <v>1</v>
-      </c>
-      <c r="M145" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>513</v>
-      </c>
-      <c r="R145" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S145" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S144" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>업비트SCO-Top3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6417,353 +6401,233 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>25</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0.74</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J146" t="n">
-        <v>1.32</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="n">
         <v>1</v>
       </c>
-      <c r="L146" t="n">
-        <v>5.67</v>
-      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>-0.217</v>
+        <v>2.876</v>
       </c>
       <c r="N146" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0.02</v>
-      </c>
+        <v>4316</v>
+      </c>
+      <c r="O146" t="inlineStr"/>
       <c r="P146" t="n">
-        <v>-53089</v>
+        <v>13859</v>
       </c>
       <c r="Q146" t="n">
-        <v>5913</v>
+        <v>327</v>
       </c>
       <c r="R146" t="n">
-        <v>-47176</v>
+        <v>14186</v>
       </c>
       <c r="S146" t="n">
-        <v>1415</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>2</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M147" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R147" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S147" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" t="n">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="n">
-        <v>14</v>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N148" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R148" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S148" t="n">
-        <v>1415</v>
-      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="n">
+        <v>2.876</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>4316</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr"/>
+      <c r="P147" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="Q147" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>14186</v>
+      </c>
+      <c r="S147" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>업비트SCO-15분</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
+        <v>3.92</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3.1</v>
+      </c>
       <c r="H149" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I149" t="inlineStr"/>
+        <v>0.79</v>
+      </c>
+      <c r="I149" t="n">
+        <v>6.36</v>
+      </c>
       <c r="J149" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K149" t="inlineStr"/>
+        <v>1.95</v>
+      </c>
+      <c r="K149" t="n">
+        <v>753.65</v>
+      </c>
       <c r="L149" t="n">
-        <v>4.67</v>
+        <v>197.67</v>
       </c>
       <c r="M149" t="n">
-        <v>-0.864</v>
+        <v>0.625</v>
       </c>
       <c r="N149" t="n">
-        <v>-28997</v>
+        <v>1249</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P149" t="n">
-        <v>-86990</v>
+        <v>13742</v>
       </c>
       <c r="Q149" t="n">
-        <v>13787</v>
+        <v>2208</v>
       </c>
       <c r="R149" t="n">
-        <v>-73203</v>
+        <v>15950</v>
       </c>
       <c r="S149" t="n">
-        <v>1411</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>2</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="n">
-        <v>4</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-0.918</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>-68185</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>5784</v>
-      </c>
-      <c r="R150" t="n">
-        <v>-62401</v>
-      </c>
-      <c r="S150" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>3</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="n">
-        <v>20</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-3.417</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-120621</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
-        <v>-324235</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>7584</v>
-      </c>
-      <c r="R151" t="n">
-        <v>-316651</v>
-      </c>
-      <c r="S151" t="n">
-        <v>1338</v>
-      </c>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>업비트SCO-15분</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>753.65</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>197.67</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>1249</v>
+      </c>
+      <c r="O150" s="2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>13742</v>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>2208</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>15950</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>바이낸스SCO-Top3</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6777,48 +6641,36 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>2.42</v>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="n">
-        <v>2.42</v>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="n">
-        <v>28</v>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="N152" t="n">
-        <v>36357</v>
-      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="n">
-        <v>-103816</v>
+        <v>2341</v>
       </c>
       <c r="Q152" t="n">
-        <v>4801</v>
+        <v>30</v>
       </c>
       <c r="R152" t="n">
-        <v>-99015</v>
+        <v>2370</v>
       </c>
       <c r="S152" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>바이낸스SCO-Top3</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -6832,108 +6684,84 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="M153" s="2" t="n">
-        <v>-0.774</v>
-      </c>
-      <c r="N153" s="2" t="n">
-        <v>-23737</v>
-      </c>
-      <c r="O153" s="2" t="n">
-        <v>0.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr"/>
       <c r="P153" s="2" t="n">
-        <v>-608573</v>
+        <v>2341</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>45560</v>
+        <v>30</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>-563014</v>
+        <v>2370</v>
       </c>
       <c r="S153" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I155" t="n">
-        <v>3.38</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="n">
-        <v>7.04</v>
+        <v>3.49</v>
       </c>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
       <c r="M155" t="n">
-        <v>-1.213</v>
+        <v>-2.607</v>
       </c>
       <c r="N155" t="n">
-        <v>-744</v>
+        <v>-8011</v>
       </c>
       <c r="O155" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>-6692</v>
+        <v>-16021</v>
       </c>
       <c r="Q155" t="n">
-        <v>2139</v>
+        <v>513</v>
       </c>
       <c r="R155" t="n">
-        <v>-4553</v>
+        <v>-15508</v>
       </c>
       <c r="S155" t="n">
         <v>1415</v>
@@ -6942,229 +6770,304 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E156" t="n">
-        <v>100</v>
-      </c>
-      <c r="F156" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G156" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I156" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M156" t="n">
-        <v>8.56</v>
+        <v>-0.217</v>
       </c>
       <c r="N156" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O156" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P156" t="n">
-        <v>114933</v>
+        <v>-53089</v>
       </c>
       <c r="Q156" t="n">
-        <v>667</v>
+        <v>5913</v>
       </c>
       <c r="R156" t="n">
-        <v>115600</v>
+        <v>-47176</v>
       </c>
       <c r="S156" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>100</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>0.16</v>
+      </c>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M157" t="n">
-        <v>4.029</v>
+        <v>-0.136</v>
       </c>
       <c r="N157" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O157" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
       <c r="P157" t="n">
-        <v>35381</v>
+        <v>-4777</v>
       </c>
       <c r="Q157" t="n">
-        <v>269</v>
+        <v>2924</v>
       </c>
       <c r="R157" t="n">
-        <v>35650</v>
+        <v>-1854</v>
       </c>
       <c r="S157" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K158" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>14</v>
+      </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="n">
-        <v>-2.191</v>
+        <v>1.042</v>
       </c>
       <c r="N158" t="n">
-        <v>-21127</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O158" t="inlineStr"/>
       <c r="P158" t="n">
-        <v>-59156</v>
+        <v>48540</v>
       </c>
       <c r="Q158" t="n">
-        <v>756</v>
+        <v>4254</v>
       </c>
       <c r="R158" t="n">
-        <v>-58400</v>
+        <v>52794</v>
       </c>
       <c r="S158" t="n">
-        <v>1369</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E159" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N159" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O159" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P159" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q159" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R159" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S159" s="2" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M159" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N159" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R159" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>4</v>
+      </c>
+      <c r="M160" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N160" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R160" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1383</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7174,62 +7077,56 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G161" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I161" t="n">
-        <v>3.38</v>
-      </c>
+        <v>3.42</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3</v>
-      </c>
+        <v>4.05</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
-        <v>1.75</v>
+        <v>20</v>
       </c>
       <c r="M161" t="n">
-        <v>-1.213</v>
+        <v>-3.417</v>
       </c>
       <c r="N161" t="n">
-        <v>-744</v>
+        <v>-120621</v>
       </c>
       <c r="O161" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>-6692</v>
+        <v>-324235</v>
       </c>
       <c r="Q161" t="n">
-        <v>2139</v>
+        <v>7584</v>
       </c>
       <c r="R161" t="n">
-        <v>-4553</v>
+        <v>-316651</v>
       </c>
       <c r="S161" t="n">
-        <v>1415</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7239,275 +7136,344 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>100</v>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>8.56</v>
+        <v>2.42</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>12.69</v>
+        <v>2.42</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
-        <v>8.56</v>
+        <v>2.425</v>
       </c>
       <c r="N162" t="n">
-        <v>57466</v>
+        <v>36411</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="n">
+        <v>-103970</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4808</v>
+      </c>
+      <c r="R162" t="n">
+        <v>-99161</v>
+      </c>
+      <c r="S162" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>-23734</v>
+      </c>
+      <c r="O163" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P163" s="2" t="n">
+        <v>-608727</v>
+      </c>
+      <c r="Q163" s="2" t="n">
+        <v>45567</v>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>-563160</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>9</v>
+      </c>
+      <c r="E165" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I165" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N165" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P165" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R165" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S165" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>100</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N166" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
         <v>114933</v>
       </c>
-      <c r="Q162" t="n">
+      <c r="Q166" t="n">
         <v>667</v>
       </c>
-      <c r="R162" t="n">
+      <c r="R166" t="n">
         <v>115600</v>
       </c>
-      <c r="S162" t="n">
+      <c r="S166" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E167" t="n">
         <v>100</v>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="n">
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="n">
         <v>4.03</v>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="n">
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
         <v>4.03</v>
       </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="n">
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="n">
         <v>4.029</v>
       </c>
-      <c r="N163" t="n">
+      <c r="N167" t="n">
         <v>35381</v>
       </c>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="n">
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
         <v>35381</v>
       </c>
-      <c r="Q163" t="n">
+      <c r="Q167" t="n">
         <v>269</v>
       </c>
-      <c r="R163" t="n">
+      <c r="R167" t="n">
         <v>35650</v>
       </c>
-      <c r="S163" t="n">
+      <c r="S167" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D164" t="n">
+      <c r="D168" t="n">
         <v>2</v>
       </c>
-      <c r="E164" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="n">
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="n">
         <v>2.19</v>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="n">
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="n">
         <v>2.96</v>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M164" t="n">
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N164" t="n">
+      <c r="N168" t="n">
         <v>-21127</v>
       </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q164" t="n">
+      <c r="Q168" t="n">
         <v>756</v>
       </c>
-      <c r="R164" t="n">
+      <c r="R168" t="n">
         <v>-58400</v>
       </c>
-      <c r="S164" t="n">
+      <c r="S168" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L165" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M165" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N165" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O165" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P165" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q165" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R165" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S165" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>미국수동</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr"/>
-      <c r="N167" s="2" t="inlineStr"/>
-      <c r="O167" s="2" t="inlineStr"/>
-      <c r="P167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -7516,34 +7482,52 @@
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="2" t="inlineStr"/>
-      <c r="N169" s="2" t="inlineStr"/>
-      <c r="O169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O169" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P169" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q169" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R169" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S169" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2X단타_시딩</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7553,40 +7537,62 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E171" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H171" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J171" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K171" t="n">
+        <v>3</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P171" t="n">
-        <v>51315</v>
+        <v>-6692</v>
       </c>
       <c r="Q171" t="n">
-        <v>1370</v>
+        <v>2139</v>
       </c>
       <c r="R171" t="n">
-        <v>52685</v>
+        <v>-4553</v>
       </c>
       <c r="S171" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2X단타_시딩</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7596,40 +7602,52 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>100</v>
+      </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="n">
+        <v>8.56</v>
+      </c>
       <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>12.69</v>
+      </c>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>4.5</v>
+      </c>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N172" t="n">
+        <v>57466</v>
+      </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="n">
-        <v>-69677</v>
+        <v>114933</v>
       </c>
       <c r="Q172" t="n">
-        <v>262</v>
+        <v>667</v>
       </c>
       <c r="R172" t="n">
-        <v>-69415</v>
+        <v>115600</v>
       </c>
       <c r="S172" t="n">
-        <v>1369</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2X단타_시딩</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7639,172 +7657,174 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="n">
-        <v>21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
       <c r="M173" t="n">
-        <v>-0.612</v>
+        <v>4.029</v>
       </c>
       <c r="N173" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O173" t="n">
-        <v>0</v>
-      </c>
+        <v>35381</v>
+      </c>
+      <c r="O173" t="inlineStr"/>
       <c r="P173" t="n">
-        <v>-19186</v>
+        <v>35381</v>
       </c>
       <c r="Q173" t="n">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="R173" t="n">
-        <v>-18985</v>
+        <v>35650</v>
       </c>
       <c r="S173" t="n">
-        <v>1338</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-2.191</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-21127</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>-59156</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>756</v>
+      </c>
+      <c r="R174" t="n">
+        <v>-58400</v>
+      </c>
+      <c r="S174" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="M174" s="2" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="N174" s="2" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="2" t="n">
-        <v>-37548</v>
-      </c>
-      <c r="Q174" s="2" t="n">
-        <v>1833</v>
-      </c>
-      <c r="R174" s="2" t="n">
-        <v>-35715</v>
-      </c>
-      <c r="S174" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>수동매매_시딩</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="n">
-        <v>3</v>
-      </c>
-      <c r="M176" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N176" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O176" t="n">
-        <v>0</v>
-      </c>
-      <c r="P176" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>257</v>
-      </c>
-      <c r="R176" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S176" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D175" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>84466</v>
+      </c>
+      <c r="Q175" s="2" t="n">
+        <v>3831</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>88297</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>수동매매_시딩</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7818,277 +7838,1032 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M177" s="2" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N177" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O177" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr"/>
       <c r="P177" s="2" t="n">
-        <v>-74087</v>
+        <v>0</v>
       </c>
       <c r="Q177" s="2" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="R177" s="2" t="n">
-        <v>-73830</v>
+        <v>0</v>
       </c>
       <c r="S177" s="2" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>주도주_시딩</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr"/>
+      <c r="P179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="n">
-        <v>3</v>
-      </c>
-      <c r="M179" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>189</v>
-      </c>
-      <c r="R179" t="n">
-        <v>-29500</v>
-      </c>
-      <c r="S179" t="n">
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R181" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S181" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>주도주_시딩</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M180" s="2" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N180" s="2" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="2" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="Q180" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="R180" s="2" t="n">
-        <v>-29500</v>
-      </c>
-      <c r="S180" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>262</v>
+      </c>
+      <c r="R182" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S182" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="n">
+        <v>21</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-37549</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-19186</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>201</v>
+      </c>
+      <c r="R183" t="n">
+        <v>-18985</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>-37549</v>
+      </c>
+      <c r="O184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" s="2" t="n">
+        <v>-37548</v>
+      </c>
+      <c r="Q184" s="2" t="n">
+        <v>1833</v>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>-35715</v>
+      </c>
+      <c r="S184" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="n">
+        <v>3654</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>33</v>
+      </c>
+      <c r="R186" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S186" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="n">
+        <v>3654</v>
+      </c>
+      <c r="Q187" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S187" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>149</v>
+      </c>
+      <c r="R189" t="n">
+        <v>-1724</v>
+      </c>
+      <c r="S189" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" t="n">
+        <v>100</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>5</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>10.223</v>
+      </c>
+      <c r="N190" t="n">
+        <v>5114</v>
+      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="n">
+        <v>11272</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>122</v>
+      </c>
+      <c r="R190" t="n">
+        <v>11395</v>
+      </c>
+      <c r="S190" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>6.399</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>2785</v>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>9399</v>
+      </c>
+      <c r="Q191" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>9671</v>
+      </c>
+      <c r="S191" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>09/14~09/18</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="n">
+        <v>54396</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>238</v>
+      </c>
+      <c r="R193" t="n">
+        <v>54634</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>100</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>6</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>29.576</v>
+      </c>
+      <c r="N194" t="n">
+        <v>88772</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="n">
+        <v>34376</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>106</v>
+      </c>
+      <c r="R194" t="n">
+        <v>34482</v>
+      </c>
+      <c r="S194" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="n">
+        <v>29.576</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>88772</v>
+      </c>
+      <c r="O195" s="2" t="inlineStr"/>
+      <c r="P195" s="2" t="n">
+        <v>88772</v>
+      </c>
+      <c r="Q195" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>89116</v>
+      </c>
+      <c r="S195" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>수동매매_시딩</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="n">
+        <v>3</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>257</v>
+      </c>
+      <c r="R197" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S197" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>수동매매_시딩</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q198" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="R198" s="2" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S198" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>3</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>189</v>
+      </c>
+      <c r="R200" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q201" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R201" s="2" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S201" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D182" t="n">
+      <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E182" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="n">
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="n">
         <v>0.87</v>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="n">
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="n">
         <v>0.87</v>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="n">
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="n">
         <v>3</v>
       </c>
-      <c r="M182" t="n">
+      <c r="M203" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N182" t="n">
+      <c r="N203" t="n">
         <v>-29188</v>
       </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q182" t="n">
+      <c r="Q203" t="n">
         <v>2950</v>
       </c>
-      <c r="R182" t="n">
+      <c r="R203" t="n">
         <v>-26238</v>
       </c>
-      <c r="S182" t="n">
+      <c r="S203" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D204" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="n">
+      <c r="E204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="n">
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="n">
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M183" s="2" t="n">
+      <c r="M204" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N183" s="2" t="n">
+      <c r="N204" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" s="2" t="n">
+      <c r="O204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q183" s="2" t="n">
+      <c r="Q204" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R183" s="2" t="n">
+      <c r="R204" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S183" s="2" t="inlineStr"/>
+      <c r="S204" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1568,16 +1568,16 @@
         <v>0.91</v>
       </c>
       <c r="P18" t="n">
-        <v>14255</v>
+        <v>14239</v>
       </c>
       <c r="Q18" t="n">
         <v>1300</v>
       </c>
       <c r="R18" t="n">
-        <v>15555</v>
+        <v>15539</v>
       </c>
       <c r="S18" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19">
@@ -1629,13 +1629,13 @@
         <v>0.9</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>-179349</v>
+        <v>-179365</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>93880</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>-85468</v>
+        <v>-85484</v>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
     </row>
@@ -4148,7 +4148,7 @@
         <v>15290</v>
       </c>
       <c r="S77" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="78">
@@ -4397,7 +4397,7 @@
         <v>-12750</v>
       </c>
       <c r="S85" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="86">
@@ -6712,7 +6712,7 @@
         <v>6858</v>
       </c>
       <c r="S150" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="151">
@@ -6895,7 +6895,7 @@
         <v>1285</v>
       </c>
       <c r="S154" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="155">
@@ -7035,16 +7035,16 @@
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="n">
-        <v>2748</v>
+        <v>2732</v>
       </c>
       <c r="Q158" t="n">
         <v>21</v>
       </c>
       <c r="R158" t="n">
-        <v>2769</v>
+        <v>2753</v>
       </c>
       <c r="S158" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="159">
@@ -7078,13 +7078,13 @@
       <c r="N159" s="2" t="inlineStr"/>
       <c r="O159" s="2" t="inlineStr"/>
       <c r="P159" s="2" t="n">
-        <v>3660</v>
+        <v>3644</v>
       </c>
       <c r="Q159" s="2" t="n">
         <v>82</v>
       </c>
       <c r="R159" s="2" t="n">
-        <v>3742</v>
+        <v>3726</v>
       </c>
       <c r="S159" s="2" t="inlineStr"/>
     </row>
@@ -8735,7 +8735,7 @@
         <v>2103</v>
       </c>
       <c r="S197" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="198">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1542,7 +1542,7 @@
         <v>43.3</v>
       </c>
       <c r="F18" t="n">
-        <v>6.76</v>
+        <v>6.74</v>
       </c>
       <c r="G18" t="n">
         <v>7.88</v>
@@ -1562,22 +1562,22 @@
         <v>2.086</v>
       </c>
       <c r="N18" t="n">
-        <v>22762</v>
+        <v>22763</v>
       </c>
       <c r="O18" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="P18" t="n">
-        <v>592075</v>
+        <v>591799</v>
       </c>
       <c r="Q18" t="n">
-        <v>12047</v>
+        <v>12073</v>
       </c>
       <c r="R18" t="n">
-        <v>604121</v>
+        <v>603871</v>
       </c>
       <c r="S18" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="19">
@@ -1623,19 +1623,19 @@
         <v>0.336</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>1.17</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>398471</v>
+        <v>398195</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>104627</v>
+        <v>104653</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>503098</v>
+        <v>502848</v>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
     </row>
@@ -3065,7 +3065,7 @@
         <v>1751</v>
       </c>
       <c r="S49" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="50">
@@ -3482,7 +3482,7 @@
         <v>241675</v>
       </c>
       <c r="S58" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="59">
@@ -4258,7 +4258,7 @@
         <v>272090</v>
       </c>
       <c r="S79" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="80">
@@ -4525,7 +4525,7 @@
         <v>153750</v>
       </c>
       <c r="S87" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="88">
@@ -5305,22 +5305,22 @@
         <v>2.292</v>
       </c>
       <c r="N109" t="n">
-        <v>26278</v>
+        <v>26375</v>
       </c>
       <c r="O109" t="n">
         <v>5.52</v>
       </c>
       <c r="P109" t="n">
-        <v>25694</v>
+        <v>25789</v>
       </c>
       <c r="Q109" t="n">
-        <v>3028</v>
+        <v>3039</v>
       </c>
       <c r="R109" t="n">
-        <v>28722</v>
+        <v>28827</v>
       </c>
       <c r="S109" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="110">
@@ -5370,19 +5370,19 @@
         <v>-0.857</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-13459</v>
+        <v>-13449</v>
       </c>
       <c r="O110" s="2" t="n">
         <v>0.46</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>-398992</v>
+        <v>-398897</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>37233</v>
+        <v>37244</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>-361759</v>
+        <v>-361654</v>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
     </row>
@@ -5550,22 +5550,22 @@
         <v>-7.472</v>
       </c>
       <c r="N118" t="n">
-        <v>-62952</v>
+        <v>-63183</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-84419</v>
+        <v>-84730</v>
       </c>
       <c r="Q118" t="n">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="R118" t="n">
-        <v>-82675</v>
+        <v>-82979</v>
       </c>
       <c r="S118" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="119">
@@ -5609,19 +5609,19 @@
         <v>-7.472</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-62952</v>
+        <v>-63183</v>
       </c>
       <c r="O119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>-84419</v>
+        <v>-84730</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>-82675</v>
+        <v>-82979</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5841,22 +5841,22 @@
         <v>-3.407</v>
       </c>
       <c r="N125" t="n">
-        <v>-13523</v>
+        <v>-13572</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-40568</v>
+        <v>-40717</v>
       </c>
       <c r="Q125" t="n">
-        <v>1783</v>
+        <v>1790</v>
       </c>
       <c r="R125" t="n">
-        <v>-38784</v>
+        <v>-38927</v>
       </c>
       <c r="S125" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="126">
@@ -5900,19 +5900,19 @@
         <v>-3.088</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-20538</v>
+        <v>-20576</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-82154</v>
+        <v>-82303</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>4485</v>
+        <v>4492</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-77667</v>
+        <v>-77810</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6266,20 +6266,20 @@
         <v>8.897</v>
       </c>
       <c r="N134" t="n">
-        <v>21711</v>
+        <v>21791</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>21711</v>
+        <v>21791</v>
       </c>
       <c r="Q134" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R134" t="n">
-        <v>22068</v>
+        <v>22149</v>
       </c>
       <c r="S134" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="135">
@@ -6321,17 +6321,17 @@
         <v>8.897</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>21711</v>
+        <v>21791</v>
       </c>
       <c r="O135" s="2" t="inlineStr"/>
       <c r="P135" s="2" t="n">
-        <v>21711</v>
+        <v>21791</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>22068</v>
+        <v>22149</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -7122,7 +7122,7 @@
         <v>7425</v>
       </c>
       <c r="S156" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="157">
@@ -7315,7 +7315,7 @@
         <v>-6620</v>
       </c>
       <c r="S160" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="161">
@@ -7471,22 +7471,22 @@
         <v>-2.454</v>
       </c>
       <c r="N164" t="n">
-        <v>-3425</v>
+        <v>-3438</v>
       </c>
       <c r="O164" t="n">
         <v>0.4</v>
       </c>
       <c r="P164" t="n">
-        <v>-7765</v>
+        <v>-7794</v>
       </c>
       <c r="Q164" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R164" t="n">
-        <v>-7643</v>
+        <v>-7671</v>
       </c>
       <c r="S164" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="165">
@@ -7536,19 +7536,19 @@
         <v>-2.454</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-3425</v>
+        <v>-3438</v>
       </c>
       <c r="O165" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="P165" s="2" t="n">
-        <v>-6853</v>
+        <v>-6882</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R165" s="2" t="n">
-        <v>-6670</v>
+        <v>-6698</v>
       </c>
       <c r="S165" s="2" t="inlineStr"/>
     </row>
@@ -9031,20 +9031,20 @@
         <v>10.37</v>
       </c>
       <c r="N199" t="n">
-        <v>14028</v>
+        <v>14079</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="n">
-        <v>10360</v>
+        <v>10399</v>
       </c>
       <c r="Q199" t="n">
         <v>69</v>
       </c>
       <c r="R199" t="n">
-        <v>10429</v>
+        <v>10467</v>
       </c>
       <c r="S199" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="200">
@@ -9086,17 +9086,17 @@
         <v>10.37</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>14028</v>
+        <v>14079</v>
       </c>
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="n">
-        <v>14014</v>
+        <v>14053</v>
       </c>
       <c r="Q200" s="2" t="n">
         <v>102</v>
       </c>
       <c r="R200" s="2" t="n">
-        <v>14116</v>
+        <v>14154</v>
       </c>
       <c r="S200" s="2" t="inlineStr"/>
     </row>
@@ -9266,7 +9266,7 @@
         <v>2103</v>
       </c>
       <c r="S204" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="205">
@@ -9486,7 +9486,7 @@
         <v>-169</v>
       </c>
       <c r="S209" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="210">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>43.3</v>
+        <v>38.9</v>
       </c>
       <c r="F18" t="n">
-        <v>6.74</v>
+        <v>7.21</v>
       </c>
       <c r="G18" t="n">
-        <v>7.88</v>
+        <v>7.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="I18" t="n">
         <v>17.63</v>
@@ -1559,22 +1559,22 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>2.086</v>
+        <v>1.527</v>
       </c>
       <c r="N18" t="n">
-        <v>22763</v>
+        <v>18426</v>
       </c>
       <c r="O18" t="n">
-        <v>5.16</v>
+        <v>4.59</v>
       </c>
       <c r="P18" t="n">
-        <v>591799</v>
+        <v>566875</v>
       </c>
       <c r="Q18" t="n">
-        <v>12073</v>
+        <v>14858</v>
       </c>
       <c r="R18" t="n">
-        <v>603871</v>
+        <v>581733</v>
       </c>
       <c r="S18" t="n">
         <v>1363</v>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>29.58</v>
@@ -1620,22 +1620,22 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="n">
-        <v>0.336</v>
+        <v>0.306</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1363</v>
+        <v>1279</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>398195</v>
+        <v>373271</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>104653</v>
+        <v>107438</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>502848</v>
+        <v>480710</v>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
     </row>
@@ -5311,13 +5311,13 @@
         <v>5.52</v>
       </c>
       <c r="P109" t="n">
-        <v>25789</v>
+        <v>20327</v>
       </c>
       <c r="Q109" t="n">
-        <v>3039</v>
+        <v>4324</v>
       </c>
       <c r="R109" t="n">
-        <v>28827</v>
+        <v>24651</v>
       </c>
       <c r="S109" t="n">
         <v>1363</v>
@@ -5376,13 +5376,13 @@
         <v>0.46</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>-398897</v>
+        <v>-404359</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>37244</v>
+        <v>38529</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>-361654</v>
+        <v>-365830</v>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
     </row>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
@@ -5835,25 +5835,25 @@
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M125" t="n">
-        <v>-3.407</v>
+        <v>-3.235</v>
       </c>
       <c r="N125" t="n">
-        <v>-13572</v>
+        <v>-12613</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-40717</v>
+        <v>-50452</v>
       </c>
       <c r="Q125" t="n">
-        <v>1790</v>
+        <v>2284</v>
       </c>
       <c r="R125" t="n">
-        <v>-38927</v>
+        <v>-48168</v>
       </c>
       <c r="S125" t="n">
         <v>1363</v>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>0</v>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="n">
@@ -5894,25 +5894,25 @@
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>-3.088</v>
+        <v>-3.014</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-20576</v>
+        <v>-18408</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-82303</v>
+        <v>-92038</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>4492</v>
+        <v>4986</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-77810</v>
+        <v>-87051</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -7113,13 +7113,13 @@
         <v>4.08</v>
       </c>
       <c r="P156" t="n">
-        <v>7071</v>
+        <v>7163</v>
       </c>
       <c r="Q156" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="R156" t="n">
-        <v>7425</v>
+        <v>7527</v>
       </c>
       <c r="S156" t="n">
         <v>1363</v>
@@ -7178,13 +7178,13 @@
         <v>4.77</v>
       </c>
       <c r="P157" s="2" t="n">
-        <v>20930</v>
+        <v>21022</v>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="R157" s="2" t="n">
-        <v>21611</v>
+        <v>21713</v>
       </c>
       <c r="S157" s="2" t="inlineStr"/>
     </row>
@@ -7270,49 +7270,49 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E160" t="n">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="F160" t="n">
-        <v>2.17</v>
+        <v>1.15</v>
       </c>
       <c r="G160" t="n">
-        <v>1.85</v>
+        <v>1.19</v>
       </c>
       <c r="H160" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="I160" t="n">
         <v>1.85</v>
       </c>
       <c r="J160" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="K160" t="n">
-        <v>239.98</v>
+        <v>157.47</v>
       </c>
       <c r="L160" t="n">
-        <v>134.54</v>
+        <v>105.96</v>
       </c>
       <c r="M160" t="n">
-        <v>-0.513</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="N160" t="n">
-        <v>-1027</v>
+        <v>-1387</v>
       </c>
       <c r="O160" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="P160" t="n">
-        <v>-8217</v>
+        <v>-18035</v>
       </c>
       <c r="Q160" t="n">
-        <v>1597</v>
+        <v>2592</v>
       </c>
       <c r="R160" t="n">
-        <v>-6620</v>
+        <v>-15443</v>
       </c>
       <c r="S160" t="n">
         <v>1363</v>
@@ -7335,49 +7335,49 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>26.3</v>
+        <v>25</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>3.47</v>
+        <v>2.62</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>6.36</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>650.92</v>
+        <v>554.9299999999999</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>166.1</v>
+        <v>141.62</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>0.146</v>
+        <v>-0.089</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>291</v>
+        <v>-179</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>1.24</v>
+        <v>0.87</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>5525</v>
+        <v>-4293</v>
       </c>
       <c r="Q161" s="2" t="n">
-        <v>3805</v>
+        <v>4800</v>
       </c>
       <c r="R161" s="2" t="n">
-        <v>9330</v>
+        <v>507</v>
       </c>
       <c r="S161" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="F18" t="n">
-        <v>7.21</v>
+        <v>6.77</v>
       </c>
       <c r="G18" t="n">
-        <v>7.35</v>
+        <v>7.01</v>
       </c>
       <c r="H18" t="n">
         <v>2.18</v>
@@ -1559,25 +1559,25 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>1.527</v>
+        <v>1.544</v>
       </c>
       <c r="N18" t="n">
-        <v>18426</v>
+        <v>18044</v>
       </c>
       <c r="O18" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
       <c r="P18" t="n">
-        <v>566875</v>
+        <v>571374</v>
       </c>
       <c r="Q18" t="n">
-        <v>14858</v>
+        <v>15041</v>
       </c>
       <c r="R18" t="n">
-        <v>581733</v>
+        <v>586415</v>
       </c>
       <c r="S18" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="19">
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.61</v>
@@ -1620,22 +1620,22 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="n">
-        <v>0.306</v>
+        <v>0.312</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1279</v>
+        <v>1288</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>1.16</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>373271</v>
+        <v>377770</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>107438</v>
+        <v>107621</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>480710</v>
+        <v>485392</v>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
     </row>
@@ -3065,7 +3065,7 @@
         <v>1751</v>
       </c>
       <c r="S49" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="50">
@@ -3482,7 +3482,7 @@
         <v>241675</v>
       </c>
       <c r="S58" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="59">
@@ -4258,7 +4258,7 @@
         <v>272090</v>
       </c>
       <c r="S79" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="80">
@@ -4525,7 +4525,7 @@
         <v>153750</v>
       </c>
       <c r="S87" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="88">
@@ -5305,22 +5305,22 @@
         <v>2.292</v>
       </c>
       <c r="N109" t="n">
-        <v>26375</v>
+        <v>26317</v>
       </c>
       <c r="O109" t="n">
         <v>5.52</v>
       </c>
       <c r="P109" t="n">
-        <v>20327</v>
+        <v>20282</v>
       </c>
       <c r="Q109" t="n">
-        <v>4324</v>
+        <v>4315</v>
       </c>
       <c r="R109" t="n">
-        <v>24651</v>
+        <v>24597</v>
       </c>
       <c r="S109" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="110">
@@ -5370,19 +5370,19 @@
         <v>-0.857</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-13449</v>
+        <v>-13455</v>
       </c>
       <c r="O110" s="2" t="n">
         <v>0.46</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>-404359</v>
+        <v>-404404</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>38529</v>
+        <v>38520</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>-365830</v>
+        <v>-365884</v>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
     </row>
@@ -5550,22 +5550,22 @@
         <v>-7.472</v>
       </c>
       <c r="N118" t="n">
-        <v>-63183</v>
+        <v>-63044</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-84730</v>
+        <v>-84543</v>
       </c>
       <c r="Q118" t="n">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="R118" t="n">
-        <v>-82979</v>
+        <v>-82797</v>
       </c>
       <c r="S118" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="119">
@@ -5609,19 +5609,19 @@
         <v>-7.472</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-63183</v>
+        <v>-63044</v>
       </c>
       <c r="O119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>-84730</v>
+        <v>-84543</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>-82979</v>
+        <v>-82797</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5841,22 +5841,22 @@
         <v>-3.235</v>
       </c>
       <c r="N125" t="n">
-        <v>-12613</v>
+        <v>-12585</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-50452</v>
+        <v>-50341</v>
       </c>
       <c r="Q125" t="n">
-        <v>2284</v>
+        <v>2279</v>
       </c>
       <c r="R125" t="n">
-        <v>-48168</v>
+        <v>-48062</v>
       </c>
       <c r="S125" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="126">
@@ -5900,19 +5900,19 @@
         <v>-3.014</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-18408</v>
+        <v>-18385</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-92038</v>
+        <v>-91927</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>4986</v>
+        <v>4981</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-87051</v>
+        <v>-86945</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6266,20 +6266,20 @@
         <v>8.897</v>
       </c>
       <c r="N134" t="n">
-        <v>21791</v>
+        <v>21743</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>21791</v>
+        <v>21743</v>
       </c>
       <c r="Q134" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R134" t="n">
-        <v>22149</v>
+        <v>22100</v>
       </c>
       <c r="S134" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="135">
@@ -6321,17 +6321,17 @@
         <v>8.897</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>21791</v>
+        <v>21743</v>
       </c>
       <c r="O135" s="2" t="inlineStr"/>
       <c r="P135" s="2" t="n">
-        <v>21791</v>
+        <v>21743</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>22149</v>
+        <v>22100</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -7122,7 +7122,7 @@
         <v>7527</v>
       </c>
       <c r="S156" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="157">
@@ -7270,52 +7270,52 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E160" t="n">
-        <v>15.4</v>
+        <v>21.4</v>
       </c>
       <c r="F160" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="G160" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="H160" t="n">
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="J160" t="n">
         <v>2.94</v>
       </c>
       <c r="K160" t="n">
-        <v>157.47</v>
+        <v>199.98</v>
       </c>
       <c r="L160" t="n">
         <v>105.96</v>
       </c>
       <c r="M160" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="N160" t="n">
-        <v>-1387</v>
+        <v>-981</v>
       </c>
       <c r="O160" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="P160" t="n">
-        <v>-18035</v>
+        <v>-13735</v>
       </c>
       <c r="Q160" t="n">
-        <v>2592</v>
+        <v>2794</v>
       </c>
       <c r="R160" t="n">
-        <v>-15443</v>
+        <v>-10941</v>
       </c>
       <c r="S160" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="161">
@@ -7335,16 +7335,16 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="H161" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -7356,28 +7356,28 @@
         <v>2.94</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>554.9299999999999</v>
+        <v>516.36</v>
       </c>
       <c r="L161" s="2" t="n">
         <v>141.62</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-179</v>
+        <v>0</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>-4293</v>
+        <v>7</v>
       </c>
       <c r="Q161" s="2" t="n">
-        <v>4800</v>
+        <v>5002</v>
       </c>
       <c r="R161" s="2" t="n">
-        <v>507</v>
+        <v>5009</v>
       </c>
       <c r="S161" s="2" t="inlineStr"/>
     </row>
@@ -7471,22 +7471,22 @@
         <v>-2.454</v>
       </c>
       <c r="N164" t="n">
-        <v>-3438</v>
+        <v>-3430</v>
       </c>
       <c r="O164" t="n">
         <v>0.4</v>
       </c>
       <c r="P164" t="n">
-        <v>-7794</v>
+        <v>-7777</v>
       </c>
       <c r="Q164" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R164" t="n">
-        <v>-7671</v>
+        <v>-7655</v>
       </c>
       <c r="S164" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="165">
@@ -7536,19 +7536,19 @@
         <v>-2.454</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-3438</v>
+        <v>-3430</v>
       </c>
       <c r="O165" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="P165" s="2" t="n">
-        <v>-6882</v>
+        <v>-6865</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R165" s="2" t="n">
-        <v>-6698</v>
+        <v>-6682</v>
       </c>
       <c r="S165" s="2" t="inlineStr"/>
     </row>
@@ -9031,20 +9031,20 @@
         <v>10.37</v>
       </c>
       <c r="N199" t="n">
-        <v>14079</v>
+        <v>14048</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="n">
-        <v>10399</v>
+        <v>10376</v>
       </c>
       <c r="Q199" t="n">
         <v>69</v>
       </c>
       <c r="R199" t="n">
-        <v>10467</v>
+        <v>10444</v>
       </c>
       <c r="S199" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="200">
@@ -9086,17 +9086,17 @@
         <v>10.37</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>14079</v>
+        <v>14048</v>
       </c>
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="n">
-        <v>14053</v>
+        <v>14030</v>
       </c>
       <c r="Q200" s="2" t="n">
         <v>102</v>
       </c>
       <c r="R200" s="2" t="n">
-        <v>14154</v>
+        <v>14131</v>
       </c>
       <c r="S200" s="2" t="inlineStr"/>
     </row>
@@ -9266,7 +9266,7 @@
         <v>2103</v>
       </c>
       <c r="S204" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="205">
@@ -9486,7 +9486,7 @@
         <v>-169</v>
       </c>
       <c r="S209" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="210">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>6.77</v>
+        <v>6.9</v>
       </c>
       <c r="G18" t="n">
-        <v>7.01</v>
+        <v>6.71</v>
       </c>
       <c r="H18" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="I18" t="n">
         <v>17.63</v>
@@ -1559,25 +1559,25 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>1.544</v>
+        <v>1.451</v>
       </c>
       <c r="N18" t="n">
-        <v>18044</v>
+        <v>16795</v>
       </c>
       <c r="O18" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>571374</v>
+        <v>589004</v>
       </c>
       <c r="Q18" t="n">
-        <v>15041</v>
+        <v>16050</v>
       </c>
       <c r="R18" t="n">
-        <v>586415</v>
+        <v>605054</v>
       </c>
       <c r="S18" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19">
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>29.58</v>
@@ -1623,19 +1623,19 @@
         <v>0.312</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>377770</v>
+        <v>395400</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>107621</v>
+        <v>108630</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>485392</v>
+        <v>504031</v>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
     </row>
@@ -3065,7 +3065,7 @@
         <v>1751</v>
       </c>
       <c r="S49" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="50">
@@ -3482,7 +3482,7 @@
         <v>241675</v>
       </c>
       <c r="S58" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="59">
@@ -4258,7 +4258,7 @@
         <v>272090</v>
       </c>
       <c r="S79" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="80">
@@ -4525,7 +4525,7 @@
         <v>153750</v>
       </c>
       <c r="S87" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="88">
@@ -5305,22 +5305,22 @@
         <v>2.292</v>
       </c>
       <c r="N109" t="n">
-        <v>26317</v>
+        <v>26162</v>
       </c>
       <c r="O109" t="n">
         <v>5.52</v>
       </c>
       <c r="P109" t="n">
-        <v>20282</v>
+        <v>33148</v>
       </c>
       <c r="Q109" t="n">
-        <v>4315</v>
+        <v>4649</v>
       </c>
       <c r="R109" t="n">
-        <v>24597</v>
+        <v>37797</v>
       </c>
       <c r="S109" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="110">
@@ -5346,7 +5346,7 @@
         <v>37.9</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>3.36</v>
@@ -5370,19 +5370,19 @@
         <v>-0.857</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-13455</v>
+        <v>-13471</v>
       </c>
       <c r="O110" s="2" t="n">
         <v>0.46</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>-404404</v>
+        <v>-391538</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>38520</v>
+        <v>38854</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>-365884</v>
+        <v>-352684</v>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
     </row>
@@ -5550,22 +5550,22 @@
         <v>-7.472</v>
       </c>
       <c r="N118" t="n">
-        <v>-63044</v>
+        <v>-62673</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-84543</v>
+        <v>-84046</v>
       </c>
       <c r="Q118" t="n">
-        <v>1746</v>
+        <v>1736</v>
       </c>
       <c r="R118" t="n">
-        <v>-82797</v>
+        <v>-82310</v>
       </c>
       <c r="S118" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="119">
@@ -5609,19 +5609,19 @@
         <v>-7.472</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-63044</v>
+        <v>-62673</v>
       </c>
       <c r="O119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>-84543</v>
+        <v>-84046</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>1746</v>
+        <v>1736</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>-82797</v>
+        <v>-82310</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5841,22 +5841,22 @@
         <v>-3.235</v>
       </c>
       <c r="N125" t="n">
-        <v>-12585</v>
+        <v>-12511</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-50341</v>
+        <v>-50045</v>
       </c>
       <c r="Q125" t="n">
-        <v>2279</v>
+        <v>2266</v>
       </c>
       <c r="R125" t="n">
-        <v>-48062</v>
+        <v>-47780</v>
       </c>
       <c r="S125" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="126">
@@ -5900,19 +5900,19 @@
         <v>-3.014</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-18385</v>
+        <v>-18326</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-91927</v>
+        <v>-91631</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>4981</v>
+        <v>4968</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-86945</v>
+        <v>-86663</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6266,20 +6266,20 @@
         <v>8.897</v>
       </c>
       <c r="N134" t="n">
-        <v>21743</v>
+        <v>21615</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>21743</v>
+        <v>21615</v>
       </c>
       <c r="Q134" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R134" t="n">
-        <v>22100</v>
+        <v>21970</v>
       </c>
       <c r="S134" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="135">
@@ -6321,17 +6321,17 @@
         <v>8.897</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>21743</v>
+        <v>21615</v>
       </c>
       <c r="O135" s="2" t="inlineStr"/>
       <c r="P135" s="2" t="n">
-        <v>21743</v>
+        <v>21615</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>22100</v>
+        <v>21970</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -7122,7 +7122,7 @@
         <v>7527</v>
       </c>
       <c r="S156" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="157">
@@ -7270,19 +7270,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E160" t="n">
-        <v>21.4</v>
+        <v>18.8</v>
       </c>
       <c r="F160" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G160" t="n">
         <v>1.51</v>
       </c>
       <c r="H160" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="I160" t="n">
         <v>2.15</v>
@@ -7294,28 +7294,28 @@
         <v>199.98</v>
       </c>
       <c r="L160" t="n">
-        <v>105.96</v>
+        <v>91.95</v>
       </c>
       <c r="M160" t="n">
-        <v>-0.49</v>
+        <v>-0.512</v>
       </c>
       <c r="N160" t="n">
-        <v>-981</v>
+        <v>-1025</v>
       </c>
       <c r="O160" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="P160" t="n">
-        <v>-13735</v>
+        <v>-16394</v>
       </c>
       <c r="Q160" t="n">
-        <v>2794</v>
+        <v>3193</v>
       </c>
       <c r="R160" t="n">
-        <v>-10941</v>
+        <v>-13201</v>
       </c>
       <c r="S160" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="161">
@@ -7335,19 +7335,19 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>28</v>
+        <v>25.9</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>2.42</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>6.36</v>
@@ -7359,25 +7359,25 @@
         <v>516.36</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>141.62</v>
+        <v>128.95</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>0</v>
+        <v>-0.049</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0</v>
+        <v>-98</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>7</v>
+        <v>-2652</v>
       </c>
       <c r="Q161" s="2" t="n">
-        <v>5002</v>
+        <v>5401</v>
       </c>
       <c r="R161" s="2" t="n">
-        <v>5009</v>
+        <v>2749</v>
       </c>
       <c r="S161" s="2" t="inlineStr"/>
     </row>
@@ -7471,22 +7471,22 @@
         <v>-2.454</v>
       </c>
       <c r="N164" t="n">
-        <v>-3430</v>
+        <v>-3410</v>
       </c>
       <c r="O164" t="n">
         <v>0.4</v>
       </c>
       <c r="P164" t="n">
-        <v>-7777</v>
+        <v>-7731</v>
       </c>
       <c r="Q164" t="n">
         <v>122</v>
       </c>
       <c r="R164" t="n">
-        <v>-7655</v>
+        <v>-7610</v>
       </c>
       <c r="S164" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="165">
@@ -7536,19 +7536,19 @@
         <v>-2.454</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-3430</v>
+        <v>-3410</v>
       </c>
       <c r="O165" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="P165" s="2" t="n">
-        <v>-6865</v>
+        <v>-6819</v>
       </c>
       <c r="Q165" s="2" t="n">
         <v>183</v>
       </c>
       <c r="R165" s="2" t="n">
-        <v>-6682</v>
+        <v>-6637</v>
       </c>
       <c r="S165" s="2" t="inlineStr"/>
     </row>
@@ -9031,20 +9031,20 @@
         <v>10.37</v>
       </c>
       <c r="N199" t="n">
-        <v>14048</v>
+        <v>13966</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="n">
-        <v>10376</v>
+        <v>10315</v>
       </c>
       <c r="Q199" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R199" t="n">
-        <v>10444</v>
+        <v>10383</v>
       </c>
       <c r="S199" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="200">
@@ -9086,17 +9086,17 @@
         <v>10.37</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>14048</v>
+        <v>13966</v>
       </c>
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="n">
-        <v>14030</v>
+        <v>13969</v>
       </c>
       <c r="Q200" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R200" s="2" t="n">
-        <v>14131</v>
+        <v>14070</v>
       </c>
       <c r="S200" s="2" t="inlineStr"/>
     </row>
@@ -9266,7 +9266,7 @@
         <v>2103</v>
       </c>
       <c r="S204" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="205">
@@ -9447,46 +9447,52 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="inlineStr"/>
+        <v>36.94</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2.26</v>
+      </c>
       <c r="H209" t="n">
         <v>1.26</v>
       </c>
-      <c r="I209" t="inlineStr"/>
+      <c r="I209" t="n">
+        <v>2.26</v>
+      </c>
       <c r="J209" t="n">
         <v>1.26</v>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="n">
+        <v>1</v>
+      </c>
       <c r="L209" t="n">
         <v>10</v>
       </c>
       <c r="M209" t="n">
-        <v>-1.26</v>
+        <v>0.498</v>
       </c>
       <c r="N209" t="n">
-        <v>-183</v>
+        <v>3295</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>36.94</v>
       </c>
       <c r="P209" t="n">
-        <v>-183</v>
+        <v>6589</v>
       </c>
       <c r="Q209" t="n">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="R209" t="n">
-        <v>-169</v>
+        <v>6907</v>
       </c>
       <c r="S209" t="n">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="210">
@@ -9506,16 +9512,16 @@
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>484.19</v>
+        <v>260.57</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>29.58</v>
+        <v>15.92</v>
       </c>
       <c r="H210" s="2" t="n">
         <v>1.26</v>
@@ -9527,28 +9533,28 @@
         <v>1.26</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="L210" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>14.158</v>
+        <v>10.191</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>44294</v>
+        <v>31787</v>
       </c>
       <c r="O210" s="2" t="n">
-        <v>484.19</v>
+        <v>521.13</v>
       </c>
       <c r="P210" s="2" t="n">
-        <v>88589</v>
+        <v>95361</v>
       </c>
       <c r="Q210" s="2" t="n">
-        <v>358</v>
+        <v>662</v>
       </c>
       <c r="R210" s="2" t="n">
-        <v>88947</v>
+        <v>96023</v>
       </c>
       <c r="S210" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S245"/>
+  <dimension ref="A1:S251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>41.5</v>
+        <v>42.3</v>
       </c>
       <c r="F18" t="n">
-        <v>5.14</v>
+        <v>5.02</v>
       </c>
       <c r="G18" t="n">
         <v>6.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
         <v>17.63</v>
@@ -1559,13 +1559,13 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>1.286</v>
+        <v>1.315</v>
       </c>
       <c r="N18" t="n">
-        <v>13094</v>
+        <v>13386</v>
       </c>
       <c r="O18" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
         <v>641351</v>
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5.23</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5.55</v>
+        <v>6.76</v>
       </c>
       <c r="J19" t="n">
         <v>5.68</v>
@@ -1620,25 +1620,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-1.249</v>
+        <v>-0.193</v>
       </c>
       <c r="N19" t="n">
-        <v>-4042</v>
+        <v>-3240</v>
       </c>
       <c r="O19" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="P19" t="n">
-        <v>-71957</v>
+        <v>-38266</v>
       </c>
       <c r="Q19" t="n">
-        <v>2368</v>
+        <v>8780</v>
       </c>
       <c r="R19" t="n">
-        <v>-69589</v>
+        <v>-29486</v>
       </c>
       <c r="S19" t="n">
-        <v>1360</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.294</v>
+        <v>0.306</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1184</v>
+        <v>1101</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>375790</v>
+        <v>409481</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>114912</v>
+        <v>121324</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>490703</v>
+        <v>530806</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5418,19 +5418,19 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F114" t="n">
-        <v>11.04</v>
+        <v>6.28</v>
       </c>
       <c r="G114" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="I114" t="n">
         <v>8.369999999999999</v>
@@ -5442,16 +5442,16 @@
         <v>6</v>
       </c>
       <c r="L114" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M114" t="n">
-        <v>2.292</v>
+        <v>3.532</v>
       </c>
       <c r="N114" t="n">
-        <v>26162</v>
+        <v>40296</v>
       </c>
       <c r="O114" t="n">
-        <v>5.52</v>
+        <v>6.28</v>
       </c>
       <c r="P114" t="n">
         <v>33148</v>
@@ -5467,113 +5467,196 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>US_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>12</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-4.385</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-45429</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>-942</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1443</v>
+      </c>
+      <c r="R115" t="n">
+        <v>501</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D116" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>37.9</v>
       </c>
-      <c r="F115" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G115" s="2" t="n">
+      <c r="F116" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G116" s="2" t="n">
         <v>3.36</v>
       </c>
-      <c r="H115" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="I115" s="2" t="n">
+      <c r="H116" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I116" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J116" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K115" s="2" t="n">
+      <c r="K116" s="2" t="n">
         <v>14.55</v>
       </c>
-      <c r="L115" s="2" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-0.857</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-13471</v>
-      </c>
-      <c r="O115" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P115" s="2" t="n">
-        <v>-391538</v>
-      </c>
-      <c r="Q115" s="2" t="n">
-        <v>38854</v>
-      </c>
-      <c r="R115" s="2" t="n">
-        <v>-352684</v>
-      </c>
-      <c r="S115" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="L116" s="2" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1.001</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-14965</v>
+      </c>
+      <c r="O116" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>-392480</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>40297</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>-352183</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>US_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr"/>
-      <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" s="2" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" t="n">
+        <v>50</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="N118" t="n">
+        <v>3708</v>
+      </c>
+      <c r="O118" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P118" t="n">
+        <v>22239</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>3311</v>
+      </c>
+      <c r="R118" t="n">
+        <v>25551</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1354</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>US_TR_BLACK_B</t>
+          <t>US_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5587,34 +5670,56 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="inlineStr"/>
-      <c r="N119" s="2" t="inlineStr"/>
-      <c r="O119" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>3708</v>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="P119" s="2" t="n">
-        <v>0</v>
+        <v>22239</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>0</v>
+        <v>3311</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>0</v>
+        <v>25551</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>US_TR_PURPLE_B</t>
+          <t>US_TR_BLACK_B</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5655,7 +5760,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_PURPLE_B</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5696,7 +5801,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -5735,416 +5840,400 @@
       <c r="S125" s="2" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VOLUME_2</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="n">
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
         <v>7.47</v>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="n">
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
         <v>7.47</v>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="n">
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
         <v>6</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M129" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N129" t="n">
         <v>-62673</v>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q129" t="n">
         <v>1736</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R129" t="n">
         <v>-82310</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S129" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="n">
+      <c r="E130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="n">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="n">
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M128" s="2" t="n">
+      <c r="M130" s="2" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N130" s="2" t="n">
         <v>-62673</v>
       </c>
-      <c r="O128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="2" t="n">
+      <c r="O130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="2" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q128" s="2" t="n">
+      <c r="Q130" s="2" t="n">
         <v>1736</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R130" s="2" t="n">
         <v>-82310</v>
       </c>
-      <c r="S128" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="S130" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
         <v>1.3</v>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="n">
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
         <v>1.3</v>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="n">
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
         <v>1</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M132" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N132" t="n">
         <v>-5227</v>
       </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
         <v>-5525</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q132" t="n">
         <v>776</v>
       </c>
-      <c r="R130" t="n">
+      <c r="R132" t="n">
         <v>-4749</v>
       </c>
-      <c r="S130" t="n">
+      <c r="S132" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="n">
+      <c r="E133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="n">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="n">
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M131" s="2" t="n">
+      <c r="M133" s="2" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N133" s="2" t="n">
         <v>-5227</v>
       </c>
-      <c r="O131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="2" t="n">
+      <c r="O133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="2" t="n">
         <v>-5525</v>
       </c>
-      <c r="Q131" s="2" t="n">
+      <c r="Q133" s="2" t="n">
         <v>776</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R133" s="2" t="n">
         <v>-4749</v>
       </c>
-      <c r="S131" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="S133" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D133" t="n">
+      <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="n">
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
         <v>2.13</v>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="n">
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
         <v>2.13</v>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="n">
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
         <v>1</v>
       </c>
-      <c r="M133" t="n">
+      <c r="M135" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N135" t="n">
         <v>-41586</v>
       </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q135" t="n">
         <v>2702</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R135" t="n">
         <v>-38883</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S135" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D134" t="n">
+      <c r="D136" t="n">
         <v>4</v>
       </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="n">
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
         <v>3.23</v>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
         <v>5.33</v>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="n">
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
         <v>7</v>
       </c>
-      <c r="M134" t="n">
+      <c r="M136" t="n">
         <v>-3.235</v>
       </c>
-      <c r="N134" t="n">
+      <c r="N136" t="n">
         <v>-12511</v>
       </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
         <v>-50045</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="Q136" t="n">
         <v>2266</v>
       </c>
-      <c r="R134" t="n">
+      <c r="R136" t="n">
         <v>-47780</v>
       </c>
-      <c r="S134" t="n">
+      <c r="S136" t="n">
         <v>1352</v>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>-3.014</v>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>-18326</v>
-      </c>
-      <c r="O135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="2" t="n">
-        <v>-91631</v>
-      </c>
-      <c r="Q135" s="2" t="n">
-        <v>4968</v>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>-86663</v>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6154,11 +6243,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -6168,161 +6257,94 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>3.34</v>
+        <v>1.96</v>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
-        <v>6.17</v>
+        <v>1.96</v>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M137" t="n">
-        <v>-3.337</v>
+        <v>-1.956</v>
       </c>
       <c r="N137" t="n">
-        <v>-7859</v>
+        <v>-9778</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-55013</v>
+        <v>-9778</v>
       </c>
       <c r="Q137" t="n">
-        <v>1884</v>
+        <v>693</v>
       </c>
       <c r="R137" t="n">
-        <v>-53128</v>
+        <v>-9085</v>
       </c>
       <c r="S137" t="n">
-        <v>1373</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G138" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H138" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I138" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J138" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K138" t="n">
-        <v>18</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-18508</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P138" t="n">
-        <v>-52375</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>4226</v>
-      </c>
-      <c r="R138" t="n">
-        <v>-48149</v>
-      </c>
-      <c r="S138" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>2</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M139" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="N139" t="n">
-        <v>-38258</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>-79635</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>4778</v>
-      </c>
-      <c r="R139" t="n">
-        <v>-74857</v>
-      </c>
-      <c r="S139" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>-2.838</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>-16902</v>
+      </c>
+      <c r="O138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>-101409</v>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>5661</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>-95748</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6337,125 +6359,180 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D140" t="n">
+        <v>7</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>8</v>
+      </c>
+      <c r="M140" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R140" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
         <v>3</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E141" t="n">
         <v>66.7</v>
       </c>
-      <c r="F140" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H140" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J140" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" t="n">
-        <v>1</v>
-      </c>
-      <c r="M140" t="n">
-        <v>-1.701</v>
-      </c>
-      <c r="N140" t="n">
-        <v>-9977</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="P140" t="n">
-        <v>-29930</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>2167</v>
-      </c>
-      <c r="R140" t="n">
-        <v>-27764</v>
-      </c>
-      <c r="S140" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="F141" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I141" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J141" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K141" t="n">
+        <v>18</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P141" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R141" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>-1.974</v>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>-14466</v>
-      </c>
-      <c r="O141" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P141" s="2" t="n">
-        <v>-216953</v>
-      </c>
-      <c r="Q141" s="2" t="n">
-        <v>13055</v>
-      </c>
-      <c r="R141" s="2" t="n">
-        <v>-203898</v>
-      </c>
-      <c r="S141" s="2" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-38258</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>-79635</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>4778</v>
+      </c>
+      <c r="R142" t="n">
+        <v>-74857</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1369</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>US_TR_ADD1</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6465,52 +6542,62 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H143" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J143" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="n">
-        <v>100</v>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="n">
-        <v>5</v>
-      </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
       <c r="M143" t="n">
-        <v>8.897</v>
+        <v>-1.701</v>
       </c>
       <c r="N143" t="n">
-        <v>21615</v>
-      </c>
-      <c r="O143" t="inlineStr"/>
+        <v>-9977</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.13</v>
+      </c>
       <c r="P143" t="n">
-        <v>21615</v>
+        <v>-29930</v>
       </c>
       <c r="Q143" t="n">
-        <v>355</v>
+        <v>2167</v>
       </c>
       <c r="R143" t="n">
-        <v>21970</v>
+        <v>-27764</v>
       </c>
       <c r="S143" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ADD1</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6524,46 +6611,56 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F144" s="2" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="G144" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr"/>
+        <v>1.68</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>3.3</v>
+      </c>
       <c r="I144" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr"/>
+        <v>3.32</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>6.17</v>
+      </c>
       <c r="K144" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L144" s="2" t="inlineStr"/>
+        <v>9.5</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>6.55</v>
+      </c>
       <c r="M144" s="2" t="n">
-        <v>8.897</v>
+        <v>-1.974</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>21615</v>
-      </c>
-      <c r="O144" s="2" t="inlineStr"/>
+        <v>-14466</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="P144" s="2" t="n">
-        <v>21615</v>
+        <v>-216953</v>
       </c>
       <c r="Q144" s="2" t="n">
-        <v>355</v>
+        <v>13055</v>
       </c>
       <c r="R144" s="2" t="n">
-        <v>21970</v>
+        <v>-203898</v>
       </c>
       <c r="S144" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6573,56 +6670,52 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>5</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>-7.145</v>
+        <v>8.897</v>
       </c>
       <c r="N146" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
+        <v>21615</v>
+      </c>
+      <c r="O146" t="inlineStr"/>
       <c r="P146" t="n">
-        <v>-54889</v>
+        <v>21615</v>
       </c>
       <c r="Q146" t="n">
-        <v>1054</v>
+        <v>355</v>
       </c>
       <c r="R146" t="n">
-        <v>-53835</v>
+        <v>21970</v>
       </c>
       <c r="S146" t="n">
-        <v>1373</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6636,50 +6729,46 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="n">
-        <v>-7.145</v>
+        <v>8.897</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O147" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>21615</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="n">
-        <v>-54889</v>
+        <v>21615</v>
       </c>
       <c r="Q147" s="2" t="n">
-        <v>1054</v>
+        <v>355</v>
       </c>
       <c r="R147" s="2" t="n">
-        <v>-53835</v>
+        <v>21970</v>
       </c>
       <c r="S147" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6693,241 +6782,229 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G149" t="n">
-        <v>7.27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I149" t="n">
-        <v>16.31</v>
-      </c>
+        <v>7.15</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0.78</v>
-      </c>
+        <v>10.49</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>2.681</v>
+        <v>-7.145</v>
       </c>
       <c r="N149" t="n">
-        <v>3410</v>
+        <v>-27445</v>
       </c>
       <c r="O149" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>134658</v>
+        <v>-54889</v>
       </c>
       <c r="Q149" t="n">
-        <v>7271</v>
+        <v>1054</v>
       </c>
       <c r="R149" t="n">
-        <v>141929</v>
+        <v>-53835</v>
       </c>
       <c r="S149" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>17</v>
+      </c>
+      <c r="E152" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G152" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I152" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J152" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N152" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P152" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R152" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D150" t="n">
+      <c r="D153" t="n">
         <v>7</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E153" t="n">
         <v>100</v>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="n">
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
         <v>6.16</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="n">
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="n">
         <v>11.46</v>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="n">
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="n">
         <v>10.43</v>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="n">
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
         <v>6.16</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N153" t="n">
         <v>18699</v>
       </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="n">
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="n">
         <v>86535</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q153" t="n">
         <v>1828</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R153" t="n">
         <v>88363</v>
       </c>
-      <c r="S150" t="n">
+      <c r="S153" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>4</v>
-      </c>
-      <c r="E151" t="n">
-        <v>50</v>
-      </c>
-      <c r="F151" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G151" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="H151" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I151" t="n">
-        <v>12</v>
-      </c>
-      <c r="J151" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K151" t="n">
-        <v>14</v>
-      </c>
-      <c r="L151" t="n">
-        <v>14</v>
-      </c>
-      <c r="M151" t="n">
-        <v>4.282</v>
-      </c>
-      <c r="N151" t="n">
-        <v>7910</v>
-      </c>
-      <c r="O151" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P151" t="n">
-        <v>-912</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>635</v>
-      </c>
-      <c r="R151" t="n">
-        <v>-278</v>
-      </c>
-      <c r="S151" t="n">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L152" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M152" s="2" t="n">
-        <v>3.779</v>
-      </c>
-      <c r="N152" s="2" t="n">
-        <v>7875</v>
-      </c>
-      <c r="O152" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P152" s="2" t="n">
-        <v>220281</v>
-      </c>
-      <c r="Q152" s="2" t="n">
-        <v>9734</v>
-      </c>
-      <c r="R152" s="2" t="n">
-        <v>230014</v>
-      </c>
-      <c r="S152" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6937,255 +7014,287 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="G154" t="n">
+        <v>11.43</v>
+      </c>
       <c r="H154" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I154" t="inlineStr"/>
+        <v>2.87</v>
+      </c>
+      <c r="I154" t="n">
+        <v>12</v>
+      </c>
       <c r="J154" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K154" t="inlineStr"/>
+        <v>4.94</v>
+      </c>
+      <c r="K154" t="n">
+        <v>14</v>
+      </c>
       <c r="L154" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M154" t="n">
-        <v>-0.54</v>
+        <v>4.282</v>
       </c>
       <c r="N154" t="n">
-        <v>-1280</v>
+        <v>7910</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P154" t="n">
-        <v>-1280</v>
+        <v>-912</v>
       </c>
       <c r="Q154" t="n">
-        <v>208</v>
+        <v>635</v>
       </c>
       <c r="R154" t="n">
-        <v>-1072</v>
+        <v>-278</v>
       </c>
       <c r="S154" t="n">
-        <v>1383</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>3.779</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>7875</v>
+      </c>
+      <c r="O155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>220281</v>
+      </c>
+      <c r="Q155" s="2" t="n">
+        <v>9734</v>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>230014</v>
+      </c>
+      <c r="S155" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>12</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N157" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>208</v>
+      </c>
+      <c r="R157" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="n">
+      <c r="E158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="n">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="n">
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M155" s="2" t="n">
+      <c r="M158" s="2" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N158" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="O155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" s="2" t="n">
+      <c r="O158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q155" s="2" t="n">
+      <c r="Q158" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="R155" s="2" t="n">
+      <c r="R158" s="2" t="n">
         <v>-1072</v>
       </c>
-      <c r="S155" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="S158" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="2" t="inlineStr"/>
-      <c r="N157" s="2" t="inlineStr"/>
-      <c r="O157" s="2" t="inlineStr"/>
-      <c r="P157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="2" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr"/>
-      <c r="O159" s="2" t="inlineStr"/>
-      <c r="P159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" t="n">
-        <v>100</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N161" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>34</v>
-      </c>
-      <c r="R161" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S161" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr"/>
+      <c r="P160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -7194,56 +7303,44 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="n">
-        <v>52.73</v>
-      </c>
+      <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N162" s="2" t="n">
-        <v>2341</v>
-      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
       <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="n">
-        <v>2341</v>
+        <v>0</v>
       </c>
       <c r="Q162" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R162" s="2" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="S162" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>업비트SCO-Top3</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7254,663 +7351,643 @@
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>52.73</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="n">
-        <v>2.876</v>
+        <v>2.102</v>
       </c>
       <c r="N164" t="n">
-        <v>4316</v>
+        <v>2341</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>34</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>100</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>2.876</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4316</v>
+      </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
         <v>13859</v>
       </c>
-      <c r="Q164" t="n">
+      <c r="Q167" t="n">
         <v>327</v>
       </c>
-      <c r="R164" t="n">
+      <c r="R167" t="n">
         <v>14186</v>
       </c>
-      <c r="S164" t="n">
+      <c r="S167" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>업비트SCO-Top3</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D165" t="n">
+      <c r="D168" t="n">
         <v>6</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E168" t="n">
         <v>50</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F168" t="n">
         <v>1.28</v>
       </c>
-      <c r="G165" t="n">
+      <c r="G168" t="n">
         <v>10.69</v>
       </c>
-      <c r="H165" t="n">
+      <c r="H168" t="n">
         <v>4.9</v>
       </c>
-      <c r="I165" t="n">
+      <c r="I168" t="n">
         <v>17.63</v>
       </c>
-      <c r="J165" t="n">
+      <c r="J168" t="n">
         <v>5.38</v>
       </c>
-      <c r="K165" t="n">
+      <c r="K168" t="n">
         <v>1</v>
       </c>
-      <c r="L165" t="n">
+      <c r="L168" t="n">
         <v>1</v>
       </c>
-      <c r="M165" t="n">
+      <c r="M168" t="n">
         <v>2.895</v>
       </c>
-      <c r="N165" t="n">
+      <c r="N168" t="n">
         <v>2294</v>
       </c>
-      <c r="O165" t="n">
+      <c r="O168" t="n">
         <v>1.28</v>
       </c>
-      <c r="P165" t="n">
+      <c r="P168" t="n">
         <v>23105</v>
       </c>
-      <c r="Q165" t="n">
+      <c r="Q168" t="n">
         <v>1932</v>
       </c>
-      <c r="R165" t="n">
+      <c r="R168" t="n">
         <v>25037</v>
       </c>
-      <c r="S165" t="n">
+      <c r="S168" t="n">
         <v>1352</v>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>10/05~10/09</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>4</v>
-      </c>
-      <c r="E166" t="n">
-        <v>50</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H166" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I166" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="J166" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="K166" t="n">
-        <v>1</v>
-      </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>-1.005</v>
-      </c>
-      <c r="N166" t="n">
-        <v>-4017</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P166" t="n">
-        <v>-44895</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>1706</v>
-      </c>
-      <c r="R166" t="n">
-        <v>-43189</v>
-      </c>
-      <c r="S166" t="n">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="H167" s="2" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="I167" s="2" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M167" s="2" t="n">
-        <v>1.475</v>
-      </c>
-      <c r="N167" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="O167" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P167" s="2" t="n">
-        <v>-7931</v>
-      </c>
-      <c r="Q167" s="2" t="n">
-        <v>3965</v>
-      </c>
-      <c r="R167" s="2" t="n">
-        <v>-3966</v>
-      </c>
-      <c r="S167" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E169" t="n">
+        <v>50</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I169" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J169" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-1.005</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-4017</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P169" t="n">
+        <v>-35570</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>2115</v>
+      </c>
+      <c r="R169" t="n">
+        <v>-33455</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="O170" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>1394</v>
+      </c>
+      <c r="Q170" s="2" t="n">
+        <v>4374</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>5768</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D169" t="n">
+      <c r="D172" t="n">
         <v>11</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E172" t="n">
         <v>36.4</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F172" t="n">
         <v>3.92</v>
       </c>
-      <c r="G169" t="n">
+      <c r="G172" t="n">
         <v>3.1</v>
       </c>
-      <c r="H169" t="n">
+      <c r="H172" t="n">
         <v>0.79</v>
       </c>
-      <c r="I169" t="n">
+      <c r="I172" t="n">
         <v>6.36</v>
       </c>
-      <c r="J169" t="n">
+      <c r="J172" t="n">
         <v>1.95</v>
       </c>
-      <c r="K169" t="n">
+      <c r="K172" t="n">
         <v>753.65</v>
       </c>
-      <c r="L169" t="n">
+      <c r="L172" t="n">
         <v>197.67</v>
       </c>
-      <c r="M169" t="n">
+      <c r="M172" t="n">
         <v>0.625</v>
       </c>
-      <c r="N169" t="n">
+      <c r="N172" t="n">
         <v>1249</v>
       </c>
-      <c r="O169" t="n">
+      <c r="O172" t="n">
         <v>2.24</v>
       </c>
-      <c r="P169" t="n">
+      <c r="P172" t="n">
         <v>13742</v>
       </c>
-      <c r="Q169" t="n">
+      <c r="Q172" t="n">
         <v>2208</v>
       </c>
-      <c r="R169" t="n">
+      <c r="R172" t="n">
         <v>15950</v>
       </c>
-      <c r="S169" t="n">
+      <c r="S172" t="n">
         <v>1353</v>
       </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>업비트SCO-15분</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>22</v>
-      </c>
-      <c r="E170" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="F170" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I170" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J170" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K170" t="n">
-        <v>208.19</v>
-      </c>
-      <c r="L170" t="n">
-        <v>99.06999999999999</v>
-      </c>
-      <c r="M170" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="N170" t="n">
-        <v>-311</v>
-      </c>
-      <c r="O170" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="P170" t="n">
-        <v>-6837</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>4398</v>
-      </c>
-      <c r="R170" t="n">
-        <v>-2439</v>
-      </c>
-      <c r="S170" t="n">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>업비트SCO-15분</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G171" s="2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="H171" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K171" s="2" t="n">
-        <v>426.38</v>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>129.08</v>
-      </c>
-      <c r="M171" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="N171" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="O171" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P171" s="2" t="n">
-        <v>6905</v>
-      </c>
-      <c r="Q171" s="2" t="n">
-        <v>6606</v>
-      </c>
-      <c r="R171" s="2" t="n">
-        <v>13511</v>
-      </c>
-      <c r="S171" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>업비트SCO-15분</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>22</v>
+      </c>
+      <c r="E173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I173" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K173" t="n">
+        <v>208.19</v>
+      </c>
+      <c r="L173" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="N173" t="n">
+        <v>-311</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P173" t="n">
+        <v>-6837</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>4398</v>
+      </c>
+      <c r="R173" t="n">
+        <v>-2439</v>
+      </c>
+      <c r="S173" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>업비트SCO-15분</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>426.38</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="O174" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>6905</v>
+      </c>
+      <c r="Q174" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>13511</v>
+      </c>
+      <c r="S174" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>바이낸스SCO-Top3</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="n">
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="n">
         <v>912</v>
       </c>
-      <c r="Q173" t="n">
+      <c r="Q176" t="n">
         <v>61</v>
       </c>
-      <c r="R173" t="n">
+      <c r="R176" t="n">
         <v>973</v>
       </c>
-      <c r="S173" t="n">
+      <c r="S176" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>바이낸스SCO-Top3</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D174" t="n">
+      <c r="D177" t="n">
         <v>6</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E177" t="n">
         <v>50</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F177" t="n">
         <v>1.28</v>
       </c>
-      <c r="G174" t="n">
+      <c r="G177" t="n">
         <v>7.01</v>
       </c>
-      <c r="H174" t="n">
+      <c r="H177" t="n">
         <v>6.41</v>
       </c>
-      <c r="I174" t="n">
+      <c r="I177" t="n">
         <v>10.66</v>
       </c>
-      <c r="J174" t="n">
+      <c r="J177" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="K174" t="n">
+      <c r="K177" t="n">
         <v>1</v>
       </c>
-      <c r="L174" t="n">
+      <c r="L177" t="n">
         <v>0.67</v>
       </c>
-      <c r="M174" t="n">
+      <c r="M177" t="n">
         <v>0.299</v>
       </c>
-      <c r="N174" t="n">
+      <c r="N177" t="n">
         <v>1885</v>
       </c>
-      <c r="O174" t="n">
+      <c r="O177" t="n">
         <v>1.28</v>
       </c>
-      <c r="P174" t="n">
+      <c r="P177" t="n">
         <v>18124</v>
       </c>
-      <c r="Q174" t="n">
+      <c r="Q177" t="n">
         <v>1048</v>
       </c>
-      <c r="R174" t="n">
+      <c r="R177" t="n">
         <v>19173</v>
       </c>
-      <c r="S174" t="n">
+      <c r="S177" t="n">
         <v>1352</v>
       </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>10/05~10/09</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>4</v>
-      </c>
-      <c r="E175" t="n">
-        <v>50</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G175" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H175" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="I175" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J175" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K175" t="n">
-        <v>1</v>
-      </c>
-      <c r="L175" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M175" t="n">
-        <v>-1.493</v>
-      </c>
-      <c r="N175" t="n">
-        <v>-4068</v>
-      </c>
-      <c r="O175" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P175" t="n">
-        <v>-27368</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>653</v>
-      </c>
-      <c r="R175" t="n">
-        <v>-26715</v>
-      </c>
-      <c r="S175" t="n">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E176" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F176" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G176" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H176" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="I176" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K176" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L176" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M176" s="2" t="n">
-        <v>-0.418</v>
-      </c>
-      <c r="N176" s="2" t="n">
-        <v>-496</v>
-      </c>
-      <c r="O176" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P176" s="2" t="n">
-        <v>-8332</v>
-      </c>
-      <c r="Q176" s="2" t="n">
-        <v>1762</v>
-      </c>
-      <c r="R176" s="2" t="n">
-        <v>-6569</v>
-      </c>
-      <c r="S176" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>바이낸스SCO-Top3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7920,289 +7997,161 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="inlineStr"/>
+        <v>0.45</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2.49</v>
+      </c>
       <c r="H178" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I178" t="inlineStr"/>
+        <v>5.48</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2.87</v>
+      </c>
       <c r="J178" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K178" t="inlineStr"/>
+        <v>5.68</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
       <c r="L178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-1.493</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-4050</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P178" t="n">
+        <v>-21356</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>775</v>
+      </c>
+      <c r="R178" t="n">
+        <v>-20580</v>
+      </c>
+      <c r="S178" t="n">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K179" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M178" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>513</v>
-      </c>
-      <c r="R178" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S178" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>4</v>
-      </c>
-      <c r="E179" t="n">
-        <v>25</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I179" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J179" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M179" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O179" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P179" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R179" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S179" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>2</v>
-      </c>
-      <c r="E180" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M180" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N180" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R180" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S180" t="n">
-        <v>1415</v>
-      </c>
+      <c r="L179" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>-0.418</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>-489</v>
+      </c>
+      <c r="O179" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>-2320</v>
+      </c>
+      <c r="Q179" s="2" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>-434</v>
+      </c>
+      <c r="S179" s="2" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>3</v>
-      </c>
-      <c r="E181" t="n">
-        <v>100</v>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="n">
-        <v>14</v>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N181" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R181" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S181" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>3</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="M182" t="n">
-        <v>-0.864</v>
-      </c>
-      <c r="N182" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>-86990</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>13787</v>
-      </c>
-      <c r="R182" t="n">
-        <v>-73203</v>
-      </c>
-      <c r="S182" t="n">
-        <v>1411</v>
-      </c>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>업비트국면v6</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr"/>
+      <c r="P181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8217,7 +8166,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -8231,36 +8180,36 @@
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>0.92</v>
+        <v>2.61</v>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
-        <v>1.07</v>
+        <v>3.49</v>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-0.918</v>
+        <v>-2.607</v>
       </c>
       <c r="N183" t="n">
-        <v>-18443</v>
+        <v>-8011</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
       </c>
       <c r="P183" t="n">
-        <v>-68185</v>
+        <v>-16021</v>
       </c>
       <c r="Q183" t="n">
-        <v>5784</v>
+        <v>513</v>
       </c>
       <c r="R183" t="n">
-        <v>-62401</v>
+        <v>-15508</v>
       </c>
       <c r="S183" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="184">
@@ -8276,50 +8225,56 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H184" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="I184" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J184" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K184" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K184" t="n">
+        <v>1</v>
+      </c>
       <c r="L184" t="n">
-        <v>20</v>
+        <v>5.67</v>
       </c>
       <c r="M184" t="n">
-        <v>-3.417</v>
+        <v>-0.217</v>
       </c>
       <c r="N184" t="n">
-        <v>-120621</v>
+        <v>-13272</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P184" t="n">
-        <v>-324235</v>
+        <v>-53089</v>
       </c>
       <c r="Q184" t="n">
-        <v>7584</v>
+        <v>5913</v>
       </c>
       <c r="R184" t="n">
-        <v>-316651</v>
+        <v>-47176</v>
       </c>
       <c r="S184" t="n">
-        <v>1338</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="185">
@@ -8335,239 +8290,298 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N185" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R185" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S185" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>3</v>
+      </c>
+      <c r="E186" t="n">
         <v>100</v>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="n">
-        <v>28</v>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="N185" t="n">
-        <v>36411</v>
-      </c>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="n">
-        <v>-98615</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>5538</v>
-      </c>
-      <c r="R185" t="n">
-        <v>-93077</v>
-      </c>
-      <c r="S185" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="n">
+        <v>14</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N186" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R186" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S186" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E186" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F186" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G186" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H186" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I186" s="2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K186" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L186" s="2" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="M186" s="2" t="n">
-        <v>-0.774</v>
-      </c>
-      <c r="N186" s="2" t="n">
-        <v>-23734</v>
-      </c>
-      <c r="O186" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P186" s="2" t="n">
-        <v>-603372</v>
-      </c>
-      <c r="Q186" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="R186" s="2" t="n">
-        <v>-557076</v>
-      </c>
-      <c r="S186" s="2" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M187" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R187" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S187" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G188" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I188" t="n">
-        <v>3.38</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
-        <v>7.04</v>
+        <v>1.07</v>
       </c>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="L188" t="n">
+        <v>4</v>
+      </c>
       <c r="M188" t="n">
-        <v>-1.213</v>
+        <v>-0.918</v>
       </c>
       <c r="N188" t="n">
-        <v>-744</v>
+        <v>-18443</v>
       </c>
       <c r="O188" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P188" t="n">
-        <v>-6692</v>
+        <v>-68185</v>
       </c>
       <c r="Q188" t="n">
-        <v>2139</v>
+        <v>5784</v>
       </c>
       <c r="R188" t="n">
-        <v>-4553</v>
+        <v>-62401</v>
       </c>
       <c r="S188" t="n">
-        <v>1415</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>100</v>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J189" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>4.05</v>
+      </c>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>20</v>
+      </c>
       <c r="M189" t="n">
-        <v>8.56</v>
+        <v>-3.417</v>
       </c>
       <c r="N189" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O189" t="inlineStr"/>
+        <v>-120621</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
       <c r="P189" t="n">
-        <v>114933</v>
+        <v>-324235</v>
       </c>
       <c r="Q189" t="n">
-        <v>667</v>
+        <v>7584</v>
       </c>
       <c r="R189" t="n">
-        <v>115600</v>
+        <v>-316651</v>
       </c>
       <c r="S189" t="n">
-        <v>1411</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -8578,843 +8592,889 @@
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>4.03</v>
+        <v>2.42</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>4.03</v>
+        <v>2.42</v>
       </c>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>28</v>
+      </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="n">
-        <v>4.029</v>
+        <v>2.425</v>
       </c>
       <c r="N190" t="n">
-        <v>35381</v>
+        <v>36411</v>
       </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
-        <v>35381</v>
+        <v>-98615</v>
       </c>
       <c r="Q190" t="n">
-        <v>269</v>
+        <v>5538</v>
       </c>
       <c r="R190" t="n">
-        <v>35650</v>
+        <v>-93077</v>
       </c>
       <c r="S190" t="n">
-        <v>1383</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>-23734</v>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>-603372</v>
+      </c>
+      <c r="Q191" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>-557076</v>
+      </c>
+      <c r="S191" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>2</v>
-      </c>
-      <c r="E191" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="n">
-        <v>-2.191</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-21127</v>
-      </c>
-      <c r="O191" t="n">
-        <v>0</v>
-      </c>
-      <c r="P191" t="n">
-        <v>-59156</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>756</v>
-      </c>
-      <c r="R191" t="n">
-        <v>-58400</v>
-      </c>
-      <c r="S191" t="n">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E192" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G192" s="2" t="n">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>9</v>
+      </c>
+      <c r="E193" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H193" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I193" t="n">
         <v>3.38</v>
       </c>
-      <c r="H192" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I192" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J192" s="2" t="n">
+      <c r="J193" t="n">
         <v>7.04</v>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N192" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P192" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q192" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R192" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S192" s="2" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P193" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R193" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E194" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H194" t="n">
-        <v>4.19</v>
-      </c>
+        <v>8.56</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J194" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K194" t="n">
-        <v>3</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1.75</v>
-      </c>
+        <v>12.69</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
-        <v>-1.213</v>
+        <v>8.56</v>
       </c>
       <c r="N194" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O194" t="n">
-        <v>0.86</v>
-      </c>
+        <v>57466</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="n">
-        <v>-6692</v>
+        <v>114933</v>
       </c>
       <c r="Q194" t="n">
-        <v>2139</v>
+        <v>667</v>
       </c>
       <c r="R194" t="n">
-        <v>-4553</v>
+        <v>115600</v>
       </c>
       <c r="S194" t="n">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="n">
         <v>100</v>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>8.56</v>
+        <v>4.03</v>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>12.69</v>
+        <v>4.03</v>
       </c>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
-        <v>8.56</v>
+        <v>4.029</v>
       </c>
       <c r="N195" t="n">
-        <v>57466</v>
+        <v>35381</v>
       </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="n">
-        <v>114933</v>
+        <v>35381</v>
       </c>
       <c r="Q195" t="n">
-        <v>667</v>
+        <v>269</v>
       </c>
       <c r="R195" t="n">
-        <v>115600</v>
+        <v>35650</v>
       </c>
       <c r="S195" t="n">
-        <v>1411</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="n">
-        <v>100</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="n">
+        <v>-2.191</v>
+      </c>
+      <c r="N196" t="n">
+        <v>-21127</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>-59156</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>756</v>
+      </c>
+      <c r="R196" t="n">
+        <v>-58400</v>
+      </c>
+      <c r="S196" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O197" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P197" s="2" t="n">
+        <v>84466</v>
+      </c>
+      <c r="Q197" s="2" t="n">
+        <v>3831</v>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>88297</v>
+      </c>
+      <c r="S197" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>9</v>
+      </c>
+      <c r="E199" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I199" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J199" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K199" t="n">
+        <v>3</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P199" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R199" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N200" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>667</v>
+      </c>
+      <c r="R200" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>100</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
         <v>4.029</v>
       </c>
-      <c r="N196" t="n">
+      <c r="N201" t="n">
         <v>35381</v>
       </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="n">
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="n">
         <v>35381</v>
       </c>
-      <c r="Q196" t="n">
+      <c r="Q201" t="n">
         <v>269</v>
       </c>
-      <c r="R196" t="n">
+      <c r="R201" t="n">
         <v>35650</v>
       </c>
-      <c r="S196" t="n">
+      <c r="S201" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D197" t="n">
+      <c r="D202" t="n">
         <v>2</v>
       </c>
-      <c r="E197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="n">
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
         <v>2.19</v>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="n">
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="n">
         <v>2.96</v>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="n">
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="n">
         <v>6.5</v>
       </c>
-      <c r="M197" t="n">
+      <c r="M202" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N197" t="n">
+      <c r="N202" t="n">
         <v>-21127</v>
       </c>
-      <c r="O197" t="n">
-        <v>0</v>
-      </c>
-      <c r="P197" t="n">
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q197" t="n">
+      <c r="Q202" t="n">
         <v>756</v>
       </c>
-      <c r="R197" t="n">
+      <c r="R202" t="n">
         <v>-58400</v>
       </c>
-      <c r="S197" t="n">
+      <c r="S202" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
+      <c r="D203" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E198" s="2" t="n">
+      <c r="E203" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F198" s="2" t="n">
+      <c r="F203" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G198" s="2" t="n">
+      <c r="G203" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H198" s="2" t="n">
+      <c r="H203" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I198" s="2" t="n">
+      <c r="I203" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J203" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K198" s="2" t="n">
+      <c r="K203" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L198" s="2" t="n">
+      <c r="L203" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="M198" s="2" t="n">
+      <c r="M203" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N198" s="2" t="n">
+      <c r="N203" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O198" s="2" t="n">
+      <c r="O203" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P198" s="2" t="n">
+      <c r="P203" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q198" s="2" t="n">
+      <c r="Q203" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R198" s="2" t="n">
+      <c r="R203" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S198" s="2" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="S203" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="2" t="inlineStr"/>
-      <c r="N200" s="2" t="inlineStr"/>
-      <c r="O200" s="2" t="inlineStr"/>
-      <c r="P200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" s="2" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="D205" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr"/>
+      <c r="P205" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q205" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr"/>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr"/>
-      <c r="P202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" s="2" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="D207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr"/>
+      <c r="P207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>KR_TR_CHART</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E204" s="2" t="inlineStr"/>
-      <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr"/>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="2" t="inlineStr"/>
-      <c r="M204" s="2" t="inlineStr"/>
-      <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr"/>
-      <c r="P204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S204" s="2" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="D209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr"/>
+      <c r="O209" s="2" t="inlineStr"/>
+      <c r="P209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>US_TR_CHART</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E206" s="2" t="inlineStr"/>
-      <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr"/>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr"/>
-      <c r="N206" s="2" t="inlineStr"/>
-      <c r="O206" s="2" t="inlineStr"/>
-      <c r="P206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="D211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>UP_TR_CHART</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D208" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
-      <c r="N208" s="2" t="inlineStr"/>
-      <c r="O208" s="2" t="inlineStr"/>
-      <c r="P208" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" s="2" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>BN_TR_CHART</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="2" t="inlineStr"/>
-      <c r="O210" s="2" t="inlineStr"/>
-      <c r="P210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" s="2" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>0</v>
-      </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R212" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S212" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>262</v>
-      </c>
-      <c r="R213" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S213" t="n">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" t="n">
-        <v>0</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="n">
-        <v>21</v>
-      </c>
-      <c r="M214" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="N214" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="n">
-        <v>-19186</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>201</v>
-      </c>
-      <c r="R214" t="n">
-        <v>-18985</v>
-      </c>
-      <c r="S214" t="n">
-        <v>1338</v>
-      </c>
+      <c r="D213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr"/>
+      <c r="P213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>2X단타_시딩</t>
+          <t>BN_TR_CHART</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -9428,50 +9488,34 @@
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="n">
-        <v>0.61</v>
-      </c>
+      <c r="H215" s="2" t="inlineStr"/>
       <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="2" t="n">
-        <v>0.61</v>
-      </c>
+      <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="M215" s="2" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="N215" s="2" t="n">
-        <v>-37549</v>
-      </c>
-      <c r="O215" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr"/>
       <c r="P215" s="2" t="n">
-        <v>-37548</v>
+        <v>0</v>
       </c>
       <c r="Q215" s="2" t="n">
-        <v>1833</v>
+        <v>0</v>
       </c>
       <c r="R215" s="2" t="n">
-        <v>-35715</v>
+        <v>0</v>
       </c>
       <c r="S215" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BN_TR_MA</t>
+          <t>2X단타_시딩</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9481,7 +9525,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -9499,22 +9543,22 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="n">
-        <v>3654</v>
+        <v>51315</v>
       </c>
       <c r="Q217" t="n">
-        <v>33</v>
+        <v>1370</v>
       </c>
       <c r="R217" t="n">
-        <v>3687</v>
+        <v>52685</v>
       </c>
       <c r="S217" t="n">
-        <v>1353</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BN_TR_MA</t>
+          <t>2X단타_시딩</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9524,303 +9568,307 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
-      <c r="I218" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="n">
-        <v>10</v>
-      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
-      <c r="M218" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="N218" t="n">
-        <v>13966</v>
-      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>262</v>
+      </c>
+      <c r="R218" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S218" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="n">
+        <v>21</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-37549</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>-19186</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>201</v>
+      </c>
+      <c r="R219" t="n">
+        <v>-18985</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>-37549</v>
+      </c>
+      <c r="O220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" s="2" t="n">
+        <v>-37548</v>
+      </c>
+      <c r="Q220" s="2" t="n">
+        <v>1833</v>
+      </c>
+      <c r="R220" s="2" t="n">
+        <v>-35715</v>
+      </c>
+      <c r="S220" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>3654</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>33</v>
+      </c>
+      <c r="R222" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S222" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>100</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="n">
+        <v>10</v>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="N223" t="n">
+        <v>13966</v>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="n">
         <v>10315</v>
       </c>
-      <c r="Q218" t="n">
+      <c r="Q223" t="n">
         <v>68</v>
       </c>
-      <c r="R218" t="n">
+      <c r="R223" t="n">
         <v>10383</v>
       </c>
-      <c r="S218" t="n">
+      <c r="S223" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D219" s="2" t="n">
+      <c r="D224" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="E224" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="n">
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="2" t="n">
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="2" t="n">
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="2" t="n">
+      <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="N219" s="2" t="n">
+      <c r="N224" s="2" t="n">
         <v>13966</v>
       </c>
-      <c r="O219" s="2" t="inlineStr"/>
-      <c r="P219" s="2" t="n">
+      <c r="O224" s="2" t="inlineStr"/>
+      <c r="P224" s="2" t="n">
         <v>13969</v>
       </c>
-      <c r="Q219" s="2" t="n">
+      <c r="Q224" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="R219" s="2" t="n">
+      <c r="R224" s="2" t="n">
         <v>14070</v>
       </c>
-      <c r="S219" s="2" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>BN_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>105</v>
-      </c>
-      <c r="R221" t="n">
-        <v>232</v>
-      </c>
-      <c r="S221" t="n">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>BN_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr"/>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr"/>
-      <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr"/>
-      <c r="N222" s="2" t="inlineStr"/>
-      <c r="O222" s="2" t="inlineStr"/>
-      <c r="P222" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q222" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="R222" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="S222" s="2" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1</v>
-      </c>
-      <c r="E224" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="n">
-        <v>1</v>
-      </c>
-      <c r="M224" t="n">
-        <v>-1.248</v>
-      </c>
-      <c r="N224" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>149</v>
-      </c>
-      <c r="R224" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="S224" t="n">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>2</v>
-      </c>
-      <c r="E225" t="n">
-        <v>100</v>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="n">
-        <v>5</v>
-      </c>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="n">
-        <v>10.223</v>
-      </c>
-      <c r="N225" t="n">
-        <v>5114</v>
-      </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="n">
-        <v>11272</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>122</v>
-      </c>
-      <c r="R225" t="n">
-        <v>11395</v>
-      </c>
-      <c r="S225" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S224" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>UP_TR_MA</t>
+          <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9834,39 +9882,27 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
-      </c>
-      <c r="E226" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="n">
-        <v>6.22</v>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
-      <c r="I226" t="n">
-        <v>6.22</v>
-      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="n">
-        <v>10</v>
-      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
-      <c r="M226" t="n">
-        <v>6.223</v>
-      </c>
-      <c r="N226" t="n">
-        <v>3113</v>
-      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="n">
-        <v>2069</v>
+        <v>127</v>
       </c>
       <c r="Q226" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="R226" t="n">
-        <v>2103</v>
+        <v>232</v>
       </c>
       <c r="S226" t="n">
         <v>1352</v>
@@ -9875,7 +9911,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>UP_TR_MA</t>
+          <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -9889,56 +9925,34 @@
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E227" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F227" s="2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G227" s="2" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="H227" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I227" s="2" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J227" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K227" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="L227" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M227" s="2" t="n">
-        <v>6.355</v>
-      </c>
-      <c r="N227" s="2" t="n">
-        <v>2867</v>
-      </c>
-      <c r="O227" s="2" t="n">
-        <v>7.12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr"/>
+      <c r="O227" s="2" t="inlineStr"/>
       <c r="P227" s="2" t="n">
-        <v>11468</v>
+        <v>127</v>
       </c>
       <c r="Q227" s="2" t="n">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="R227" s="2" t="n">
-        <v>11774</v>
+        <v>232</v>
       </c>
       <c r="S227" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_1A0</t>
+          <t>UP_TR_MA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9948,40 +9962,56 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
-      </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="n">
+        <v>1.25</v>
+      </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>1.25</v>
+      </c>
       <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="N229" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
       <c r="P229" t="n">
-        <v>866</v>
+        <v>-1873</v>
       </c>
       <c r="Q229" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="R229" t="n">
-        <v>975</v>
+        <v>-1724</v>
       </c>
       <c r="S229" t="n">
-        <v>1352</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_1A0</t>
+          <t>UP_TR_MA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9991,124 +10021,170 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E230" t="n">
+        <v>100</v>
+      </c>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>10.22</v>
+      </c>
       <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
+      <c r="I230" t="n">
+        <v>16.37</v>
+      </c>
       <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="n">
+        <v>5</v>
+      </c>
       <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>10.223</v>
+      </c>
+      <c r="N230" t="n">
+        <v>5114</v>
+      </c>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="n">
-        <v>306</v>
+        <v>11272</v>
       </c>
       <c r="Q230" t="n">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="R230" t="n">
-        <v>314</v>
+        <v>11395</v>
       </c>
       <c r="S230" t="n">
-        <v>1360</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>100</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="n">
+        <v>10</v>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3113</v>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="n">
+        <v>2069</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>34</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2103</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D231" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
-      <c r="N231" s="2" t="inlineStr"/>
-      <c r="O231" s="2" t="inlineStr"/>
-      <c r="P231" s="2" t="n">
-        <v>1172</v>
-      </c>
-      <c r="Q231" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="R231" s="2" t="n">
-        <v>1289</v>
-      </c>
-      <c r="S231" s="2" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>09/14~09/18</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>0</v>
-      </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="n">
-        <v>54396</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>238</v>
-      </c>
-      <c r="R233" t="n">
-        <v>54634</v>
-      </c>
-      <c r="S233" t="n">
-        <v>1378</v>
-      </c>
+      <c r="D232" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I232" s="2" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J232" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K232" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="L232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>6.355</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>2867</v>
+      </c>
+      <c r="O232" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>11468</v>
+      </c>
+      <c r="Q232" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="R232" s="2" t="n">
+        <v>11774</v>
+      </c>
+      <c r="S232" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10118,52 +10194,40 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
-      <c r="G234" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
-      <c r="I234" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="n">
-        <v>6</v>
-      </c>
+      <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
-      <c r="M234" t="n">
-        <v>29.576</v>
-      </c>
-      <c r="N234" t="n">
-        <v>88772</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="n">
-        <v>34376</v>
+        <v>866</v>
       </c>
       <c r="Q234" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="R234" t="n">
-        <v>34482</v>
+        <v>975</v>
       </c>
       <c r="S234" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10173,62 +10237,52 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>50</v>
-      </c>
-      <c r="F235" t="n">
-        <v>36.94</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H235" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J235" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="J235" t="inlineStr"/>
       <c r="K235" t="n">
         <v>1</v>
       </c>
-      <c r="L235" t="n">
-        <v>10</v>
-      </c>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="n">
-        <v>0.498</v>
+        <v>6.755</v>
       </c>
       <c r="N235" t="n">
-        <v>3295</v>
-      </c>
-      <c r="O235" t="n">
-        <v>36.94</v>
-      </c>
+        <v>10138</v>
+      </c>
+      <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
-        <v>6589</v>
+        <v>8746</v>
       </c>
       <c r="Q235" t="n">
-        <v>318</v>
+        <v>393</v>
       </c>
       <c r="R235" t="n">
-        <v>6907</v>
+        <v>9139</v>
       </c>
       <c r="S235" t="n">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10242,56 +10296,46 @@
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F236" s="2" t="n">
-        <v>260.57</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="H236" s="2" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="2" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="J236" s="2" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L236" s="2" t="n">
-        <v>10</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L236" s="2" t="inlineStr"/>
       <c r="M236" s="2" t="n">
-        <v>10.191</v>
+        <v>6.755</v>
       </c>
       <c r="N236" s="2" t="n">
-        <v>31787</v>
-      </c>
-      <c r="O236" s="2" t="n">
-        <v>521.13</v>
-      </c>
+        <v>10138</v>
+      </c>
+      <c r="O236" s="2" t="inlineStr"/>
       <c r="P236" s="2" t="n">
-        <v>95361</v>
+        <v>9612</v>
       </c>
       <c r="Q236" s="2" t="n">
-        <v>662</v>
+        <v>502</v>
       </c>
       <c r="R236" s="2" t="n">
-        <v>96023</v>
+        <v>10114</v>
       </c>
       <c r="S236" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>수동매매_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10301,113 +10345,160 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>09/14~09/18</t>
         </is>
       </c>
       <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>54396</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>238</v>
+      </c>
+      <c r="R238" t="n">
+        <v>54634</v>
+      </c>
+      <c r="S238" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
         <v>1</v>
       </c>
-      <c r="E238" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="n">
-        <v>3</v>
-      </c>
-      <c r="M238" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N238" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="P238" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>257</v>
-      </c>
-      <c r="R238" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S238" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>수동매매_시딩</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="n">
+      <c r="E239" t="n">
+        <v>100</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="n">
+        <v>6</v>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>29.576</v>
+      </c>
+      <c r="N239" t="n">
+        <v>88772</v>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>34376</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>106</v>
+      </c>
+      <c r="R239" t="n">
+        <v>34482</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>2</v>
+      </c>
+      <c r="E240" t="n">
+        <v>50</v>
+      </c>
+      <c r="F240" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G240" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I240" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K240" t="n">
         <v>1</v>
       </c>
-      <c r="E239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I239" s="2" t="inlineStr"/>
-      <c r="J239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M239" s="2" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N239" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P239" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q239" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="R239" s="2" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S239" s="2" t="inlineStr"/>
+      <c r="L240" t="n">
+        <v>10</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N240" t="n">
+        <v>3295</v>
+      </c>
+      <c r="O240" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P240" t="n">
+        <v>6589</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>318</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6907</v>
+      </c>
+      <c r="S240" t="n">
+        <v>1352</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10417,56 +10508,40 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
-      <c r="H241" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
-      <c r="L241" t="n">
-        <v>3</v>
-      </c>
-      <c r="M241" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N241" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
-        <v>-29689</v>
+        <v>-1605</v>
       </c>
       <c r="Q241" t="n">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="R241" t="n">
-        <v>-29500</v>
+        <v>-1556</v>
       </c>
       <c r="S241" t="n">
-        <v>1373</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -10480,50 +10555,56 @@
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="2" t="inlineStr"/>
+        <v>260.57</v>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>15.92</v>
+      </c>
       <c r="H242" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I242" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="I242" s="2" t="n">
+        <v>29.58</v>
+      </c>
       <c r="J242" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K242" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="K242" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="L242" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M242" s="2" t="n">
-        <v>-4.602</v>
+        <v>10.191</v>
       </c>
       <c r="N242" s="2" t="n">
-        <v>-29689</v>
+        <v>31787</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>0</v>
+        <v>521.13</v>
       </c>
       <c r="P242" s="2" t="n">
-        <v>-29689</v>
+        <v>93756</v>
       </c>
       <c r="Q242" s="2" t="n">
-        <v>189</v>
+        <v>711</v>
       </c>
       <c r="R242" s="2" t="n">
-        <v>-29500</v>
+        <v>94467</v>
       </c>
       <c r="S242" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10547,33 +10628,33 @@
       </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="n">
         <v>3</v>
       </c>
       <c r="M244" t="n">
-        <v>-0.867</v>
+        <v>-8.304</v>
       </c>
       <c r="N244" t="n">
-        <v>-29188</v>
+        <v>-74087</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
       </c>
       <c r="P244" t="n">
-        <v>-29188</v>
+        <v>-74087</v>
       </c>
       <c r="Q244" t="n">
-        <v>2950</v>
+        <v>257</v>
       </c>
       <c r="R244" t="n">
-        <v>-26238</v>
+        <v>-73830</v>
       </c>
       <c r="S244" t="n">
         <v>1373</v>
@@ -10582,7 +10663,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -10606,35 +10687,267 @@
       </c>
       <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" s="2" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M245" s="2" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q245" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S245" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="n">
+        <v>3</v>
+      </c>
+      <c r="M247" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N247" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>189</v>
+      </c>
+      <c r="R247" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S247" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I248" s="2" t="inlineStr"/>
+      <c r="J248" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q248" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R248" s="2" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S248" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="n">
+        <v>3</v>
+      </c>
+      <c r="M250" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N245" s="2" t="n">
+      <c r="N250" t="n">
         <v>-29188</v>
       </c>
-      <c r="O245" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P245" s="2" t="n">
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q245" s="2" t="n">
+      <c r="Q250" t="n">
         <v>2950</v>
       </c>
-      <c r="R245" s="2" t="n">
+      <c r="R250" t="n">
         <v>-26238</v>
       </c>
-      <c r="S245" s="2" t="inlineStr"/>
+      <c r="S250" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q251" s="2" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R251" s="2" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S251" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S251"/>
+  <dimension ref="A1:S253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>47.1</v>
+        <v>52.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
@@ -1620,25 +1620,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-0.193</v>
+        <v>0.021</v>
       </c>
       <c r="N19" t="n">
-        <v>-3240</v>
+        <v>-1966</v>
       </c>
       <c r="O19" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="P19" t="n">
-        <v>-38266</v>
+        <v>-15578</v>
       </c>
       <c r="Q19" t="n">
-        <v>8780</v>
+        <v>10813</v>
       </c>
       <c r="R19" t="n">
-        <v>-29486</v>
+        <v>-4764</v>
       </c>
       <c r="S19" t="n">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="20">
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>2.65</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.306</v>
+        <v>0.313</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>409481</v>
+        <v>432169</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>121324</v>
+        <v>123357</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>530806</v>
+        <v>555528</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5483,46 +5483,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
+        <v>0.39</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.91</v>
+      </c>
       <c r="H115" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="I115" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.91</v>
+      </c>
       <c r="J115" t="n">
         <v>4.39</v>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>14</v>
+      </c>
       <c r="L115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M115" t="n">
-        <v>-4.385</v>
+        <v>-1.345</v>
       </c>
       <c r="N115" t="n">
-        <v>-45429</v>
+        <v>-13887</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P115" t="n">
-        <v>-942</v>
+        <v>4838</v>
       </c>
       <c r="Q115" t="n">
-        <v>1443</v>
+        <v>2740</v>
       </c>
       <c r="R115" t="n">
-        <v>501</v>
+        <v>7578</v>
       </c>
       <c r="S115" t="n">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="116">
@@ -5542,19 +5548,19 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>37.9</v>
+        <v>38.7</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>8.369999999999999</v>
@@ -5563,28 +5569,28 @@
         <v>10.01</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>9.83</v>
+        <v>10.05</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>-1.001</v>
+        <v>-0.925</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-14965</v>
+        <v>-13878</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>0.44</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-392480</v>
+        <v>-386700</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>40297</v>
+        <v>41594</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-352183</v>
+        <v>-345106</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5605,16 +5611,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E118" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="F118" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="G118" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="H118" t="n">
         <v>0.8100000000000001</v>
@@ -5632,25 +5638,25 @@
         <v>0.67</v>
       </c>
       <c r="M118" t="n">
-        <v>1.049</v>
+        <v>1.335</v>
       </c>
       <c r="N118" t="n">
-        <v>3708</v>
+        <v>4452</v>
       </c>
       <c r="O118" t="n">
-        <v>3.95</v>
+        <v>5.12</v>
       </c>
       <c r="P118" t="n">
-        <v>22239</v>
+        <v>31154</v>
       </c>
       <c r="Q118" t="n">
-        <v>3311</v>
+        <v>3734</v>
       </c>
       <c r="R118" t="n">
-        <v>25551</v>
+        <v>34888</v>
       </c>
       <c r="S118" t="n">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="119">
@@ -5670,16 +5676,16 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>0.8100000000000001</v>
@@ -5697,538 +5703,524 @@
         <v>0.67</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1.049</v>
+        <v>1.335</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>3708</v>
+        <v>4452</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>3.95</v>
+        <v>5.12</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>22239</v>
+        <v>31154</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>3311</v>
+        <v>3734</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>25551</v>
+        <v>34888</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>US_TR_BLACK_B</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>6856</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>185</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7041</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BLACK_B</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr"/>
-      <c r="N121" s="2" t="inlineStr"/>
-      <c r="O121" s="2" t="inlineStr"/>
-      <c r="P121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="D122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="n">
+        <v>6856</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>7041</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>US_TR_PURPLE_B</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="inlineStr"/>
-      <c r="N123" s="2" t="inlineStr"/>
-      <c r="O123" s="2" t="inlineStr"/>
-      <c r="P123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="D124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="D126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="D128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D129" t="n">
+      <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="n">
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
         <v>7.47</v>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="n">
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
         <v>7.47</v>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="n">
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="n">
         <v>6</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M130" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N130" t="n">
         <v>-62673</v>
       </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="Q130" t="n">
         <v>1736</v>
       </c>
-      <c r="R129" t="n">
+      <c r="R130" t="n">
         <v>-82310</v>
       </c>
-      <c r="S129" t="n">
+      <c r="S130" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="n">
+      <c r="E131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="n">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="n">
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M130" s="2" t="n">
+      <c r="M131" s="2" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N130" s="2" t="n">
+      <c r="N131" s="2" t="n">
         <v>-62673</v>
       </c>
-      <c r="O130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="2" t="n">
+      <c r="O131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="2" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q130" s="2" t="n">
+      <c r="Q131" s="2" t="n">
         <v>1736</v>
       </c>
-      <c r="R130" s="2" t="n">
+      <c r="R131" s="2" t="n">
         <v>-82310</v>
       </c>
-      <c r="S130" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="S131" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="n">
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
         <v>1.3</v>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="n">
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
         <v>1.3</v>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="n">
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="n">
         <v>1</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M133" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>-5227</v>
       </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
         <v>-5525</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>776</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>-4749</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>100</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>14</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1207</v>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>1507</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>110</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1616</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L135" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>-5227</v>
-      </c>
-      <c r="O133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="2" t="n">
-        <v>-5525</v>
-      </c>
-      <c r="Q133" s="2" t="n">
-        <v>776</v>
-      </c>
-      <c r="R133" s="2" t="n">
-        <v>-4749</v>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="n">
-        <v>1</v>
-      </c>
-      <c r="M135" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R135" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S135" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>4</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="n">
-        <v>7</v>
-      </c>
-      <c r="M136" t="n">
-        <v>-3.235</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-12511</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>-50045</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>2266</v>
-      </c>
-      <c r="R136" t="n">
-        <v>-47780</v>
-      </c>
-      <c r="S136" t="n">
-        <v>1352</v>
-      </c>
+      <c r="M135" s="2" t="n">
+        <v>-0.487</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>-2010</v>
+      </c>
+      <c r="O135" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>-4018</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>886</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>-3133</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6243,7 +6235,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6257,218 +6249,212 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>2702</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-38883</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>7</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-3.235</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-12511</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-50045</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>2266</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-47780</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
         <v>3</v>
       </c>
-      <c r="M137" t="n">
+      <c r="M139" t="n">
         <v>-1.956</v>
       </c>
-      <c r="N137" t="n">
-        <v>-9778</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>-9778</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>693</v>
-      </c>
-      <c r="R137" t="n">
-        <v>-9085</v>
-      </c>
-      <c r="S137" t="n">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="N139" t="n">
+        <v>-9807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-9807</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>695</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-9112</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D140" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="n">
+      <c r="E140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="n">
         <v>2.84</v>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="n">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="n">
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="M138" s="2" t="n">
+      <c r="M140" s="2" t="n">
         <v>-2.838</v>
       </c>
-      <c r="N138" s="2" t="n">
-        <v>-16902</v>
-      </c>
-      <c r="O138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="2" t="n">
-        <v>-101409</v>
-      </c>
-      <c r="Q138" s="2" t="n">
-        <v>5661</v>
-      </c>
-      <c r="R138" s="2" t="n">
-        <v>-95748</v>
-      </c>
-      <c r="S138" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>7</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="n">
-        <v>8</v>
-      </c>
-      <c r="M140" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N140" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R140" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S140" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G141" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H141" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I141" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J141" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K141" t="n">
-        <v>18</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-18508</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P141" t="n">
-        <v>-52375</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>4226</v>
-      </c>
-      <c r="R141" t="n">
-        <v>-48149</v>
-      </c>
-      <c r="S141" t="n">
-        <v>1383</v>
-      </c>
+      <c r="N140" s="2" t="n">
+        <v>-16906</v>
+      </c>
+      <c r="O140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>-101438</v>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>5663</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>-95775</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6483,11 +6469,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -6497,36 +6483,36 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>2.68</v>
+        <v>6.17</v>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M142" t="n">
-        <v>-1.87</v>
+        <v>-3.337</v>
       </c>
       <c r="N142" t="n">
-        <v>-38258</v>
+        <v>-7859</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>-79635</v>
+        <v>-55013</v>
       </c>
       <c r="Q142" t="n">
-        <v>4778</v>
+        <v>1884</v>
       </c>
       <c r="R142" t="n">
-        <v>-74857</v>
+        <v>-53128</v>
       </c>
       <c r="S142" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="143">
@@ -6542,7 +6528,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6552,454 +6538,458 @@
         <v>66.7</v>
       </c>
       <c r="F143" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K143" t="n">
+        <v>18</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N144" t="n">
+        <v>-38258</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>-79635</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>4778</v>
+      </c>
+      <c r="R144" t="n">
+        <v>-74857</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F145" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G145" t="n">
         <v>0.47</v>
       </c>
-      <c r="H143" t="n">
+      <c r="H145" t="n">
         <v>6.05</v>
       </c>
-      <c r="I143" t="n">
+      <c r="I145" t="n">
         <v>0.51</v>
       </c>
-      <c r="J143" t="n">
+      <c r="J145" t="n">
         <v>6.05</v>
       </c>
-      <c r="K143" t="n">
+      <c r="K145" t="n">
         <v>1</v>
       </c>
-      <c r="L143" t="n">
+      <c r="L145" t="n">
         <v>1</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M145" t="n">
         <v>-1.701</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N145" t="n">
         <v>-9977</v>
       </c>
-      <c r="O143" t="n">
+      <c r="O145" t="n">
         <v>0.13</v>
       </c>
-      <c r="P143" t="n">
+      <c r="P145" t="n">
         <v>-29930</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="Q145" t="n">
         <v>2167</v>
       </c>
-      <c r="R143" t="n">
+      <c r="R145" t="n">
         <v>-27764</v>
       </c>
-      <c r="S143" t="n">
+      <c r="S145" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D144" s="2" t="n">
+      <c r="D146" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E144" s="2" t="n">
+      <c r="E146" s="2" t="n">
         <v>26.7</v>
       </c>
-      <c r="F144" s="2" t="n">
+      <c r="F146" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G144" s="2" t="n">
+      <c r="G146" s="2" t="n">
         <v>1.68</v>
       </c>
-      <c r="H144" s="2" t="n">
+      <c r="H146" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="I144" s="2" t="n">
+      <c r="I146" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J146" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K144" s="2" t="n">
+      <c r="K146" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="L144" s="2" t="n">
+      <c r="L146" s="2" t="n">
         <v>6.55</v>
       </c>
-      <c r="M144" s="2" t="n">
+      <c r="M146" s="2" t="n">
         <v>-1.974</v>
       </c>
-      <c r="N144" s="2" t="n">
+      <c r="N146" s="2" t="n">
         <v>-14466</v>
       </c>
-      <c r="O144" s="2" t="n">
+      <c r="O146" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P144" s="2" t="n">
+      <c r="P146" s="2" t="n">
         <v>-216953</v>
       </c>
-      <c r="Q144" s="2" t="n">
+      <c r="Q146" s="2" t="n">
         <v>13055</v>
       </c>
-      <c r="R144" s="2" t="n">
+      <c r="R146" s="2" t="n">
         <v>-203898</v>
       </c>
-      <c r="S144" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="S146" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D146" t="n">
+      <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E148" t="n">
         <v>100</v>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="n">
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
         <v>8.9</v>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="n">
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="n">
         <v>8.9</v>
       </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="n">
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
         <v>5</v>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="n">
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
         <v>8.897</v>
       </c>
-      <c r="N146" t="n">
+      <c r="N148" t="n">
         <v>21615</v>
       </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="n">
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
         <v>21615</v>
       </c>
-      <c r="Q146" t="n">
+      <c r="Q148" t="n">
         <v>355</v>
       </c>
-      <c r="R146" t="n">
+      <c r="R148" t="n">
         <v>21970</v>
       </c>
-      <c r="S146" t="n">
+      <c r="S148" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D149" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E149" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="n">
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="n">
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="2" t="n">
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L147" s="2" t="inlineStr"/>
-      <c r="M147" s="2" t="n">
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="n">
         <v>8.897</v>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N149" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="O147" s="2" t="inlineStr"/>
-      <c r="P147" s="2" t="n">
+      <c r="O149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="Q147" s="2" t="n">
+      <c r="Q149" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="R147" s="2" t="n">
+      <c r="R149" s="2" t="n">
         <v>21970</v>
       </c>
-      <c r="S147" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="S149" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D149" t="n">
+      <c r="D151" t="n">
         <v>2</v>
       </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="n">
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
         <v>7.15</v>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="n">
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="n">
         <v>10.49</v>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="n">
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
         <v>1</v>
       </c>
-      <c r="M149" t="n">
+      <c r="M151" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N149" t="n">
+      <c r="N151" t="n">
         <v>-27445</v>
       </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="Q151" t="n">
         <v>1054</v>
       </c>
-      <c r="R149" t="n">
+      <c r="R151" t="n">
         <v>-53835</v>
       </c>
-      <c r="S149" t="n">
+      <c r="S151" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n">
+      <c r="D152" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="n">
+      <c r="E152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="n">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="n">
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M150" s="2" t="n">
+      <c r="M152" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N150" s="2" t="n">
+      <c r="N152" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" s="2" t="n">
+      <c r="O152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q150" s="2" t="n">
+      <c r="Q152" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R150" s="2" t="n">
+      <c r="R152" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S150" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>17</v>
-      </c>
-      <c r="E152" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G152" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H152" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I152" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J152" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M152" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N152" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O152" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P152" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R152" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S152" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>7</v>
-      </c>
-      <c r="E153" t="n">
-        <v>100</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N153" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R153" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S153" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S152" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7014,241 +7004,304 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>17</v>
+      </c>
+      <c r="E154" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G154" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I154" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J154" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N154" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O154" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P154" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R154" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>7</v>
+      </c>
+      <c r="E155" t="n">
+        <v>100</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N155" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R155" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D156" t="n">
         <v>4</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E156" t="n">
         <v>50</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F156" t="n">
         <v>2.51</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G156" t="n">
         <v>11.43</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H156" t="n">
         <v>2.87</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I156" t="n">
         <v>12</v>
       </c>
-      <c r="J154" t="n">
+      <c r="J156" t="n">
         <v>4.94</v>
       </c>
-      <c r="K154" t="n">
+      <c r="K156" t="n">
         <v>14</v>
       </c>
-      <c r="L154" t="n">
+      <c r="L156" t="n">
         <v>14</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M156" t="n">
         <v>4.282</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N156" t="n">
         <v>7910</v>
       </c>
-      <c r="O154" t="n">
+      <c r="O156" t="n">
         <v>2.51</v>
       </c>
-      <c r="P154" t="n">
+      <c r="P156" t="n">
         <v>-912</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="Q156" t="n">
         <v>635</v>
       </c>
-      <c r="R154" t="n">
+      <c r="R156" t="n">
         <v>-278</v>
       </c>
-      <c r="S154" t="n">
+      <c r="S156" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D157" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E157" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F155" s="2" t="n">
+      <c r="F157" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G155" s="2" t="n">
+      <c r="G157" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H155" s="2" t="n">
+      <c r="H157" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I155" s="2" t="n">
+      <c r="I157" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J157" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K155" s="2" t="n">
+      <c r="K157" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L155" s="2" t="n">
+      <c r="L157" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M155" s="2" t="n">
+      <c r="M157" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N157" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O155" s="2" t="n">
+      <c r="O157" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P155" s="2" t="n">
+      <c r="P157" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q155" s="2" t="n">
+      <c r="Q157" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R155" s="2" t="n">
+      <c r="R157" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S155" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="S157" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D157" t="n">
+      <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="n">
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
         <v>0.54</v>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="n">
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
         <v>0.54</v>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="n">
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="n">
         <v>12</v>
       </c>
-      <c r="M157" t="n">
+      <c r="M159" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N157" t="n">
+      <c r="N159" t="n">
         <v>-1280</v>
       </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q157" t="n">
+      <c r="Q159" t="n">
         <v>208</v>
       </c>
-      <c r="R157" t="n">
+      <c r="R159" t="n">
         <v>-1072</v>
       </c>
-      <c r="S157" t="n">
+      <c r="S159" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M158" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N158" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q158" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R158" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S158" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7262,34 +7315,50 @@
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
-      <c r="O160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O160" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P160" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q160" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R160" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S160" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7328,232 +7397,153 @@
       <c r="S162" s="2" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D164" t="n">
+      <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E166" t="n">
         <v>100</v>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="n">
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="n">
         <v>2.1</v>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="n">
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
         <v>2.1</v>
       </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="n">
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="n">
         <v>52.73</v>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="n">
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
         <v>2.102</v>
       </c>
-      <c r="N164" t="n">
+      <c r="N166" t="n">
         <v>2341</v>
       </c>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="n">
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
         <v>2341</v>
       </c>
-      <c r="Q164" t="n">
+      <c r="Q166" t="n">
         <v>34</v>
       </c>
-      <c r="R164" t="n">
+      <c r="R166" t="n">
         <v>2375</v>
       </c>
-      <c r="S164" t="n">
+      <c r="S166" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D165" s="2" t="n">
+      <c r="D167" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E167" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="n">
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="n">
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="2" t="n">
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="n">
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N167" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O165" s="2" t="inlineStr"/>
-      <c r="P165" s="2" t="n">
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q165" s="2" t="n">
+      <c r="Q167" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R165" s="2" t="n">
+      <c r="R167" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S165" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" t="n">
-        <v>100</v>
-      </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="n">
-        <v>2.876</v>
-      </c>
-      <c r="N167" t="n">
-        <v>4316</v>
-      </c>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="n">
-        <v>13859</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>327</v>
-      </c>
-      <c r="R167" t="n">
-        <v>14186</v>
-      </c>
-      <c r="S167" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>6</v>
-      </c>
-      <c r="E168" t="n">
-        <v>50</v>
-      </c>
-      <c r="F168" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G168" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="H168" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I168" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="J168" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1</v>
-      </c>
-      <c r="L168" t="n">
-        <v>1</v>
-      </c>
-      <c r="M168" t="n">
-        <v>2.895</v>
-      </c>
-      <c r="N168" t="n">
-        <v>2294</v>
-      </c>
-      <c r="O168" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P168" t="n">
-        <v>23105</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>1932</v>
-      </c>
-      <c r="R168" t="n">
-        <v>25037</v>
-      </c>
-      <c r="S168" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S167" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7568,421 +7558,433 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>50</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H169" t="n">
-        <v>4.98</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="J169" t="n">
-        <v>5.27</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
         <v>1</v>
       </c>
-      <c r="L169" t="n">
-        <v>0</v>
-      </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="n">
+        <v>2.876</v>
+      </c>
+      <c r="N169" t="n">
+        <v>4316</v>
+      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>13859</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>327</v>
+      </c>
+      <c r="R169" t="n">
+        <v>14186</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>6</v>
+      </c>
+      <c r="E170" t="n">
+        <v>50</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G170" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I170" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="J170" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2294</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P170" t="n">
+        <v>23105</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>1932</v>
+      </c>
+      <c r="R170" t="n">
+        <v>25037</v>
+      </c>
+      <c r="S170" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" t="n">
+        <v>50</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H171" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I171" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J171" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
         <v>-1.005</v>
       </c>
-      <c r="N169" t="n">
+      <c r="N171" t="n">
         <v>-4017</v>
       </c>
-      <c r="O169" t="n">
+      <c r="O171" t="n">
         <v>0.6</v>
       </c>
-      <c r="P169" t="n">
+      <c r="P171" t="n">
         <v>-35570</v>
       </c>
-      <c r="Q169" t="n">
+      <c r="Q171" t="n">
         <v>2115</v>
       </c>
-      <c r="R169" t="n">
+      <c r="R171" t="n">
         <v>-33455</v>
       </c>
-      <c r="S169" t="n">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="S171" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-Top3</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D172" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="E172" s="2" t="n">
         <v>54.5</v>
       </c>
-      <c r="F170" s="2" t="n">
+      <c r="F172" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="G170" s="2" t="n">
+      <c r="G172" s="2" t="n">
         <v>6.81</v>
       </c>
-      <c r="H170" s="2" t="n">
+      <c r="H172" s="2" t="n">
         <v>4.93</v>
       </c>
-      <c r="I170" s="2" t="n">
+      <c r="I172" s="2" t="n">
         <v>17.63</v>
       </c>
-      <c r="J170" s="2" t="n">
+      <c r="J172" s="2" t="n">
         <v>5.38</v>
       </c>
-      <c r="K170" s="2" t="n">
+      <c r="K172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L170" s="2" t="n">
+      <c r="L172" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M170" s="2" t="n">
+      <c r="M172" s="2" t="n">
         <v>1.475</v>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N172" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="O170" s="2" t="n">
+      <c r="O172" s="2" t="n">
         <v>1.02</v>
       </c>
-      <c r="P170" s="2" t="n">
+      <c r="P172" s="2" t="n">
         <v>1394</v>
       </c>
-      <c r="Q170" s="2" t="n">
+      <c r="Q172" s="2" t="n">
         <v>4374</v>
       </c>
-      <c r="R170" s="2" t="n">
+      <c r="R172" s="2" t="n">
         <v>5768</v>
       </c>
-      <c r="S170" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="S172" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D172" t="n">
+      <c r="D174" t="n">
         <v>11</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E174" t="n">
         <v>36.4</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F174" t="n">
         <v>3.92</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G174" t="n">
         <v>3.1</v>
       </c>
-      <c r="H172" t="n">
+      <c r="H174" t="n">
         <v>0.79</v>
       </c>
-      <c r="I172" t="n">
+      <c r="I174" t="n">
         <v>6.36</v>
       </c>
-      <c r="J172" t="n">
+      <c r="J174" t="n">
         <v>1.95</v>
       </c>
-      <c r="K172" t="n">
+      <c r="K174" t="n">
         <v>753.65</v>
       </c>
-      <c r="L172" t="n">
+      <c r="L174" t="n">
         <v>197.67</v>
       </c>
-      <c r="M172" t="n">
+      <c r="M174" t="n">
         <v>0.625</v>
       </c>
-      <c r="N172" t="n">
+      <c r="N174" t="n">
         <v>1249</v>
       </c>
-      <c r="O172" t="n">
+      <c r="O174" t="n">
         <v>2.24</v>
       </c>
-      <c r="P172" t="n">
+      <c r="P174" t="n">
         <v>13742</v>
       </c>
-      <c r="Q172" t="n">
+      <c r="Q174" t="n">
         <v>2208</v>
       </c>
-      <c r="R172" t="n">
+      <c r="R174" t="n">
         <v>15950</v>
       </c>
-      <c r="S172" t="n">
+      <c r="S174" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D173" t="n">
+      <c r="D175" t="n">
         <v>22</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E175" t="n">
         <v>27.3</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F175" t="n">
         <v>2.05</v>
       </c>
-      <c r="G173" t="n">
+      <c r="G175" t="n">
         <v>1.89</v>
       </c>
-      <c r="H173" t="n">
+      <c r="H175" t="n">
         <v>0.92</v>
       </c>
-      <c r="I173" t="n">
+      <c r="I175" t="n">
         <v>6.1</v>
       </c>
-      <c r="J173" t="n">
+      <c r="J175" t="n">
         <v>2.94</v>
       </c>
-      <c r="K173" t="n">
+      <c r="K175" t="n">
         <v>208.19</v>
       </c>
-      <c r="L173" t="n">
+      <c r="L175" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="M173" t="n">
+      <c r="M175" t="n">
         <v>-0.155</v>
       </c>
-      <c r="N173" t="n">
+      <c r="N175" t="n">
         <v>-311</v>
       </c>
-      <c r="O173" t="n">
+      <c r="O175" t="n">
         <v>0.77</v>
       </c>
-      <c r="P173" t="n">
+      <c r="P175" t="n">
         <v>-6837</v>
       </c>
-      <c r="Q173" t="n">
+      <c r="Q175" t="n">
         <v>4398</v>
       </c>
-      <c r="R173" t="n">
+      <c r="R175" t="n">
         <v>-2439</v>
       </c>
-      <c r="S173" t="n">
+      <c r="S175" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n">
+      <c r="D176" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E176" s="2" t="n">
         <v>30.3</v>
       </c>
-      <c r="F174" s="2" t="n">
+      <c r="F176" s="2" t="n">
         <v>2.69</v>
       </c>
-      <c r="G174" s="2" t="n">
+      <c r="G176" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="H174" s="2" t="n">
+      <c r="H176" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="I174" s="2" t="n">
+      <c r="I176" s="2" t="n">
         <v>6.36</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J176" s="2" t="n">
         <v>2.94</v>
       </c>
-      <c r="K174" s="2" t="n">
+      <c r="K176" s="2" t="n">
         <v>426.38</v>
       </c>
-      <c r="L174" s="2" t="n">
+      <c r="L176" s="2" t="n">
         <v>129.08</v>
       </c>
-      <c r="M174" s="2" t="n">
+      <c r="M176" s="2" t="n">
         <v>0.105</v>
       </c>
-      <c r="N174" s="2" t="n">
+      <c r="N176" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="O174" s="2" t="n">
+      <c r="O176" s="2" t="n">
         <v>1.17</v>
       </c>
-      <c r="P174" s="2" t="n">
+      <c r="P176" s="2" t="n">
         <v>6905</v>
       </c>
-      <c r="Q174" s="2" t="n">
+      <c r="Q176" s="2" t="n">
         <v>6606</v>
       </c>
-      <c r="R174" s="2" t="n">
+      <c r="R176" s="2" t="n">
         <v>13511</v>
       </c>
-      <c r="S174" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>61</v>
-      </c>
-      <c r="R176" t="n">
-        <v>973</v>
-      </c>
-      <c r="S176" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>6</v>
-      </c>
-      <c r="E177" t="n">
-        <v>50</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G177" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H177" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I177" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J177" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K177" t="n">
-        <v>1</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="N177" t="n">
-        <v>1885</v>
-      </c>
-      <c r="O177" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P177" t="n">
-        <v>18124</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>1048</v>
-      </c>
-      <c r="R177" t="n">
-        <v>19173</v>
-      </c>
-      <c r="S177" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S176" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7997,285 +7999,269 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>61</v>
+      </c>
+      <c r="R178" t="n">
+        <v>973</v>
+      </c>
+      <c r="S178" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>6</v>
+      </c>
+      <c r="E179" t="n">
+        <v>50</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G179" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="H179" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I179" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J179" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P179" t="n">
+        <v>18124</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1048</v>
+      </c>
+      <c r="R179" t="n">
+        <v>19173</v>
+      </c>
+      <c r="S179" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D180" t="n">
         <v>4</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E180" t="n">
         <v>50</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F180" t="n">
         <v>0.45</v>
       </c>
-      <c r="G178" t="n">
+      <c r="G180" t="n">
         <v>2.49</v>
       </c>
-      <c r="H178" t="n">
+      <c r="H180" t="n">
         <v>5.48</v>
       </c>
-      <c r="I178" t="n">
+      <c r="I180" t="n">
         <v>2.87</v>
       </c>
-      <c r="J178" t="n">
+      <c r="J180" t="n">
         <v>5.68</v>
       </c>
-      <c r="K178" t="n">
+      <c r="K180" t="n">
         <v>1</v>
       </c>
-      <c r="L178" t="n">
+      <c r="L180" t="n">
         <v>0.5</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M180" t="n">
         <v>-1.493</v>
       </c>
-      <c r="N178" t="n">
-        <v>-4050</v>
-      </c>
-      <c r="O178" t="n">
+      <c r="N180" t="n">
+        <v>-4062</v>
+      </c>
+      <c r="O180" t="n">
         <v>0.45</v>
       </c>
-      <c r="P178" t="n">
-        <v>-21356</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>775</v>
-      </c>
-      <c r="R178" t="n">
-        <v>-20580</v>
-      </c>
-      <c r="S178" t="n">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E179" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F179" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G179" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H179" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="I179" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K179" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M179" s="2" t="n">
-        <v>-0.418</v>
-      </c>
-      <c r="N179" s="2" t="n">
-        <v>-489</v>
-      </c>
-      <c r="O179" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P179" s="2" t="n">
-        <v>-2320</v>
-      </c>
-      <c r="Q179" s="2" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R179" s="2" t="n">
-        <v>-434</v>
-      </c>
-      <c r="S179" s="2" t="inlineStr"/>
+      <c r="P180" t="n">
+        <v>-21419</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>778</v>
+      </c>
+      <c r="R180" t="n">
+        <v>-20641</v>
+      </c>
+      <c r="S180" t="n">
+        <v>1358</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>-0.418</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>-494</v>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>-2383</v>
+      </c>
+      <c r="Q181" s="2" t="n">
+        <v>1887</v>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="S181" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="2" t="inlineStr"/>
-      <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="2" t="inlineStr"/>
-      <c r="N181" s="2" t="inlineStr"/>
-      <c r="O181" s="2" t="inlineStr"/>
-      <c r="P181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>2</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="n">
-        <v>1</v>
-      </c>
-      <c r="M183" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N183" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>513</v>
-      </c>
-      <c r="R183" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S183" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>4</v>
-      </c>
-      <c r="E184" t="n">
-        <v>25</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G184" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I184" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J184" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K184" t="n">
-        <v>1</v>
-      </c>
-      <c r="L184" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M184" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N184" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O184" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P184" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R184" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S184" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr"/>
+      <c r="P183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8290,7 +8276,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -8304,33 +8290,33 @@
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N185" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
       </c>
       <c r="P185" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q185" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R185" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S185" t="n">
         <v>1415</v>
@@ -8349,43 +8335,53 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E186" t="n">
-        <v>100</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G186" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H186" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I186" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J186" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K186" t="n">
-        <v>14</v>
-      </c>
-      <c r="L186" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M186" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N186" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O186" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P186" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q186" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R186" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S186" t="n">
         <v>1415</v>
@@ -8404,11 +8400,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -8418,36 +8414,36 @@
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N187" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
       </c>
       <c r="P187" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q187" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R187" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S187" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="188">
@@ -8463,50 +8459,46 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="n">
+        <v>14</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
       <c r="M188" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N188" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O188" t="inlineStr"/>
       <c r="P188" t="n">
-        <v>-68185</v>
+        <v>48540</v>
       </c>
       <c r="Q188" t="n">
-        <v>5784</v>
+        <v>4254</v>
       </c>
       <c r="R188" t="n">
-        <v>-62401</v>
+        <v>52794</v>
       </c>
       <c r="S188" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="189">
@@ -8522,7 +8514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8536,36 +8528,36 @@
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
-        <v>20</v>
+        <v>4.67</v>
       </c>
       <c r="M189" t="n">
-        <v>-3.417</v>
+        <v>-0.864</v>
       </c>
       <c r="N189" t="n">
-        <v>-120621</v>
+        <v>-28997</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>-324235</v>
+        <v>-86990</v>
       </c>
       <c r="Q189" t="n">
-        <v>7584</v>
+        <v>13787</v>
       </c>
       <c r="R189" t="n">
-        <v>-316651</v>
+        <v>-73203</v>
       </c>
       <c r="S189" t="n">
-        <v>1338</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="190">
@@ -8581,224 +8573,228 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>4</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R190" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S190" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>20</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R191" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S191" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D190" t="n">
+      <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E192" t="n">
         <v>100</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="n">
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
         <v>2.42</v>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="n">
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
         <v>2.42</v>
       </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="n">
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="n">
         <v>28</v>
       </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="n">
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="n">
         <v>2.425</v>
       </c>
-      <c r="N190" t="n">
+      <c r="N192" t="n">
         <v>36411</v>
       </c>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="n">
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="n">
         <v>-98615</v>
       </c>
-      <c r="Q190" t="n">
+      <c r="Q192" t="n">
         <v>5538</v>
       </c>
-      <c r="R190" t="n">
+      <c r="R192" t="n">
         <v>-93077</v>
       </c>
-      <c r="S190" t="n">
+      <c r="S192" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n">
+      <c r="D193" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E191" s="2" t="n">
+      <c r="E193" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F191" s="2" t="n">
+      <c r="F193" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="G191" s="2" t="n">
+      <c r="G193" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H191" s="2" t="n">
+      <c r="H193" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I191" s="2" t="n">
+      <c r="I193" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J191" s="2" t="n">
+      <c r="J193" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K191" s="2" t="n">
+      <c r="K193" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L191" s="2" t="n">
+      <c r="L193" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M191" s="2" t="n">
+      <c r="M193" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N191" s="2" t="n">
+      <c r="N193" s="2" t="n">
         <v>-23734</v>
       </c>
-      <c r="O191" s="2" t="n">
+      <c r="O193" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="P191" s="2" t="n">
+      <c r="P193" s="2" t="n">
         <v>-603372</v>
       </c>
-      <c r="Q191" s="2" t="n">
+      <c r="Q193" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="R191" s="2" t="n">
+      <c r="R193" s="2" t="n">
         <v>-557076</v>
       </c>
-      <c r="S191" s="2" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>9</v>
-      </c>
-      <c r="E193" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G193" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H193" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I193" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J193" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N193" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P193" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R193" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S193" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>2</v>
-      </c>
-      <c r="E194" t="n">
-        <v>100</v>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N194" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>667</v>
-      </c>
-      <c r="R194" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S194" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S193" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8813,44 +8809,52 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E195" t="n">
-        <v>100</v>
-      </c>
-      <c r="F195" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G195" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H195" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H195" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I195" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J195" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J195" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N195" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O195" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P195" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q195" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R195" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S195" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="196">
@@ -8866,228 +8870,214 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D196" t="n">
         <v>2</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N196" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>667</v>
+      </c>
+      <c r="R196" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S196" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>100</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N197" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>269</v>
+      </c>
+      <c r="R197" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S197" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N196" t="n">
+      <c r="N198" t="n">
         <v>-21127</v>
       </c>
-      <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="P196" t="n">
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q196" t="n">
+      <c r="Q198" t="n">
         <v>756</v>
       </c>
-      <c r="R196" t="n">
+      <c r="R198" t="n">
         <v>-58400</v>
       </c>
-      <c r="S196" t="n">
+      <c r="S198" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n">
+      <c r="D199" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E197" s="2" t="n">
+      <c r="E199" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F197" s="2" t="n">
+      <c r="F199" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G197" s="2" t="n">
+      <c r="G199" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H197" s="2" t="n">
+      <c r="H199" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I197" s="2" t="n">
+      <c r="I199" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J199" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="inlineStr"/>
-      <c r="M197" s="2" t="n">
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N197" s="2" t="n">
+      <c r="N199" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O197" s="2" t="n">
+      <c r="O199" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P197" s="2" t="n">
+      <c r="P199" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q197" s="2" t="n">
+      <c r="Q199" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R197" s="2" t="n">
+      <c r="R199" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S197" s="2" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>9</v>
-      </c>
-      <c r="E199" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H199" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I199" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J199" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K199" t="n">
-        <v>3</v>
-      </c>
-      <c r="L199" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M199" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N199" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P199" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R199" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S199" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>2</v>
-      </c>
-      <c r="E200" t="n">
-        <v>100</v>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N200" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>667</v>
-      </c>
-      <c r="R200" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S200" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S199" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9102,46 +9092,56 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E201" t="n">
-        <v>100</v>
-      </c>
-      <c r="F201" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G201" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H201" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H201" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I201" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J201" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J201" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K201" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M201" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N201" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O201" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P201" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q201" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R201" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S201" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="202">
@@ -9157,119 +9157,166 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D202" t="n">
         <v>2</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="n">
+        <v>100</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N202" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>667</v>
+      </c>
+      <c r="R202" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S202" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>100</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N203" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>269</v>
+      </c>
+      <c r="R203" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S203" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>2</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="n">
         <v>2.19</v>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="n">
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="n">
         <v>2.96</v>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="n">
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="n">
         <v>6.5</v>
       </c>
-      <c r="M202" t="n">
+      <c r="M204" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N202" t="n">
+      <c r="N204" t="n">
         <v>-21127</v>
       </c>
-      <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="P202" t="n">
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q202" t="n">
+      <c r="Q204" t="n">
         <v>756</v>
       </c>
-      <c r="R202" t="n">
+      <c r="R204" t="n">
         <v>-58400</v>
       </c>
-      <c r="S202" t="n">
+      <c r="S204" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E203" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F203" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G203" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H203" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I203" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J203" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K203" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L203" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M203" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N203" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O203" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P203" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q203" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R203" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S203" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -9283,39 +9330,61 @@
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr"/>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="2" t="inlineStr"/>
-      <c r="M205" s="2" t="inlineStr"/>
-      <c r="N205" s="2" t="inlineStr"/>
-      <c r="O205" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O205" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P205" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q205" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R205" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S205" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9351,12 +9420,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_CHART</t>
+          <t>기타(8042)</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9392,7 +9461,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>US_TR_CHART</t>
+          <t>KR_TR_CHART</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -9433,7 +9502,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>UP_TR_CHART</t>
+          <t>US_TR_CHART</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -9474,7 +9543,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>BN_TR_CHART</t>
+          <t>UP_TR_CHART</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -9513,90 +9582,45 @@
       <c r="S215" s="2" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>0</v>
-      </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R217" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S217" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>262</v>
-      </c>
-      <c r="R218" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S218" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>BN_TR_CHART</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9611,457 +9635,429 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R219" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>262</v>
+      </c>
+      <c r="R220" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S220" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D219" t="n">
+      <c r="D221" t="n">
         <v>1</v>
       </c>
-      <c r="E219" t="n">
-        <v>0</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="n">
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="n">
         <v>0.61</v>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="n">
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="n">
         <v>0.61</v>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="n">
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="n">
         <v>21</v>
       </c>
-      <c r="M219" t="n">
+      <c r="M221" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N219" t="n">
+      <c r="N221" t="n">
         <v>-37549</v>
       </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="P219" t="n">
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q219" t="n">
+      <c r="Q221" t="n">
         <v>201</v>
       </c>
-      <c r="R219" t="n">
+      <c r="R221" t="n">
         <v>-18985</v>
       </c>
-      <c r="S219" t="n">
+      <c r="S221" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D220" s="2" t="n">
+      <c r="D222" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="n">
+      <c r="E222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="n">
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="n">
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M220" s="2" t="n">
+      <c r="M222" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N220" s="2" t="n">
+      <c r="N222" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" s="2" t="n">
+      <c r="O222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q220" s="2" t="n">
+      <c r="Q222" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R220" s="2" t="n">
+      <c r="R222" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S220" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="S222" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D222" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="n">
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="n">
         <v>3654</v>
       </c>
-      <c r="Q222" t="n">
+      <c r="Q224" t="n">
         <v>33</v>
       </c>
-      <c r="R222" t="n">
+      <c r="R224" t="n">
         <v>3687</v>
       </c>
-      <c r="S222" t="n">
+      <c r="S224" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D223" t="n">
+      <c r="D225" t="n">
         <v>1</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E225" t="n">
         <v>100</v>
       </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="n">
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="n">
         <v>10.37</v>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="n">
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="n">
         <v>10.37</v>
       </c>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="n">
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="n">
         <v>10</v>
       </c>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="n">
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="n">
         <v>10.37</v>
       </c>
-      <c r="N223" t="n">
+      <c r="N225" t="n">
         <v>13966</v>
       </c>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="n">
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="n">
         <v>10315</v>
       </c>
-      <c r="Q223" t="n">
+      <c r="Q225" t="n">
         <v>68</v>
       </c>
-      <c r="R223" t="n">
+      <c r="R225" t="n">
         <v>10383</v>
       </c>
-      <c r="S223" t="n">
+      <c r="S225" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D224" s="2" t="n">
+      <c r="D226" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="E226" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="n">
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="n">
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="n">
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="n">
+      <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="N224" s="2" t="n">
+      <c r="N226" s="2" t="n">
         <v>13966</v>
       </c>
-      <c r="O224" s="2" t="inlineStr"/>
-      <c r="P224" s="2" t="n">
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="n">
         <v>13969</v>
       </c>
-      <c r="Q224" s="2" t="n">
+      <c r="Q226" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="R224" s="2" t="n">
+      <c r="R226" s="2" t="n">
         <v>14070</v>
       </c>
-      <c r="S224" s="2" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="S226" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D226" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="n">
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="n">
         <v>127</v>
       </c>
-      <c r="Q226" t="n">
+      <c r="Q228" t="n">
         <v>105</v>
       </c>
-      <c r="R226" t="n">
+      <c r="R228" t="n">
         <v>232</v>
       </c>
-      <c r="S226" t="n">
+      <c r="S228" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D227" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="2" t="inlineStr"/>
-      <c r="J227" s="2" t="inlineStr"/>
-      <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="2" t="inlineStr"/>
-      <c r="N227" s="2" t="inlineStr"/>
-      <c r="O227" s="2" t="inlineStr"/>
-      <c r="P227" s="2" t="n">
+      <c r="D229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr"/>
+      <c r="O229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="Q227" s="2" t="n">
+      <c r="Q229" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="R227" s="2" t="n">
+      <c r="R229" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="S227" s="2" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" t="n">
-        <v>0</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="n">
-        <v>1</v>
-      </c>
-      <c r="M229" t="n">
-        <v>-1.248</v>
-      </c>
-      <c r="N229" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="O229" t="n">
-        <v>0</v>
-      </c>
-      <c r="P229" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="Q229" t="n">
-        <v>149</v>
-      </c>
-      <c r="R229" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="S229" t="n">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>2</v>
-      </c>
-      <c r="E230" t="n">
-        <v>100</v>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="n">
-        <v>5</v>
-      </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="n">
-        <v>10.223</v>
-      </c>
-      <c r="N230" t="n">
-        <v>5114</v>
-      </c>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="n">
-        <v>11272</v>
-      </c>
-      <c r="Q230" t="n">
-        <v>122</v>
-      </c>
-      <c r="R230" t="n">
-        <v>11395</v>
-      </c>
-      <c r="S230" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S229" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10076,359 +10072,375 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D231" t="n">
         <v>1</v>
       </c>
       <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="N231" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>149</v>
+      </c>
+      <c r="R231" t="n">
+        <v>-1724</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" t="n">
         <v>100</v>
       </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="n">
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="n">
+        <v>5</v>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>10.223</v>
+      </c>
+      <c r="N232" t="n">
+        <v>5114</v>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="n">
+        <v>11272</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>122</v>
+      </c>
+      <c r="R232" t="n">
+        <v>11395</v>
+      </c>
+      <c r="S232" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
+        <v>100</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
         <v>6.22</v>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="n">
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="n">
         <v>6.22</v>
       </c>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="n">
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="n">
         <v>10</v>
       </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="n">
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
         <v>6.223</v>
       </c>
-      <c r="N231" t="n">
+      <c r="N233" t="n">
         <v>3113</v>
       </c>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="n">
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="n">
         <v>2069</v>
       </c>
-      <c r="Q231" t="n">
+      <c r="Q233" t="n">
         <v>34</v>
       </c>
-      <c r="R231" t="n">
+      <c r="R233" t="n">
         <v>2103</v>
       </c>
-      <c r="S231" t="n">
+      <c r="S233" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>UP_TR_MA</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D232" s="2" t="n">
+      <c r="D234" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E232" s="2" t="n">
+      <c r="E234" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F232" s="2" t="n">
+      <c r="F234" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="G232" s="2" t="n">
+      <c r="G234" s="2" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="H232" s="2" t="n">
+      <c r="H234" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="I232" s="2" t="n">
+      <c r="I234" s="2" t="n">
         <v>16.37</v>
       </c>
-      <c r="J232" s="2" t="n">
+      <c r="J234" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="K232" s="2" t="n">
+      <c r="K234" s="2" t="n">
         <v>6.67</v>
       </c>
-      <c r="L232" s="2" t="n">
+      <c r="L234" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M232" s="2" t="n">
+      <c r="M234" s="2" t="n">
         <v>6.355</v>
       </c>
-      <c r="N232" s="2" t="n">
+      <c r="N234" s="2" t="n">
         <v>2867</v>
       </c>
-      <c r="O232" s="2" t="n">
+      <c r="O234" s="2" t="n">
         <v>7.12</v>
       </c>
-      <c r="P232" s="2" t="n">
+      <c r="P234" s="2" t="n">
         <v>11468</v>
       </c>
-      <c r="Q232" s="2" t="n">
+      <c r="Q234" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="R232" s="2" t="n">
+      <c r="R234" s="2" t="n">
         <v>11774</v>
       </c>
-      <c r="S232" s="2" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="S234" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D234" t="n">
-        <v>0</v>
-      </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="n">
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="n">
         <v>866</v>
       </c>
-      <c r="Q234" t="n">
+      <c r="Q236" t="n">
         <v>109</v>
       </c>
-      <c r="R234" t="n">
+      <c r="R236" t="n">
         <v>975</v>
       </c>
-      <c r="S234" t="n">
+      <c r="S236" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D235" t="n">
+      <c r="D237" t="n">
         <v>1</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E237" t="n">
         <v>100</v>
       </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="n">
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="n">
         <v>6.76</v>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="n">
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="n">
         <v>6.76</v>
       </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="n">
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="n">
         <v>1</v>
       </c>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="n">
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
         <v>6.755</v>
       </c>
-      <c r="N235" t="n">
+      <c r="N237" t="n">
         <v>10138</v>
       </c>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="n">
-        <v>8746</v>
-      </c>
-      <c r="Q235" t="n">
-        <v>393</v>
-      </c>
-      <c r="R235" t="n">
-        <v>9139</v>
-      </c>
-      <c r="S235" t="n">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="n">
+        <v>8469</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>408</v>
+      </c>
+      <c r="R237" t="n">
+        <v>8877</v>
+      </c>
+      <c r="S237" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D236" s="2" t="n">
+      <c r="D238" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E236" s="2" t="n">
+      <c r="E238" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" s="2" t="n">
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="n">
         <v>6.76</v>
       </c>
-      <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="n">
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="n">
         <v>6.76</v>
       </c>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="n">
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="2" t="n">
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="n">
         <v>6.755</v>
       </c>
-      <c r="N236" s="2" t="n">
+      <c r="N238" s="2" t="n">
         <v>10138</v>
       </c>
-      <c r="O236" s="2" t="inlineStr"/>
-      <c r="P236" s="2" t="n">
-        <v>9612</v>
-      </c>
-      <c r="Q236" s="2" t="n">
-        <v>502</v>
-      </c>
-      <c r="R236" s="2" t="n">
-        <v>10114</v>
-      </c>
-      <c r="S236" s="2" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>09/14~09/18</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>0</v>
-      </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="n">
-        <v>54396</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>238</v>
-      </c>
-      <c r="R238" t="n">
-        <v>54634</v>
-      </c>
-      <c r="S238" t="n">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>1</v>
-      </c>
-      <c r="E239" t="n">
-        <v>100</v>
-      </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="n">
-        <v>6</v>
-      </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="n">
-        <v>29.576</v>
-      </c>
-      <c r="N239" t="n">
-        <v>88772</v>
-      </c>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="n">
-        <v>34376</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>106</v>
-      </c>
-      <c r="R239" t="n">
-        <v>34482</v>
-      </c>
-      <c r="S239" t="n">
-        <v>1353</v>
-      </c>
+      <c r="O238" s="2" t="inlineStr"/>
+      <c r="P238" s="2" t="n">
+        <v>9335</v>
+      </c>
+      <c r="Q238" s="2" t="n">
+        <v>517</v>
+      </c>
+      <c r="R238" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="S238" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10443,56 +10455,34 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/14~09/18</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
-      </c>
-      <c r="E240" t="n">
-        <v>50</v>
-      </c>
-      <c r="F240" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="G240" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H240" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I240" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J240" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K240" t="n">
-        <v>1</v>
-      </c>
-      <c r="L240" t="n">
-        <v>10</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="N240" t="n">
-        <v>3295</v>
-      </c>
-      <c r="O240" t="n">
-        <v>36.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
       <c r="P240" t="n">
-        <v>6589</v>
+        <v>54396</v>
       </c>
       <c r="Q240" t="n">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="R240" t="n">
-        <v>6907</v>
+        <v>54634</v>
       </c>
       <c r="S240" t="n">
-        <v>1352</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="241">
@@ -10508,446 +10498,566 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
-      </c>
-      <c r="E241" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>100</v>
+      </c>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>29.58</v>
+      </c>
       <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="n">
+        <v>29.58</v>
+      </c>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="n">
+        <v>6</v>
+      </c>
       <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>29.576</v>
+      </c>
+      <c r="N241" t="n">
+        <v>88772</v>
+      </c>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
+        <v>34376</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>106</v>
+      </c>
+      <c r="R241" t="n">
+        <v>34482</v>
+      </c>
+      <c r="S241" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>2</v>
+      </c>
+      <c r="E242" t="n">
+        <v>50</v>
+      </c>
+      <c r="F242" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I242" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>10</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N242" t="n">
+        <v>3295</v>
+      </c>
+      <c r="O242" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P242" t="n">
+        <v>6589</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>318</v>
+      </c>
+      <c r="R242" t="n">
+        <v>6907</v>
+      </c>
+      <c r="S242" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="n">
         <v>-1605</v>
       </c>
-      <c r="Q241" t="n">
+      <c r="Q243" t="n">
         <v>49</v>
       </c>
-      <c r="R241" t="n">
+      <c r="R243" t="n">
         <v>-1556</v>
       </c>
-      <c r="S241" t="n">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+      <c r="S243" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D242" s="2" t="n">
+      <c r="D244" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E242" s="2" t="n">
+      <c r="E244" s="2" t="n">
         <v>66.7</v>
       </c>
-      <c r="F242" s="2" t="n">
+      <c r="F244" s="2" t="n">
         <v>260.57</v>
       </c>
-      <c r="G242" s="2" t="n">
+      <c r="G244" s="2" t="n">
         <v>15.92</v>
       </c>
-      <c r="H242" s="2" t="n">
+      <c r="H244" s="2" t="n">
         <v>1.26</v>
       </c>
-      <c r="I242" s="2" t="n">
+      <c r="I244" s="2" t="n">
         <v>29.58</v>
       </c>
-      <c r="J242" s="2" t="n">
+      <c r="J244" s="2" t="n">
         <v>1.26</v>
       </c>
-      <c r="K242" s="2" t="n">
+      <c r="K244" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="L242" s="2" t="n">
+      <c r="L244" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M242" s="2" t="n">
+      <c r="M244" s="2" t="n">
         <v>10.191</v>
       </c>
-      <c r="N242" s="2" t="n">
+      <c r="N244" s="2" t="n">
         <v>31787</v>
       </c>
-      <c r="O242" s="2" t="n">
+      <c r="O244" s="2" t="n">
         <v>521.13</v>
       </c>
-      <c r="P242" s="2" t="n">
+      <c r="P244" s="2" t="n">
         <v>93756</v>
       </c>
-      <c r="Q242" s="2" t="n">
+      <c r="Q244" s="2" t="n">
         <v>711</v>
       </c>
-      <c r="R242" s="2" t="n">
+      <c r="R244" s="2" t="n">
         <v>94467</v>
       </c>
-      <c r="S242" s="2" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="S244" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D244" t="n">
+      <c r="D246" t="n">
         <v>1</v>
       </c>
-      <c r="E244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="n">
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="n">
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="n">
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="n">
         <v>3</v>
       </c>
-      <c r="M244" t="n">
+      <c r="M246" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N244" t="n">
+      <c r="N246" t="n">
         <v>-74087</v>
       </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q244" t="n">
+      <c r="Q246" t="n">
         <v>257</v>
       </c>
-      <c r="R244" t="n">
+      <c r="R246" t="n">
         <v>-73830</v>
       </c>
-      <c r="S244" t="n">
+      <c r="S246" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D245" s="2" t="n">
+      <c r="D247" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F245" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="n">
+      <c r="E247" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I245" s="2" t="inlineStr"/>
-      <c r="J245" s="2" t="n">
+      <c r="I247" s="2" t="inlineStr"/>
+      <c r="J247" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="n">
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M245" s="2" t="n">
+      <c r="M247" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N245" s="2" t="n">
+      <c r="N247" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O245" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P245" s="2" t="n">
+      <c r="O247" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q245" s="2" t="n">
+      <c r="Q247" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R245" s="2" t="n">
+      <c r="R247" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S245" s="2" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="S247" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D247" t="n">
+      <c r="D249" t="n">
         <v>1</v>
       </c>
-      <c r="E247" t="n">
-        <v>0</v>
-      </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="n">
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
         <v>4.6</v>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="n">
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="n">
         <v>4.6</v>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="n">
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="n">
         <v>3</v>
       </c>
-      <c r="M247" t="n">
+      <c r="M249" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N247" t="n">
+      <c r="N249" t="n">
         <v>-29689</v>
       </c>
-      <c r="O247" t="n">
-        <v>0</v>
-      </c>
-      <c r="P247" t="n">
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q247" t="n">
+      <c r="Q249" t="n">
         <v>189</v>
       </c>
-      <c r="R247" t="n">
+      <c r="R249" t="n">
         <v>-29500</v>
       </c>
-      <c r="S247" t="n">
+      <c r="S249" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D248" s="2" t="n">
+      <c r="D250" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E248" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F248" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="n">
+      <c r="E250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I248" s="2" t="inlineStr"/>
-      <c r="J248" s="2" t="n">
+      <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K248" s="2" t="inlineStr"/>
-      <c r="L248" s="2" t="n">
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M248" s="2" t="n">
+      <c r="M250" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N248" s="2" t="n">
+      <c r="N250" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O248" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P248" s="2" t="n">
+      <c r="O250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q248" s="2" t="n">
+      <c r="Q250" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R248" s="2" t="n">
+      <c r="R250" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S248" s="2" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="S250" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D250" t="n">
+      <c r="D252" t="n">
         <v>1</v>
       </c>
-      <c r="E250" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="n">
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="n">
         <v>0.87</v>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="n">
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="n">
         <v>0.87</v>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="n">
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="n">
         <v>3</v>
       </c>
-      <c r="M250" t="n">
+      <c r="M252" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N250" t="n">
+      <c r="N252" t="n">
         <v>-29188</v>
       </c>
-      <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="P250" t="n">
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q250" t="n">
+      <c r="Q252" t="n">
         <v>2950</v>
       </c>
-      <c r="R250" t="n">
+      <c r="R252" t="n">
         <v>-26238</v>
       </c>
-      <c r="S250" t="n">
+      <c r="S252" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D251" s="2" t="n">
+      <c r="D253" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E251" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="n">
+      <c r="E253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I251" s="2" t="inlineStr"/>
-      <c r="J251" s="2" t="n">
+      <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K251" s="2" t="inlineStr"/>
-      <c r="L251" s="2" t="n">
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M251" s="2" t="n">
+      <c r="M253" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N251" s="2" t="n">
+      <c r="N253" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O251" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P251" s="2" t="n">
+      <c r="O253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q251" s="2" t="n">
+      <c r="Q253" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R251" s="2" t="n">
+      <c r="R253" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S251" s="2" t="inlineStr"/>
+      <c r="S253" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S253"/>
+  <dimension ref="A1:S259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1597,48 +1597,48 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>52.4</v>
+        <v>48.1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="G19" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>3.03</v>
+        <v>3.24</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
       </c>
       <c r="J19" t="n">
-        <v>5.68</v>
+        <v>6.02</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>0.021</v>
+        <v>-0.477</v>
       </c>
       <c r="N19" t="n">
-        <v>-1966</v>
+        <v>-3799</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="P19" t="n">
-        <v>-15578</v>
+        <v>-56592</v>
       </c>
       <c r="Q19" t="n">
-        <v>10813</v>
+        <v>17238</v>
       </c>
       <c r="R19" t="n">
-        <v>-4764</v>
+        <v>-39355</v>
       </c>
       <c r="S19" t="n">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.313</v>
+        <v>0.273</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1127</v>
+        <v>945</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>432169</v>
+        <v>391155</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>123357</v>
+        <v>129782</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>555528</v>
+        <v>520937</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5483,52 +5483,46 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0.91</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2.47</v>
       </c>
-      <c r="I115" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
         <v>4.39</v>
       </c>
-      <c r="K115" t="n">
-        <v>14</v>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>13</v>
       </c>
       <c r="M115" t="n">
-        <v>-1.345</v>
+        <v>-2.474</v>
       </c>
       <c r="N115" t="n">
-        <v>-13887</v>
+        <v>-25860</v>
       </c>
       <c r="O115" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>4838</v>
+        <v>4834</v>
       </c>
       <c r="Q115" t="n">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="R115" t="n">
-        <v>7578</v>
+        <v>7572</v>
       </c>
       <c r="S115" t="n">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="116">
@@ -5548,16 +5542,16 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>38.7</v>
+        <v>36.7</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>3.5</v>
@@ -5569,28 +5563,28 @@
         <v>10.01</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>14.5</v>
+        <v>14.55</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>10.05</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>-0.925</v>
+        <v>-0.987</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-13878</v>
+        <v>-14676</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-386700</v>
+        <v>-386704</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>41594</v>
+        <v>41592</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-345106</v>
+        <v>-345112</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5611,52 +5605,52 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E118" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>3.84</v>
+        <v>1.53</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="H118" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="I118" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
       <c r="J118" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="L118" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="M118" t="n">
-        <v>1.335</v>
+        <v>1.024</v>
       </c>
       <c r="N118" t="n">
-        <v>4452</v>
+        <v>2801</v>
       </c>
       <c r="O118" t="n">
-        <v>5.12</v>
+        <v>2.29</v>
       </c>
       <c r="P118" t="n">
-        <v>31154</v>
+        <v>16701</v>
       </c>
       <c r="Q118" t="n">
-        <v>3734</v>
+        <v>6966</v>
       </c>
       <c r="R118" t="n">
-        <v>34888</v>
+        <v>23667</v>
       </c>
       <c r="S118" t="n">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="119">
@@ -5676,49 +5670,49 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>3.84</v>
+        <v>1.53</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1.335</v>
+        <v>1.024</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>4452</v>
+        <v>2801</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>5.12</v>
+        <v>2.29</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>31154</v>
+        <v>16701</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>3734</v>
+        <v>6966</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>34888</v>
+        <v>23667</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5753,16 +5747,16 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>6856</v>
+        <v>16702</v>
       </c>
       <c r="Q121" t="n">
-        <v>185</v>
+        <v>552</v>
       </c>
       <c r="R121" t="n">
-        <v>7041</v>
+        <v>17254</v>
       </c>
       <c r="S121" t="n">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="122">
@@ -5796,313 +5790,297 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="n">
-        <v>6856</v>
+        <v>16702</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>185</v>
+        <v>552</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>7041</v>
+        <v>17254</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>US_TR_PURPLE_B</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>-2365</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>187</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-2178</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_PURPLE_B</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
-      <c r="P124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="D125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="n">
+        <v>-2365</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>-2178</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
-      <c r="P128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="D129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
         <v>7.47</v>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="n">
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
         <v>7.47</v>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="n">
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
         <v>6</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M131" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N131" t="n">
         <v>-62673</v>
       </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q131" t="n">
         <v>1736</v>
       </c>
-      <c r="R130" t="n">
+      <c r="R131" t="n">
         <v>-82310</v>
       </c>
-      <c r="S130" t="n">
+      <c r="S131" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="n">
+      <c r="E132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="n">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="n">
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M131" s="2" t="n">
+      <c r="M132" s="2" t="n">
         <v>-7.472</v>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N132" s="2" t="n">
         <v>-62673</v>
       </c>
-      <c r="O131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="2" t="n">
+      <c r="O132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="2" t="n">
         <v>-84046</v>
       </c>
-      <c r="Q131" s="2" t="n">
+      <c r="Q132" s="2" t="n">
         <v>1736</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R132" s="2" t="n">
         <v>-82310</v>
       </c>
-      <c r="S131" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>US_TR_BASE</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M133" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="N133" t="n">
-        <v>-5227</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>-5525</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>776</v>
-      </c>
-      <c r="R133" t="n">
-        <v>-4749</v>
-      </c>
-      <c r="S133" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S132" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6117,169 +6095,179 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>100</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-5227</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-5525</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>776</v>
+      </c>
+      <c r="R134" t="n">
+        <v>-4749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>50</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G135" t="n">
         <v>0.33</v>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="n">
+      <c r="H135" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="I135" t="n">
         <v>0.33</v>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="n">
+      <c r="J135" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K135" t="n">
         <v>14</v>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>1507</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>110</v>
-      </c>
-      <c r="R134" t="n">
-        <v>1616</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-2.845</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-12600</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-24901</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>705</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-24195</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G135" s="2" t="n">
+      <c r="D136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G136" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="H135" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I135" s="2" t="n">
+      <c r="H136" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I136" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="J135" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K135" s="2" t="n">
+      <c r="J136" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K136" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>-0.487</v>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>-2010</v>
-      </c>
-      <c r="O135" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P135" s="2" t="n">
-        <v>-4018</v>
-      </c>
-      <c r="Q135" s="2" t="n">
-        <v>886</v>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>-3133</v>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="n">
-        <v>1</v>
-      </c>
-      <c r="M137" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N137" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R137" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S137" t="n">
-        <v>1373</v>
-      </c>
+      <c r="L136" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>-10142</v>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>-30426</v>
+      </c>
+      <c r="Q136" s="2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>-28944</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6294,11 +6282,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -6308,36 +6296,36 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>3.23</v>
+        <v>2.13</v>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
-        <v>5.33</v>
+        <v>2.13</v>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-3.235</v>
+        <v>-2.131</v>
       </c>
       <c r="N138" t="n">
-        <v>-12511</v>
+        <v>-41586</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-50045</v>
+        <v>-41586</v>
       </c>
       <c r="Q138" t="n">
-        <v>2266</v>
+        <v>2702</v>
       </c>
       <c r="R138" t="n">
-        <v>-47780</v>
+        <v>-38883</v>
       </c>
       <c r="S138" t="n">
-        <v>1352</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="139">
@@ -6353,11 +6341,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -6367,153 +6355,165 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>1.96</v>
+        <v>3.23</v>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
-        <v>1.96</v>
+        <v>5.33</v>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
+        <v>7</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-3.235</v>
+      </c>
+      <c r="N139" t="n">
+        <v>-12511</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-50045</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2266</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-47780</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
         <v>3</v>
       </c>
-      <c r="M139" t="n">
-        <v>-1.956</v>
-      </c>
-      <c r="N139" t="n">
-        <v>-9807</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>-9807</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>695</v>
-      </c>
-      <c r="R139" t="n">
-        <v>-9112</v>
-      </c>
-      <c r="S139" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="M140" t="n">
+        <v>-0.911</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-4678</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P140" t="n">
+        <v>-9356</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1159</v>
+      </c>
+      <c r="R140" t="n">
+        <v>-8196</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="n">
+      <c r="D141" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H141" s="2" t="n">
         <v>2.84</v>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="n">
+      <c r="I141" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J141" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="n">
+      <c r="K141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="M140" s="2" t="n">
-        <v>-2.838</v>
-      </c>
-      <c r="N140" s="2" t="n">
-        <v>-16906</v>
-      </c>
-      <c r="O140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" s="2" t="n">
-        <v>-101438</v>
-      </c>
-      <c r="Q140" s="2" t="n">
-        <v>5663</v>
-      </c>
-      <c r="R140" s="2" t="n">
-        <v>-95775</v>
-      </c>
-      <c r="S140" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>7</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="n">
-        <v>8</v>
-      </c>
-      <c r="M142" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N142" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R142" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S142" t="n">
-        <v>1373</v>
-      </c>
+      <c r="M141" s="2" t="n">
+        <v>-2.413</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>-14427</v>
+      </c>
+      <c r="O141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>-100987</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>6127</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>-94859</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6528,56 +6528,50 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E143" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G143" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I143" t="n">
-        <v>3.32</v>
-      </c>
+        <v>3.34</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K143" t="n">
-        <v>18</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M143" t="n">
-        <v>0.864</v>
+        <v>-3.337</v>
       </c>
       <c r="N143" t="n">
-        <v>-18508</v>
+        <v>-7859</v>
       </c>
       <c r="O143" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>-52375</v>
+        <v>-55013</v>
       </c>
       <c r="Q143" t="n">
-        <v>4226</v>
+        <v>1884</v>
       </c>
       <c r="R143" t="n">
-        <v>-48149</v>
+        <v>-53128</v>
       </c>
       <c r="S143" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="144">
@@ -6593,50 +6587,56 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H144" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I144" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="I144" t="n">
+        <v>3.32</v>
+      </c>
       <c r="J144" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K144" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="K144" t="n">
+        <v>18</v>
+      </c>
       <c r="L144" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>-1.87</v>
+        <v>0.864</v>
       </c>
       <c r="N144" t="n">
-        <v>-38258</v>
+        <v>-18508</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P144" t="n">
-        <v>-79635</v>
+        <v>-52375</v>
       </c>
       <c r="Q144" t="n">
-        <v>4778</v>
+        <v>4226</v>
       </c>
       <c r="R144" t="n">
-        <v>-74857</v>
+        <v>-48149</v>
       </c>
       <c r="S144" t="n">
-        <v>1369</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="145">
@@ -6652,464 +6652,462 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-38258</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>-79635</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>4778</v>
+      </c>
+      <c r="R145" t="n">
+        <v>-74857</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D145" t="n">
+      <c r="D146" t="n">
         <v>3</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E146" t="n">
         <v>66.7</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F146" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G146" t="n">
         <v>0.47</v>
       </c>
-      <c r="H145" t="n">
+      <c r="H146" t="n">
         <v>6.05</v>
       </c>
-      <c r="I145" t="n">
+      <c r="I146" t="n">
         <v>0.51</v>
       </c>
-      <c r="J145" t="n">
+      <c r="J146" t="n">
         <v>6.05</v>
       </c>
-      <c r="K145" t="n">
+      <c r="K146" t="n">
         <v>1</v>
       </c>
-      <c r="L145" t="n">
+      <c r="L146" t="n">
         <v>1</v>
       </c>
-      <c r="M145" t="n">
+      <c r="M146" t="n">
         <v>-1.701</v>
       </c>
-      <c r="N145" t="n">
+      <c r="N146" t="n">
         <v>-9977</v>
       </c>
-      <c r="O145" t="n">
+      <c r="O146" t="n">
         <v>0.13</v>
       </c>
-      <c r="P145" t="n">
+      <c r="P146" t="n">
         <v>-29930</v>
       </c>
-      <c r="Q145" t="n">
+      <c r="Q146" t="n">
         <v>2167</v>
       </c>
-      <c r="R145" t="n">
+      <c r="R146" t="n">
         <v>-27764</v>
       </c>
-      <c r="S145" t="n">
+      <c r="S146" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>5</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-2.222</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-20840</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>-20840</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1299</v>
+      </c>
+      <c r="R147" t="n">
+        <v>-19541</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D146" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F146" s="2" t="n">
+      <c r="D148" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F148" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G146" s="2" t="n">
+      <c r="G148" s="2" t="n">
         <v>1.68</v>
       </c>
-      <c r="H146" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
+      <c r="H148" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I148" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="J148" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K146" s="2" t="n">
+      <c r="K148" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="L146" s="2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M146" s="2" t="n">
-        <v>-1.974</v>
-      </c>
-      <c r="N146" s="2" t="n">
-        <v>-14466</v>
-      </c>
-      <c r="O146" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P146" s="2" t="n">
-        <v>-216953</v>
-      </c>
-      <c r="Q146" s="2" t="n">
-        <v>13055</v>
-      </c>
-      <c r="R146" s="2" t="n">
-        <v>-203898</v>
-      </c>
-      <c r="S146" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="L148" s="2" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1.989</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-14864</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>-237793</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>14354</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>-223439</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D148" t="n">
+      <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E150" t="n">
         <v>100</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
         <v>8.9</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="n">
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="n">
         <v>8.9</v>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="n">
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
         <v>5</v>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="n">
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
         <v>8.897</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N150" t="n">
         <v>21615</v>
       </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="n">
         <v>21615</v>
       </c>
-      <c r="Q148" t="n">
+      <c r="Q150" t="n">
         <v>355</v>
       </c>
-      <c r="R148" t="n">
+      <c r="R150" t="n">
         <v>21970</v>
       </c>
-      <c r="S148" t="n">
+      <c r="S150" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D151" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E151" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="n">
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="n">
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="2" t="n">
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="2" t="n">
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="n">
         <v>8.897</v>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N151" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="O149" s="2" t="inlineStr"/>
-      <c r="P149" s="2" t="n">
+      <c r="O151" s="2" t="inlineStr"/>
+      <c r="P151" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="Q149" s="2" t="n">
+      <c r="Q151" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="R149" s="2" t="n">
+      <c r="R151" s="2" t="n">
         <v>21970</v>
       </c>
-      <c r="S149" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="S151" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D151" t="n">
+      <c r="D153" t="n">
         <v>2</v>
       </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="n">
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="n">
         <v>7.15</v>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="n">
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="n">
         <v>10.49</v>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="n">
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="n">
         <v>1</v>
       </c>
-      <c r="M151" t="n">
+      <c r="M153" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N151" t="n">
+      <c r="N153" t="n">
         <v>-27445</v>
       </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q151" t="n">
+      <c r="Q153" t="n">
         <v>1054</v>
       </c>
-      <c r="R151" t="n">
+      <c r="R153" t="n">
         <v>-53835</v>
       </c>
-      <c r="S151" t="n">
+      <c r="S153" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n">
+      <c r="D154" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="n">
+      <c r="E154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="n">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="n">
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M152" s="2" t="n">
+      <c r="M154" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N152" s="2" t="n">
+      <c r="N154" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" s="2" t="n">
+      <c r="O154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q152" s="2" t="n">
+      <c r="Q154" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R152" s="2" t="n">
+      <c r="R154" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S152" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>17</v>
-      </c>
-      <c r="E154" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G154" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H154" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I154" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J154" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M154" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N154" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O154" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P154" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R154" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S154" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>7</v>
-      </c>
-      <c r="E155" t="n">
-        <v>100</v>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N155" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R155" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S155" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S154" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7124,241 +7122,304 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>17</v>
+      </c>
+      <c r="E156" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G156" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I156" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J156" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N156" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O156" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P156" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R156" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>7</v>
+      </c>
+      <c r="E157" t="n">
+        <v>100</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N157" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R157" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D158" t="n">
         <v>4</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E158" t="n">
         <v>50</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F158" t="n">
         <v>2.51</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G158" t="n">
         <v>11.43</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H158" t="n">
         <v>2.87</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I158" t="n">
         <v>12</v>
       </c>
-      <c r="J156" t="n">
+      <c r="J158" t="n">
         <v>4.94</v>
       </c>
-      <c r="K156" t="n">
+      <c r="K158" t="n">
         <v>14</v>
       </c>
-      <c r="L156" t="n">
+      <c r="L158" t="n">
         <v>14</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M158" t="n">
         <v>4.282</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N158" t="n">
         <v>7910</v>
       </c>
-      <c r="O156" t="n">
+      <c r="O158" t="n">
         <v>2.51</v>
       </c>
-      <c r="P156" t="n">
+      <c r="P158" t="n">
         <v>-912</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="Q158" t="n">
         <v>635</v>
       </c>
-      <c r="R156" t="n">
+      <c r="R158" t="n">
         <v>-278</v>
       </c>
-      <c r="S156" t="n">
+      <c r="S158" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D159" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E159" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F157" s="2" t="n">
+      <c r="F159" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G157" s="2" t="n">
+      <c r="G159" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H159" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I157" s="2" t="n">
+      <c r="I159" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J159" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K157" s="2" t="n">
+      <c r="K159" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L157" s="2" t="n">
+      <c r="L159" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M157" s="2" t="n">
+      <c r="M159" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N159" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O157" s="2" t="n">
+      <c r="O159" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P157" s="2" t="n">
+      <c r="P159" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q157" s="2" t="n">
+      <c r="Q159" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R157" s="2" t="n">
+      <c r="R159" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S157" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="S159" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D159" t="n">
+      <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="n">
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="n">
         <v>0.54</v>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="n">
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="n">
         <v>0.54</v>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="n">
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="n">
         <v>12</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M161" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N161" t="n">
         <v>-1280</v>
       </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q159" t="n">
+      <c r="Q161" t="n">
         <v>208</v>
       </c>
-      <c r="R159" t="n">
+      <c r="R161" t="n">
         <v>-1072</v>
       </c>
-      <c r="S159" t="n">
+      <c r="S161" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M160" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N160" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q160" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R160" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S160" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7372,34 +7433,50 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="2" t="inlineStr"/>
-      <c r="F162" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O162" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P162" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q162" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R162" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S162" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -7438,232 +7515,153 @@
       <c r="S164" s="2" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D166" t="n">
+      <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E168" t="n">
         <v>100</v>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="n">
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="n">
         <v>2.1</v>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="n">
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="n">
         <v>2.1</v>
       </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="n">
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="n">
         <v>52.73</v>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="n">
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
         <v>2.102</v>
       </c>
-      <c r="N166" t="n">
+      <c r="N168" t="n">
         <v>2341</v>
       </c>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="n">
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
         <v>2341</v>
       </c>
-      <c r="Q166" t="n">
+      <c r="Q168" t="n">
         <v>34</v>
       </c>
-      <c r="R166" t="n">
+      <c r="R168" t="n">
         <v>2375</v>
       </c>
-      <c r="S166" t="n">
+      <c r="S168" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E169" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="n">
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="n">
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="n">
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N169" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O167" s="2" t="inlineStr"/>
-      <c r="P167" s="2" t="n">
+      <c r="O169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q167" s="2" t="n">
+      <c r="Q169" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R167" s="2" t="n">
+      <c r="R169" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S167" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" t="n">
-        <v>100</v>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="n">
-        <v>2.876</v>
-      </c>
-      <c r="N169" t="n">
-        <v>4316</v>
-      </c>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="n">
-        <v>13859</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>327</v>
-      </c>
-      <c r="R169" t="n">
-        <v>14186</v>
-      </c>
-      <c r="S169" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>6</v>
-      </c>
-      <c r="E170" t="n">
-        <v>50</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G170" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="H170" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I170" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="J170" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K170" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="n">
-        <v>2.895</v>
-      </c>
-      <c r="N170" t="n">
-        <v>2294</v>
-      </c>
-      <c r="O170" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P170" t="n">
-        <v>23105</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>1932</v>
-      </c>
-      <c r="R170" t="n">
-        <v>25037</v>
-      </c>
-      <c r="S170" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S169" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7678,421 +7676,433 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>50</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H171" t="n">
-        <v>4.98</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="J171" t="n">
-        <v>5.27</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
         <v>1</v>
       </c>
-      <c r="L171" t="n">
-        <v>0</v>
-      </c>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="n">
+        <v>2.876</v>
+      </c>
+      <c r="N171" t="n">
+        <v>4316</v>
+      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>13859</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>327</v>
+      </c>
+      <c r="R171" t="n">
+        <v>14186</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>6</v>
+      </c>
+      <c r="E172" t="n">
+        <v>50</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G172" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="H172" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I172" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="J172" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2294</v>
+      </c>
+      <c r="O172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P172" t="n">
+        <v>23105</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>1932</v>
+      </c>
+      <c r="R172" t="n">
+        <v>25037</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>4</v>
+      </c>
+      <c r="E173" t="n">
+        <v>50</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H173" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I173" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J173" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
         <v>-1.005</v>
       </c>
-      <c r="N171" t="n">
+      <c r="N173" t="n">
         <v>-4017</v>
       </c>
-      <c r="O171" t="n">
+      <c r="O173" t="n">
         <v>0.6</v>
       </c>
-      <c r="P171" t="n">
-        <v>-35570</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>2115</v>
-      </c>
-      <c r="R171" t="n">
-        <v>-33455</v>
-      </c>
-      <c r="S171" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="P173" t="n">
+        <v>-34883</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>2123</v>
+      </c>
+      <c r="R173" t="n">
+        <v>-32760</v>
+      </c>
+      <c r="S173" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-Top3</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D174" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E174" s="2" t="n">
         <v>54.5</v>
       </c>
-      <c r="F172" s="2" t="n">
+      <c r="F174" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="G172" s="2" t="n">
+      <c r="G174" s="2" t="n">
         <v>6.81</v>
       </c>
-      <c r="H172" s="2" t="n">
+      <c r="H174" s="2" t="n">
         <v>4.93</v>
       </c>
-      <c r="I172" s="2" t="n">
+      <c r="I174" s="2" t="n">
         <v>17.63</v>
       </c>
-      <c r="J172" s="2" t="n">
+      <c r="J174" s="2" t="n">
         <v>5.38</v>
       </c>
-      <c r="K172" s="2" t="n">
+      <c r="K174" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L172" s="2" t="n">
+      <c r="L174" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M172" s="2" t="n">
+      <c r="M174" s="2" t="n">
         <v>1.475</v>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N174" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="O172" s="2" t="n">
+      <c r="O174" s="2" t="n">
         <v>1.02</v>
       </c>
-      <c r="P172" s="2" t="n">
-        <v>1394</v>
-      </c>
-      <c r="Q172" s="2" t="n">
-        <v>4374</v>
-      </c>
-      <c r="R172" s="2" t="n">
-        <v>5768</v>
-      </c>
-      <c r="S172" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="P174" s="2" t="n">
+        <v>2081</v>
+      </c>
+      <c r="Q174" s="2" t="n">
+        <v>4382</v>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>6463</v>
+      </c>
+      <c r="S174" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D174" t="n">
+      <c r="D176" t="n">
         <v>11</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E176" t="n">
         <v>36.4</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F176" t="n">
         <v>3.92</v>
       </c>
-      <c r="G174" t="n">
+      <c r="G176" t="n">
         <v>3.1</v>
       </c>
-      <c r="H174" t="n">
+      <c r="H176" t="n">
         <v>0.79</v>
       </c>
-      <c r="I174" t="n">
+      <c r="I176" t="n">
         <v>6.36</v>
       </c>
-      <c r="J174" t="n">
+      <c r="J176" t="n">
         <v>1.95</v>
       </c>
-      <c r="K174" t="n">
+      <c r="K176" t="n">
         <v>753.65</v>
       </c>
-      <c r="L174" t="n">
+      <c r="L176" t="n">
         <v>197.67</v>
       </c>
-      <c r="M174" t="n">
+      <c r="M176" t="n">
         <v>0.625</v>
       </c>
-      <c r="N174" t="n">
+      <c r="N176" t="n">
         <v>1249</v>
       </c>
-      <c r="O174" t="n">
+      <c r="O176" t="n">
         <v>2.24</v>
       </c>
-      <c r="P174" t="n">
+      <c r="P176" t="n">
         <v>13742</v>
       </c>
-      <c r="Q174" t="n">
+      <c r="Q176" t="n">
         <v>2208</v>
       </c>
-      <c r="R174" t="n">
+      <c r="R176" t="n">
         <v>15950</v>
       </c>
-      <c r="S174" t="n">
+      <c r="S176" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D177" t="n">
         <v>22</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E177" t="n">
         <v>27.3</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F177" t="n">
         <v>2.05</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G177" t="n">
         <v>1.89</v>
       </c>
-      <c r="H175" t="n">
+      <c r="H177" t="n">
         <v>0.92</v>
       </c>
-      <c r="I175" t="n">
+      <c r="I177" t="n">
         <v>6.1</v>
       </c>
-      <c r="J175" t="n">
+      <c r="J177" t="n">
         <v>2.94</v>
       </c>
-      <c r="K175" t="n">
+      <c r="K177" t="n">
         <v>208.19</v>
       </c>
-      <c r="L175" t="n">
+      <c r="L177" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M177" t="n">
         <v>-0.155</v>
       </c>
-      <c r="N175" t="n">
+      <c r="N177" t="n">
         <v>-311</v>
       </c>
-      <c r="O175" t="n">
+      <c r="O177" t="n">
         <v>0.77</v>
       </c>
-      <c r="P175" t="n">
+      <c r="P177" t="n">
         <v>-6837</v>
       </c>
-      <c r="Q175" t="n">
+      <c r="Q177" t="n">
         <v>4398</v>
       </c>
-      <c r="R175" t="n">
+      <c r="R177" t="n">
         <v>-2439</v>
       </c>
-      <c r="S175" t="n">
+      <c r="S177" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D178" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E178" s="2" t="n">
         <v>30.3</v>
       </c>
-      <c r="F176" s="2" t="n">
+      <c r="F178" s="2" t="n">
         <v>2.69</v>
       </c>
-      <c r="G176" s="2" t="n">
+      <c r="G178" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="H176" s="2" t="n">
+      <c r="H178" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="I176" s="2" t="n">
+      <c r="I178" s="2" t="n">
         <v>6.36</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J178" s="2" t="n">
         <v>2.94</v>
       </c>
-      <c r="K176" s="2" t="n">
+      <c r="K178" s="2" t="n">
         <v>426.38</v>
       </c>
-      <c r="L176" s="2" t="n">
+      <c r="L178" s="2" t="n">
         <v>129.08</v>
       </c>
-      <c r="M176" s="2" t="n">
+      <c r="M178" s="2" t="n">
         <v>0.105</v>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N178" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="O176" s="2" t="n">
+      <c r="O178" s="2" t="n">
         <v>1.17</v>
       </c>
-      <c r="P176" s="2" t="n">
+      <c r="P178" s="2" t="n">
         <v>6905</v>
       </c>
-      <c r="Q176" s="2" t="n">
+      <c r="Q178" s="2" t="n">
         <v>6606</v>
       </c>
-      <c r="R176" s="2" t="n">
+      <c r="R178" s="2" t="n">
         <v>13511</v>
       </c>
-      <c r="S176" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>61</v>
-      </c>
-      <c r="R178" t="n">
-        <v>973</v>
-      </c>
-      <c r="S178" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>6</v>
-      </c>
-      <c r="E179" t="n">
-        <v>50</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G179" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H179" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I179" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J179" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="N179" t="n">
-        <v>1885</v>
-      </c>
-      <c r="O179" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P179" t="n">
-        <v>18124</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>1048</v>
-      </c>
-      <c r="R179" t="n">
-        <v>19173</v>
-      </c>
-      <c r="S179" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S178" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8107,285 +8117,269 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>61</v>
+      </c>
+      <c r="R180" t="n">
+        <v>973</v>
+      </c>
+      <c r="S180" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>6</v>
+      </c>
+      <c r="E181" t="n">
+        <v>50</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G181" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="H181" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I181" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J181" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P181" t="n">
+        <v>18124</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1048</v>
+      </c>
+      <c r="R181" t="n">
+        <v>19173</v>
+      </c>
+      <c r="S181" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D180" t="n">
+      <c r="D182" t="n">
         <v>4</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E182" t="n">
         <v>50</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F182" t="n">
         <v>0.45</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G182" t="n">
         <v>2.49</v>
       </c>
-      <c r="H180" t="n">
+      <c r="H182" t="n">
         <v>5.48</v>
       </c>
-      <c r="I180" t="n">
+      <c r="I182" t="n">
         <v>2.87</v>
       </c>
-      <c r="J180" t="n">
+      <c r="J182" t="n">
         <v>5.68</v>
       </c>
-      <c r="K180" t="n">
+      <c r="K182" t="n">
         <v>1</v>
       </c>
-      <c r="L180" t="n">
+      <c r="L182" t="n">
         <v>0.5</v>
       </c>
-      <c r="M180" t="n">
+      <c r="M182" t="n">
         <v>-1.493</v>
       </c>
-      <c r="N180" t="n">
-        <v>-4062</v>
-      </c>
-      <c r="O180" t="n">
+      <c r="N182" t="n">
+        <v>-4059</v>
+      </c>
+      <c r="O182" t="n">
         <v>0.45</v>
       </c>
-      <c r="P180" t="n">
-        <v>-21419</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>778</v>
-      </c>
-      <c r="R180" t="n">
-        <v>-20641</v>
-      </c>
-      <c r="S180" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E181" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F181" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G181" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H181" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="I181" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K181" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M181" s="2" t="n">
-        <v>-0.418</v>
-      </c>
-      <c r="N181" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="O181" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P181" s="2" t="n">
-        <v>-2383</v>
-      </c>
-      <c r="Q181" s="2" t="n">
-        <v>1887</v>
-      </c>
-      <c r="R181" s="2" t="n">
-        <v>-495</v>
-      </c>
-      <c r="S181" s="2" t="inlineStr"/>
+      <c r="P182" t="n">
+        <v>-13858</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>829</v>
+      </c>
+      <c r="R182" t="n">
+        <v>-13030</v>
+      </c>
+      <c r="S182" t="n">
+        <v>1357</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>-0.418</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P183" s="2" t="n">
+        <v>5178</v>
+      </c>
+      <c r="Q183" s="2" t="n">
+        <v>1938</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>7116</v>
+      </c>
+      <c r="S183" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
-      <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr"/>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="inlineStr"/>
-      <c r="M183" s="2" t="inlineStr"/>
-      <c r="N183" s="2" t="inlineStr"/>
-      <c r="O183" s="2" t="inlineStr"/>
-      <c r="P183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N185" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>513</v>
-      </c>
-      <c r="R185" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S185" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>4</v>
-      </c>
-      <c r="E186" t="n">
-        <v>25</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G186" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I186" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J186" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K186" t="n">
-        <v>1</v>
-      </c>
-      <c r="L186" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M186" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N186" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O186" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P186" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R186" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S186" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr"/>
+      <c r="P185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8400,7 +8394,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -8414,33 +8408,33 @@
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N187" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
       </c>
       <c r="P187" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q187" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R187" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S187" t="n">
         <v>1415</v>
@@ -8459,43 +8453,53 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E188" t="n">
-        <v>100</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G188" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I188" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J188" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K188" t="n">
-        <v>14</v>
-      </c>
-      <c r="L188" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M188" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N188" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O188" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P188" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q188" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R188" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S188" t="n">
         <v>1415</v>
@@ -8514,11 +8518,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
@@ -8528,36 +8532,36 @@
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N189" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q189" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R189" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S189" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="190">
@@ -8573,50 +8577,46 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>14</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
       <c r="M190" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N190" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
-        <v>-68185</v>
+        <v>48540</v>
       </c>
       <c r="Q190" t="n">
-        <v>5784</v>
+        <v>4254</v>
       </c>
       <c r="R190" t="n">
-        <v>-62401</v>
+        <v>52794</v>
       </c>
       <c r="S190" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="191">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -8646,36 +8646,36 @@
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="n">
-        <v>20</v>
+        <v>4.67</v>
       </c>
       <c r="M191" t="n">
-        <v>-3.417</v>
+        <v>-0.864</v>
       </c>
       <c r="N191" t="n">
-        <v>-120621</v>
+        <v>-28997</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
       </c>
       <c r="P191" t="n">
-        <v>-324235</v>
+        <v>-86990</v>
       </c>
       <c r="Q191" t="n">
-        <v>7584</v>
+        <v>13787</v>
       </c>
       <c r="R191" t="n">
-        <v>-316651</v>
+        <v>-73203</v>
       </c>
       <c r="S191" t="n">
-        <v>1338</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="192">
@@ -8691,224 +8691,228 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>4</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R192" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S192" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>3</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="n">
+        <v>20</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R193" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D192" t="n">
+      <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E194" t="n">
         <v>100</v>
       </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="n">
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
         <v>2.42</v>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="n">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="n">
         <v>2.42</v>
       </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="n">
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="n">
         <v>28</v>
       </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="n">
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
         <v>2.425</v>
       </c>
-      <c r="N192" t="n">
+      <c r="N194" t="n">
         <v>36411</v>
       </c>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="n">
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="n">
         <v>-98615</v>
       </c>
-      <c r="Q192" t="n">
+      <c r="Q194" t="n">
         <v>5538</v>
       </c>
-      <c r="R192" t="n">
+      <c r="R194" t="n">
         <v>-93077</v>
       </c>
-      <c r="S192" t="n">
+      <c r="S194" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n">
+      <c r="D195" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E193" s="2" t="n">
+      <c r="E195" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F193" s="2" t="n">
+      <c r="F195" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="G193" s="2" t="n">
+      <c r="G195" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H193" s="2" t="n">
+      <c r="H195" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I193" s="2" t="n">
+      <c r="I195" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J195" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K193" s="2" t="n">
+      <c r="K195" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L193" s="2" t="n">
+      <c r="L195" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M193" s="2" t="n">
+      <c r="M195" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N193" s="2" t="n">
+      <c r="N195" s="2" t="n">
         <v>-23734</v>
       </c>
-      <c r="O193" s="2" t="n">
+      <c r="O195" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="P193" s="2" t="n">
+      <c r="P195" s="2" t="n">
         <v>-603372</v>
       </c>
-      <c r="Q193" s="2" t="n">
+      <c r="Q195" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="R193" s="2" t="n">
+      <c r="R195" s="2" t="n">
         <v>-557076</v>
       </c>
-      <c r="S193" s="2" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>9</v>
-      </c>
-      <c r="E195" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G195" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H195" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I195" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J195" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N195" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O195" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P195" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R195" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S195" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>2</v>
-      </c>
-      <c r="E196" t="n">
-        <v>100</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N196" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>667</v>
-      </c>
-      <c r="R196" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S196" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S195" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8923,44 +8927,52 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E197" t="n">
-        <v>100</v>
-      </c>
-      <c r="F197" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G197" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H197" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I197" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J197" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J197" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N197" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O197" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P197" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q197" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R197" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S197" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="198">
@@ -8976,228 +8988,214 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D198" t="n">
         <v>2</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N198" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>667</v>
+      </c>
+      <c r="R198" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S198" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>100</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N199" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>269</v>
+      </c>
+      <c r="R199" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N198" t="n">
+      <c r="N200" t="n">
         <v>-21127</v>
       </c>
-      <c r="O198" t="n">
-        <v>0</v>
-      </c>
-      <c r="P198" t="n">
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q198" t="n">
+      <c r="Q200" t="n">
         <v>756</v>
       </c>
-      <c r="R198" t="n">
+      <c r="R200" t="n">
         <v>-58400</v>
       </c>
-      <c r="S198" t="n">
+      <c r="S200" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D199" s="2" t="n">
+      <c r="D201" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="E201" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F199" s="2" t="n">
+      <c r="F201" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G199" s="2" t="n">
+      <c r="G201" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H199" s="2" t="n">
+      <c r="H201" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I199" s="2" t="n">
+      <c r="I201" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="J201" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="2" t="n">
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N199" s="2" t="n">
+      <c r="N201" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O199" s="2" t="n">
+      <c r="O201" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P199" s="2" t="n">
+      <c r="P201" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q199" s="2" t="n">
+      <c r="Q201" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R199" s="2" t="n">
+      <c r="R201" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S199" s="2" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>9</v>
-      </c>
-      <c r="E201" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H201" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I201" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J201" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K201" t="n">
-        <v>3</v>
-      </c>
-      <c r="L201" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M201" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N201" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P201" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R201" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S201" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>2</v>
-      </c>
-      <c r="E202" t="n">
-        <v>100</v>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N202" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>667</v>
-      </c>
-      <c r="R202" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S202" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S201" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9212,46 +9210,56 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E203" t="n">
-        <v>100</v>
-      </c>
-      <c r="F203" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G203" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H203" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H203" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I203" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J203" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J203" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K203" t="n">
-        <v>1</v>
-      </c>
-      <c r="L203" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M203" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N203" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O203" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P203" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q203" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R203" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S203" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="204">
@@ -9267,119 +9275,166 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D204" t="n">
         <v>2</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="n">
+        <v>100</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N204" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>667</v>
+      </c>
+      <c r="R204" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>100</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N205" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>269</v>
+      </c>
+      <c r="R205" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="n">
         <v>2.19</v>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="n">
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="n">
         <v>2.96</v>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="n">
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="n">
         <v>6.5</v>
       </c>
-      <c r="M204" t="n">
+      <c r="M206" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N204" t="n">
+      <c r="N206" t="n">
         <v>-21127</v>
       </c>
-      <c r="O204" t="n">
-        <v>0</v>
-      </c>
-      <c r="P204" t="n">
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q204" t="n">
+      <c r="Q206" t="n">
         <v>756</v>
       </c>
-      <c r="R204" t="n">
+      <c r="R206" t="n">
         <v>-58400</v>
       </c>
-      <c r="S204" t="n">
+      <c r="S206" t="n">
         <v>1369</v>
       </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E205" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F205" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G205" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H205" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I205" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J205" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K205" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L205" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M205" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="N205" s="2" t="n">
-        <v>7241</v>
-      </c>
-      <c r="O205" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P205" s="2" t="n">
-        <v>84466</v>
-      </c>
-      <c r="Q205" s="2" t="n">
-        <v>3831</v>
-      </c>
-      <c r="R205" s="2" t="n">
-        <v>88297</v>
-      </c>
-      <c r="S205" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -9393,39 +9448,61 @@
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr"/>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="2" t="inlineStr"/>
-      <c r="N207" s="2" t="inlineStr"/>
-      <c r="O207" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="O207" s="2" t="n">
+        <v>2.12</v>
+      </c>
       <c r="P207" s="2" t="n">
-        <v>0</v>
+        <v>84466</v>
       </c>
       <c r="Q207" s="2" t="n">
-        <v>0</v>
+        <v>3831</v>
       </c>
       <c r="R207" s="2" t="n">
-        <v>0</v>
+        <v>88297</v>
       </c>
       <c r="S207" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9461,12 +9538,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_CHART</t>
+          <t>기타(8042)</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9502,7 +9579,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>US_TR_CHART</t>
+          <t>KR_TR_CHART</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -9543,7 +9620,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>UP_TR_CHART</t>
+          <t>US_TR_CHART</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -9584,7 +9661,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>BN_TR_CHART</t>
+          <t>UP_TR_CHART</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -9623,90 +9700,45 @@
       <c r="S217" s="2" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q219" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R219" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S219" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>08/31~09/04</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="n">
-        <v>-69677</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>262</v>
-      </c>
-      <c r="R220" t="n">
-        <v>-69415</v>
-      </c>
-      <c r="S220" t="n">
-        <v>1369</v>
-      </c>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>BN_TR_CHART</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr"/>
+      <c r="O219" s="2" t="inlineStr"/>
+      <c r="P219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9721,348 +9753,393 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="n">
+        <v>51315</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>1370</v>
+      </c>
+      <c r="R221" t="n">
+        <v>52685</v>
+      </c>
+      <c r="S221" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>262</v>
+      </c>
+      <c r="R222" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S222" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D221" t="n">
+      <c r="D223" t="n">
         <v>1</v>
       </c>
-      <c r="E221" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="n">
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="n">
         <v>0.61</v>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="n">
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="n">
         <v>0.61</v>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="n">
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="n">
         <v>21</v>
       </c>
-      <c r="M221" t="n">
+      <c r="M223" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N221" t="n">
+      <c r="N223" t="n">
         <v>-37549</v>
       </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q221" t="n">
+      <c r="Q223" t="n">
         <v>201</v>
       </c>
-      <c r="R221" t="n">
+      <c r="R223" t="n">
         <v>-18985</v>
       </c>
-      <c r="S221" t="n">
+      <c r="S223" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D222" s="2" t="n">
+      <c r="D224" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="n">
+      <c r="E224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="n">
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="n">
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M222" s="2" t="n">
+      <c r="M224" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N222" s="2" t="n">
+      <c r="N224" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" s="2" t="n">
+      <c r="O224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q222" s="2" t="n">
+      <c r="Q224" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R222" s="2" t="n">
+      <c r="R224" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S222" s="2" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="S224" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D224" t="n">
-        <v>0</v>
-      </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="n">
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="n">
         <v>3654</v>
       </c>
-      <c r="Q224" t="n">
+      <c r="Q226" t="n">
         <v>33</v>
       </c>
-      <c r="R224" t="n">
+      <c r="R226" t="n">
         <v>3687</v>
       </c>
-      <c r="S224" t="n">
+      <c r="S226" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D225" t="n">
+      <c r="D227" t="n">
         <v>1</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E227" t="n">
         <v>100</v>
       </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="n">
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="n">
         <v>10.37</v>
       </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="n">
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="n">
         <v>10.37</v>
       </c>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="n">
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="n">
         <v>10</v>
       </c>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="n">
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="n">
         <v>10.37</v>
       </c>
-      <c r="N225" t="n">
+      <c r="N227" t="n">
         <v>13966</v>
       </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="n">
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="n">
         <v>10315</v>
       </c>
-      <c r="Q225" t="n">
+      <c r="Q227" t="n">
         <v>68</v>
       </c>
-      <c r="R225" t="n">
+      <c r="R227" t="n">
         <v>10383</v>
       </c>
-      <c r="S225" t="n">
+      <c r="S227" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D226" s="2" t="n">
+      <c r="D228" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E226" s="2" t="n">
+      <c r="E228" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F226" s="2" t="inlineStr"/>
-      <c r="G226" s="2" t="n">
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="n">
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="2" t="n">
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="n">
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="N226" s="2" t="n">
+      <c r="N228" s="2" t="n">
         <v>13966</v>
       </c>
-      <c r="O226" s="2" t="inlineStr"/>
-      <c r="P226" s="2" t="n">
+      <c r="O228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="n">
         <v>13969</v>
       </c>
-      <c r="Q226" s="2" t="n">
+      <c r="Q228" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="R226" s="2" t="n">
+      <c r="R228" s="2" t="n">
         <v>14070</v>
       </c>
-      <c r="S226" s="2" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="S228" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D228" t="n">
-        <v>0</v>
-      </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="n">
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="n">
         <v>127</v>
       </c>
-      <c r="Q228" t="n">
+      <c r="Q230" t="n">
         <v>105</v>
       </c>
-      <c r="R228" t="n">
+      <c r="R230" t="n">
         <v>232</v>
       </c>
-      <c r="S228" t="n">
+      <c r="S230" t="n">
         <v>1352</v>
       </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>BN_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
-      <c r="N229" s="2" t="inlineStr"/>
-      <c r="O229" s="2" t="inlineStr"/>
-      <c r="P229" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q229" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="R229" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="S229" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>UP_TR_MA</t>
+          <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10072,272 +10149,197 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="n">
+        <v>3149</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>47</v>
+      </c>
+      <c r="R231" t="n">
+        <v>3196</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>BN_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr"/>
+      <c r="O232" s="2" t="inlineStr"/>
+      <c r="P232" s="2" t="n">
+        <v>3276</v>
+      </c>
+      <c r="Q232" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="R232" s="2" t="n">
+        <v>3428</v>
+      </c>
+      <c r="S232" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>UP_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
         <v>1</v>
       </c>
-      <c r="E231" t="n">
-        <v>0</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="n">
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="n">
+        <v>2</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-5.204</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>24</v>
+      </c>
+      <c r="R234" t="n">
+        <v>-1277</v>
+      </c>
+      <c r="S234" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M231" t="n">
-        <v>-1.248</v>
-      </c>
-      <c r="N231" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="O231" t="n">
-        <v>0</v>
-      </c>
-      <c r="P231" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>149</v>
-      </c>
-      <c r="R231" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="S231" t="n">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
+      <c r="E235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E232" t="n">
-        <v>100</v>
-      </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="n">
-        <v>5</v>
-      </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="n">
-        <v>10.223</v>
-      </c>
-      <c r="N232" t="n">
-        <v>5114</v>
-      </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="n">
-        <v>11272</v>
-      </c>
-      <c r="Q232" t="n">
-        <v>122</v>
-      </c>
-      <c r="R232" t="n">
-        <v>11395</v>
-      </c>
-      <c r="S232" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>1</v>
-      </c>
-      <c r="E233" t="n">
-        <v>100</v>
-      </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="n">
-        <v>10</v>
-      </c>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="n">
-        <v>6.223</v>
-      </c>
-      <c r="N233" t="n">
-        <v>3113</v>
-      </c>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="n">
-        <v>2069</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>34</v>
-      </c>
-      <c r="R233" t="n">
-        <v>2103</v>
-      </c>
-      <c r="S233" t="n">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E234" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F234" s="2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G234" s="2" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="H234" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I234" s="2" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J234" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K234" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="L234" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M234" s="2" t="n">
-        <v>6.355</v>
-      </c>
-      <c r="N234" s="2" t="n">
-        <v>2867</v>
-      </c>
-      <c r="O234" s="2" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="P234" s="2" t="n">
-        <v>11468</v>
-      </c>
-      <c r="Q234" s="2" t="n">
-        <v>305</v>
-      </c>
-      <c r="R234" s="2" t="n">
-        <v>11774</v>
-      </c>
-      <c r="S234" s="2" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>0</v>
-      </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="n">
-        <v>866</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>109</v>
-      </c>
-      <c r="R236" t="n">
-        <v>975</v>
-      </c>
-      <c r="S236" t="n">
-        <v>1352</v>
-      </c>
+      <c r="M235" s="2" t="n">
+        <v>-5.204</v>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="O235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" s="2" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="Q235" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R235" s="2" t="n">
+        <v>-1277</v>
+      </c>
+      <c r="S235" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_1A0</t>
+          <t>UP_TR_MA</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10347,203 +10349,229 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D237" t="n">
         <v>1</v>
       </c>
       <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="N237" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>-1873</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>149</v>
+      </c>
+      <c r="R237" t="n">
+        <v>-1724</v>
+      </c>
+      <c r="S237" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>2</v>
+      </c>
+      <c r="E238" t="n">
         <v>100</v>
       </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="n">
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="n">
+        <v>5</v>
+      </c>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>10.223</v>
+      </c>
+      <c r="N238" t="n">
+        <v>5114</v>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>11272</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>122</v>
+      </c>
+      <c r="R238" t="n">
+        <v>11395</v>
+      </c>
+      <c r="S238" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
         <v>1</v>
       </c>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="N237" t="n">
-        <v>10138</v>
-      </c>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="n">
-        <v>8469</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>408</v>
-      </c>
-      <c r="R237" t="n">
-        <v>8877</v>
-      </c>
-      <c r="S237" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="E239" t="n">
+        <v>100</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="n">
+        <v>10</v>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="N239" t="n">
+        <v>3113</v>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>2069</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>34</v>
+      </c>
+      <c r="R239" t="n">
+        <v>2103</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D238" s="2" t="n">
+      <c r="D240" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I240" s="2" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K240" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="L240" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E238" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="H238" s="2" t="inlineStr"/>
-      <c r="I238" s="2" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="N238" s="2" t="n">
-        <v>10138</v>
-      </c>
-      <c r="O238" s="2" t="inlineStr"/>
-      <c r="P238" s="2" t="n">
-        <v>9335</v>
-      </c>
-      <c r="Q238" s="2" t="n">
-        <v>517</v>
-      </c>
-      <c r="R238" s="2" t="n">
-        <v>9852</v>
-      </c>
-      <c r="S238" s="2" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>09/14~09/18</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>0</v>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="n">
-        <v>54396</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>238</v>
-      </c>
-      <c r="R240" t="n">
-        <v>54634</v>
-      </c>
-      <c r="S240" t="n">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" t="n">
-        <v>100</v>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="n">
-        <v>6</v>
-      </c>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="n">
-        <v>29.576</v>
-      </c>
-      <c r="N241" t="n">
-        <v>88772</v>
-      </c>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="n">
-        <v>34376</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>106</v>
-      </c>
-      <c r="R241" t="n">
-        <v>34482</v>
-      </c>
-      <c r="S241" t="n">
-        <v>1353</v>
-      </c>
+      <c r="M240" s="2" t="n">
+        <v>6.355</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>2867</v>
+      </c>
+      <c r="O240" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="P240" s="2" t="n">
+        <v>11468</v>
+      </c>
+      <c r="Q240" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="R240" s="2" t="n">
+        <v>11774</v>
+      </c>
+      <c r="S240" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10557,49 +10585,27 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
-      </c>
-      <c r="E242" t="n">
-        <v>50</v>
-      </c>
-      <c r="F242" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="G242" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H242" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I242" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J242" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K242" t="n">
-        <v>1</v>
-      </c>
-      <c r="L242" t="n">
-        <v>10</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="N242" t="n">
-        <v>3295</v>
-      </c>
-      <c r="O242" t="n">
-        <v>36.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
       <c r="P242" t="n">
-        <v>6589</v>
+        <v>866</v>
       </c>
       <c r="Q242" t="n">
-        <v>318</v>
+        <v>109</v>
       </c>
       <c r="R242" t="n">
-        <v>6907</v>
+        <v>975</v>
       </c>
       <c r="S242" t="n">
         <v>1352</v>
@@ -10608,7 +10614,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10622,36 +10628,48 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>100</v>
+      </c>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="G243" t="n">
+        <v>6.76</v>
+      </c>
       <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
+      <c r="I243" t="n">
+        <v>6.76</v>
+      </c>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="n">
+        <v>1</v>
+      </c>
       <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="N243" t="n">
+        <v>10138</v>
+      </c>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
-        <v>-1605</v>
+        <v>12171</v>
       </c>
       <c r="Q243" t="n">
-        <v>49</v>
+        <v>526</v>
       </c>
       <c r="R243" t="n">
-        <v>-1556</v>
+        <v>12697</v>
       </c>
       <c r="S243" t="n">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>UP_TR_ORD_B</t>
+          <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -10665,56 +10683,46 @@
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F244" s="2" t="n">
-        <v>260.57</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="H244" s="2" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="2" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="J244" s="2" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.76</v>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
       <c r="K244" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L244" s="2" t="n">
-        <v>10</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L244" s="2" t="inlineStr"/>
       <c r="M244" s="2" t="n">
-        <v>10.191</v>
+        <v>6.755</v>
       </c>
       <c r="N244" s="2" t="n">
-        <v>31787</v>
-      </c>
-      <c r="O244" s="2" t="n">
-        <v>521.13</v>
-      </c>
+        <v>10138</v>
+      </c>
+      <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="n">
-        <v>93756</v>
+        <v>13037</v>
       </c>
       <c r="Q244" s="2" t="n">
-        <v>711</v>
+        <v>635</v>
       </c>
       <c r="R244" s="2" t="n">
-        <v>94467</v>
+        <v>13672</v>
       </c>
       <c r="S244" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>수동매매_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10724,113 +10732,160 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>09/14~09/18</t>
         </is>
       </c>
       <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="n">
+        <v>54396</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>238</v>
+      </c>
+      <c r="R246" t="n">
+        <v>54634</v>
+      </c>
+      <c r="S246" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
         <v>1</v>
       </c>
-      <c r="E246" t="n">
-        <v>0</v>
-      </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="n">
-        <v>3</v>
-      </c>
-      <c r="M246" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N246" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O246" t="n">
-        <v>0</v>
-      </c>
-      <c r="P246" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>257</v>
-      </c>
-      <c r="R246" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S246" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>수동매매_시딩</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="n">
+      <c r="E247" t="n">
+        <v>100</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="n">
+        <v>6</v>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>29.576</v>
+      </c>
+      <c r="N247" t="n">
+        <v>88772</v>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="n">
+        <v>34376</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>106</v>
+      </c>
+      <c r="R247" t="n">
+        <v>34482</v>
+      </c>
+      <c r="S247" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>2</v>
+      </c>
+      <c r="E248" t="n">
+        <v>50</v>
+      </c>
+      <c r="F248" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G248" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I248" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K248" t="n">
         <v>1</v>
       </c>
-      <c r="E247" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F247" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I247" s="2" t="inlineStr"/>
-      <c r="J247" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M247" s="2" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N247" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O247" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P247" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q247" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="R247" s="2" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S247" s="2" t="inlineStr"/>
+      <c r="L248" t="n">
+        <v>10</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N248" t="n">
+        <v>3295</v>
+      </c>
+      <c r="O248" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P248" t="n">
+        <v>6589</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>318</v>
+      </c>
+      <c r="R248" t="n">
+        <v>6907</v>
+      </c>
+      <c r="S248" t="n">
+        <v>1352</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10840,56 +10895,40 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" t="n">
-        <v>0</v>
-      </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
-      <c r="H249" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
-      <c r="L249" t="n">
-        <v>3</v>
-      </c>
-      <c r="M249" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N249" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O249" t="n">
-        <v>0</v>
-      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
-        <v>-29689</v>
+        <v>-2646</v>
       </c>
       <c r="Q249" t="n">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="R249" t="n">
-        <v>-29500</v>
+        <v>-2564</v>
       </c>
       <c r="S249" t="n">
-        <v>1373</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>주도주_시딩</t>
+          <t>UP_TR_ORD_B</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -10903,50 +10942,56 @@
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="2" t="inlineStr"/>
+        <v>260.57</v>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>15.92</v>
+      </c>
       <c r="H250" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I250" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="I250" s="2" t="n">
+        <v>29.58</v>
+      </c>
       <c r="J250" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K250" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="K250" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="L250" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M250" s="2" t="n">
-        <v>-4.602</v>
+        <v>10.191</v>
       </c>
       <c r="N250" s="2" t="n">
-        <v>-29689</v>
+        <v>31787</v>
       </c>
       <c r="O250" s="2" t="n">
-        <v>0</v>
+        <v>521.13</v>
       </c>
       <c r="P250" s="2" t="n">
-        <v>-29689</v>
+        <v>92715</v>
       </c>
       <c r="Q250" s="2" t="n">
-        <v>189</v>
+        <v>744</v>
       </c>
       <c r="R250" s="2" t="n">
-        <v>-29500</v>
+        <v>93459</v>
       </c>
       <c r="S250" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10970,33 +11015,33 @@
       </c>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="n">
         <v>3</v>
       </c>
       <c r="M252" t="n">
-        <v>-0.867</v>
+        <v>-8.304</v>
       </c>
       <c r="N252" t="n">
-        <v>-29188</v>
+        <v>-74087</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
       </c>
       <c r="P252" t="n">
-        <v>-29188</v>
+        <v>-74087</v>
       </c>
       <c r="Q252" t="n">
-        <v>2950</v>
+        <v>257</v>
       </c>
       <c r="R252" t="n">
-        <v>-26238</v>
+        <v>-73830</v>
       </c>
       <c r="S252" t="n">
         <v>1373</v>
@@ -11005,7 +11050,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>통합ETF_시딩</t>
+          <t>수동매매_시딩</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -11029,35 +11074,267 @@
       </c>
       <c r="G253" s="2" t="inlineStr"/>
       <c r="H253" s="2" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
       <c r="J253" s="2" t="n">
-        <v>0.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M253" s="2" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q253" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="R253" s="2" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S253" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="n">
+        <v>3</v>
+      </c>
+      <c r="M255" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N255" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>189</v>
+      </c>
+      <c r="R255" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I256" s="2" t="inlineStr"/>
+      <c r="J256" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q256" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R256" s="2" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S256" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="n">
+        <v>3</v>
+      </c>
+      <c r="M258" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N253" s="2" t="n">
+      <c r="N258" t="n">
         <v>-29188</v>
       </c>
-      <c r="O253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" s="2" t="n">
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q253" s="2" t="n">
+      <c r="Q258" t="n">
         <v>2950</v>
       </c>
-      <c r="R253" s="2" t="n">
+      <c r="R258" t="n">
         <v>-26238</v>
       </c>
-      <c r="S253" s="2" t="inlineStr"/>
+      <c r="S258" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" s="2" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q259" s="2" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R259" s="2" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S259" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S259"/>
+  <dimension ref="A1:S260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1597,48 +1597,48 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>48.1</v>
+        <v>42.1</v>
       </c>
       <c r="F19" t="n">
         <v>0.53</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="H19" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
       </c>
       <c r="J19" t="n">
-        <v>6.02</v>
+        <v>6.55</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-0.477</v>
+        <v>-0.883</v>
       </c>
       <c r="N19" t="n">
-        <v>-3799</v>
+        <v>-4695</v>
       </c>
       <c r="O19" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="P19" t="n">
-        <v>-56592</v>
+        <v>-112710</v>
       </c>
       <c r="Q19" t="n">
-        <v>17238</v>
+        <v>20740</v>
       </c>
       <c r="R19" t="n">
-        <v>-39355</v>
+        <v>-91969</v>
       </c>
       <c r="S19" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.273</v>
+        <v>0.211</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>945</v>
+        <v>721</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>391155</v>
+        <v>335037</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>129782</v>
+        <v>133284</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>520937</v>
+        <v>468323</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5507,22 +5507,22 @@
         <v>-2.474</v>
       </c>
       <c r="N115" t="n">
-        <v>-25860</v>
+        <v>-25822</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>4834</v>
+        <v>17188</v>
       </c>
       <c r="Q115" t="n">
-        <v>2738</v>
+        <v>3706</v>
       </c>
       <c r="R115" t="n">
-        <v>7572</v>
+        <v>20894</v>
       </c>
       <c r="S115" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="116">
@@ -5572,19 +5572,19 @@
         <v>-0.987</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-14676</v>
+        <v>-14674</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>0.43</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-386704</v>
+        <v>-374350</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>41592</v>
+        <v>42560</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-345112</v>
+        <v>-331790</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5605,52 +5605,52 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E118" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F118" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="G118" t="n">
         <v>2.39</v>
       </c>
       <c r="H118" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="I118" t="n">
         <v>5.07</v>
       </c>
       <c r="J118" t="n">
-        <v>1.55</v>
+        <v>3.77</v>
       </c>
       <c r="K118" t="n">
         <v>1.33</v>
       </c>
       <c r="L118" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="M118" t="n">
-        <v>1.024</v>
+        <v>0.589</v>
       </c>
       <c r="N118" t="n">
-        <v>2801</v>
+        <v>943</v>
       </c>
       <c r="O118" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="P118" t="n">
-        <v>16701</v>
+        <v>7102</v>
       </c>
       <c r="Q118" t="n">
-        <v>6966</v>
+        <v>7167</v>
       </c>
       <c r="R118" t="n">
-        <v>23667</v>
+        <v>14269</v>
       </c>
       <c r="S118" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="119">
@@ -5670,49 +5670,49 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>2.39</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>5.07</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.55</v>
+        <v>3.77</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>1.33</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1.024</v>
+        <v>0.589</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>2801</v>
+        <v>943</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>16701</v>
+        <v>7102</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>6966</v>
+        <v>7167</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>23667</v>
+        <v>14269</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5747,16 +5747,16 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>16702</v>
+        <v>16677</v>
       </c>
       <c r="Q121" t="n">
         <v>552</v>
       </c>
       <c r="R121" t="n">
-        <v>17254</v>
+        <v>17229</v>
       </c>
       <c r="S121" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="122">
@@ -5790,13 +5790,13 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="n">
-        <v>16702</v>
+        <v>16677</v>
       </c>
       <c r="Q122" s="2" t="n">
         <v>552</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>17254</v>
+        <v>17229</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5831,16 +5831,16 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>-2365</v>
+        <v>-2361</v>
       </c>
       <c r="Q124" t="n">
         <v>187</v>
       </c>
       <c r="R124" t="n">
-        <v>-2178</v>
+        <v>-2175</v>
       </c>
       <c r="S124" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="125">
@@ -5874,13 +5874,13 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
       <c r="P125" s="2" t="n">
-        <v>-2365</v>
+        <v>-2361</v>
       </c>
       <c r="Q125" s="2" t="n">
         <v>187</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-2178</v>
+        <v>-2175</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -6026,120 +6026,120 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>14</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-27555</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-6135</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>173</v>
+      </c>
+      <c r="R132" t="n">
+        <v>-5962</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="n">
+      <c r="D133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>-7.472</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>-62673</v>
-      </c>
-      <c r="O132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="2" t="n">
-        <v>-84046</v>
-      </c>
-      <c r="Q132" s="2" t="n">
-        <v>1736</v>
-      </c>
-      <c r="R132" s="2" t="n">
-        <v>-82310</v>
-      </c>
-      <c r="S132" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>US_TR_BASE</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="n">
-        <v>1</v>
-      </c>
-      <c r="M134" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="N134" t="n">
-        <v>-5227</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>-5525</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>776</v>
-      </c>
-      <c r="R134" t="n">
-        <v>-4749</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1353</v>
-      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-5.266</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>-45114</v>
+      </c>
+      <c r="O133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>-90181</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>1909</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>-88272</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6154,179 +6154,179 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-5227</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-5525</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>776</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-4749</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D136" t="n">
         <v>2</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E136" t="n">
         <v>50</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F136" t="n">
         <v>0.05</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G136" t="n">
         <v>0.33</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H136" t="n">
         <v>6.02</v>
       </c>
-      <c r="I135" t="n">
+      <c r="I136" t="n">
         <v>0.33</v>
       </c>
-      <c r="J135" t="n">
+      <c r="J136" t="n">
         <v>6.02</v>
       </c>
-      <c r="K135" t="n">
+      <c r="K136" t="n">
         <v>14</v>
       </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
         <v>-2.845</v>
       </c>
-      <c r="N135" t="n">
-        <v>-12600</v>
-      </c>
-      <c r="O135" t="n">
+      <c r="N136" t="n">
+        <v>-12581</v>
+      </c>
+      <c r="O136" t="n">
         <v>0.05</v>
       </c>
-      <c r="P135" t="n">
-        <v>-24901</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>705</v>
-      </c>
-      <c r="R135" t="n">
-        <v>-24195</v>
-      </c>
-      <c r="S135" t="n">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="P136" t="n">
+        <v>-24864</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>704</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-24160</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
+      <c r="D137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E137" s="2" t="n">
         <v>33.3</v>
       </c>
-      <c r="F136" s="2" t="n">
+      <c r="F137" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="G136" s="2" t="n">
+      <c r="G137" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H137" s="2" t="n">
         <v>3.66</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="I137" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J137" s="2" t="n">
         <v>6.02</v>
       </c>
-      <c r="K136" s="2" t="n">
+      <c r="K137" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L136" s="2" t="n">
+      <c r="L137" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="M137" s="2" t="n">
         <v>-2.33</v>
       </c>
-      <c r="N136" s="2" t="n">
-        <v>-10142</v>
-      </c>
-      <c r="O136" s="2" t="n">
+      <c r="N137" s="2" t="n">
+        <v>-10130</v>
+      </c>
+      <c r="O137" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="P136" s="2" t="n">
-        <v>-30426</v>
-      </c>
-      <c r="Q136" s="2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="R136" s="2" t="n">
-        <v>-28944</v>
-      </c>
-      <c r="S136" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="n">
-        <v>1</v>
-      </c>
-      <c r="M138" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R138" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S138" t="n">
-        <v>1373</v>
-      </c>
+      <c r="P137" s="2" t="n">
+        <v>-30389</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>1480</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>-28909</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6341,11 +6341,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -6355,36 +6355,36 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>3.23</v>
+        <v>2.13</v>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
-        <v>5.33</v>
+        <v>2.13</v>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-3.235</v>
+        <v>-2.131</v>
       </c>
       <c r="N139" t="n">
-        <v>-12511</v>
+        <v>-41586</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>-50045</v>
+        <v>-41586</v>
       </c>
       <c r="Q139" t="n">
-        <v>2266</v>
+        <v>2702</v>
       </c>
       <c r="R139" t="n">
-        <v>-47780</v>
+        <v>-38883</v>
       </c>
       <c r="S139" t="n">
-        <v>1352</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="140">
@@ -6400,179 +6400,179 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>7</v>
+      </c>
+      <c r="M140" t="n">
+        <v>-3.235</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-12511</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>-50045</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>2266</v>
+      </c>
+      <c r="R140" t="n">
+        <v>-47780</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" t="n">
-        <v>50</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G140" t="n">
+      <c r="D141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G141" t="n">
         <v>0.13</v>
       </c>
-      <c r="H140" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I140" t="n">
+      <c r="H141" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I141" t="n">
         <v>0.13</v>
       </c>
-      <c r="J140" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="K140" t="n">
+      <c r="J141" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K141" t="n">
         <v>1</v>
       </c>
-      <c r="L140" t="n">
-        <v>3</v>
-      </c>
-      <c r="M140" t="n">
-        <v>-0.911</v>
-      </c>
-      <c r="N140" t="n">
-        <v>-4678</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P140" t="n">
-        <v>-9356</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>1159</v>
-      </c>
-      <c r="R140" t="n">
-        <v>-8196</v>
-      </c>
-      <c r="S140" t="n">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="L141" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M141" t="n">
+        <v>-1.598</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-8016</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P141" t="n">
+        <v>-24049</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1840</v>
+      </c>
+      <c r="R141" t="n">
+        <v>-22208</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F141" s="2" t="n">
+      <c r="D142" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F142" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="G141" s="2" t="n">
+      <c r="G142" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="H141" s="2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I141" s="2" t="n">
+      <c r="H142" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I142" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J142" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="K141" s="2" t="n">
+      <c r="K142" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L141" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>-2.413</v>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>-14427</v>
-      </c>
-      <c r="O141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" s="2" t="n">
-        <v>-100987</v>
-      </c>
-      <c r="Q141" s="2" t="n">
-        <v>6127</v>
-      </c>
-      <c r="R141" s="2" t="n">
-        <v>-94859</v>
-      </c>
-      <c r="S141" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>7</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="n">
-        <v>8</v>
-      </c>
-      <c r="M143" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N143" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R143" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S143" t="n">
-        <v>1373</v>
-      </c>
+      <c r="L142" s="2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>-2.483</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>-14460</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>-115680</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>6808</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>-108871</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6587,56 +6587,50 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E144" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G144" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I144" t="n">
-        <v>3.32</v>
-      </c>
+        <v>3.34</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K144" t="n">
-        <v>18</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M144" t="n">
-        <v>0.864</v>
+        <v>-3.337</v>
       </c>
       <c r="N144" t="n">
-        <v>-18508</v>
+        <v>-7859</v>
       </c>
       <c r="O144" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>-52375</v>
+        <v>-55013</v>
       </c>
       <c r="Q144" t="n">
-        <v>4226</v>
+        <v>1884</v>
       </c>
       <c r="R144" t="n">
-        <v>-48149</v>
+        <v>-53128</v>
       </c>
       <c r="S144" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="145">
@@ -6652,50 +6646,56 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H145" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I145" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="I145" t="n">
+        <v>3.32</v>
+      </c>
       <c r="J145" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K145" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="K145" t="n">
+        <v>18</v>
+      </c>
       <c r="L145" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>-1.87</v>
+        <v>0.864</v>
       </c>
       <c r="N145" t="n">
-        <v>-38258</v>
+        <v>-18508</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P145" t="n">
-        <v>-79635</v>
+        <v>-52375</v>
       </c>
       <c r="Q145" t="n">
-        <v>4778</v>
+        <v>4226</v>
       </c>
       <c r="R145" t="n">
-        <v>-74857</v>
+        <v>-48149</v>
       </c>
       <c r="S145" t="n">
-        <v>1369</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="146">
@@ -6711,56 +6711,50 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0.51</v>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="M146" t="n">
-        <v>-1.701</v>
+        <v>-1.87</v>
       </c>
       <c r="N146" t="n">
-        <v>-9977</v>
+        <v>-38258</v>
       </c>
       <c r="O146" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>-29930</v>
+        <v>-79635</v>
       </c>
       <c r="Q146" t="n">
-        <v>2167</v>
+        <v>4778</v>
       </c>
       <c r="R146" t="n">
-        <v>-27764</v>
+        <v>-74857</v>
       </c>
       <c r="S146" t="n">
-        <v>1353</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="147">
@@ -6776,403 +6770,403 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H147" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J147" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-1.701</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-9977</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P147" t="n">
+        <v>-29930</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>2167</v>
+      </c>
+      <c r="R147" t="n">
+        <v>-27764</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D147" t="n">
+      <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="n">
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
         <v>2.22</v>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="n">
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
         <v>2.22</v>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="n">
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
         <v>5</v>
       </c>
-      <c r="M147" t="n">
+      <c r="M148" t="n">
         <v>-2.222</v>
       </c>
-      <c r="N147" t="n">
-        <v>-20840</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>-20840</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>1299</v>
-      </c>
-      <c r="R147" t="n">
-        <v>-19541</v>
-      </c>
-      <c r="S147" t="n">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="N148" t="n">
+        <v>-20809</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>-26386</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R148" t="n">
+        <v>-24363</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n">
+      <c r="D149" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E149" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F148" s="2" t="n">
+      <c r="F149" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="G149" s="2" t="n">
         <v>1.68</v>
       </c>
-      <c r="H148" s="2" t="n">
+      <c r="H149" s="2" t="n">
         <v>3.21</v>
       </c>
-      <c r="I148" s="2" t="n">
+      <c r="I149" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J149" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K148" s="2" t="n">
+      <c r="K149" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="L148" s="2" t="n">
+      <c r="L149" s="2" t="n">
         <v>6.42</v>
       </c>
-      <c r="M148" s="2" t="n">
+      <c r="M149" s="2" t="n">
         <v>-1.989</v>
       </c>
-      <c r="N148" s="2" t="n">
-        <v>-14864</v>
-      </c>
-      <c r="O148" s="2" t="n">
+      <c r="N149" s="2" t="n">
+        <v>-14862</v>
+      </c>
+      <c r="O149" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="P148" s="2" t="n">
-        <v>-237793</v>
-      </c>
-      <c r="Q148" s="2" t="n">
-        <v>14354</v>
-      </c>
-      <c r="R148" s="2" t="n">
-        <v>-223439</v>
-      </c>
-      <c r="S148" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="P149" s="2" t="n">
+        <v>-243339</v>
+      </c>
+      <c r="Q149" s="2" t="n">
+        <v>15078</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>-228261</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D150" t="n">
+      <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E151" t="n">
         <v>100</v>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="n">
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
         <v>8.9</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="n">
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="n">
         <v>8.9</v>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="n">
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="n">
         <v>5</v>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="n">
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
         <v>8.897</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N151" t="n">
         <v>21615</v>
       </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="n">
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="n">
         <v>21615</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q151" t="n">
         <v>355</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R151" t="n">
         <v>21970</v>
       </c>
-      <c r="S150" t="n">
+      <c r="S151" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n">
+      <c r="D152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E152" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="n">
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="n">
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="n">
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="2" t="n">
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="n">
         <v>8.897</v>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N152" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="O151" s="2" t="inlineStr"/>
-      <c r="P151" s="2" t="n">
+      <c r="O152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="n">
         <v>21615</v>
       </c>
-      <c r="Q151" s="2" t="n">
+      <c r="Q152" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="R151" s="2" t="n">
+      <c r="R152" s="2" t="n">
         <v>21970</v>
       </c>
-      <c r="S151" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="S152" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D153" t="n">
+      <c r="D154" t="n">
         <v>2</v>
       </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="n">
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="n">
         <v>7.15</v>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="n">
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
         <v>10.49</v>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="n">
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="n">
         <v>1</v>
       </c>
-      <c r="M153" t="n">
+      <c r="M154" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N153" t="n">
+      <c r="N154" t="n">
         <v>-27445</v>
       </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="Q154" t="n">
         <v>1054</v>
       </c>
-      <c r="R153" t="n">
+      <c r="R154" t="n">
         <v>-53835</v>
       </c>
-      <c r="S153" t="n">
+      <c r="S154" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D155" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="n">
+      <c r="E155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="n">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="n">
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M154" s="2" t="n">
+      <c r="M155" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N155" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="2" t="n">
+      <c r="O155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q154" s="2" t="n">
+      <c r="Q155" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R154" s="2" t="n">
+      <c r="R155" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S154" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>17</v>
-      </c>
-      <c r="E156" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G156" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H156" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I156" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J156" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M156" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N156" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O156" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P156" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R156" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S156" t="n">
-        <v>1373</v>
-      </c>
+      <c r="S155" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7187,46 +7181,56 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E157" t="n">
-        <v>100</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
+        <v>52.9</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.87</v>
+      </c>
       <c r="G157" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
+        <v>7.27</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2.48</v>
+      </c>
       <c r="I157" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
+        <v>16.31</v>
+      </c>
+      <c r="J157" t="n">
+        <v>5.68</v>
+      </c>
       <c r="K157" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
+        <v>0.78</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M157" t="n">
-        <v>6.16</v>
+        <v>2.681</v>
       </c>
       <c r="N157" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O157" t="inlineStr"/>
+        <v>3410</v>
+      </c>
+      <c r="O157" t="n">
+        <v>2.11</v>
+      </c>
       <c r="P157" t="n">
-        <v>86535</v>
+        <v>134658</v>
       </c>
       <c r="Q157" t="n">
-        <v>1828</v>
+        <v>7271</v>
       </c>
       <c r="R157" t="n">
-        <v>88363</v>
+        <v>141929</v>
       </c>
       <c r="S157" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="158">
@@ -7242,481 +7246,481 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>7</v>
+      </c>
+      <c r="E158" t="n">
+        <v>100</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N158" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R158" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D158" t="n">
+      <c r="D159" t="n">
         <v>4</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E159" t="n">
         <v>50</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F159" t="n">
         <v>2.51</v>
       </c>
-      <c r="G158" t="n">
+      <c r="G159" t="n">
         <v>11.43</v>
       </c>
-      <c r="H158" t="n">
+      <c r="H159" t="n">
         <v>2.87</v>
       </c>
-      <c r="I158" t="n">
+      <c r="I159" t="n">
         <v>12</v>
       </c>
-      <c r="J158" t="n">
+      <c r="J159" t="n">
         <v>4.94</v>
       </c>
-      <c r="K158" t="n">
+      <c r="K159" t="n">
         <v>14</v>
       </c>
-      <c r="L158" t="n">
+      <c r="L159" t="n">
         <v>14</v>
       </c>
-      <c r="M158" t="n">
+      <c r="M159" t="n">
         <v>4.282</v>
       </c>
-      <c r="N158" t="n">
+      <c r="N159" t="n">
         <v>7910</v>
       </c>
-      <c r="O158" t="n">
+      <c r="O159" t="n">
         <v>2.51</v>
       </c>
-      <c r="P158" t="n">
+      <c r="P159" t="n">
         <v>-912</v>
       </c>
-      <c r="Q158" t="n">
+      <c r="Q159" t="n">
         <v>635</v>
       </c>
-      <c r="R158" t="n">
+      <c r="R159" t="n">
         <v>-278</v>
       </c>
-      <c r="S158" t="n">
+      <c r="S159" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D159" s="2" t="n">
+      <c r="D160" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F159" s="2" t="n">
+      <c r="F160" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G159" s="2" t="n">
+      <c r="G160" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H159" s="2" t="n">
+      <c r="H160" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I159" s="2" t="n">
+      <c r="I160" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="J160" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K159" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L159" s="2" t="n">
+      <c r="L160" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M159" s="2" t="n">
+      <c r="M160" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N159" s="2" t="n">
+      <c r="N160" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O159" s="2" t="n">
+      <c r="O160" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P159" s="2" t="n">
+      <c r="P160" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q159" s="2" t="n">
+      <c r="Q160" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R159" s="2" t="n">
+      <c r="R160" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S159" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="S160" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D161" t="n">
+      <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="n">
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
         <v>0.54</v>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="n">
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
         <v>0.54</v>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="n">
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="n">
         <v>12</v>
       </c>
-      <c r="M161" t="n">
+      <c r="M162" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N161" t="n">
+      <c r="N162" t="n">
         <v>-1280</v>
       </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q161" t="n">
+      <c r="Q162" t="n">
         <v>208</v>
       </c>
-      <c r="R161" t="n">
+      <c r="R162" t="n">
         <v>-1072</v>
       </c>
-      <c r="S161" t="n">
+      <c r="S162" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n">
+      <c r="D163" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="n">
+      <c r="E163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="n">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="n">
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M162" s="2" t="n">
+      <c r="M163" s="2" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N162" s="2" t="n">
+      <c r="N163" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="O162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" s="2" t="n">
+      <c r="O163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="2" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q162" s="2" t="n">
+      <c r="Q163" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="R162" s="2" t="n">
+      <c r="R163" s="2" t="n">
         <v>-1072</v>
       </c>
-      <c r="S162" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="S163" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr"/>
-      <c r="P164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="D165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="2" t="inlineStr"/>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr"/>
-      <c r="P166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="D167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D168" t="n">
+      <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E169" t="n">
         <v>100</v>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="n">
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="n">
         <v>2.1</v>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="n">
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="n">
         <v>2.1</v>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="n">
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="n">
         <v>52.73</v>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="n">
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
         <v>2.102</v>
       </c>
-      <c r="N168" t="n">
+      <c r="N169" t="n">
         <v>2341</v>
       </c>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="n">
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
         <v>2341</v>
       </c>
-      <c r="Q168" t="n">
+      <c r="Q169" t="n">
         <v>34</v>
       </c>
-      <c r="R168" t="n">
+      <c r="R169" t="n">
         <v>2375</v>
       </c>
-      <c r="S168" t="n">
+      <c r="S169" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D169" s="2" t="n">
+      <c r="D170" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="E170" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="n">
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="n">
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="2" t="n">
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="2" t="n">
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N170" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O169" s="2" t="inlineStr"/>
-      <c r="P169" s="2" t="n">
+      <c r="O170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q169" s="2" t="n">
+      <c r="Q170" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R169" s="2" t="n">
+      <c r="R170" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S169" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" t="n">
-        <v>100</v>
-      </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="n">
-        <v>1</v>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="n">
-        <v>2.876</v>
-      </c>
-      <c r="N171" t="n">
-        <v>4316</v>
-      </c>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="n">
-        <v>13859</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>327</v>
-      </c>
-      <c r="R171" t="n">
-        <v>14186</v>
-      </c>
-      <c r="S171" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S170" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7731,56 +7735,46 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>50</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1.28</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="H172" t="n">
-        <v>4.9</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="J172" t="n">
-        <v>5.38</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="n">
         <v>1</v>
       </c>
-      <c r="L172" t="n">
-        <v>1</v>
-      </c>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="n">
-        <v>2.895</v>
+        <v>2.876</v>
       </c>
       <c r="N172" t="n">
-        <v>2294</v>
-      </c>
-      <c r="O172" t="n">
-        <v>1.28</v>
-      </c>
+        <v>4316</v>
+      </c>
+      <c r="O172" t="inlineStr"/>
       <c r="P172" t="n">
-        <v>23105</v>
+        <v>13859</v>
       </c>
       <c r="Q172" t="n">
-        <v>1932</v>
+        <v>327</v>
       </c>
       <c r="R172" t="n">
-        <v>25037</v>
+        <v>14186</v>
       </c>
       <c r="S172" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="173">
@@ -7796,185 +7790,185 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E173" t="n">
         <v>50</v>
       </c>
       <c r="F173" t="n">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="G173" t="n">
-        <v>2.97</v>
+        <v>10.69</v>
       </c>
       <c r="H173" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="I173" t="n">
-        <v>5.55</v>
+        <v>17.63</v>
       </c>
       <c r="J173" t="n">
-        <v>5.27</v>
+        <v>5.38</v>
       </c>
       <c r="K173" t="n">
         <v>1</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-1.005</v>
+        <v>2.895</v>
       </c>
       <c r="N173" t="n">
-        <v>-4017</v>
+        <v>2294</v>
       </c>
       <c r="O173" t="n">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="P173" t="n">
-        <v>-34883</v>
+        <v>23105</v>
       </c>
       <c r="Q173" t="n">
-        <v>2123</v>
+        <v>1932</v>
       </c>
       <c r="R173" t="n">
-        <v>-32760</v>
+        <v>25037</v>
       </c>
       <c r="S173" t="n">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>업비트SCO-Top3</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>5</v>
+      </c>
+      <c r="E174" t="n">
+        <v>40</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I174" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J174" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
+      <c r="L174" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-1.168</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-3759</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P174" t="n">
+        <v>-37779</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>2247</v>
+      </c>
+      <c r="R174" t="n">
+        <v>-35532</v>
+      </c>
+      <c r="S174" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G174" s="2" t="n">
+      <c r="D175" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G175" s="2" t="n">
         <v>6.81</v>
       </c>
-      <c r="H174" s="2" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="I174" s="2" t="n">
+      <c r="H175" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>17.63</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J175" s="2" t="n">
         <v>5.38</v>
       </c>
-      <c r="K174" s="2" t="n">
+      <c r="K175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L174" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M174" s="2" t="n">
-        <v>1.475</v>
-      </c>
-      <c r="N174" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="O174" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P174" s="2" t="n">
-        <v>2081</v>
-      </c>
-      <c r="Q174" s="2" t="n">
-        <v>4382</v>
-      </c>
-      <c r="R174" s="2" t="n">
-        <v>6463</v>
-      </c>
-      <c r="S174" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>업비트SCO-15분</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>11</v>
-      </c>
-      <c r="E176" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F176" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="G176" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H176" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I176" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="J176" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K176" t="n">
-        <v>753.65</v>
-      </c>
-      <c r="L176" t="n">
-        <v>197.67</v>
-      </c>
-      <c r="M176" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N176" t="n">
-        <v>1249</v>
-      </c>
-      <c r="O176" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P176" t="n">
-        <v>13742</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>2208</v>
-      </c>
-      <c r="R176" t="n">
-        <v>15950</v>
-      </c>
-      <c r="S176" t="n">
-        <v>1353</v>
-      </c>
+      <c r="L175" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>-60</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>-815</v>
+      </c>
+      <c r="Q175" s="2" t="n">
+        <v>4506</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>3691</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7989,163 +7983,185 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>09/21~09/25</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11</v>
+      </c>
+      <c r="E177" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F177" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I177" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K177" t="n">
+        <v>753.65</v>
+      </c>
+      <c r="L177" t="n">
+        <v>197.67</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1249</v>
+      </c>
+      <c r="O177" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P177" t="n">
+        <v>13742</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>2208</v>
+      </c>
+      <c r="R177" t="n">
+        <v>15950</v>
+      </c>
+      <c r="S177" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>업비트SCO-15분</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D177" t="n">
+      <c r="D178" t="n">
         <v>22</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E178" t="n">
         <v>27.3</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F178" t="n">
         <v>2.05</v>
       </c>
-      <c r="G177" t="n">
+      <c r="G178" t="n">
         <v>1.89</v>
       </c>
-      <c r="H177" t="n">
+      <c r="H178" t="n">
         <v>0.92</v>
       </c>
-      <c r="I177" t="n">
+      <c r="I178" t="n">
         <v>6.1</v>
       </c>
-      <c r="J177" t="n">
+      <c r="J178" t="n">
         <v>2.94</v>
       </c>
-      <c r="K177" t="n">
+      <c r="K178" t="n">
         <v>208.19</v>
       </c>
-      <c r="L177" t="n">
+      <c r="L178" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="M177" t="n">
+      <c r="M178" t="n">
         <v>-0.155</v>
       </c>
-      <c r="N177" t="n">
+      <c r="N178" t="n">
         <v>-311</v>
       </c>
-      <c r="O177" t="n">
+      <c r="O178" t="n">
         <v>0.77</v>
       </c>
-      <c r="P177" t="n">
+      <c r="P178" t="n">
         <v>-6837</v>
       </c>
-      <c r="Q177" t="n">
+      <c r="Q178" t="n">
         <v>4398</v>
       </c>
-      <c r="R177" t="n">
+      <c r="R178" t="n">
         <v>-2439</v>
       </c>
-      <c r="S177" t="n">
+      <c r="S178" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D179" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="E179" s="2" t="n">
         <v>30.3</v>
       </c>
-      <c r="F178" s="2" t="n">
+      <c r="F179" s="2" t="n">
         <v>2.69</v>
       </c>
-      <c r="G178" s="2" t="n">
+      <c r="G179" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="H178" s="2" t="n">
+      <c r="H179" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="I178" s="2" t="n">
+      <c r="I179" s="2" t="n">
         <v>6.36</v>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="J179" s="2" t="n">
         <v>2.94</v>
       </c>
-      <c r="K178" s="2" t="n">
+      <c r="K179" s="2" t="n">
         <v>426.38</v>
       </c>
-      <c r="L178" s="2" t="n">
+      <c r="L179" s="2" t="n">
         <v>129.08</v>
       </c>
-      <c r="M178" s="2" t="n">
+      <c r="M179" s="2" t="n">
         <v>0.105</v>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N179" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="O178" s="2" t="n">
+      <c r="O179" s="2" t="n">
         <v>1.17</v>
       </c>
-      <c r="P178" s="2" t="n">
+      <c r="P179" s="2" t="n">
         <v>6905</v>
       </c>
-      <c r="Q178" s="2" t="n">
+      <c r="Q179" s="2" t="n">
         <v>6606</v>
       </c>
-      <c r="R178" s="2" t="n">
+      <c r="R179" s="2" t="n">
         <v>13511</v>
       </c>
-      <c r="S178" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>61</v>
-      </c>
-      <c r="R180" t="n">
-        <v>973</v>
-      </c>
-      <c r="S180" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S179" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8160,56 +8176,34 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
-      </c>
-      <c r="E181" t="n">
-        <v>50</v>
-      </c>
-      <c r="F181" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G181" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H181" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I181" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J181" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K181" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="N181" t="n">
-        <v>1885</v>
-      </c>
-      <c r="O181" t="n">
-        <v>1.28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
       <c r="P181" t="n">
-        <v>18124</v>
+        <v>912</v>
       </c>
       <c r="Q181" t="n">
-        <v>1048</v>
+        <v>61</v>
       </c>
       <c r="R181" t="n">
-        <v>19173</v>
+        <v>973</v>
       </c>
       <c r="S181" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="182">
@@ -8225,220 +8219,226 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E182" t="n">
         <v>50</v>
       </c>
       <c r="F182" t="n">
-        <v>0.45</v>
+        <v>1.28</v>
       </c>
       <c r="G182" t="n">
-        <v>2.49</v>
+        <v>7.01</v>
       </c>
       <c r="H182" t="n">
-        <v>5.48</v>
+        <v>6.41</v>
       </c>
       <c r="I182" t="n">
-        <v>2.87</v>
+        <v>10.66</v>
       </c>
       <c r="J182" t="n">
-        <v>5.68</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K182" t="n">
         <v>1</v>
       </c>
       <c r="L182" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="M182" t="n">
-        <v>-1.493</v>
+        <v>0.299</v>
       </c>
       <c r="N182" t="n">
-        <v>-4059</v>
+        <v>1885</v>
       </c>
       <c r="O182" t="n">
-        <v>0.45</v>
+        <v>1.28</v>
       </c>
       <c r="P182" t="n">
-        <v>-13858</v>
+        <v>18124</v>
       </c>
       <c r="Q182" t="n">
-        <v>829</v>
+        <v>1048</v>
       </c>
       <c r="R182" t="n">
-        <v>-13030</v>
+        <v>19173</v>
       </c>
       <c r="S182" t="n">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>바이낸스SCO-Top3</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>6</v>
+      </c>
+      <c r="E183" t="n">
+        <v>50</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H183" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I183" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="J183" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-1.043</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-2831</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-24727</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>968</v>
+      </c>
+      <c r="R183" t="n">
+        <v>-23758</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E183" s="2" t="n">
+      <c r="D184" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E184" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F183" s="2" t="n">
+      <c r="F184" s="2" t="n">
         <v>0.93</v>
       </c>
-      <c r="G183" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H183" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="I183" s="2" t="n">
+      <c r="G184" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="I184" s="2" t="n">
         <v>10.66</v>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="J184" s="2" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="K183" s="2" t="n">
+      <c r="K184" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L184" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L183" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M183" s="2" t="n">
-        <v>-0.418</v>
-      </c>
-      <c r="N183" s="2" t="n">
-        <v>-493</v>
-      </c>
-      <c r="O183" s="2" t="n">
+      <c r="M184" s="2" t="n">
+        <v>-0.372</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>-473</v>
+      </c>
+      <c r="O184" s="2" t="n">
         <v>0.93</v>
       </c>
-      <c r="P183" s="2" t="n">
-        <v>5178</v>
-      </c>
-      <c r="Q183" s="2" t="n">
-        <v>1938</v>
-      </c>
-      <c r="R183" s="2" t="n">
-        <v>7116</v>
-      </c>
-      <c r="S183" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="P184" s="2" t="n">
+        <v>-5691</v>
+      </c>
+      <c r="Q184" s="2" t="n">
+        <v>2077</v>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>-3612</v>
+      </c>
+      <c r="S184" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" s="2" t="inlineStr"/>
-      <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr"/>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="2" t="inlineStr"/>
-      <c r="M185" s="2" t="inlineStr"/>
-      <c r="N185" s="2" t="inlineStr"/>
-      <c r="O185" s="2" t="inlineStr"/>
-      <c r="P185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" s="2" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>2</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="n">
-        <v>1</v>
-      </c>
-      <c r="M187" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N187" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>513</v>
-      </c>
-      <c r="R187" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S187" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8453,53 +8453,47 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G188" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I188" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K188" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="n">
         <v>1</v>
       </c>
-      <c r="L188" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M188" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N188" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O188" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P188" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q188" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R188" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S188" t="n">
         <v>1415</v>
@@ -8518,47 +8512,53 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
-      </c>
-      <c r="G189" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H189" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I189" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J189" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K189" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
       <c r="L189" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N189" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P189" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q189" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R189" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S189" t="n">
         <v>1415</v>
@@ -8577,43 +8577,47 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190" t="n">
-        <v>100</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="n">
-        <v>14</v>
-      </c>
-      <c r="L190" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M190" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N190" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O190" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
       <c r="P190" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q190" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R190" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S190" t="n">
         <v>1415</v>
@@ -8632,50 +8636,46 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D191" t="n">
         <v>3</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="n">
-        <v>4.67</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="n">
+        <v>14</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
       <c r="M191" t="n">
-        <v>-0.864</v>
+        <v>1.042</v>
       </c>
       <c r="N191" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O191" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O191" t="inlineStr"/>
       <c r="P191" t="n">
-        <v>-86990</v>
+        <v>48540</v>
       </c>
       <c r="Q191" t="n">
-        <v>13787</v>
+        <v>4254</v>
       </c>
       <c r="R191" t="n">
-        <v>-73203</v>
+        <v>52794</v>
       </c>
       <c r="S191" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="192">
@@ -8691,11 +8691,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -8705,36 +8705,36 @@
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="M192" t="n">
-        <v>-0.918</v>
+        <v>-0.864</v>
       </c>
       <c r="N192" t="n">
-        <v>-18443</v>
+        <v>-28997</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
       </c>
       <c r="P192" t="n">
-        <v>-68185</v>
+        <v>-86990</v>
       </c>
       <c r="Q192" t="n">
-        <v>5784</v>
+        <v>13787</v>
       </c>
       <c r="R192" t="n">
-        <v>-62401</v>
+        <v>-73203</v>
       </c>
       <c r="S192" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="193">
@@ -8750,11 +8750,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -8764,36 +8764,36 @@
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>3.42</v>
+        <v>0.92</v>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
-        <v>4.05</v>
+        <v>1.07</v>
       </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M193" t="n">
-        <v>-3.417</v>
+        <v>-0.918</v>
       </c>
       <c r="N193" t="n">
-        <v>-120621</v>
+        <v>-18443</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
       </c>
       <c r="P193" t="n">
-        <v>-324235</v>
+        <v>-68185</v>
       </c>
       <c r="Q193" t="n">
-        <v>7584</v>
+        <v>5784</v>
       </c>
       <c r="R193" t="n">
-        <v>-316651</v>
+        <v>-62401</v>
       </c>
       <c r="S193" t="n">
-        <v>1338</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="194">
@@ -8809,171 +8809,169 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>3</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>20</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R194" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S194" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D194" t="n">
+      <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E195" t="n">
         <v>100</v>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="n">
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="n">
         <v>2.42</v>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="n">
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="n">
         <v>2.42</v>
       </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="n">
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="n">
         <v>28</v>
       </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="n">
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
         <v>2.425</v>
       </c>
-      <c r="N194" t="n">
+      <c r="N195" t="n">
         <v>36411</v>
       </c>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="n">
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="n">
         <v>-98615</v>
       </c>
-      <c r="Q194" t="n">
+      <c r="Q195" t="n">
         <v>5538</v>
       </c>
-      <c r="R194" t="n">
+      <c r="R195" t="n">
         <v>-93077</v>
       </c>
-      <c r="S194" t="n">
+      <c r="S195" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n">
+      <c r="D196" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E195" s="2" t="n">
+      <c r="E196" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F195" s="2" t="n">
+      <c r="F196" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="G195" s="2" t="n">
+      <c r="G196" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H195" s="2" t="n">
+      <c r="H196" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I195" s="2" t="n">
+      <c r="I196" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="J196" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K195" s="2" t="n">
+      <c r="K196" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L195" s="2" t="n">
+      <c r="L196" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M195" s="2" t="n">
+      <c r="M196" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N195" s="2" t="n">
+      <c r="N196" s="2" t="n">
         <v>-23734</v>
       </c>
-      <c r="O195" s="2" t="n">
+      <c r="O196" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="P195" s="2" t="n">
+      <c r="P196" s="2" t="n">
         <v>-603372</v>
       </c>
-      <c r="Q195" s="2" t="n">
+      <c r="Q196" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="R195" s="2" t="n">
+      <c r="R196" s="2" t="n">
         <v>-557076</v>
       </c>
-      <c r="S195" s="2" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>9</v>
-      </c>
-      <c r="E197" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H197" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I197" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J197" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O197" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P197" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R197" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S197" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S196" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8988,44 +8986,52 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E198" t="n">
-        <v>100</v>
-      </c>
-      <c r="F198" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G198" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H198" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H198" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I198" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J198" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J198" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N198" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O198" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P198" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q198" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R198" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S198" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="199">
@@ -9041,44 +9047,44 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
         <v>100</v>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N199" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q199" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R199" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S199" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="200">
@@ -9094,173 +9100,161 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N200" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>269</v>
+      </c>
+      <c r="R200" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N200" t="n">
+      <c r="N201" t="n">
         <v>-21127</v>
       </c>
-      <c r="O200" t="n">
-        <v>0</v>
-      </c>
-      <c r="P200" t="n">
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q200" t="n">
+      <c r="Q201" t="n">
         <v>756</v>
       </c>
-      <c r="R200" t="n">
+      <c r="R201" t="n">
         <v>-58400</v>
       </c>
-      <c r="S200" t="n">
+      <c r="S201" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D201" s="2" t="n">
+      <c r="D202" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="E202" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F201" s="2" t="n">
+      <c r="F202" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G201" s="2" t="n">
+      <c r="G202" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H201" s="2" t="n">
+      <c r="H202" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I201" s="2" t="n">
+      <c r="I202" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="J202" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="n">
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N201" s="2" t="n">
+      <c r="N202" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O201" s="2" t="n">
+      <c r="O202" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P201" s="2" t="n">
+      <c r="P202" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q201" s="2" t="n">
+      <c r="Q202" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R201" s="2" t="n">
+      <c r="R202" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S201" s="2" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>9</v>
-      </c>
-      <c r="E203" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H203" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I203" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J203" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K203" t="n">
-        <v>3</v>
-      </c>
-      <c r="L203" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M203" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N203" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O203" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P203" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R203" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S203" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S202" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9275,46 +9269,56 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E204" t="n">
-        <v>100</v>
-      </c>
-      <c r="F204" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G204" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H204" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H204" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I204" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J204" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J204" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K204" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L204" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M204" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N204" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O204" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P204" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q204" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R204" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S204" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="205">
@@ -9330,46 +9334,46 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
         <v>100</v>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N205" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q205" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R205" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S205" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="206">
@@ -9385,403 +9389,415 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>100</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N206" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>269</v>
+      </c>
+      <c r="R206" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S206" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D206" t="n">
+      <c r="D207" t="n">
         <v>2</v>
       </c>
-      <c r="E206" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="n">
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="n">
         <v>2.19</v>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="n">
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="n">
         <v>2.96</v>
       </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="n">
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="n">
         <v>6.5</v>
       </c>
-      <c r="M206" t="n">
+      <c r="M207" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N206" t="n">
+      <c r="N207" t="n">
         <v>-21127</v>
       </c>
-      <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" t="n">
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q206" t="n">
+      <c r="Q207" t="n">
         <v>756</v>
       </c>
-      <c r="R206" t="n">
+      <c r="R207" t="n">
         <v>-58400</v>
       </c>
-      <c r="S206" t="n">
+      <c r="S207" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D207" s="2" t="n">
+      <c r="D208" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E207" s="2" t="n">
+      <c r="E208" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F207" s="2" t="n">
+      <c r="F208" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G207" s="2" t="n">
+      <c r="G208" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H207" s="2" t="n">
+      <c r="H208" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I207" s="2" t="n">
+      <c r="I208" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J207" s="2" t="n">
+      <c r="J208" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K207" s="2" t="n">
+      <c r="K208" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L207" s="2" t="n">
+      <c r="L208" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="M207" s="2" t="n">
+      <c r="M208" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N207" s="2" t="n">
+      <c r="N208" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O207" s="2" t="n">
+      <c r="O208" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P207" s="2" t="n">
+      <c r="P208" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q207" s="2" t="n">
+      <c r="Q208" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R207" s="2" t="n">
+      <c r="R208" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S207" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="S208" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr"/>
-      <c r="N209" s="2" t="inlineStr"/>
-      <c r="O209" s="2" t="inlineStr"/>
-      <c r="P209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" s="2" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="D210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr"/>
+      <c r="O210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D211" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr"/>
-      <c r="N211" s="2" t="inlineStr"/>
-      <c r="O211" s="2" t="inlineStr"/>
-      <c r="P211" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q211" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="D212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr"/>
+      <c r="O212" s="2" t="inlineStr"/>
+      <c r="P212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>KR_TR_CHART</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="2" t="inlineStr"/>
-      <c r="N213" s="2" t="inlineStr"/>
-      <c r="O213" s="2" t="inlineStr"/>
-      <c r="P213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" s="2" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+      <c r="D214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>US_TR_CHART</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E215" s="2" t="inlineStr"/>
-      <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="2" t="inlineStr"/>
-      <c r="N215" s="2" t="inlineStr"/>
-      <c r="O215" s="2" t="inlineStr"/>
-      <c r="P215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S215" s="2" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+      <c r="D216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr"/>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr"/>
+      <c r="O216" s="2" t="inlineStr"/>
+      <c r="P216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>UP_TR_CHART</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E217" s="2" t="inlineStr"/>
-      <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" s="2" t="inlineStr"/>
-      <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="2" t="inlineStr"/>
-      <c r="N217" s="2" t="inlineStr"/>
-      <c r="O217" s="2" t="inlineStr"/>
-      <c r="P217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" s="2" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+      <c r="D218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr"/>
+      <c r="O218" s="2" t="inlineStr"/>
+      <c r="P218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>BN_TR_CHART</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="2" t="inlineStr"/>
-      <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="2" t="inlineStr"/>
-      <c r="N219" s="2" t="inlineStr"/>
-      <c r="O219" s="2" t="inlineStr"/>
-      <c r="P219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" s="2" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R221" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S221" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr"/>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9796,7 +9812,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -9814,16 +9830,16 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="n">
-        <v>-69677</v>
+        <v>51315</v>
       </c>
       <c r="Q222" t="n">
-        <v>262</v>
+        <v>1370</v>
       </c>
       <c r="R222" t="n">
-        <v>-69415</v>
+        <v>52685</v>
       </c>
       <c r="S222" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="223">
@@ -9839,151 +9855,151 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>262</v>
+      </c>
+      <c r="R223" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S223" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D223" t="n">
+      <c r="D224" t="n">
         <v>1</v>
       </c>
-      <c r="E223" t="n">
-        <v>0</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="n">
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="n">
         <v>0.61</v>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="n">
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="n">
         <v>0.61</v>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="n">
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="n">
         <v>21</v>
       </c>
-      <c r="M223" t="n">
+      <c r="M224" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N223" t="n">
+      <c r="N224" t="n">
         <v>-37549</v>
       </c>
-      <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="P223" t="n">
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q223" t="n">
+      <c r="Q224" t="n">
         <v>201</v>
       </c>
-      <c r="R223" t="n">
+      <c r="R224" t="n">
         <v>-18985</v>
       </c>
-      <c r="S223" t="n">
+      <c r="S224" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D224" s="2" t="n">
+      <c r="D225" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E224" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="n">
+      <c r="E225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="n">
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="n">
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M224" s="2" t="n">
+      <c r="M225" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N224" s="2" t="n">
+      <c r="N225" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O224" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" s="2" t="n">
+      <c r="O225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q224" s="2" t="n">
+      <c r="Q225" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R224" s="2" t="n">
+      <c r="R225" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S224" s="2" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>BN_TR_MA</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="n">
-        <v>3654</v>
-      </c>
-      <c r="Q226" t="n">
-        <v>33</v>
-      </c>
-      <c r="R226" t="n">
-        <v>3687</v>
-      </c>
-      <c r="S226" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S225" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9998,143 +10014,143 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
-      </c>
-      <c r="E227" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
-      <c r="I227" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="n">
-        <v>10</v>
-      </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
-      <c r="M227" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="N227" t="n">
-        <v>13966</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
+        <v>3654</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>33</v>
+      </c>
+      <c r="R227" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S227" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>100</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="n">
+        <v>10</v>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="N228" t="n">
+        <v>13966</v>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="n">
         <v>10315</v>
       </c>
-      <c r="Q227" t="n">
+      <c r="Q228" t="n">
         <v>68</v>
       </c>
-      <c r="R227" t="n">
+      <c r="R228" t="n">
         <v>10383</v>
       </c>
-      <c r="S227" t="n">
+      <c r="S228" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D228" s="2" t="n">
+      <c r="D229" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E228" s="2" t="n">
+      <c r="E229" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="n">
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="2" t="n">
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="J228" s="2" t="inlineStr"/>
-      <c r="K228" s="2" t="n">
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L228" s="2" t="inlineStr"/>
-      <c r="M228" s="2" t="n">
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="N228" s="2" t="n">
+      <c r="N229" s="2" t="n">
         <v>13966</v>
       </c>
-      <c r="O228" s="2" t="inlineStr"/>
-      <c r="P228" s="2" t="n">
+      <c r="O229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="n">
         <v>13969</v>
       </c>
-      <c r="Q228" s="2" t="n">
+      <c r="Q229" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="R228" s="2" t="n">
+      <c r="R229" s="2" t="n">
         <v>14070</v>
       </c>
-      <c r="S228" s="2" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>BN_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q230" t="n">
-        <v>105</v>
-      </c>
-      <c r="R230" t="n">
-        <v>232</v>
-      </c>
-      <c r="S230" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S229" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10149,7 +10165,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -10167,233 +10183,241 @@
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="n">
-        <v>3149</v>
+        <v>127</v>
       </c>
       <c r="Q231" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="R231" t="n">
-        <v>3196</v>
+        <v>232</v>
       </c>
       <c r="S231" t="n">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+      <c r="A232" t="inlineStr">
         <is>
           <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>100</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="n">
+        <v>3</v>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="N232" t="n">
+        <v>3243</v>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="n">
+        <v>3116</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>86</v>
+      </c>
+      <c r="R232" t="n">
+        <v>3201</v>
+      </c>
+      <c r="S232" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>BN_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
-      <c r="I232" s="2" t="inlineStr"/>
-      <c r="J232" s="2" t="inlineStr"/>
-      <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="2" t="inlineStr"/>
-      <c r="M232" s="2" t="inlineStr"/>
-      <c r="N232" s="2" t="inlineStr"/>
-      <c r="O232" s="2" t="inlineStr"/>
-      <c r="P232" s="2" t="n">
-        <v>3276</v>
-      </c>
-      <c r="Q232" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="R232" s="2" t="n">
-        <v>3428</v>
-      </c>
-      <c r="S232" s="2" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="D233" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>3243</v>
+      </c>
+      <c r="O233" s="2" t="inlineStr"/>
+      <c r="P233" s="2" t="n">
+        <v>3243</v>
+      </c>
+      <c r="Q233" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="R233" s="2" t="n">
+        <v>3433</v>
+      </c>
+      <c r="S233" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>UP_TR_ADD1</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D234" t="n">
+      <c r="D235" t="n">
         <v>1</v>
       </c>
-      <c r="E234" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="n">
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="n">
         <v>5.2</v>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="n">
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="n">
         <v>5.2</v>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="n">
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="n">
         <v>2</v>
       </c>
-      <c r="M234" t="n">
+      <c r="M235" t="n">
         <v>-5.204</v>
       </c>
-      <c r="N234" t="n">
+      <c r="N235" t="n">
         <v>-1302</v>
       </c>
-      <c r="O234" t="n">
-        <v>0</v>
-      </c>
-      <c r="P234" t="n">
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
         <v>-1302</v>
       </c>
-      <c r="Q234" t="n">
+      <c r="Q235" t="n">
         <v>24</v>
       </c>
-      <c r="R234" t="n">
+      <c r="R235" t="n">
         <v>-1277</v>
       </c>
-      <c r="S234" t="n">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+      <c r="S235" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ADD1</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D235" s="2" t="n">
+      <c r="D236" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E235" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="n">
+      <c r="E236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="n">
         <v>5.2</v>
       </c>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="n">
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="n">
         <v>5.2</v>
       </c>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="n">
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M235" s="2" t="n">
+      <c r="M236" s="2" t="n">
         <v>-5.204</v>
       </c>
-      <c r="N235" s="2" t="n">
+      <c r="N236" s="2" t="n">
         <v>-1302</v>
       </c>
-      <c r="O235" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P235" s="2" t="n">
+      <c r="O236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" s="2" t="n">
         <v>-1302</v>
       </c>
-      <c r="Q235" s="2" t="n">
+      <c r="Q236" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="R235" s="2" t="n">
+      <c r="R236" s="2" t="n">
         <v>-1277</v>
       </c>
-      <c r="S235" s="2" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="n">
-        <v>1</v>
-      </c>
-      <c r="M237" t="n">
-        <v>-1.248</v>
-      </c>
-      <c r="N237" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="P237" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>149</v>
-      </c>
-      <c r="R237" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="S237" t="n">
-        <v>1338</v>
-      </c>
+      <c r="S236" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10408,46 +10432,50 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>100</v>
-      </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="n">
-        <v>5</v>
-      </c>
-      <c r="L238" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
       <c r="M238" t="n">
-        <v>10.223</v>
+        <v>-1.248</v>
       </c>
       <c r="N238" t="n">
-        <v>5114</v>
-      </c>
-      <c r="O238" t="inlineStr"/>
+        <v>-1873</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
       <c r="P238" t="n">
-        <v>11272</v>
+        <v>-1873</v>
       </c>
       <c r="Q238" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="R238" t="n">
-        <v>11395</v>
+        <v>-1724</v>
       </c>
       <c r="S238" t="n">
-        <v>1353</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="239">
@@ -10463,153 +10491,165 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E239" t="n">
         <v>100</v>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>6.22</v>
+        <v>10.22</v>
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>6.22</v>
+        <v>16.37</v>
       </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="n">
-        <v>6.223</v>
+        <v>10.223</v>
       </c>
       <c r="N239" t="n">
-        <v>3113</v>
+        <v>5114</v>
       </c>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="n">
+        <v>11272</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>122</v>
+      </c>
+      <c r="R239" t="n">
+        <v>11395</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>100</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="n">
+        <v>10</v>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="N240" t="n">
+        <v>3113</v>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="n">
         <v>2069</v>
       </c>
-      <c r="Q239" t="n">
+      <c r="Q240" t="n">
         <v>34</v>
       </c>
-      <c r="R239" t="n">
+      <c r="R240" t="n">
         <v>2103</v>
       </c>
-      <c r="S239" t="n">
+      <c r="S240" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>UP_TR_MA</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D240" s="2" t="n">
+      <c r="D241" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E240" s="2" t="n">
+      <c r="E241" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F240" s="2" t="n">
+      <c r="F241" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="G240" s="2" t="n">
+      <c r="G241" s="2" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="H240" s="2" t="n">
+      <c r="H241" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="I240" s="2" t="n">
+      <c r="I241" s="2" t="n">
         <v>16.37</v>
       </c>
-      <c r="J240" s="2" t="n">
+      <c r="J241" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="K240" s="2" t="n">
+      <c r="K241" s="2" t="n">
         <v>6.67</v>
       </c>
-      <c r="L240" s="2" t="n">
+      <c r="L241" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M240" s="2" t="n">
+      <c r="M241" s="2" t="n">
         <v>6.355</v>
       </c>
-      <c r="N240" s="2" t="n">
+      <c r="N241" s="2" t="n">
         <v>2867</v>
       </c>
-      <c r="O240" s="2" t="n">
+      <c r="O241" s="2" t="n">
         <v>7.12</v>
       </c>
-      <c r="P240" s="2" t="n">
+      <c r="P241" s="2" t="n">
         <v>11468</v>
       </c>
-      <c r="Q240" s="2" t="n">
+      <c r="Q241" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="R240" s="2" t="n">
+      <c r="R241" s="2" t="n">
         <v>11774</v>
       </c>
-      <c r="S240" s="2" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>0</v>
-      </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="n">
-        <v>866</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>109</v>
-      </c>
-      <c r="R242" t="n">
-        <v>975</v>
-      </c>
-      <c r="S242" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S241" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10624,143 +10664,163 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
-      </c>
-      <c r="E243" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="n">
-        <v>6.76</v>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
-      <c r="I243" t="n">
-        <v>6.76</v>
-      </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="n">
-        <v>1</v>
-      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
-      <c r="M243" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="N243" t="n">
-        <v>10138</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
-        <v>12171</v>
+        <v>866</v>
       </c>
       <c r="Q243" t="n">
-        <v>526</v>
+        <v>109</v>
       </c>
       <c r="R243" t="n">
-        <v>12697</v>
+        <v>975</v>
       </c>
       <c r="S243" t="n">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>3</v>
+      </c>
+      <c r="E244" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F244" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G244" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I244" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K244" t="n">
+        <v>2</v>
+      </c>
+      <c r="L244" t="n">
+        <v>3</v>
+      </c>
+      <c r="M244" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="N244" t="n">
+        <v>3673</v>
+      </c>
+      <c r="O244" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="P244" t="n">
+        <v>9422</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>638</v>
+      </c>
+      <c r="R244" t="n">
+        <v>10060</v>
+      </c>
+      <c r="S244" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D244" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E244" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F244" s="2" t="inlineStr"/>
-      <c r="G244" s="2" t="n">
+      <c r="D245" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I245" s="2" t="n">
         <v>6.76</v>
       </c>
-      <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="2" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="2" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="N244" s="2" t="n">
-        <v>10138</v>
-      </c>
-      <c r="O244" s="2" t="inlineStr"/>
-      <c r="P244" s="2" t="n">
-        <v>13037</v>
-      </c>
-      <c r="Q244" s="2" t="n">
-        <v>635</v>
-      </c>
-      <c r="R244" s="2" t="n">
-        <v>13672</v>
-      </c>
-      <c r="S244" s="2" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>09/14~09/18</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>0</v>
-      </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="n">
-        <v>54396</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>238</v>
-      </c>
-      <c r="R246" t="n">
-        <v>54634</v>
-      </c>
-      <c r="S246" t="n">
-        <v>1378</v>
-      </c>
+      <c r="J245" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K245" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L245" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>3673</v>
+      </c>
+      <c r="O245" s="2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>10288</v>
+      </c>
+      <c r="Q245" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>11035</v>
+      </c>
+      <c r="S245" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10775,46 +10835,34 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>09/14~09/18</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
-      </c>
-      <c r="E247" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
-      <c r="G247" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
-      <c r="I247" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="n">
-        <v>6</v>
-      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
-      <c r="M247" t="n">
-        <v>29.576</v>
-      </c>
-      <c r="N247" t="n">
-        <v>88772</v>
-      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
-        <v>34376</v>
+        <v>54396</v>
       </c>
       <c r="Q247" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="R247" t="n">
-        <v>34482</v>
+        <v>54634</v>
       </c>
       <c r="S247" t="n">
-        <v>1353</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="248">
@@ -10830,56 +10878,46 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>50</v>
-      </c>
-      <c r="F248" t="n">
-        <v>36.94</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H248" t="n">
-        <v>1.26</v>
-      </c>
+        <v>29.58</v>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J248" t="n">
-        <v>1.26</v>
-      </c>
+        <v>29.58</v>
+      </c>
+      <c r="J248" t="inlineStr"/>
       <c r="K248" t="n">
-        <v>1</v>
-      </c>
-      <c r="L248" t="n">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L248" t="inlineStr"/>
       <c r="M248" t="n">
-        <v>0.498</v>
+        <v>29.576</v>
       </c>
       <c r="N248" t="n">
-        <v>3295</v>
-      </c>
-      <c r="O248" t="n">
-        <v>36.94</v>
-      </c>
+        <v>88772</v>
+      </c>
+      <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
-        <v>6589</v>
+        <v>34376</v>
       </c>
       <c r="Q248" t="n">
-        <v>318</v>
+        <v>106</v>
       </c>
       <c r="R248" t="n">
-        <v>6907</v>
+        <v>34482</v>
       </c>
       <c r="S248" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="249">
@@ -10895,446 +10933,527 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>2</v>
+      </c>
+      <c r="E249" t="n">
+        <v>50</v>
+      </c>
+      <c r="F249" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H249" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I249" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" t="n">
+        <v>10</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N249" t="n">
+        <v>3295</v>
+      </c>
+      <c r="O249" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P249" t="n">
+        <v>6589</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>318</v>
+      </c>
+      <c r="R249" t="n">
+        <v>6907</v>
+      </c>
+      <c r="S249" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D249" t="n">
-        <v>0</v>
-      </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="n">
-        <v>-2646</v>
-      </c>
-      <c r="Q249" t="n">
-        <v>82</v>
-      </c>
-      <c r="R249" t="n">
-        <v>-2564</v>
-      </c>
-      <c r="S249" t="n">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+      <c r="D250" t="n">
+        <v>2</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M250" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="N250" t="n">
+        <v>-8374</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>-18611</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>424</v>
+      </c>
+      <c r="R250" t="n">
+        <v>-18187</v>
+      </c>
+      <c r="S250" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D250" s="2" t="n">
+      <c r="D251" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="G251" s="2" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I251" s="2" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="J251" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="K251" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L251" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>3.882</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>15722</v>
+      </c>
+      <c r="O251" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>76750</v>
+      </c>
+      <c r="Q251" s="2" t="n">
+        <v>1086</v>
+      </c>
+      <c r="R251" s="2" t="n">
+        <v>77836</v>
+      </c>
+      <c r="S251" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>수동매매_시딩</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="n">
         <v>3</v>
       </c>
-      <c r="E250" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F250" s="2" t="n">
-        <v>260.57</v>
-      </c>
-      <c r="G250" s="2" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="H250" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I250" s="2" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="J250" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K250" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L250" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M250" s="2" t="n">
-        <v>10.191</v>
-      </c>
-      <c r="N250" s="2" t="n">
-        <v>31787</v>
-      </c>
-      <c r="O250" s="2" t="n">
-        <v>521.13</v>
-      </c>
-      <c r="P250" s="2" t="n">
-        <v>92715</v>
-      </c>
-      <c r="Q250" s="2" t="n">
-        <v>744</v>
-      </c>
-      <c r="R250" s="2" t="n">
-        <v>93459</v>
-      </c>
-      <c r="S250" s="2" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="M253" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N253" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>257</v>
+      </c>
+      <c r="R253" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S253" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I254" s="2" t="inlineStr"/>
+      <c r="J254" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M254" s="2" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O254" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" s="2" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q254" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="R254" s="2" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S254" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D252" t="n">
+      <c r="D256" t="n">
         <v>1</v>
       </c>
-      <c r="E252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="n">
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="n">
         <v>3</v>
       </c>
-      <c r="M252" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N252" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="P252" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>257</v>
-      </c>
-      <c r="R252" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S252" t="n">
+      <c r="M256" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N256" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>189</v>
+      </c>
+      <c r="R256" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S256" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>수동매매_시딩</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>주도주_시딩</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D253" s="2" t="n">
+      <c r="D257" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="n">
+      <c r="E257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M253" s="2" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N253" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" s="2" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q253" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="R253" s="2" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S253" s="2" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>주도주_시딩</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="M257" s="2" t="n">
+        <v>-4.602</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="O257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" s="2" t="n">
+        <v>-29689</v>
+      </c>
+      <c r="Q257" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R257" s="2" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="S257" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D255" t="n">
+      <c r="D259" t="n">
         <v>1</v>
       </c>
-      <c r="E255" t="n">
-        <v>0</v>
-      </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="n">
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="n">
         <v>3</v>
       </c>
-      <c r="M255" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N255" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>189</v>
-      </c>
-      <c r="R255" t="n">
-        <v>-29500</v>
-      </c>
-      <c r="S255" t="n">
+      <c r="M259" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N259" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R259" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S259" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>주도주_시딩</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF_시딩</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D256" s="2" t="n">
+      <c r="D260" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F256" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="n">
+      <c r="E260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M256" s="2" t="n">
-        <v>-4.602</v>
-      </c>
-      <c r="N256" s="2" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="O256" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P256" s="2" t="n">
-        <v>-29689</v>
-      </c>
-      <c r="Q256" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="R256" s="2" t="n">
-        <v>-29500</v>
-      </c>
-      <c r="S256" s="2" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>통합ETF_시딩</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="n">
-        <v>3</v>
-      </c>
-      <c r="M258" t="n">
+      <c r="M260" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N258" t="n">
+      <c r="N260" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
+      <c r="O260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q258" t="n">
+      <c r="Q260" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R258" t="n">
+      <c r="R260" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S258" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>통합ETF_시딩</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I259" s="2" t="inlineStr"/>
-      <c r="J259" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M259" s="2" t="n">
-        <v>-0.867</v>
-      </c>
-      <c r="N259" s="2" t="n">
-        <v>-29188</v>
-      </c>
-      <c r="O259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" s="2" t="n">
-        <v>-29188</v>
-      </c>
-      <c r="Q259" s="2" t="n">
-        <v>2950</v>
-      </c>
-      <c r="R259" s="2" t="n">
-        <v>-26238</v>
-      </c>
-      <c r="S259" s="2" t="inlineStr"/>
+      <c r="S260" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S260"/>
+  <dimension ref="A1:S261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>42.1</v>
+        <v>36.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="G19" t="n">
         <v>2.49</v>
       </c>
       <c r="H19" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
@@ -1620,25 +1620,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-0.883</v>
+        <v>-1.186</v>
       </c>
       <c r="N19" t="n">
-        <v>-4695</v>
+        <v>-8930</v>
       </c>
       <c r="O19" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="P19" t="n">
-        <v>-112710</v>
+        <v>-327703</v>
       </c>
       <c r="Q19" t="n">
-        <v>20740</v>
+        <v>28271</v>
       </c>
       <c r="R19" t="n">
-        <v>-91969</v>
+        <v>-299432</v>
       </c>
       <c r="S19" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.7</v>
+        <v>39.1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>4.62</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.211</v>
+        <v>0.16</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>721</v>
+        <v>161</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>335037</v>
+        <v>120044</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>133284</v>
+        <v>140815</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>468323</v>
+        <v>260860</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5507,22 +5507,22 @@
         <v>-2.474</v>
       </c>
       <c r="N115" t="n">
-        <v>-25822</v>
+        <v>-25974</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>17188</v>
+        <v>17289</v>
       </c>
       <c r="Q115" t="n">
-        <v>3706</v>
+        <v>3728</v>
       </c>
       <c r="R115" t="n">
-        <v>20894</v>
+        <v>21017</v>
       </c>
       <c r="S115" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="116">
@@ -5572,19 +5572,19 @@
         <v>-0.987</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-14674</v>
+        <v>-14684</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>0.43</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-374350</v>
+        <v>-374249</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>42560</v>
+        <v>42582</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-331790</v>
+        <v>-331667</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5635,22 +5635,22 @@
         <v>0.589</v>
       </c>
       <c r="N118" t="n">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="O118" t="n">
         <v>1.26</v>
       </c>
       <c r="P118" t="n">
-        <v>7102</v>
+        <v>7144</v>
       </c>
       <c r="Q118" t="n">
-        <v>7167</v>
+        <v>7209</v>
       </c>
       <c r="R118" t="n">
-        <v>14269</v>
+        <v>14353</v>
       </c>
       <c r="S118" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="119">
@@ -5700,19 +5700,19 @@
         <v>0.589</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="O119" s="2" t="n">
         <v>1.26</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>7102</v>
+        <v>7144</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>7167</v>
+        <v>7209</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>14269</v>
+        <v>14353</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5747,16 +5747,16 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>16677</v>
+        <v>16776</v>
       </c>
       <c r="Q121" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="R121" t="n">
-        <v>17229</v>
+        <v>17331</v>
       </c>
       <c r="S121" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="122">
@@ -5790,13 +5790,13 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="n">
-        <v>16677</v>
+        <v>16776</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>17229</v>
+        <v>17331</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5831,16 +5831,16 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>-2361</v>
+        <v>-2375</v>
       </c>
       <c r="Q124" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R124" t="n">
-        <v>-2175</v>
+        <v>-2188</v>
       </c>
       <c r="S124" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="125">
@@ -5874,13 +5874,13 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
       <c r="P125" s="2" t="n">
-        <v>-2361</v>
+        <v>-2375</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-2175</v>
+        <v>-2188</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -6066,22 +6066,22 @@
         <v>-3.06</v>
       </c>
       <c r="N132" t="n">
-        <v>-27555</v>
+        <v>-27718</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-6135</v>
+        <v>-6172</v>
       </c>
       <c r="Q132" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R132" t="n">
-        <v>-5962</v>
+        <v>-5997</v>
       </c>
       <c r="S132" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="133">
@@ -6125,19 +6125,19 @@
         <v>-5.266</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-45114</v>
+        <v>-45196</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>-90181</v>
+        <v>-90218</v>
       </c>
       <c r="Q133" s="2" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="R133" s="2" t="n">
-        <v>-88272</v>
+        <v>-88307</v>
       </c>
       <c r="S133" s="2" t="inlineStr"/>
     </row>
@@ -6247,22 +6247,22 @@
         <v>-2.845</v>
       </c>
       <c r="N136" t="n">
-        <v>-12581</v>
+        <v>-12655</v>
       </c>
       <c r="O136" t="n">
         <v>0.05</v>
       </c>
       <c r="P136" t="n">
-        <v>-24864</v>
+        <v>-25011</v>
       </c>
       <c r="Q136" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="R136" t="n">
-        <v>-24160</v>
+        <v>-24302</v>
       </c>
       <c r="S136" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="137">
@@ -6312,19 +6312,19 @@
         <v>-2.33</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-10130</v>
+        <v>-10179</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>-30389</v>
+        <v>-30536</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>-28909</v>
+        <v>-29051</v>
       </c>
       <c r="S137" s="2" t="inlineStr"/>
     </row>
@@ -6493,22 +6493,22 @@
         <v>-1.598</v>
       </c>
       <c r="N141" t="n">
-        <v>-8016</v>
+        <v>-8064</v>
       </c>
       <c r="O141" t="n">
         <v>0.02</v>
       </c>
       <c r="P141" t="n">
-        <v>-24049</v>
+        <v>-24191</v>
       </c>
       <c r="Q141" t="n">
-        <v>1840</v>
+        <v>1851</v>
       </c>
       <c r="R141" t="n">
-        <v>-22208</v>
+        <v>-22340</v>
       </c>
       <c r="S141" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="142">
@@ -6558,19 +6558,19 @@
         <v>-2.483</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-14460</v>
+        <v>-14478</v>
       </c>
       <c r="O142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>-115680</v>
+        <v>-115822</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>6808</v>
+        <v>6819</v>
       </c>
       <c r="R142" s="2" t="n">
-        <v>-108871</v>
+        <v>-109003</v>
       </c>
       <c r="S142" s="2" t="inlineStr"/>
     </row>
@@ -6863,22 +6863,22 @@
         <v>-2.222</v>
       </c>
       <c r="N148" t="n">
-        <v>-20809</v>
+        <v>-20932</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>-26386</v>
+        <v>-26542</v>
       </c>
       <c r="Q148" t="n">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="R148" t="n">
-        <v>-24363</v>
+        <v>-24507</v>
       </c>
       <c r="S148" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="149">
@@ -6928,19 +6928,19 @@
         <v>-1.989</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-14862</v>
+        <v>-14870</v>
       </c>
       <c r="O149" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>-243339</v>
+        <v>-243495</v>
       </c>
       <c r="Q149" s="2" t="n">
-        <v>15078</v>
+        <v>15090</v>
       </c>
       <c r="R149" s="2" t="n">
-        <v>-228261</v>
+        <v>-228405</v>
       </c>
       <c r="S149" s="2" t="inlineStr"/>
     </row>
@@ -7895,16 +7895,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P174" t="n">
-        <v>-37779</v>
+        <v>-43718</v>
       </c>
       <c r="Q174" t="n">
-        <v>2247</v>
+        <v>2459</v>
       </c>
       <c r="R174" t="n">
-        <v>-35532</v>
+        <v>-41259</v>
       </c>
       <c r="S174" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="175">
@@ -7960,13 +7960,13 @@
         <v>0.99</v>
       </c>
       <c r="P175" s="2" t="n">
-        <v>-815</v>
+        <v>-6754</v>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>4506</v>
+        <v>4718</v>
       </c>
       <c r="R175" s="2" t="n">
-        <v>3691</v>
+        <v>-2036</v>
       </c>
       <c r="S175" s="2" t="inlineStr"/>
     </row>
@@ -8318,22 +8318,22 @@
         <v>-1.043</v>
       </c>
       <c r="N183" t="n">
-        <v>-2831</v>
+        <v>-2847</v>
       </c>
       <c r="O183" t="n">
         <v>0.57</v>
       </c>
       <c r="P183" t="n">
-        <v>-24727</v>
+        <v>-24873</v>
       </c>
       <c r="Q183" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="R183" t="n">
-        <v>-23758</v>
+        <v>-23899</v>
       </c>
       <c r="S183" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="184">
@@ -8383,121 +8383,137 @@
         <v>-0.372</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-473</v>
+        <v>-481</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>0.93</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>-5691</v>
+        <v>-5837</v>
       </c>
       <c r="Q184" s="2" t="n">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="R184" s="2" t="n">
-        <v>-3612</v>
+        <v>-3753</v>
       </c>
       <c r="S184" s="2" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-3.133</v>
+      </c>
+      <c r="N186" t="n">
+        <v>-95612</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>-191223</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>6904</v>
+      </c>
+      <c r="R186" t="n">
+        <v>-184319</v>
+      </c>
+      <c r="S186" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>업비트국면v6</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr"/>
-      <c r="O186" s="2" t="inlineStr"/>
-      <c r="P186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" s="2" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
+      <c r="D187" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="n">
+      <c r="E187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M188" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N188" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>513</v>
-      </c>
-      <c r="R188" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S188" t="n">
-        <v>1415</v>
-      </c>
+      <c r="M187" s="2" t="n">
+        <v>-3.133</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>-95612</v>
+      </c>
+      <c r="O187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>-191223</v>
+      </c>
+      <c r="Q187" s="2" t="n">
+        <v>6904</v>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>-184319</v>
+      </c>
+      <c r="S187" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8512,53 +8528,47 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G189" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I189" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K189" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
         <v>1</v>
       </c>
-      <c r="L189" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M189" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N189" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O189" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q189" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R189" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S189" t="n">
         <v>1415</v>
@@ -8577,47 +8587,53 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H190" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I190" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J190" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K190" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
       <c r="L190" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N190" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P190" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q190" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R190" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S190" t="n">
         <v>1415</v>
@@ -8636,43 +8652,47 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E191" t="n">
-        <v>100</v>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="n">
-        <v>14</v>
-      </c>
-      <c r="L191" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M191" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N191" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O191" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
       <c r="P191" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q191" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R191" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S191" t="n">
         <v>1415</v>
@@ -8691,50 +8711,46 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D192" t="n">
         <v>3</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="n">
-        <v>4.67</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="n">
+        <v>14</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="n">
-        <v>-0.864</v>
+        <v>1.042</v>
       </c>
       <c r="N192" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O192" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
-        <v>-86990</v>
+        <v>48540</v>
       </c>
       <c r="Q192" t="n">
-        <v>13787</v>
+        <v>4254</v>
       </c>
       <c r="R192" t="n">
-        <v>-73203</v>
+        <v>52794</v>
       </c>
       <c r="S192" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="193">
@@ -8750,11 +8766,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -8764,36 +8780,36 @@
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="M193" t="n">
-        <v>-0.918</v>
+        <v>-0.864</v>
       </c>
       <c r="N193" t="n">
-        <v>-18443</v>
+        <v>-28997</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
       </c>
       <c r="P193" t="n">
-        <v>-68185</v>
+        <v>-86990</v>
       </c>
       <c r="Q193" t="n">
-        <v>5784</v>
+        <v>13787</v>
       </c>
       <c r="R193" t="n">
-        <v>-62401</v>
+        <v>-73203</v>
       </c>
       <c r="S193" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="194">
@@ -8809,11 +8825,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
@@ -8823,36 +8839,36 @@
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>3.42</v>
+        <v>0.92</v>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="n">
-        <v>4.05</v>
+        <v>1.07</v>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M194" t="n">
-        <v>-3.417</v>
+        <v>-0.918</v>
       </c>
       <c r="N194" t="n">
-        <v>-120621</v>
+        <v>-18443</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
       </c>
       <c r="P194" t="n">
-        <v>-324235</v>
+        <v>-68185</v>
       </c>
       <c r="Q194" t="n">
-        <v>7584</v>
+        <v>5784</v>
       </c>
       <c r="R194" t="n">
-        <v>-316651</v>
+        <v>-62401</v>
       </c>
       <c r="S194" t="n">
-        <v>1338</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="195">
@@ -8868,171 +8884,169 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>09/07~09/11</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>3</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>20</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-3.417</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-120621</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>-324235</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>7584</v>
+      </c>
+      <c r="R195" t="n">
+        <v>-316651</v>
+      </c>
+      <c r="S195" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D195" t="n">
+      <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E196" t="n">
         <v>100</v>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="n">
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="n">
         <v>2.42</v>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="n">
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="n">
         <v>2.42</v>
       </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="n">
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="n">
         <v>28</v>
       </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="n">
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
         <v>2.425</v>
       </c>
-      <c r="N195" t="n">
+      <c r="N196" t="n">
         <v>36411</v>
       </c>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="n">
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="n">
         <v>-98615</v>
       </c>
-      <c r="Q195" t="n">
+      <c r="Q196" t="n">
         <v>5538</v>
       </c>
-      <c r="R195" t="n">
+      <c r="R196" t="n">
         <v>-93077</v>
       </c>
-      <c r="S195" t="n">
+      <c r="S196" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n">
+      <c r="D197" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E196" s="2" t="n">
+      <c r="E197" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F196" s="2" t="n">
+      <c r="F197" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="G196" s="2" t="n">
+      <c r="G197" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="H196" s="2" t="n">
+      <c r="H197" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="I196" s="2" t="n">
+      <c r="I197" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="J197" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="K196" s="2" t="n">
+      <c r="K197" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="L196" s="2" t="n">
+      <c r="L197" s="2" t="n">
         <v>7.47</v>
       </c>
-      <c r="M196" s="2" t="n">
+      <c r="M197" s="2" t="n">
         <v>-0.774</v>
       </c>
-      <c r="N196" s="2" t="n">
+      <c r="N197" s="2" t="n">
         <v>-23734</v>
       </c>
-      <c r="O196" s="2" t="n">
+      <c r="O197" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="P196" s="2" t="n">
+      <c r="P197" s="2" t="n">
         <v>-603372</v>
       </c>
-      <c r="Q196" s="2" t="n">
+      <c r="Q197" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="R196" s="2" t="n">
+      <c r="R197" s="2" t="n">
         <v>-557076</v>
       </c>
-      <c r="S196" s="2" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>9</v>
-      </c>
-      <c r="E198" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H198" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I198" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J198" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N198" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P198" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R198" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S198" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S197" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9047,44 +9061,52 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>100</v>
-      </c>
-      <c r="F199" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G199" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H199" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I199" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J199" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J199" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N199" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O199" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P199" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q199" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R199" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S199" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="200">
@@ -9100,44 +9122,44 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200" t="n">
         <v>100</v>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N200" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q200" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R200" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S200" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="201">
@@ -9153,173 +9175,161 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="n">
-        <v>2.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N201" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>269</v>
+      </c>
+      <c r="R201" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S201" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N201" t="n">
+      <c r="N202" t="n">
         <v>-21127</v>
       </c>
-      <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q201" t="n">
+      <c r="Q202" t="n">
         <v>756</v>
       </c>
-      <c r="R201" t="n">
+      <c r="R202" t="n">
         <v>-58400</v>
       </c>
-      <c r="S201" t="n">
+      <c r="S202" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n">
+      <c r="D203" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E202" s="2" t="n">
+      <c r="E203" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F202" s="2" t="n">
+      <c r="F203" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G202" s="2" t="n">
+      <c r="G203" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H202" s="2" t="n">
+      <c r="H203" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I202" s="2" t="n">
+      <c r="I203" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="J203" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="n">
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N202" s="2" t="n">
+      <c r="N203" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O202" s="2" t="n">
+      <c r="O203" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P202" s="2" t="n">
+      <c r="P203" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q202" s="2" t="n">
+      <c r="Q203" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R202" s="2" t="n">
+      <c r="R203" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S202" s="2" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>9</v>
-      </c>
-      <c r="E204" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H204" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I204" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J204" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K204" t="n">
-        <v>3</v>
-      </c>
-      <c r="L204" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M204" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N204" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O204" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P204" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R204" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S204" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S203" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9334,46 +9344,56 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E205" t="n">
-        <v>100</v>
-      </c>
-      <c r="F205" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G205" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H205" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H205" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I205" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J205" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J205" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K205" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L205" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M205" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N205" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O205" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P205" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q205" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R205" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S205" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="206">
@@ -9389,46 +9409,46 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="n">
         <v>100</v>
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>4.03</v>
+        <v>8.56</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>4.03</v>
+        <v>12.69</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="n">
-        <v>4.029</v>
+        <v>8.56</v>
       </c>
       <c r="N206" t="n">
-        <v>35381</v>
+        <v>57466</v>
       </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="n">
-        <v>35381</v>
+        <v>114933</v>
       </c>
       <c r="Q206" t="n">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="R206" t="n">
-        <v>35650</v>
+        <v>115600</v>
       </c>
       <c r="S206" t="n">
-        <v>1383</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="207">
@@ -9444,403 +9464,415 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>100</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N207" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>269</v>
+      </c>
+      <c r="R207" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S207" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D207" t="n">
+      <c r="D208" t="n">
         <v>2</v>
       </c>
-      <c r="E207" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="n">
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="n">
         <v>2.19</v>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="n">
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="n">
         <v>2.96</v>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="n">
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="n">
         <v>6.5</v>
       </c>
-      <c r="M207" t="n">
+      <c r="M208" t="n">
         <v>-2.191</v>
       </c>
-      <c r="N207" t="n">
+      <c r="N208" t="n">
         <v>-21127</v>
       </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
         <v>-59156</v>
       </c>
-      <c r="Q207" t="n">
+      <c r="Q208" t="n">
         <v>756</v>
       </c>
-      <c r="R207" t="n">
+      <c r="R208" t="n">
         <v>-58400</v>
       </c>
-      <c r="S207" t="n">
+      <c r="S208" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D208" s="2" t="n">
+      <c r="D209" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E208" s="2" t="n">
+      <c r="E209" s="2" t="n">
         <v>57.1</v>
       </c>
-      <c r="F208" s="2" t="n">
+      <c r="F209" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="G208" s="2" t="n">
+      <c r="G209" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H208" s="2" t="n">
+      <c r="H209" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="I208" s="2" t="n">
+      <c r="I209" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J208" s="2" t="n">
+      <c r="J209" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K208" s="2" t="n">
+      <c r="K209" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L208" s="2" t="n">
+      <c r="L209" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="M208" s="2" t="n">
+      <c r="M209" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="N208" s="2" t="n">
+      <c r="N209" s="2" t="n">
         <v>7241</v>
       </c>
-      <c r="O208" s="2" t="n">
+      <c r="O209" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="P208" s="2" t="n">
+      <c r="P209" s="2" t="n">
         <v>84466</v>
       </c>
-      <c r="Q208" s="2" t="n">
+      <c r="Q209" s="2" t="n">
         <v>3831</v>
       </c>
-      <c r="R208" s="2" t="n">
+      <c r="R209" s="2" t="n">
         <v>88297</v>
       </c>
-      <c r="S208" s="2" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="S209" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="2" t="inlineStr"/>
-      <c r="O210" s="2" t="inlineStr"/>
-      <c r="P210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" s="2" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+      <c r="D211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr"/>
-      <c r="N212" s="2" t="inlineStr"/>
-      <c r="O212" s="2" t="inlineStr"/>
-      <c r="P212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" s="2" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+      <c r="D213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr"/>
+      <c r="P213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>KR_TR_CHART</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D214" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E214" s="2" t="inlineStr"/>
-      <c r="F214" s="2" t="inlineStr"/>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="2" t="inlineStr"/>
-      <c r="J214" s="2" t="inlineStr"/>
-      <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="2" t="inlineStr"/>
-      <c r="M214" s="2" t="inlineStr"/>
-      <c r="N214" s="2" t="inlineStr"/>
-      <c r="O214" s="2" t="inlineStr"/>
-      <c r="P214" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q214" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R214" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" s="2" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+      <c r="D215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>US_TR_CHART</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E216" s="2" t="inlineStr"/>
-      <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="2" t="inlineStr"/>
-      <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="2" t="inlineStr"/>
-      <c r="M216" s="2" t="inlineStr"/>
-      <c r="N216" s="2" t="inlineStr"/>
-      <c r="O216" s="2" t="inlineStr"/>
-      <c r="P216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" s="2" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="D217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>UP_TR_CHART</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr"/>
-      <c r="N218" s="2" t="inlineStr"/>
-      <c r="O218" s="2" t="inlineStr"/>
-      <c r="P218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" s="2" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+      <c r="D219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr"/>
+      <c r="O219" s="2" t="inlineStr"/>
+      <c r="P219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>BN_TR_CHART</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="2" t="inlineStr"/>
-      <c r="O220" s="2" t="inlineStr"/>
-      <c r="P220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2X단타_시딩</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="n">
-        <v>51315</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>1370</v>
-      </c>
-      <c r="R222" t="n">
-        <v>52685</v>
-      </c>
-      <c r="S222" t="n">
-        <v>1373</v>
-      </c>
+      <c r="D221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr"/>
+      <c r="O221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9855,7 +9887,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -9873,16 +9905,16 @@
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="n">
-        <v>-69677</v>
+        <v>51315</v>
       </c>
       <c r="Q223" t="n">
-        <v>262</v>
+        <v>1370</v>
       </c>
       <c r="R223" t="n">
-        <v>-69415</v>
+        <v>52685</v>
       </c>
       <c r="S223" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="224">
@@ -9898,151 +9930,151 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="n">
+        <v>-69677</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>262</v>
+      </c>
+      <c r="R224" t="n">
+        <v>-69415</v>
+      </c>
+      <c r="S224" t="n">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2X단타_시딩</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
           <t>09/07~09/11</t>
         </is>
       </c>
-      <c r="D224" t="n">
+      <c r="D225" t="n">
         <v>1</v>
       </c>
-      <c r="E224" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="n">
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
         <v>0.61</v>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="n">
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="n">
         <v>0.61</v>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="n">
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="n">
         <v>21</v>
       </c>
-      <c r="M224" t="n">
+      <c r="M225" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N224" t="n">
+      <c r="N225" t="n">
         <v>-37549</v>
       </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
         <v>-19186</v>
       </c>
-      <c r="Q224" t="n">
+      <c r="Q225" t="n">
         <v>201</v>
       </c>
-      <c r="R224" t="n">
+      <c r="R225" t="n">
         <v>-18985</v>
       </c>
-      <c r="S224" t="n">
+      <c r="S225" t="n">
         <v>1338</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>2X단타_시딩</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D225" s="2" t="n">
+      <c r="D226" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E225" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F225" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="n">
+      <c r="E226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I225" s="2" t="inlineStr"/>
-      <c r="J225" s="2" t="n">
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="n">
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M225" s="2" t="n">
+      <c r="M226" s="2" t="n">
         <v>-0.612</v>
       </c>
-      <c r="N225" s="2" t="n">
+      <c r="N226" s="2" t="n">
         <v>-37549</v>
       </c>
-      <c r="O225" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P225" s="2" t="n">
+      <c r="O226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" s="2" t="n">
         <v>-37548</v>
       </c>
-      <c r="Q225" s="2" t="n">
+      <c r="Q226" s="2" t="n">
         <v>1833</v>
       </c>
-      <c r="R225" s="2" t="n">
+      <c r="R226" s="2" t="n">
         <v>-35715</v>
       </c>
-      <c r="S225" s="2" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>BN_TR_MA</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="n">
-        <v>3654</v>
-      </c>
-      <c r="Q227" t="n">
-        <v>33</v>
-      </c>
-      <c r="R227" t="n">
-        <v>3687</v>
-      </c>
-      <c r="S227" t="n">
-        <v>1353</v>
-      </c>
+      <c r="S226" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10057,143 +10089,143 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
-      </c>
-      <c r="E228" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
-      <c r="I228" t="n">
-        <v>10.37</v>
-      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="n">
-        <v>10</v>
-      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
-      <c r="M228" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="N228" t="n">
-        <v>13966</v>
-      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="n">
+        <v>3654</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>33</v>
+      </c>
+      <c r="R228" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S228" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BN_TR_MA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>100</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="n">
+        <v>10</v>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="N229" t="n">
+        <v>13966</v>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="n">
         <v>10315</v>
       </c>
-      <c r="Q228" t="n">
+      <c r="Q229" t="n">
         <v>68</v>
       </c>
-      <c r="R228" t="n">
+      <c r="R229" t="n">
         <v>10383</v>
       </c>
-      <c r="S228" t="n">
+      <c r="S229" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>BN_TR_MA</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D229" s="2" t="n">
+      <c r="D230" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E229" s="2" t="n">
+      <c r="E230" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="n">
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="n">
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="n">
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="n">
+      <c r="L230" s="2" t="inlineStr"/>
+      <c r="M230" s="2" t="n">
         <v>10.37</v>
       </c>
-      <c r="N229" s="2" t="n">
+      <c r="N230" s="2" t="n">
         <v>13966</v>
       </c>
-      <c r="O229" s="2" t="inlineStr"/>
-      <c r="P229" s="2" t="n">
+      <c r="O230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="n">
         <v>13969</v>
       </c>
-      <c r="Q229" s="2" t="n">
+      <c r="Q230" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="R229" s="2" t="n">
+      <c r="R230" s="2" t="n">
         <v>14070</v>
       </c>
-      <c r="S229" s="2" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>BN_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>0</v>
-      </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>105</v>
-      </c>
-      <c r="R231" t="n">
-        <v>232</v>
-      </c>
-      <c r="S231" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S230" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10208,275 +10240,259 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
-      <c r="I232" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="n">
-        <v>3</v>
-      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
-      <c r="M232" t="n">
-        <v>1.201</v>
-      </c>
-      <c r="N232" t="n">
-        <v>3243</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
-        <v>3116</v>
+        <v>127</v>
       </c>
       <c r="Q232" t="n">
+        <v>105</v>
+      </c>
+      <c r="R232" t="n">
+        <v>232</v>
+      </c>
+      <c r="S232" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>BN_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
+        <v>100</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="n">
+        <v>3</v>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="N233" t="n">
+        <v>3263</v>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="n">
+        <v>3134</v>
+      </c>
+      <c r="Q233" t="n">
         <v>86</v>
       </c>
-      <c r="R232" t="n">
-        <v>3201</v>
-      </c>
-      <c r="S232" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+      <c r="R233" t="n">
+        <v>3220</v>
+      </c>
+      <c r="S233" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>BN_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D233" s="2" t="n">
+      <c r="D234" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E233" s="2" t="n">
+      <c r="E234" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" s="2" t="n">
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="2" t="n">
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="2" t="n">
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="2" t="n">
+      <c r="L234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="n">
         <v>1.201</v>
       </c>
-      <c r="N233" s="2" t="n">
-        <v>3243</v>
-      </c>
-      <c r="O233" s="2" t="inlineStr"/>
-      <c r="P233" s="2" t="n">
-        <v>3243</v>
-      </c>
-      <c r="Q233" s="2" t="n">
+      <c r="N234" s="2" t="n">
+        <v>3263</v>
+      </c>
+      <c r="O234" s="2" t="inlineStr"/>
+      <c r="P234" s="2" t="n">
+        <v>3261</v>
+      </c>
+      <c r="Q234" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="R233" s="2" t="n">
-        <v>3433</v>
-      </c>
-      <c r="S233" s="2" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="R234" s="2" t="n">
+        <v>3452</v>
+      </c>
+      <c r="S234" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>UP_TR_ADD1</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D235" t="n">
+      <c r="D236" t="n">
         <v>1</v>
       </c>
-      <c r="E235" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="n">
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
         <v>5.2</v>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="n">
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="n">
         <v>5.2</v>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="n">
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="n">
         <v>2</v>
       </c>
-      <c r="M235" t="n">
+      <c r="M236" t="n">
         <v>-5.204</v>
       </c>
-      <c r="N235" t="n">
+      <c r="N236" t="n">
         <v>-1302</v>
       </c>
-      <c r="O235" t="n">
-        <v>0</v>
-      </c>
-      <c r="P235" t="n">
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
         <v>-1302</v>
       </c>
-      <c r="Q235" t="n">
+      <c r="Q236" t="n">
         <v>24</v>
       </c>
-      <c r="R235" t="n">
+      <c r="R236" t="n">
         <v>-1277</v>
       </c>
-      <c r="S235" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+      <c r="S236" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ADD1</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D236" s="2" t="n">
+      <c r="D237" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E236" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F236" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="n">
+      <c r="E237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="n">
         <v>5.2</v>
       </c>
-      <c r="I236" s="2" t="inlineStr"/>
-      <c r="J236" s="2" t="n">
+      <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="n">
         <v>5.2</v>
       </c>
-      <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="n">
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M236" s="2" t="n">
+      <c r="M237" s="2" t="n">
         <v>-5.204</v>
       </c>
-      <c r="N236" s="2" t="n">
+      <c r="N237" s="2" t="n">
         <v>-1302</v>
       </c>
-      <c r="O236" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P236" s="2" t="n">
+      <c r="O237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" s="2" t="n">
         <v>-1302</v>
       </c>
-      <c r="Q236" s="2" t="n">
+      <c r="Q237" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="R236" s="2" t="n">
+      <c r="R237" s="2" t="n">
         <v>-1277</v>
       </c>
-      <c r="S236" s="2" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>UP_TR_MA</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>09/07~09/11</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="n">
-        <v>1</v>
-      </c>
-      <c r="M238" t="n">
-        <v>-1.248</v>
-      </c>
-      <c r="N238" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="P238" t="n">
-        <v>-1873</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>149</v>
-      </c>
-      <c r="R238" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="S238" t="n">
-        <v>1338</v>
-      </c>
+      <c r="S237" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10491,46 +10507,50 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>09/07~09/11</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>100</v>
-      </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="n">
-        <v>5</v>
-      </c>
-      <c r="L239" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
       <c r="M239" t="n">
-        <v>10.223</v>
+        <v>-1.248</v>
       </c>
       <c r="N239" t="n">
-        <v>5114</v>
-      </c>
-      <c r="O239" t="inlineStr"/>
+        <v>-1873</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
       <c r="P239" t="n">
-        <v>11272</v>
+        <v>-1873</v>
       </c>
       <c r="Q239" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="R239" t="n">
-        <v>11395</v>
+        <v>-1724</v>
       </c>
       <c r="S239" t="n">
-        <v>1353</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="240">
@@ -10546,153 +10566,165 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
         <v>100</v>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>6.22</v>
+        <v>10.22</v>
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>6.22</v>
+        <v>16.37</v>
       </c>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="n">
-        <v>6.223</v>
+        <v>10.223</v>
       </c>
       <c r="N240" t="n">
-        <v>3113</v>
+        <v>5114</v>
       </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="n">
+        <v>11272</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>122</v>
+      </c>
+      <c r="R240" t="n">
+        <v>11395</v>
+      </c>
+      <c r="S240" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>UP_TR_MA</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>100</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="n">
+        <v>10</v>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="N241" t="n">
+        <v>3113</v>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="n">
         <v>2069</v>
       </c>
-      <c r="Q240" t="n">
+      <c r="Q241" t="n">
         <v>34</v>
       </c>
-      <c r="R240" t="n">
+      <c r="R241" t="n">
         <v>2103</v>
       </c>
-      <c r="S240" t="n">
+      <c r="S241" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>UP_TR_MA</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D241" s="2" t="n">
+      <c r="D242" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E241" s="2" t="n">
+      <c r="E242" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F241" s="2" t="n">
+      <c r="F242" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="G241" s="2" t="n">
+      <c r="G242" s="2" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="H241" s="2" t="n">
+      <c r="H242" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="I241" s="2" t="n">
+      <c r="I242" s="2" t="n">
         <v>16.37</v>
       </c>
-      <c r="J241" s="2" t="n">
+      <c r="J242" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="K241" s="2" t="n">
+      <c r="K242" s="2" t="n">
         <v>6.67</v>
       </c>
-      <c r="L241" s="2" t="n">
+      <c r="L242" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M241" s="2" t="n">
+      <c r="M242" s="2" t="n">
         <v>6.355</v>
       </c>
-      <c r="N241" s="2" t="n">
+      <c r="N242" s="2" t="n">
         <v>2867</v>
       </c>
-      <c r="O241" s="2" t="n">
+      <c r="O242" s="2" t="n">
         <v>7.12</v>
       </c>
-      <c r="P241" s="2" t="n">
+      <c r="P242" s="2" t="n">
         <v>11468</v>
       </c>
-      <c r="Q241" s="2" t="n">
+      <c r="Q242" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="R241" s="2" t="n">
+      <c r="R242" s="2" t="n">
         <v>11774</v>
       </c>
-      <c r="S241" s="2" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_1A0</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="n">
-        <v>866</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>109</v>
-      </c>
-      <c r="R243" t="n">
-        <v>975</v>
-      </c>
-      <c r="S243" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S242" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10707,163 +10739,163 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
+          <t>09/28~10/02</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="n">
+        <v>866</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>109</v>
+      </c>
+      <c r="R244" t="n">
+        <v>975</v>
+      </c>
+      <c r="S244" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_1A0</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D244" t="n">
-        <v>3</v>
-      </c>
-      <c r="E244" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F244" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G244" t="n">
+      <c r="D245" t="n">
+        <v>5</v>
+      </c>
+      <c r="E245" t="n">
+        <v>40</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G245" t="n">
         <v>4.69</v>
       </c>
-      <c r="H244" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I244" t="n">
+      <c r="H245" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I245" t="n">
         <v>6.76</v>
       </c>
-      <c r="J244" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="K244" t="n">
+      <c r="J245" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K245" t="n">
         <v>2</v>
       </c>
-      <c r="L244" t="n">
-        <v>3</v>
-      </c>
-      <c r="M244" t="n">
-        <v>2.643</v>
-      </c>
-      <c r="N244" t="n">
-        <v>3673</v>
-      </c>
-      <c r="O244" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="P244" t="n">
-        <v>9422</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>638</v>
-      </c>
-      <c r="R244" t="n">
-        <v>10060</v>
-      </c>
-      <c r="S244" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+      <c r="L245" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="N245" t="n">
+        <v>-355</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P245" t="n">
+        <v>-304</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>787</v>
+      </c>
+      <c r="R245" t="n">
+        <v>482</v>
+      </c>
+      <c r="S245" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ORD_1A0</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D245" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E245" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F245" s="2" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G245" s="2" t="n">
+      <c r="D246" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G246" s="2" t="n">
         <v>4.69</v>
       </c>
-      <c r="H245" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I245" s="2" t="n">
+      <c r="H246" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I246" s="2" t="n">
         <v>6.76</v>
       </c>
-      <c r="J245" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="K245" s="2" t="n">
+      <c r="J246" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K246" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L245" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M245" s="2" t="n">
-        <v>2.643</v>
-      </c>
-      <c r="N245" s="2" t="n">
-        <v>3673</v>
-      </c>
-      <c r="O245" s="2" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="P245" s="2" t="n">
-        <v>10288</v>
-      </c>
-      <c r="Q245" s="2" t="n">
-        <v>747</v>
-      </c>
-      <c r="R245" s="2" t="n">
-        <v>11035</v>
-      </c>
-      <c r="S245" s="2" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>UP_TR_ORD_B</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>09/14~09/18</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>0</v>
-      </c>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="n">
-        <v>54396</v>
-      </c>
-      <c r="Q247" t="n">
-        <v>238</v>
-      </c>
-      <c r="R247" t="n">
-        <v>54634</v>
-      </c>
-      <c r="S247" t="n">
-        <v>1378</v>
-      </c>
+      <c r="L246" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>-355</v>
+      </c>
+      <c r="O246" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P246" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q246" s="2" t="n">
+        <v>896</v>
+      </c>
+      <c r="R246" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="S246" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10878,46 +10910,34 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>09/14~09/18</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
-      <c r="I248" t="n">
-        <v>29.58</v>
-      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="n">
-        <v>6</v>
-      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
-      <c r="M248" t="n">
-        <v>29.576</v>
-      </c>
-      <c r="N248" t="n">
-        <v>88772</v>
-      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
-        <v>34376</v>
+        <v>54396</v>
       </c>
       <c r="Q248" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="R248" t="n">
-        <v>34482</v>
+        <v>54634</v>
       </c>
       <c r="S248" t="n">
-        <v>1353</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="249">
@@ -10933,56 +10953,46 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>50</v>
-      </c>
-      <c r="F249" t="n">
-        <v>36.94</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
       <c r="G249" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H249" t="n">
-        <v>1.26</v>
-      </c>
+        <v>29.58</v>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J249" t="n">
-        <v>1.26</v>
-      </c>
+        <v>29.58</v>
+      </c>
+      <c r="J249" t="inlineStr"/>
       <c r="K249" t="n">
-        <v>1</v>
-      </c>
-      <c r="L249" t="n">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L249" t="inlineStr"/>
       <c r="M249" t="n">
-        <v>0.498</v>
+        <v>29.576</v>
       </c>
       <c r="N249" t="n">
-        <v>3295</v>
-      </c>
-      <c r="O249" t="n">
-        <v>36.94</v>
-      </c>
+        <v>88772</v>
+      </c>
+      <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
-        <v>6589</v>
+        <v>34376</v>
       </c>
       <c r="Q249" t="n">
-        <v>318</v>
+        <v>106</v>
       </c>
       <c r="R249" t="n">
-        <v>6907</v>
+        <v>34482</v>
       </c>
       <c r="S249" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="250">
@@ -10998,462 +11008,527 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D250" t="n">
         <v>2</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="inlineStr"/>
+        <v>36.94</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2.26</v>
+      </c>
       <c r="H250" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="I250" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="I250" t="n">
+        <v>2.26</v>
+      </c>
       <c r="J250" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>10</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N250" t="n">
+        <v>3295</v>
+      </c>
+      <c r="O250" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P250" t="n">
+        <v>6589</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>318</v>
+      </c>
+      <c r="R250" t="n">
+        <v>6907</v>
+      </c>
+      <c r="S250" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>UP_TR_ORD_B</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>4</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="n">
         <v>6.55</v>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M250" t="n">
-        <v>-5.58</v>
-      </c>
-      <c r="N250" t="n">
-        <v>-8374</v>
-      </c>
-      <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="P250" t="n">
-        <v>-18611</v>
-      </c>
-      <c r="Q250" t="n">
-        <v>424</v>
-      </c>
-      <c r="R250" t="n">
-        <v>-18187</v>
-      </c>
-      <c r="S250" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="n">
+        <v>2</v>
+      </c>
+      <c r="M251" t="n">
+        <v>-4.387</v>
+      </c>
+      <c r="N251" t="n">
+        <v>-6584</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>-26336</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>587</v>
+      </c>
+      <c r="R251" t="n">
+        <v>-25748</v>
+      </c>
+      <c r="S251" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>UP_TR_ORD_B</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D251" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E251" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F251" s="2" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="G251" s="2" t="n">
+      <c r="D252" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="G252" s="2" t="n">
         <v>15.92</v>
       </c>
-      <c r="H251" s="2" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="I251" s="2" t="n">
+      <c r="H252" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I252" s="2" t="n">
         <v>29.58</v>
       </c>
-      <c r="J251" s="2" t="n">
+      <c r="J252" s="2" t="n">
         <v>6.55</v>
       </c>
-      <c r="K251" s="2" t="n">
+      <c r="K252" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="L251" s="2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="M251" s="2" t="n">
-        <v>3.882</v>
-      </c>
-      <c r="N251" s="2" t="n">
-        <v>15722</v>
-      </c>
-      <c r="O251" s="2" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="P251" s="2" t="n">
-        <v>76750</v>
-      </c>
-      <c r="Q251" s="2" t="n">
-        <v>1086</v>
-      </c>
-      <c r="R251" s="2" t="n">
-        <v>77836</v>
-      </c>
-      <c r="S251" s="2" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="L252" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>9861</v>
+      </c>
+      <c r="O252" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P252" s="2" t="n">
+        <v>69025</v>
+      </c>
+      <c r="Q252" s="2" t="n">
+        <v>1249</v>
+      </c>
+      <c r="R252" s="2" t="n">
+        <v>70275</v>
+      </c>
+      <c r="S252" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D253" t="n">
+      <c r="D254" t="n">
         <v>1</v>
       </c>
-      <c r="E253" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="n">
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="n">
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="n">
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="n">
         <v>3</v>
       </c>
-      <c r="M253" t="n">
+      <c r="M254" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N253" t="n">
+      <c r="N254" t="n">
         <v>-74087</v>
       </c>
-      <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" t="n">
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q253" t="n">
+      <c r="Q254" t="n">
         <v>257</v>
       </c>
-      <c r="R253" t="n">
+      <c r="R254" t="n">
         <v>-73830</v>
       </c>
-      <c r="S253" t="n">
+      <c r="S254" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>수동매매_시딩</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D254" s="2" t="n">
+      <c r="D255" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E254" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="n">
+      <c r="E255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I254" s="2" t="inlineStr"/>
-      <c r="J254" s="2" t="n">
+      <c r="I255" s="2" t="inlineStr"/>
+      <c r="J255" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="2" t="n">
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M254" s="2" t="n">
+      <c r="M255" s="2" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N254" s="2" t="n">
+      <c r="N255" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="O254" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" s="2" t="n">
+      <c r="O255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" s="2" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q254" s="2" t="n">
+      <c r="Q255" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="R254" s="2" t="n">
+      <c r="R255" s="2" t="n">
         <v>-73830</v>
       </c>
-      <c r="S254" s="2" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="S255" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D256" t="n">
+      <c r="D257" t="n">
         <v>1</v>
       </c>
-      <c r="E256" t="n">
-        <v>0</v>
-      </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="n">
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="n">
         <v>4.6</v>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="n">
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="n">
         <v>4.6</v>
       </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="n">
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="n">
         <v>3</v>
       </c>
-      <c r="M256" t="n">
+      <c r="M257" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N256" t="n">
+      <c r="N257" t="n">
         <v>-29689</v>
       </c>
-      <c r="O256" t="n">
-        <v>0</v>
-      </c>
-      <c r="P256" t="n">
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q256" t="n">
+      <c r="Q257" t="n">
         <v>189</v>
       </c>
-      <c r="R256" t="n">
+      <c r="R257" t="n">
         <v>-29500</v>
       </c>
-      <c r="S256" t="n">
+      <c r="S257" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>주도주_시딩</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D257" s="2" t="n">
+      <c r="D258" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E257" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F257" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="n">
+      <c r="E258" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I257" s="2" t="inlineStr"/>
-      <c r="J257" s="2" t="n">
+      <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="K257" s="2" t="inlineStr"/>
-      <c r="L257" s="2" t="n">
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M257" s="2" t="n">
+      <c r="M258" s="2" t="n">
         <v>-4.602</v>
       </c>
-      <c r="N257" s="2" t="n">
+      <c r="N258" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="O257" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" s="2" t="n">
+      <c r="O258" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" s="2" t="n">
         <v>-29689</v>
       </c>
-      <c r="Q257" s="2" t="n">
+      <c r="Q258" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="R257" s="2" t="n">
+      <c r="R258" s="2" t="n">
         <v>-29500</v>
       </c>
-      <c r="S257" s="2" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="S258" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D259" t="n">
+      <c r="D260" t="n">
         <v>1</v>
       </c>
-      <c r="E259" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="n">
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="n">
         <v>0.87</v>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="n">
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="n">
         <v>0.87</v>
       </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="n">
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="n">
         <v>3</v>
       </c>
-      <c r="M259" t="n">
+      <c r="M260" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N259" t="n">
+      <c r="N260" t="n">
         <v>-29188</v>
       </c>
-      <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q259" t="n">
+      <c r="Q260" t="n">
         <v>2950</v>
       </c>
-      <c r="R259" t="n">
+      <c r="R260" t="n">
         <v>-26238</v>
       </c>
-      <c r="S259" t="n">
+      <c r="S260" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>통합ETF_시딩</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D260" s="2" t="n">
+      <c r="D261" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="n">
+      <c r="E261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="2" t="n">
+      <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="2" t="n">
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M260" s="2" t="n">
+      <c r="M261" s="2" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N260" s="2" t="n">
+      <c r="N261" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="O260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" s="2" t="n">
+      <c r="O261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" s="2" t="n">
         <v>-29188</v>
       </c>
-      <c r="Q260" s="2" t="n">
+      <c r="Q261" s="2" t="n">
         <v>2950</v>
       </c>
-      <c r="R260" s="2" t="n">
+      <c r="R261" s="2" t="n">
         <v>-26238</v>
       </c>
-      <c r="S260" s="2" t="inlineStr"/>
+      <c r="S261" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>36.4</v>
+        <v>34.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="G19" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="H19" t="n">
-        <v>3.29</v>
+        <v>3.51</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
@@ -1620,25 +1620,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-1.186</v>
+        <v>-1.397</v>
       </c>
       <c r="N19" t="n">
-        <v>-8930</v>
+        <v>-9940</v>
       </c>
       <c r="O19" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="P19" t="n">
-        <v>-327703</v>
+        <v>-536975</v>
       </c>
       <c r="Q19" t="n">
-        <v>28271</v>
+        <v>35710</v>
       </c>
       <c r="R19" t="n">
-        <v>-299432</v>
+        <v>-501265</v>
       </c>
       <c r="S19" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.16</v>
+        <v>0.106</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>161</v>
+        <v>-153</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>120044</v>
+        <v>-89228</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>140815</v>
+        <v>148254</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>260860</v>
+        <v>59027</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5483,46 +5483,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4.67</v>
+      </c>
       <c r="H115" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I115" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="I115" t="n">
+        <v>4.67</v>
+      </c>
       <c r="J115" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="K115" t="inlineStr"/>
+        <v>5.84</v>
+      </c>
+      <c r="K115" t="n">
+        <v>15</v>
+      </c>
       <c r="L115" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M115" t="n">
-        <v>-2.474</v>
+        <v>-1.529</v>
       </c>
       <c r="N115" t="n">
-        <v>-25974</v>
+        <v>-30090</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="P115" t="n">
-        <v>17289</v>
+        <v>-117599</v>
       </c>
       <c r="Q115" t="n">
-        <v>3728</v>
+        <v>8756</v>
       </c>
       <c r="R115" t="n">
-        <v>21017</v>
+        <v>-108843</v>
       </c>
       <c r="S115" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="116">
@@ -5542,19 +5548,19 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>8.369999999999999</v>
@@ -5563,28 +5569,28 @@
         <v>10.01</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>14.55</v>
+        <v>14.58</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>10.05</v>
+        <v>9.75</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>-0.987</v>
+        <v>-0.961</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-14684</v>
+        <v>-15904</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>0.43</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-374249</v>
+        <v>-509137</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>42582</v>
+        <v>47610</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-331667</v>
+        <v>-461527</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5635,22 +5641,22 @@
         <v>0.589</v>
       </c>
       <c r="N118" t="n">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="O118" t="n">
         <v>1.26</v>
       </c>
       <c r="P118" t="n">
-        <v>7144</v>
+        <v>3738</v>
       </c>
       <c r="Q118" t="n">
-        <v>7209</v>
+        <v>7362</v>
       </c>
       <c r="R118" t="n">
-        <v>14353</v>
+        <v>11099</v>
       </c>
       <c r="S118" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="119">
@@ -5700,19 +5706,19 @@
         <v>0.589</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="O119" s="2" t="n">
         <v>1.26</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>7144</v>
+        <v>3738</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>7209</v>
+        <v>7362</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>14353</v>
+        <v>11099</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5733,30 +5739,42 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>100</v>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="n">
+        <v>2.19</v>
+      </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>2.19</v>
+      </c>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>4</v>
+      </c>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>2.189</v>
+      </c>
+      <c r="N121" t="n">
+        <v>19855</v>
+      </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>16776</v>
+        <v>19855</v>
       </c>
       <c r="Q121" t="n">
-        <v>555</v>
+        <v>1284</v>
       </c>
       <c r="R121" t="n">
-        <v>17331</v>
+        <v>21139</v>
       </c>
       <c r="S121" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="122">
@@ -5776,27 +5794,39 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="n">
+        <v>2.19</v>
+      </c>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="n">
+        <v>2.19</v>
+      </c>
       <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
-      <c r="N122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="n">
+        <v>2.189</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>19855</v>
+      </c>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="n">
-        <v>16776</v>
+        <v>19855</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>555</v>
+        <v>1284</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>17331</v>
+        <v>21139</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5817,30 +5847,46 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>6.28</v>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>6.38</v>
+      </c>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>4</v>
+      </c>
+      <c r="M124" t="n">
+        <v>-6.279</v>
+      </c>
+      <c r="N124" t="n">
+        <v>-28443</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
       <c r="P124" t="n">
-        <v>-2375</v>
+        <v>-59266</v>
       </c>
       <c r="Q124" t="n">
-        <v>188</v>
+        <v>1416</v>
       </c>
       <c r="R124" t="n">
-        <v>-2188</v>
+        <v>-57850</v>
       </c>
       <c r="S124" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="125">
@@ -5860,27 +5906,43 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="n">
+        <v>6.28</v>
+      </c>
       <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="n">
+        <v>6.38</v>
+      </c>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-6.279</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-28443</v>
+      </c>
+      <c r="O125" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P125" s="2" t="n">
-        <v>-2375</v>
+        <v>-59266</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>188</v>
+        <v>1416</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-2188</v>
+        <v>-57850</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -6066,22 +6128,22 @@
         <v>-3.06</v>
       </c>
       <c r="N132" t="n">
-        <v>-27718</v>
+        <v>-27779</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-6172</v>
+        <v>-6185</v>
       </c>
       <c r="Q132" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R132" t="n">
-        <v>-5997</v>
+        <v>-6010</v>
       </c>
       <c r="S132" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="133">
@@ -6125,19 +6187,19 @@
         <v>-5.266</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-45196</v>
+        <v>-45226</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>-90218</v>
+        <v>-90231</v>
       </c>
       <c r="Q133" s="2" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="R133" s="2" t="n">
-        <v>-88307</v>
+        <v>-88320</v>
       </c>
       <c r="S133" s="2" t="inlineStr"/>
     </row>
@@ -6247,22 +6309,22 @@
         <v>-2.845</v>
       </c>
       <c r="N136" t="n">
-        <v>-12655</v>
+        <v>-12683</v>
       </c>
       <c r="O136" t="n">
         <v>0.05</v>
       </c>
       <c r="P136" t="n">
-        <v>-25011</v>
+        <v>-25066</v>
       </c>
       <c r="Q136" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R136" t="n">
-        <v>-24302</v>
+        <v>-24356</v>
       </c>
       <c r="S136" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="137">
@@ -6312,19 +6374,19 @@
         <v>-2.33</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-10179</v>
+        <v>-10198</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>-30536</v>
+        <v>-30591</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>-29051</v>
+        <v>-29105</v>
       </c>
       <c r="S137" s="2" t="inlineStr"/>
     </row>
@@ -6493,22 +6555,22 @@
         <v>-1.598</v>
       </c>
       <c r="N141" t="n">
-        <v>-8064</v>
+        <v>-8081</v>
       </c>
       <c r="O141" t="n">
         <v>0.02</v>
       </c>
       <c r="P141" t="n">
-        <v>-24191</v>
+        <v>-24244</v>
       </c>
       <c r="Q141" t="n">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="R141" t="n">
-        <v>-22340</v>
+        <v>-22389</v>
       </c>
       <c r="S141" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="142">
@@ -6558,19 +6620,19 @@
         <v>-2.483</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-14478</v>
+        <v>-14484</v>
       </c>
       <c r="O142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>-115822</v>
+        <v>-115875</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>6819</v>
+        <v>6823</v>
       </c>
       <c r="R142" s="2" t="n">
-        <v>-109003</v>
+        <v>-109052</v>
       </c>
       <c r="S142" s="2" t="inlineStr"/>
     </row>
@@ -6863,22 +6925,22 @@
         <v>-2.222</v>
       </c>
       <c r="N148" t="n">
-        <v>-20932</v>
+        <v>-20978</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>-26542</v>
+        <v>-26600</v>
       </c>
       <c r="Q148" t="n">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="R148" t="n">
-        <v>-24507</v>
+        <v>-24561</v>
       </c>
       <c r="S148" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="149">
@@ -6928,19 +6990,19 @@
         <v>-1.989</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-14870</v>
+        <v>-14873</v>
       </c>
       <c r="O149" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>-243495</v>
+        <v>-243553</v>
       </c>
       <c r="Q149" s="2" t="n">
-        <v>15090</v>
+        <v>15095</v>
       </c>
       <c r="R149" s="2" t="n">
-        <v>-228405</v>
+        <v>-228459</v>
       </c>
       <c r="S149" s="2" t="inlineStr"/>
     </row>
@@ -7859,19 +7921,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E174" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F174" t="n">
-        <v>0.84</v>
+        <v>1.17</v>
       </c>
       <c r="G174" t="n">
         <v>2.97</v>
       </c>
       <c r="H174" t="n">
-        <v>3.93</v>
+        <v>3.45</v>
       </c>
       <c r="I174" t="n">
         <v>5.55</v>
@@ -7883,28 +7945,28 @@
         <v>1</v>
       </c>
       <c r="L174" t="n">
-        <v>3.33</v>
+        <v>3.17</v>
       </c>
       <c r="M174" t="n">
-        <v>-1.168</v>
+        <v>-1.847</v>
       </c>
       <c r="N174" t="n">
-        <v>-3759</v>
+        <v>-4637</v>
       </c>
       <c r="O174" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="P174" t="n">
-        <v>-43718</v>
+        <v>-60655</v>
       </c>
       <c r="Q174" t="n">
-        <v>2459</v>
+        <v>2747</v>
       </c>
       <c r="R174" t="n">
-        <v>-41259</v>
+        <v>-57908</v>
       </c>
       <c r="S174" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="175">
@@ -7924,19 +7986,19 @@
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
       <c r="G175" s="2" t="n">
         <v>6.81</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>4.41</v>
+        <v>3.94</v>
       </c>
       <c r="I175" s="2" t="n">
         <v>17.63</v>
@@ -7948,25 +8010,25 @@
         <v>1</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1.2</v>
+        <v>0.364</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-60</v>
+        <v>-1268</v>
       </c>
       <c r="O175" s="2" t="n">
-        <v>0.99</v>
+        <v>0.83</v>
       </c>
       <c r="P175" s="2" t="n">
-        <v>-6754</v>
+        <v>-23691</v>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>4718</v>
+        <v>5006</v>
       </c>
       <c r="R175" s="2" t="n">
-        <v>-2036</v>
+        <v>-18685</v>
       </c>
       <c r="S175" s="2" t="inlineStr"/>
     </row>
@@ -8318,22 +8380,22 @@
         <v>-1.043</v>
       </c>
       <c r="N183" t="n">
-        <v>-2847</v>
+        <v>-2854</v>
       </c>
       <c r="O183" t="n">
         <v>0.57</v>
       </c>
       <c r="P183" t="n">
-        <v>-24873</v>
+        <v>-24928</v>
       </c>
       <c r="Q183" t="n">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="R183" t="n">
-        <v>-23899</v>
+        <v>-23951</v>
       </c>
       <c r="S183" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="184">
@@ -8383,19 +8445,19 @@
         <v>-0.372</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-481</v>
+        <v>-484</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>0.93</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>-5837</v>
+        <v>-5892</v>
       </c>
       <c r="Q184" s="2" t="n">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="R184" s="2" t="n">
-        <v>-3753</v>
+        <v>-3805</v>
       </c>
       <c r="S184" s="2" t="inlineStr"/>
     </row>
@@ -8455,7 +8517,7 @@
         <v>-184319</v>
       </c>
       <c r="S186" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="187">
@@ -10309,20 +10371,20 @@
         <v>1.201</v>
       </c>
       <c r="N233" t="n">
-        <v>3263</v>
+        <v>3270</v>
       </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="n">
-        <v>3134</v>
+        <v>3141</v>
       </c>
       <c r="Q233" t="n">
         <v>86</v>
       </c>
       <c r="R233" t="n">
-        <v>3220</v>
+        <v>3227</v>
       </c>
       <c r="S233" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="234">
@@ -10364,17 +10426,17 @@
         <v>1.201</v>
       </c>
       <c r="N234" s="2" t="n">
-        <v>3263</v>
+        <v>3270</v>
       </c>
       <c r="O234" s="2" t="inlineStr"/>
       <c r="P234" s="2" t="n">
-        <v>3261</v>
+        <v>3268</v>
       </c>
       <c r="Q234" s="2" t="n">
         <v>191</v>
       </c>
       <c r="R234" s="2" t="n">
-        <v>3452</v>
+        <v>3459</v>
       </c>
       <c r="S234" s="2" t="inlineStr"/>
     </row>
@@ -10434,7 +10496,7 @@
         <v>-1277</v>
       </c>
       <c r="S236" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="237">
@@ -10831,7 +10893,7 @@
         <v>482</v>
       </c>
       <c r="S245" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="246">
@@ -11116,7 +11178,7 @@
         <v>-25748</v>
       </c>
       <c r="S251" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="252">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>34.6</v>
+        <v>36.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="n">
         <v>6.76</v>
@@ -1620,25 +1620,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-1.397</v>
+        <v>-1.191</v>
       </c>
       <c r="N19" t="n">
-        <v>-9940</v>
+        <v>-10300</v>
       </c>
       <c r="O19" t="n">
         <v>0.26</v>
       </c>
       <c r="P19" t="n">
-        <v>-536975</v>
+        <v>-521010</v>
       </c>
       <c r="Q19" t="n">
-        <v>35710</v>
+        <v>38669</v>
       </c>
       <c r="R19" t="n">
-        <v>-501265</v>
+        <v>-482341</v>
       </c>
       <c r="S19" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="20">
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>29.58</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-153</v>
+        <v>-325</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>-89228</v>
+        <v>-73263</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>148254</v>
+        <v>151213</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>59027</v>
+        <v>77951</v>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
     </row>
@@ -5483,19 +5483,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F115" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="G115" t="n">
         <v>4.67</v>
       </c>
       <c r="H115" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="I115" t="n">
         <v>4.67</v>
@@ -5507,28 +5507,28 @@
         <v>15</v>
       </c>
       <c r="L115" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="M115" t="n">
-        <v>-1.529</v>
+        <v>-1.815</v>
       </c>
       <c r="N115" t="n">
-        <v>-30090</v>
+        <v>-42957</v>
       </c>
       <c r="O115" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="P115" t="n">
-        <v>-117599</v>
+        <v>-156305</v>
       </c>
       <c r="Q115" t="n">
-        <v>8756</v>
+        <v>10396</v>
       </c>
       <c r="R115" t="n">
-        <v>-108843</v>
+        <v>-145909</v>
       </c>
       <c r="S115" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="116">
@@ -5548,19 +5548,19 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>37.5</v>
+        <v>36.4</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>3.47</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>8.369999999999999</v>
@@ -5572,25 +5572,25 @@
         <v>14.58</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>9.75</v>
+        <v>10.05</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>-0.961</v>
+        <v>-1.022</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-15904</v>
+        <v>-18283</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>-509137</v>
+        <v>-547843</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>47610</v>
+        <v>49250</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>-461527</v>
+        <v>-498593</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
@@ -5611,19 +5611,19 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>54.5</v>
+        <v>53.8</v>
       </c>
       <c r="F118" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="G118" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="H118" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="I118" t="n">
         <v>5.07</v>
@@ -5632,31 +5632,31 @@
         <v>3.77</v>
       </c>
       <c r="K118" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="L118" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="M118" t="n">
-        <v>0.589</v>
+        <v>0.797</v>
       </c>
       <c r="N118" t="n">
-        <v>951</v>
+        <v>1889</v>
       </c>
       <c r="O118" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="P118" t="n">
-        <v>3738</v>
+        <v>19497</v>
       </c>
       <c r="Q118" t="n">
-        <v>7362</v>
+        <v>8067</v>
       </c>
       <c r="R118" t="n">
-        <v>11099</v>
+        <v>27565</v>
       </c>
       <c r="S118" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="119">
@@ -5676,19 +5676,19 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>54.5</v>
+        <v>53.8</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>5.07</v>
@@ -5697,28 +5697,28 @@
         <v>3.77</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>0.589</v>
+        <v>0.797</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>951</v>
+        <v>1889</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>3738</v>
+        <v>19497</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>7362</v>
+        <v>8067</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>11099</v>
+        <v>27565</v>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
     </row>
@@ -5761,20 +5761,20 @@
         <v>2.189</v>
       </c>
       <c r="N121" t="n">
-        <v>19855</v>
+        <v>19928</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>19855</v>
+        <v>19928</v>
       </c>
       <c r="Q121" t="n">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="R121" t="n">
-        <v>21139</v>
+        <v>21216</v>
       </c>
       <c r="S121" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="122">
@@ -5816,17 +5816,17 @@
         <v>2.189</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>19855</v>
+        <v>19928</v>
       </c>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="n">
-        <v>19855</v>
+        <v>19928</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>21139</v>
+        <v>21216</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5847,46 +5847,52 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.52</v>
+      </c>
       <c r="H124" t="n">
         <v>6.28</v>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>0.52</v>
+      </c>
       <c r="J124" t="n">
         <v>6.38</v>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>3</v>
+      </c>
       <c r="L124" t="n">
         <v>4</v>
       </c>
       <c r="M124" t="n">
-        <v>-6.279</v>
+        <v>-4.013</v>
       </c>
       <c r="N124" t="n">
-        <v>-28443</v>
+        <v>-18560</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P124" t="n">
-        <v>-59266</v>
+        <v>-55680</v>
       </c>
       <c r="Q124" t="n">
-        <v>1416</v>
+        <v>1615</v>
       </c>
       <c r="R124" t="n">
-        <v>-57850</v>
+        <v>-54065</v>
       </c>
       <c r="S124" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="125">
@@ -5906,43 +5912,49 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="H125" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="J125" s="2" t="n">
         <v>6.38</v>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="L125" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>-6.279</v>
+        <v>-4.013</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-28443</v>
+        <v>-18560</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>-59266</v>
+        <v>-55680</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>1416</v>
+        <v>1615</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-57850</v>
+        <v>-54065</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -6128,22 +6140,22 @@
         <v>-3.06</v>
       </c>
       <c r="N132" t="n">
-        <v>-27779</v>
+        <v>-27881</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-6185</v>
+        <v>-6208</v>
       </c>
       <c r="Q132" t="n">
         <v>175</v>
       </c>
       <c r="R132" t="n">
-        <v>-6010</v>
+        <v>-6032</v>
       </c>
       <c r="S132" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="133">
@@ -6187,19 +6199,19 @@
         <v>-5.266</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-45226</v>
+        <v>-45277</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>-90231</v>
+        <v>-90254</v>
       </c>
       <c r="Q133" s="2" t="n">
         <v>1911</v>
       </c>
       <c r="R133" s="2" t="n">
-        <v>-88320</v>
+        <v>-88342</v>
       </c>
       <c r="S133" s="2" t="inlineStr"/>
     </row>
@@ -6309,22 +6321,22 @@
         <v>-2.845</v>
       </c>
       <c r="N136" t="n">
-        <v>-12683</v>
+        <v>-12730</v>
       </c>
       <c r="O136" t="n">
         <v>0.05</v>
       </c>
       <c r="P136" t="n">
-        <v>-25066</v>
+        <v>-25158</v>
       </c>
       <c r="Q136" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="R136" t="n">
-        <v>-24356</v>
+        <v>-24445</v>
       </c>
       <c r="S136" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="137">
@@ -6374,19 +6386,19 @@
         <v>-2.33</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-10198</v>
+        <v>-10229</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>-30591</v>
+        <v>-30683</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>-29105</v>
+        <v>-29194</v>
       </c>
       <c r="S137" s="2" t="inlineStr"/>
     </row>
@@ -6555,22 +6567,22 @@
         <v>-1.598</v>
       </c>
       <c r="N141" t="n">
-        <v>-8081</v>
+        <v>-8111</v>
       </c>
       <c r="O141" t="n">
         <v>0.02</v>
       </c>
       <c r="P141" t="n">
-        <v>-24244</v>
+        <v>-24333</v>
       </c>
       <c r="Q141" t="n">
-        <v>1855</v>
+        <v>1862</v>
       </c>
       <c r="R141" t="n">
-        <v>-22389</v>
+        <v>-22471</v>
       </c>
       <c r="S141" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="142">
@@ -6620,19 +6632,19 @@
         <v>-2.483</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-14484</v>
+        <v>-14495</v>
       </c>
       <c r="O142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>-115875</v>
+        <v>-115964</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>6823</v>
+        <v>6830</v>
       </c>
       <c r="R142" s="2" t="n">
-        <v>-109052</v>
+        <v>-109134</v>
       </c>
       <c r="S142" s="2" t="inlineStr"/>
     </row>
@@ -6925,22 +6937,22 @@
         <v>-2.222</v>
       </c>
       <c r="N148" t="n">
-        <v>-20978</v>
+        <v>-21055</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>-26600</v>
+        <v>-26698</v>
       </c>
       <c r="Q148" t="n">
-        <v>2040</v>
+        <v>2047</v>
       </c>
       <c r="R148" t="n">
-        <v>-24561</v>
+        <v>-24651</v>
       </c>
       <c r="S148" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="149">
@@ -6990,19 +7002,19 @@
         <v>-1.989</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-14873</v>
+        <v>-14877</v>
       </c>
       <c r="O149" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>-243553</v>
+        <v>-243651</v>
       </c>
       <c r="Q149" s="2" t="n">
-        <v>15095</v>
+        <v>15102</v>
       </c>
       <c r="R149" s="2" t="n">
-        <v>-228459</v>
+        <v>-228549</v>
       </c>
       <c r="S149" s="2" t="inlineStr"/>
     </row>
@@ -7966,7 +7978,7 @@
         <v>-57908</v>
       </c>
       <c r="S174" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="175">
@@ -8350,16 +8362,16 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E183" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="G183" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="H183" t="n">
         <v>4.91</v>
@@ -8371,31 +8383,31 @@
         <v>5.68</v>
       </c>
       <c r="K183" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="L183" t="n">
         <v>1.33</v>
       </c>
       <c r="M183" t="n">
-        <v>-1.043</v>
+        <v>-0.423</v>
       </c>
       <c r="N183" t="n">
-        <v>-2854</v>
+        <v>-1133</v>
       </c>
       <c r="O183" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="P183" t="n">
-        <v>-24928</v>
+        <v>10613</v>
       </c>
       <c r="Q183" t="n">
-        <v>976</v>
+        <v>1369</v>
       </c>
       <c r="R183" t="n">
-        <v>-23951</v>
+        <v>11982</v>
       </c>
       <c r="S183" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="184">
@@ -8415,16 +8427,16 @@
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>4.92</v>
+        <v>4.68</v>
       </c>
       <c r="H184" s="2" t="n">
         <v>5.66</v>
@@ -8436,28 +8448,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="L184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>-0.372</v>
+        <v>-0.09</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-484</v>
+        <v>260</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>-5892</v>
+        <v>29649</v>
       </c>
       <c r="Q184" s="2" t="n">
-        <v>2085</v>
+        <v>2478</v>
       </c>
       <c r="R184" s="2" t="n">
-        <v>-3805</v>
+        <v>32128</v>
       </c>
       <c r="S184" s="2" t="inlineStr"/>
     </row>
@@ -8517,7 +8529,7 @@
         <v>-184319</v>
       </c>
       <c r="S186" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="187">
@@ -10371,20 +10383,20 @@
         <v>1.201</v>
       </c>
       <c r="N233" t="n">
-        <v>3270</v>
+        <v>3282</v>
       </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="n">
-        <v>3141</v>
+        <v>3153</v>
       </c>
       <c r="Q233" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R233" t="n">
-        <v>3227</v>
+        <v>3239</v>
       </c>
       <c r="S233" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="234">
@@ -10426,17 +10438,17 @@
         <v>1.201</v>
       </c>
       <c r="N234" s="2" t="n">
-        <v>3270</v>
+        <v>3282</v>
       </c>
       <c r="O234" s="2" t="inlineStr"/>
       <c r="P234" s="2" t="n">
-        <v>3268</v>
+        <v>3280</v>
       </c>
       <c r="Q234" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R234" s="2" t="n">
-        <v>3459</v>
+        <v>3471</v>
       </c>
       <c r="S234" s="2" t="inlineStr"/>
     </row>
@@ -10496,7 +10508,7 @@
         <v>-1277</v>
       </c>
       <c r="S236" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="237">
@@ -10893,7 +10905,7 @@
         <v>482</v>
       </c>
       <c r="S245" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="246">
@@ -11178,7 +11190,7 @@
         <v>-25748</v>
       </c>
       <c r="S251" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="252">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1672,16 +1672,16 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>14814</v>
+        <v>17538</v>
       </c>
       <c r="Q20" t="n">
-        <v>210</v>
+        <v>309</v>
       </c>
       <c r="R20" t="n">
-        <v>15024</v>
+        <v>17847</v>
       </c>
       <c r="S20" t="n">
-        <v>1339</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="21">
@@ -1733,13 +1733,13 @@
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-40183</v>
+        <v>-37459</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>151748</v>
+        <v>151847</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>111566</v>
+        <v>114389</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -8055,16 +8055,16 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="n">
-        <v>13780</v>
+        <v>16492</v>
       </c>
       <c r="Q176" t="n">
-        <v>167</v>
+        <v>266</v>
       </c>
       <c r="R176" t="n">
-        <v>13948</v>
+        <v>16758</v>
       </c>
       <c r="S176" t="n">
-        <v>1339</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="177">
@@ -8120,13 +8120,13 @@
         <v>0.83</v>
       </c>
       <c r="P177" s="2" t="n">
-        <v>-9911</v>
+        <v>-7199</v>
       </c>
       <c r="Q177" s="2" t="n">
-        <v>5173</v>
+        <v>5272</v>
       </c>
       <c r="R177" s="2" t="n">
-        <v>-4737</v>
+        <v>-1927</v>
       </c>
       <c r="S177" s="2" t="inlineStr"/>
     </row>
@@ -8527,16 +8527,16 @@
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="n">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="Q186" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R186" t="n">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="S186" t="n">
-        <v>1339</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="187">
@@ -8592,13 +8592,13 @@
         <v>1.5</v>
       </c>
       <c r="P187" s="2" t="n">
-        <v>48949</v>
+        <v>48961</v>
       </c>
       <c r="Q187" s="2" t="n">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="R187" s="2" t="n">
-        <v>51795</v>
+        <v>51808</v>
       </c>
       <c r="S187" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1672,13 +1672,13 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>17538</v>
+        <v>16139</v>
       </c>
       <c r="Q20" t="n">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="R20" t="n">
-        <v>17847</v>
+        <v>16492</v>
       </c>
       <c r="S20" t="n">
         <v>1355</v>
@@ -1733,13 +1733,13 @@
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-37459</v>
+        <v>-38858</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>151847</v>
+        <v>151891</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>114389</v>
+        <v>113034</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -8055,13 +8055,13 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="n">
-        <v>16492</v>
+        <v>15093</v>
       </c>
       <c r="Q176" t="n">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="R176" t="n">
-        <v>16758</v>
+        <v>15403</v>
       </c>
       <c r="S176" t="n">
         <v>1355</v>
@@ -8120,13 +8120,13 @@
         <v>0.83</v>
       </c>
       <c r="P177" s="2" t="n">
-        <v>-7199</v>
+        <v>-8598</v>
       </c>
       <c r="Q177" s="2" t="n">
-        <v>5272</v>
+        <v>5316</v>
       </c>
       <c r="R177" s="2" t="n">
-        <v>-1927</v>
+        <v>-3282</v>
       </c>
       <c r="S177" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1658,27 +1658,45 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.46</v>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>-1.288</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-2578</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.7</v>
+      </c>
       <c r="P20" t="n">
-        <v>16139</v>
+        <v>-7597</v>
       </c>
       <c r="Q20" t="n">
-        <v>353</v>
+        <v>1051</v>
       </c>
       <c r="R20" t="n">
-        <v>16492</v>
+        <v>-6546</v>
       </c>
       <c r="S20" t="n">
         <v>1355</v>
@@ -1701,7 +1719,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>39.4</v>
@@ -1710,10 +1728,10 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>29.58</v>
@@ -1724,22 +1742,22 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
-        <v>0.149</v>
+        <v>0.139</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-230</v>
+        <v>-248</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-38858</v>
+        <v>-62594</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>151891</v>
+        <v>152589</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>113034</v>
+        <v>89996</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -8041,27 +8059,49 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E176" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G176" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H176" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="J176" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="K176" t="n">
+        <v>2</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-1.288</v>
+      </c>
+      <c r="N176" t="n">
+        <v>-2578</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.7</v>
+      </c>
       <c r="P176" t="n">
-        <v>15093</v>
+        <v>-8644</v>
       </c>
       <c r="Q176" t="n">
-        <v>310</v>
+        <v>1009</v>
       </c>
       <c r="R176" t="n">
-        <v>15403</v>
+        <v>-7635</v>
       </c>
       <c r="S176" t="n">
         <v>1355</v>
@@ -8084,49 +8124,49 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>6.81</v>
+        <v>7.11</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>3.94</v>
+        <v>4.38</v>
       </c>
       <c r="I177" s="2" t="n">
         <v>17.63</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>5.38</v>
+        <v>6.46</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="L177" s="2" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="M177" s="2" t="n">
-        <v>0.364</v>
+        <v>0.089</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-1268</v>
+        <v>-1486</v>
       </c>
       <c r="O177" s="2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="P177" s="2" t="n">
-        <v>-8598</v>
+        <v>-32335</v>
       </c>
       <c r="Q177" s="2" t="n">
-        <v>5316</v>
+        <v>6015</v>
       </c>
       <c r="R177" s="2" t="n">
-        <v>-3282</v>
+        <v>-26320</v>
       </c>
       <c r="S177" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1684,22 +1684,22 @@
         <v>-0.536</v>
       </c>
       <c r="N20" t="n">
-        <v>-1750</v>
+        <v>-1757</v>
       </c>
       <c r="O20" t="n">
         <v>0.77</v>
       </c>
       <c r="P20" t="n">
-        <v>34393</v>
+        <v>34858</v>
       </c>
       <c r="Q20" t="n">
-        <v>4964</v>
+        <v>5007</v>
       </c>
       <c r="R20" t="n">
-        <v>39357</v>
+        <v>39866</v>
       </c>
       <c r="S20" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="21">
@@ -1751,13 +1751,13 @@
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-20604</v>
+        <v>-20139</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>156502</v>
+        <v>156545</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>135899</v>
+        <v>136408</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -5633,22 +5633,22 @@
         <v>-0.494</v>
       </c>
       <c r="N117" t="n">
-        <v>-7393</v>
+        <v>-7476</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>44964</v>
+        <v>45468</v>
       </c>
       <c r="Q117" t="n">
-        <v>2979</v>
+        <v>3012</v>
       </c>
       <c r="R117" t="n">
-        <v>47942</v>
+        <v>48481</v>
       </c>
       <c r="S117" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="118">
@@ -5674,7 +5674,7 @@
         <v>35.3</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>3.47</v>
@@ -5698,19 +5698,19 @@
         <v>-1.007</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-17963</v>
+        <v>-17965</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>0.38</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>-502879</v>
+        <v>-502375</v>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>52229</v>
+        <v>52262</v>
       </c>
       <c r="R118" s="2" t="n">
-        <v>-450651</v>
+        <v>-450112</v>
       </c>
       <c r="S118" s="2" t="inlineStr"/>
     </row>
@@ -5818,20 +5818,20 @@
         <v>1.162</v>
       </c>
       <c r="N121" t="n">
-        <v>4391</v>
+        <v>4440</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>9995</v>
+        <v>10108</v>
       </c>
       <c r="Q121" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="R121" t="n">
-        <v>10268</v>
+        <v>10383</v>
       </c>
       <c r="S121" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="122">
@@ -5881,19 +5881,19 @@
         <v>0.823</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>1.67</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>29492</v>
+        <v>29605</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>8339</v>
+        <v>8342</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>37833</v>
+        <v>37948</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -6545,16 +6545,16 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="n">
-        <v>-5050</v>
+        <v>-5107</v>
       </c>
       <c r="Q140" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="R140" t="n">
-        <v>-4703</v>
+        <v>-4756</v>
       </c>
       <c r="S140" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="141">
@@ -6610,13 +6610,13 @@
         <v>0.04</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>-35733</v>
+        <v>-35790</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="R141" s="2" t="n">
-        <v>-33897</v>
+        <v>-33950</v>
       </c>
       <c r="S141" s="2" t="inlineStr"/>
     </row>
@@ -8261,7 +8261,7 @@
         <v>-5960</v>
       </c>
       <c r="S179" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="180">
@@ -8740,22 +8740,22 @@
         <v>-0.279</v>
       </c>
       <c r="N189" t="n">
-        <v>-758</v>
+        <v>-766</v>
       </c>
       <c r="O189" t="n">
         <v>0.93</v>
       </c>
       <c r="P189" t="n">
-        <v>-8456</v>
+        <v>-8551</v>
       </c>
       <c r="Q189" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R189" t="n">
-        <v>-8190</v>
+        <v>-8282</v>
       </c>
       <c r="S189" t="n">
-        <v>1336</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="190">
@@ -8805,19 +8805,19 @@
         <v>0.704</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>39459</v>
+        <v>39364</v>
       </c>
       <c r="Q190" s="2" t="n">
-        <v>3069</v>
+        <v>3072</v>
       </c>
       <c r="R190" s="2" t="n">
-        <v>42529</v>
+        <v>42437</v>
       </c>
       <c r="S190" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1690,13 +1690,13 @@
         <v>0.77</v>
       </c>
       <c r="P20" t="n">
-        <v>34858</v>
+        <v>34768</v>
       </c>
       <c r="Q20" t="n">
-        <v>5007</v>
+        <v>5050</v>
       </c>
       <c r="R20" t="n">
-        <v>39866</v>
+        <v>39818</v>
       </c>
       <c r="S20" t="n">
         <v>1351</v>
@@ -1751,13 +1751,13 @@
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-20139</v>
+        <v>-20229</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>156545</v>
+        <v>156588</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>136408</v>
+        <v>136360</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -8252,13 +8252,13 @@
         <v>0.7</v>
       </c>
       <c r="P179" t="n">
-        <v>-7060</v>
+        <v>-7150</v>
       </c>
       <c r="Q179" t="n">
-        <v>1100</v>
+        <v>1142</v>
       </c>
       <c r="R179" t="n">
-        <v>-5960</v>
+        <v>-6008</v>
       </c>
       <c r="S179" t="n">
         <v>1351</v>
@@ -8317,13 +8317,13 @@
         <v>0.8</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>-30751</v>
+        <v>-30841</v>
       </c>
       <c r="Q180" s="2" t="n">
-        <v>6106</v>
+        <v>6148</v>
       </c>
       <c r="R180" s="2" t="n">
-        <v>-24645</v>
+        <v>-24693</v>
       </c>
       <c r="S180" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>5.79</v>
+        <v>5.34</v>
       </c>
       <c r="H20" t="n">
         <v>5.28</v>
@@ -1681,25 +1681,25 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>-0.536</v>
+        <v>0.028</v>
       </c>
       <c r="N20" t="n">
-        <v>-1757</v>
+        <v>301</v>
       </c>
       <c r="O20" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="P20" t="n">
-        <v>34768</v>
+        <v>94105</v>
       </c>
       <c r="Q20" t="n">
-        <v>5050</v>
+        <v>6585</v>
       </c>
       <c r="R20" t="n">
-        <v>39818</v>
+        <v>100690</v>
       </c>
       <c r="S20" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="21">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1.49</v>
@@ -1742,22 +1742,22 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
-        <v>0.138</v>
+        <v>0.147</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-256</v>
+        <v>-220</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0.97</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>-20229</v>
+        <v>39108</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>156588</v>
+        <v>158123</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>136360</v>
+        <v>197232</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -5633,22 +5633,22 @@
         <v>-0.494</v>
       </c>
       <c r="N117" t="n">
-        <v>-7476</v>
+        <v>-7487</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>45468</v>
+        <v>93351</v>
       </c>
       <c r="Q117" t="n">
-        <v>3012</v>
+        <v>3882</v>
       </c>
       <c r="R117" t="n">
-        <v>48481</v>
+        <v>97233</v>
       </c>
       <c r="S117" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="118">
@@ -5698,19 +5698,19 @@
         <v>-1.007</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-17965</v>
+        <v>-17966</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>0.38</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>-502375</v>
+        <v>-454492</v>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>52262</v>
+        <v>53132</v>
       </c>
       <c r="R118" s="2" t="n">
-        <v>-450112</v>
+        <v>-401360</v>
       </c>
       <c r="S118" s="2" t="inlineStr"/>
     </row>
@@ -5796,42 +5796,42 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>1.16</v>
+        <v>2.57</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>1.16</v>
+        <v>3.98</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>1.162</v>
+        <v>2.57</v>
       </c>
       <c r="N121" t="n">
-        <v>4440</v>
+        <v>9583</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>10108</v>
+        <v>21581</v>
       </c>
       <c r="Q121" t="n">
-        <v>275</v>
+        <v>940</v>
       </c>
       <c r="R121" t="n">
-        <v>10383</v>
+        <v>22521</v>
       </c>
       <c r="S121" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="122">
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>1.49</v>
@@ -5872,28 +5872,28 @@
         <v>3.77</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>1.83</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>0.823</v>
+        <v>1.034</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>2071</v>
+        <v>2915</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>29605</v>
+        <v>41078</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>8342</v>
+        <v>9007</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>37948</v>
+        <v>50086</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -6545,16 +6545,16 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="n">
-        <v>-5107</v>
+        <v>-5114</v>
       </c>
       <c r="Q140" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R140" t="n">
-        <v>-4756</v>
+        <v>-4763</v>
       </c>
       <c r="S140" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="141">
@@ -6610,13 +6610,13 @@
         <v>0.04</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>-35790</v>
+        <v>-35797</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="R141" s="2" t="n">
-        <v>-33950</v>
+        <v>-33957</v>
       </c>
       <c r="S141" s="2" t="inlineStr"/>
     </row>
@@ -8261,7 +8261,7 @@
         <v>-6008</v>
       </c>
       <c r="S179" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="180">
@@ -8740,22 +8740,22 @@
         <v>-0.279</v>
       </c>
       <c r="N189" t="n">
-        <v>-766</v>
+        <v>-767</v>
       </c>
       <c r="O189" t="n">
         <v>0.93</v>
       </c>
       <c r="P189" t="n">
-        <v>-8551</v>
+        <v>-8564</v>
       </c>
       <c r="Q189" t="n">
         <v>269</v>
       </c>
       <c r="R189" t="n">
-        <v>-8282</v>
+        <v>-8294</v>
       </c>
       <c r="S189" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="190">
@@ -8811,13 +8811,13 @@
         <v>1.38</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>39364</v>
+        <v>39351</v>
       </c>
       <c r="Q190" s="2" t="n">
         <v>3072</v>
       </c>
       <c r="R190" s="2" t="n">
-        <v>42437</v>
+        <v>42425</v>
       </c>
       <c r="S190" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>0.53</v>
       </c>
       <c r="G20" t="n">
-        <v>5.34</v>
+        <v>4.28</v>
       </c>
       <c r="H20" t="n">
-        <v>5.28</v>
+        <v>4.64</v>
       </c>
       <c r="I20" t="n">
         <v>8.890000000000001</v>
@@ -1681,22 +1681,22 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>0.028</v>
+        <v>-0.182</v>
       </c>
       <c r="N20" t="n">
-        <v>301</v>
+        <v>-4976</v>
       </c>
       <c r="O20" t="n">
-        <v>1.04</v>
+        <v>0.53</v>
       </c>
       <c r="P20" t="n">
-        <v>94105</v>
+        <v>86618</v>
       </c>
       <c r="Q20" t="n">
-        <v>6585</v>
+        <v>7673</v>
       </c>
       <c r="R20" t="n">
-        <v>100690</v>
+        <v>94291</v>
       </c>
       <c r="S20" t="n">
         <v>1353</v>
@@ -1719,16 +1719,16 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.78</v>
@@ -1742,22 +1742,22 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
-        <v>0.147</v>
+        <v>0.141</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-220</v>
+        <v>-345</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>39108</v>
+        <v>31621</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>158123</v>
+        <v>159211</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>197232</v>
+        <v>190833</v>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -5619,33 +5619,33 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0.49</v>
+        <v>1.28</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>0.49</v>
+        <v>2.07</v>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.494</v>
+        <v>-1.285</v>
       </c>
       <c r="N117" t="n">
-        <v>-7487</v>
+        <v>-29865</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>93351</v>
+        <v>85890</v>
       </c>
       <c r="Q117" t="n">
-        <v>3882</v>
+        <v>4957</v>
       </c>
       <c r="R117" t="n">
-        <v>97233</v>
+        <v>90847</v>
       </c>
       <c r="S117" t="n">
         <v>1353</v>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>35.3</v>
+        <v>34.3</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0.7</v>
@@ -5680,7 +5680,7 @@
         <v>3.47</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="I118" s="2" t="n">
         <v>8.369999999999999</v>
@@ -5692,25 +5692,25 @@
         <v>14.58</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>-1.007</v>
+        <v>-1.037</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-17966</v>
+        <v>-18945</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>-454492</v>
+        <v>-461953</v>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>53132</v>
+        <v>54207</v>
       </c>
       <c r="R118" s="2" t="n">
-        <v>-401360</v>
+        <v>-407746</v>
       </c>
       <c r="S118" s="2" t="inlineStr"/>
     </row>
@@ -8216,16 +8216,16 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F179" t="n">
-        <v>1.39</v>
+        <v>0.7</v>
       </c>
       <c r="G179" t="n">
-        <v>8.890000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="H179" t="n">
         <v>6.38</v>
@@ -8237,28 +8237,28 @@
         <v>6.46</v>
       </c>
       <c r="K179" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L179" t="n">
         <v>1.5</v>
       </c>
       <c r="M179" t="n">
-        <v>-1.288</v>
+        <v>-0.957</v>
       </c>
       <c r="N179" t="n">
-        <v>-2578</v>
+        <v>-1916</v>
       </c>
       <c r="O179" t="n">
         <v>0.7</v>
       </c>
       <c r="P179" t="n">
-        <v>-7150</v>
+        <v>-7176</v>
       </c>
       <c r="Q179" t="n">
-        <v>1142</v>
+        <v>1156</v>
       </c>
       <c r="R179" t="n">
-        <v>-6008</v>
+        <v>-6020</v>
       </c>
       <c r="S179" t="n">
         <v>1353</v>
@@ -8281,16 +8281,16 @@
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>7.11</v>
+        <v>6.23</v>
       </c>
       <c r="H180" s="2" t="n">
         <v>4.38</v>
@@ -8302,28 +8302,28 @@
         <v>6.46</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="L180" s="2" t="n">
         <v>2.27</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-1486</v>
+        <v>-1404</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>-30841</v>
+        <v>-30867</v>
       </c>
       <c r="Q180" s="2" t="n">
-        <v>6148</v>
+        <v>6162</v>
       </c>
       <c r="R180" s="2" t="n">
-        <v>-24693</v>
+        <v>-24705</v>
       </c>
       <c r="S180" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1745,22 +1745,22 @@
         <v>1.9</v>
       </c>
       <c r="N21" t="n">
-        <v>6191</v>
+        <v>6293</v>
       </c>
       <c r="O21" t="n">
         <v>1.87</v>
       </c>
       <c r="P21" t="n">
-        <v>-520015</v>
+        <v>-519033</v>
       </c>
       <c r="Q21" t="n">
-        <v>9073</v>
+        <v>9213</v>
       </c>
       <c r="R21" t="n">
-        <v>-510941</v>
+        <v>-509820</v>
       </c>
       <c r="S21" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="22">
@@ -1806,19 +1806,19 @@
         <v>0.136</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>-440125</v>
+        <v>-439143</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>182700</v>
+        <v>182840</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>-257424</v>
+        <v>-256303</v>
       </c>
       <c r="S22" s="2" t="inlineStr"/>
     </row>
@@ -3291,7 +3291,7 @@
         <v>-578762</v>
       </c>
       <c r="S53" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="54">
@@ -5802,22 +5802,22 @@
         <v>-2.398</v>
       </c>
       <c r="N120" t="n">
-        <v>-22487</v>
+        <v>-22859</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-44974</v>
+        <v>-45717</v>
       </c>
       <c r="Q120" t="n">
-        <v>2581</v>
+        <v>2624</v>
       </c>
       <c r="R120" t="n">
-        <v>-42392</v>
+        <v>-43093</v>
       </c>
       <c r="S120" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="121">
@@ -5867,19 +5867,19 @@
         <v>-0.651</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-11164</v>
+        <v>-11184</v>
       </c>
       <c r="O121" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>-447683</v>
+        <v>-448426</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>58709</v>
+        <v>58752</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>-388973</v>
+        <v>-389674</v>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
     </row>
@@ -6054,22 +6054,22 @@
         <v>-2.027</v>
       </c>
       <c r="N125" t="n">
-        <v>-19259</v>
+        <v>-19577</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-6033</v>
+        <v>-6133</v>
       </c>
       <c r="Q125" t="n">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="R125" t="n">
-        <v>-5484</v>
+        <v>-5574</v>
       </c>
       <c r="S125" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="126">
@@ -6119,19 +6119,19 @@
         <v>-0.74</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-5480</v>
+        <v>-5497</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0.34</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-76283</v>
+        <v>-76383</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>14026</v>
+        <v>14035</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-62256</v>
+        <v>-62346</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6229,20 +6229,20 @@
         <v>2.926</v>
       </c>
       <c r="N129" t="n">
-        <v>26752</v>
+        <v>27194</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>26752</v>
+        <v>27194</v>
       </c>
       <c r="Q129" t="n">
-        <v>1299</v>
+        <v>1320</v>
       </c>
       <c r="R129" t="n">
-        <v>28051</v>
+        <v>28514</v>
       </c>
       <c r="S129" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="130">
@@ -6284,17 +6284,17 @@
         <v>2.557</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>23340</v>
+        <v>23561</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="n">
-        <v>46680</v>
+        <v>47122</v>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>2587</v>
+        <v>2608</v>
       </c>
       <c r="R130" s="2" t="n">
-        <v>49267</v>
+        <v>49730</v>
       </c>
       <c r="S130" s="2" t="inlineStr"/>
     </row>
@@ -6437,16 +6437,16 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>-6574</v>
+        <v>-6683</v>
       </c>
       <c r="Q134" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="R134" t="n">
-        <v>-6282</v>
+        <v>-6386</v>
       </c>
       <c r="S134" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="135">
@@ -6502,13 +6502,13 @@
         <v>0.02</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>-75921</v>
+        <v>-76030</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>2500</v>
+        <v>2505</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>-73421</v>
+        <v>-73525</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -7298,20 +7298,20 @@
         <v>4.867</v>
       </c>
       <c r="N154" t="n">
-        <v>16421</v>
+        <v>16693</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="n">
-        <v>60624</v>
+        <v>61627</v>
       </c>
       <c r="Q154" t="n">
-        <v>1746</v>
+        <v>1775</v>
       </c>
       <c r="R154" t="n">
-        <v>62371</v>
+        <v>63402</v>
       </c>
       <c r="S154" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="155">
@@ -7337,7 +7337,7 @@
         <v>50</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>4.37</v>
@@ -7361,19 +7361,19 @@
         <v>0.756</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-88</v>
+        <v>-11</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="P155" s="2" t="n">
-        <v>-1157</v>
+        <v>-154</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>10048</v>
+        <v>10077</v>
       </c>
       <c r="R155" s="2" t="n">
-        <v>8892</v>
+        <v>9923</v>
       </c>
       <c r="S155" s="2" t="inlineStr"/>
     </row>
@@ -7778,20 +7778,20 @@
         <v>1.534</v>
       </c>
       <c r="N163" t="n">
-        <v>27510</v>
+        <v>27965</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="n">
-        <v>29579</v>
+        <v>30068</v>
       </c>
       <c r="Q163" t="n">
-        <v>1979</v>
+        <v>2011</v>
       </c>
       <c r="R163" t="n">
-        <v>31558</v>
+        <v>32080</v>
       </c>
       <c r="S163" t="n">
-        <v>1331</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="164">
@@ -7841,19 +7841,19 @@
         <v>-1.031</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-7100</v>
+        <v>-7075</v>
       </c>
       <c r="O164" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>-134297</v>
+        <v>-133808</v>
       </c>
       <c r="Q164" s="2" t="n">
-        <v>18291</v>
+        <v>18323</v>
       </c>
       <c r="R164" s="2" t="n">
-        <v>-116006</v>
+        <v>-115484</v>
       </c>
       <c r="S164" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1719,48 +1719,48 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="F21" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99</v>
+        <v>4.12</v>
       </c>
       <c r="H21" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="I21" t="n">
         <v>7.16</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>4.83</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>1.9</v>
+        <v>1.564</v>
       </c>
       <c r="N21" t="n">
-        <v>6293</v>
+        <v>4116</v>
       </c>
       <c r="O21" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>-519033</v>
+        <v>-524131</v>
       </c>
       <c r="Q21" t="n">
-        <v>9213</v>
+        <v>10077</v>
       </c>
       <c r="R21" t="n">
-        <v>-509820</v>
+        <v>-514054</v>
       </c>
       <c r="S21" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="22">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>4.65</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>29.58</v>
@@ -1806,19 +1806,19 @@
         <v>0.136</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>-439143</v>
+        <v>-444241</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>182840</v>
+        <v>183704</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>-256303</v>
+        <v>-260537</v>
       </c>
       <c r="S22" s="2" t="inlineStr"/>
     </row>
@@ -3291,7 +3291,7 @@
         <v>-578762</v>
       </c>
       <c r="S53" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="54">
@@ -5802,22 +5802,22 @@
         <v>-2.398</v>
       </c>
       <c r="N120" t="n">
-        <v>-22859</v>
+        <v>-22504</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-45717</v>
+        <v>-45008</v>
       </c>
       <c r="Q120" t="n">
-        <v>2624</v>
+        <v>2583</v>
       </c>
       <c r="R120" t="n">
-        <v>-43093</v>
+        <v>-42424</v>
       </c>
       <c r="S120" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="121">
@@ -5867,19 +5867,19 @@
         <v>-0.651</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-11184</v>
+        <v>-11165</v>
       </c>
       <c r="O121" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>-448426</v>
+        <v>-447717</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>58752</v>
+        <v>58711</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>-389674</v>
+        <v>-389005</v>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
     </row>
@@ -6030,46 +6030,52 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
+        <v>0.93</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.93</v>
+      </c>
       <c r="H125" t="n">
         <v>2.03</v>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>4.93</v>
+      </c>
       <c r="J125" t="n">
         <v>2.03</v>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>6</v>
+      </c>
       <c r="L125" t="n">
         <v>16</v>
       </c>
       <c r="M125" t="n">
-        <v>-2.027</v>
+        <v>1.45</v>
       </c>
       <c r="N125" t="n">
-        <v>-19577</v>
+        <v>-709</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="P125" t="n">
-        <v>-6133</v>
+        <v>11818</v>
       </c>
       <c r="Q125" t="n">
-        <v>558</v>
+        <v>1069</v>
       </c>
       <c r="R125" t="n">
-        <v>-5574</v>
+        <v>12887</v>
       </c>
       <c r="S125" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="126">
@@ -6089,16 +6095,16 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>33.3</v>
+        <v>36.8</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>2.31</v>
@@ -6110,28 +6116,28 @@
         <v>4.78</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>5.25</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.441</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-5497</v>
+        <v>-4252</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-76383</v>
+        <v>-58432</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>14035</v>
+        <v>14546</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-62346</v>
+        <v>-43885</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6229,20 +6235,20 @@
         <v>2.926</v>
       </c>
       <c r="N129" t="n">
-        <v>27194</v>
+        <v>26772</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>27194</v>
+        <v>26772</v>
       </c>
       <c r="Q129" t="n">
-        <v>1320</v>
+        <v>1300</v>
       </c>
       <c r="R129" t="n">
-        <v>28514</v>
+        <v>28072</v>
       </c>
       <c r="S129" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="130">
@@ -6284,17 +6290,17 @@
         <v>2.557</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>23561</v>
+        <v>23350</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="n">
-        <v>47122</v>
+        <v>46700</v>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>2608</v>
+        <v>2588</v>
       </c>
       <c r="R130" s="2" t="n">
-        <v>49730</v>
+        <v>49288</v>
       </c>
       <c r="S130" s="2" t="inlineStr"/>
     </row>
@@ -6437,16 +6443,16 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>-6683</v>
+        <v>-6579</v>
       </c>
       <c r="Q134" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="R134" t="n">
-        <v>-6386</v>
+        <v>-6287</v>
       </c>
       <c r="S134" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="135">
@@ -6502,13 +6508,13 @@
         <v>0.02</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>-76030</v>
+        <v>-75926</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>2505</v>
+        <v>2500</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>-73525</v>
+        <v>-73426</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -7298,20 +7304,20 @@
         <v>4.867</v>
       </c>
       <c r="N154" t="n">
-        <v>16693</v>
+        <v>16434</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="n">
-        <v>61627</v>
+        <v>60670</v>
       </c>
       <c r="Q154" t="n">
-        <v>1775</v>
+        <v>1748</v>
       </c>
       <c r="R154" t="n">
-        <v>63402</v>
+        <v>62418</v>
       </c>
       <c r="S154" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="155">
@@ -7337,7 +7343,7 @@
         <v>50</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>4.37</v>
@@ -7361,19 +7367,19 @@
         <v>0.756</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-11</v>
+        <v>-85</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="P155" s="2" t="n">
-        <v>-154</v>
+        <v>-1111</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>10077</v>
+        <v>10050</v>
       </c>
       <c r="R155" s="2" t="n">
-        <v>9923</v>
+        <v>8939</v>
       </c>
       <c r="S155" s="2" t="inlineStr"/>
     </row>
@@ -7756,42 +7762,52 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>100</v>
-      </c>
-      <c r="F163" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.97</v>
+      </c>
       <c r="G163" t="n">
         <v>1.53</v>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>4.83</v>
+      </c>
       <c r="I163" t="n">
         <v>1.53</v>
       </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="J163" t="n">
+        <v>4.83</v>
+      </c>
       <c r="K163" t="n">
         <v>16</v>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>5</v>
+      </c>
       <c r="M163" t="n">
-        <v>1.534</v>
+        <v>-1.647</v>
       </c>
       <c r="N163" t="n">
-        <v>27965</v>
-      </c>
-      <c r="O163" t="inlineStr"/>
+        <v>-402</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.97</v>
+      </c>
       <c r="P163" t="n">
-        <v>30068</v>
+        <v>7586</v>
       </c>
       <c r="Q163" t="n">
-        <v>2011</v>
+        <v>2458</v>
       </c>
       <c r="R163" t="n">
-        <v>32080</v>
+        <v>10043</v>
       </c>
       <c r="S163" t="n">
-        <v>1353</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="164">
@@ -7811,19 +7827,19 @@
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>33.3</v>
+        <v>31.6</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="G164" s="2" t="n">
         <v>3.33</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>3.21</v>
+        <v>3.34</v>
       </c>
       <c r="I164" s="2" t="n">
         <v>11.73</v>
@@ -7835,25 +7851,25 @@
         <v>11.33</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>6.42</v>
+        <v>6.31</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>-1.031</v>
+        <v>-1.231</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-7075</v>
+        <v>-8217</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>-133808</v>
+        <v>-156290</v>
       </c>
       <c r="Q164" s="2" t="n">
-        <v>18323</v>
+        <v>18770</v>
       </c>
       <c r="R164" s="2" t="n">
-        <v>-115484</v>
+        <v>-137521</v>
       </c>
       <c r="S164" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S283"/>
+  <dimension ref="A1:S285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
-        <v>37.7</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="H19" t="n">
         <v>3.54</v>
@@ -1620,22 +1620,22 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>-1.087</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-10437</v>
+        <v>-10004</v>
       </c>
       <c r="O19" t="n">
         <v>0.28</v>
       </c>
       <c r="P19" t="n">
-        <v>-501731</v>
+        <v>-500490</v>
       </c>
       <c r="Q19" t="n">
-        <v>39007</v>
+        <v>39018</v>
       </c>
       <c r="R19" t="n">
-        <v>-462725</v>
+        <v>-461471</v>
       </c>
       <c r="S19" t="n">
         <v>1371</v>
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="G21" t="n">
-        <v>4.12</v>
+        <v>3.84</v>
       </c>
       <c r="H21" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="I21" t="n">
         <v>7.16</v>
@@ -1742,25 +1742,25 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>1.168</v>
+        <v>-0.179</v>
       </c>
       <c r="N21" t="n">
-        <v>1520</v>
+        <v>-2160</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="P21" t="n">
-        <v>-534281</v>
+        <v>-559533</v>
       </c>
       <c r="Q21" t="n">
-        <v>10455</v>
+        <v>15989</v>
       </c>
       <c r="R21" t="n">
-        <v>-523826</v>
+        <v>-543544</v>
       </c>
       <c r="S21" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="22">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>4.65</v>
@@ -1803,22 +1803,22 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="n">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>298</v>
+        <v>165</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>-454391</v>
+        <v>-478402</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>184082</v>
+        <v>189627</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>-270309</v>
+        <v>-288773</v>
       </c>
       <c r="S22" s="2" t="inlineStr"/>
     </row>
@@ -3291,7 +3291,7 @@
         <v>-578762</v>
       </c>
       <c r="S53" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="54">
@@ -5802,22 +5802,22 @@
         <v>-2.398</v>
       </c>
       <c r="N120" t="n">
-        <v>-22436</v>
+        <v>-22571</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-44872</v>
+        <v>-15981</v>
       </c>
       <c r="Q120" t="n">
-        <v>2576</v>
+        <v>4197</v>
       </c>
       <c r="R120" t="n">
-        <v>-42297</v>
+        <v>-11784</v>
       </c>
       <c r="S120" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="121">
@@ -5867,19 +5867,19 @@
         <v>-0.651</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-11162</v>
+        <v>-11169</v>
       </c>
       <c r="O121" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>-447581</v>
+        <v>-418690</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>58704</v>
+        <v>60325</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>-388878</v>
+        <v>-358365</v>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
     </row>
@@ -6060,22 +6060,22 @@
         <v>1.45</v>
       </c>
       <c r="N125" t="n">
-        <v>-707</v>
+        <v>-711</v>
       </c>
       <c r="O125" t="n">
         <v>0.93</v>
       </c>
       <c r="P125" t="n">
-        <v>11782</v>
+        <v>11853</v>
       </c>
       <c r="Q125" t="n">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="R125" t="n">
-        <v>12848</v>
+        <v>12926</v>
       </c>
       <c r="S125" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="126">
@@ -6125,19 +6125,19 @@
         <v>-0.441</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-4252</v>
+        <v>-4253</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>0.46</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>-58468</v>
+        <v>-58397</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>14543</v>
+        <v>14550</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>-43924</v>
+        <v>-43846</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>
@@ -6235,20 +6235,20 @@
         <v>2.926</v>
       </c>
       <c r="N129" t="n">
-        <v>26692</v>
+        <v>26853</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>26692</v>
+        <v>26853</v>
       </c>
       <c r="Q129" t="n">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="R129" t="n">
-        <v>27988</v>
+        <v>28156</v>
       </c>
       <c r="S129" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="130">
@@ -6290,17 +6290,17 @@
         <v>2.557</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>23310</v>
+        <v>23390</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="n">
-        <v>46620</v>
+        <v>46781</v>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>2584</v>
+        <v>2592</v>
       </c>
       <c r="R130" s="2" t="n">
-        <v>49204</v>
+        <v>49372</v>
       </c>
       <c r="S130" s="2" t="inlineStr"/>
     </row>
@@ -6453,22 +6453,22 @@
         <v>-3.183</v>
       </c>
       <c r="N134" t="n">
-        <v>-26901</v>
+        <v>-27063</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>-13477</v>
+        <v>-13558</v>
       </c>
       <c r="Q134" t="n">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="R134" t="n">
-        <v>-12895</v>
+        <v>-12973</v>
       </c>
       <c r="S134" t="n">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="135">
@@ -6518,19 +6518,19 @@
         <v>-3.805</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-20645</v>
+        <v>-20686</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>-82824</v>
+        <v>-82905</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>2790</v>
+        <v>2794</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>-80034</v>
+        <v>-80112</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
@@ -6981,126 +6981,126 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>US_TR_BASE</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>10/19~10/23</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>6</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-1.164</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-3027</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>-1414</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>686</v>
+      </c>
+      <c r="R148" t="n">
+        <v>-728</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G148" s="2" t="n">
+      <c r="D149" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G149" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="H148" s="2" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="I148" s="2" t="n">
+      <c r="H149" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="I149" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J149" s="2" t="n">
         <v>6.02</v>
       </c>
-      <c r="K148" s="2" t="n">
+      <c r="K149" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L148" s="2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="M148" s="2" t="n">
-        <v>-2.329</v>
-      </c>
-      <c r="N148" s="2" t="n">
-        <v>-13213</v>
-      </c>
-      <c r="O148" s="2" t="n">
+      <c r="L149" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-2.135</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-11515</v>
+      </c>
+      <c r="O149" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="P148" s="2" t="n">
-        <v>-66061</v>
-      </c>
-      <c r="Q148" s="2" t="n">
-        <v>3709</v>
-      </c>
-      <c r="R148" s="2" t="n">
-        <v>-62352</v>
-      </c>
-      <c r="S148" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R150" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S150" t="n">
-        <v>1373</v>
-      </c>
+      <c r="P149" s="2" t="n">
+        <v>-67475</v>
+      </c>
+      <c r="Q149" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>-63080</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7115,11 +7115,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>09/28~10/02</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -7129,36 +7129,36 @@
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>3.23</v>
+        <v>2.13</v>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
-        <v>5.33</v>
+        <v>2.13</v>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-3.235</v>
+        <v>-2.131</v>
       </c>
       <c r="N151" t="n">
-        <v>-12511</v>
+        <v>-41586</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>-50045</v>
+        <v>-41586</v>
       </c>
       <c r="Q151" t="n">
-        <v>2266</v>
+        <v>2702</v>
       </c>
       <c r="R151" t="n">
-        <v>-47780</v>
+        <v>-38883</v>
       </c>
       <c r="S151" t="n">
-        <v>1352</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="152">
@@ -7174,56 +7174,50 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E152" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0.13</v>
-      </c>
+        <v>3.23</v>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="K152" t="n">
-        <v>1</v>
-      </c>
+        <v>5.33</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.598</v>
+        <v>-3.235</v>
       </c>
       <c r="N152" t="n">
-        <v>-8111</v>
+        <v>-12511</v>
       </c>
       <c r="O152" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>-24333</v>
+        <v>-50045</v>
       </c>
       <c r="Q152" t="n">
-        <v>1862</v>
+        <v>2266</v>
       </c>
       <c r="R152" t="n">
-        <v>-22471</v>
+        <v>-47780</v>
       </c>
       <c r="S152" t="n">
-        <v>1371</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="153">
@@ -7239,46 +7233,56 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>10/12~10/16</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.04</v>
+      </c>
       <c r="G153" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
+        <v>0.13</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2.46</v>
+      </c>
       <c r="I153" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
+        <v>0.13</v>
+      </c>
+      <c r="J153" t="n">
+        <v>2.97</v>
+      </c>
       <c r="K153" t="n">
-        <v>14</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M153" t="n">
-        <v>5.494</v>
+        <v>-1.598</v>
       </c>
       <c r="N153" t="n">
-        <v>24521</v>
-      </c>
-      <c r="O153" t="inlineStr"/>
+        <v>-8111</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P153" t="n">
-        <v>54183</v>
+        <v>-24333</v>
       </c>
       <c r="Q153" t="n">
-        <v>1472</v>
+        <v>1862</v>
       </c>
       <c r="R153" t="n">
-        <v>55655</v>
+        <v>-22471</v>
       </c>
       <c r="S153" t="n">
-        <v>1352</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="154">
@@ -7294,169 +7298,175 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>10/19~10/23</t>
+          <t>10/12~10/16</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>100</v>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>4.87</v>
+        <v>5.49</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>7.16</v>
+        <v>6.37</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
-        <v>4.867</v>
+        <v>5.494</v>
       </c>
       <c r="N154" t="n">
-        <v>16384</v>
+        <v>24521</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="n">
-        <v>60488</v>
+        <v>54183</v>
       </c>
       <c r="Q154" t="n">
-        <v>1742</v>
+        <v>1472</v>
       </c>
       <c r="R154" t="n">
-        <v>62230</v>
+        <v>55655</v>
       </c>
       <c r="S154" t="n">
-        <v>1328</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10/19~10/23</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>80</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H155" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="J155" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="K155" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L155" t="n">
+        <v>6</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.059</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5478</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P155" t="n">
+        <v>22311</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>3019</v>
+      </c>
+      <c r="R155" t="n">
+        <v>25331</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="G155" s="2" t="n">
+      <c r="D156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G156" s="2" t="n">
         <v>4.37</v>
       </c>
-      <c r="H155" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I155" s="2" t="n">
+      <c r="H156" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I156" s="2" t="n">
         <v>7.16</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J156" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="K155" s="2" t="n">
+      <c r="K156" s="2" t="n">
         <v>12.43</v>
       </c>
-      <c r="L155" s="2" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="M155" s="2" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>-99</v>
-      </c>
-      <c r="O155" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="P155" s="2" t="n">
-        <v>-1293</v>
-      </c>
-      <c r="Q155" s="2" t="n">
-        <v>10044</v>
-      </c>
-      <c r="R155" s="2" t="n">
-        <v>8751</v>
-      </c>
-      <c r="S155" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>7</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="n">
-        <v>8</v>
-      </c>
-      <c r="M157" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N157" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R157" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S157" t="n">
-        <v>1373</v>
-      </c>
+      <c r="L156" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>-2635</v>
+      </c>
+      <c r="O156" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>-39470</v>
+      </c>
+      <c r="Q156" s="2" t="n">
+        <v>11321</v>
+      </c>
+      <c r="R156" s="2" t="n">
+        <v>-28148</v>
+      </c>
+      <c r="S156" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7471,56 +7481,50 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E158" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I158" t="n">
-        <v>3.32</v>
-      </c>
+        <v>3.34</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K158" t="n">
-        <v>18</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M158" t="n">
-        <v>0.864</v>
+        <v>-3.337</v>
       </c>
       <c r="N158" t="n">
-        <v>-18508</v>
+        <v>-7859</v>
       </c>
       <c r="O158" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>-52375</v>
+        <v>-55013</v>
       </c>
       <c r="Q158" t="n">
-        <v>4226</v>
+        <v>1884</v>
       </c>
       <c r="R158" t="n">
-        <v>-48149</v>
+        <v>-53128</v>
       </c>
       <c r="S158" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="159">
@@ -7536,50 +7540,56 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H159" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I159" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="I159" t="n">
+        <v>3.32</v>
+      </c>
       <c r="J159" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K159" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="K159" t="n">
+        <v>18</v>
+      </c>
       <c r="L159" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>-1.87</v>
+        <v>0.864</v>
       </c>
       <c r="N159" t="n">
-        <v>-38258</v>
+        <v>-18508</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P159" t="n">
-        <v>-79635</v>
+        <v>-52375</v>
       </c>
       <c r="Q159" t="n">
-        <v>4778</v>
+        <v>4226</v>
       </c>
       <c r="R159" t="n">
-        <v>-74857</v>
+        <v>-48149</v>
       </c>
       <c r="S159" t="n">
-        <v>1369</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="160">
@@ -7595,56 +7605,50 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>09/21~09/25</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0.51</v>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K160" t="n">
-        <v>1</v>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="M160" t="n">
-        <v>-1.701</v>
+        <v>-1.87</v>
       </c>
       <c r="N160" t="n">
-        <v>-9977</v>
+        <v>-38258</v>
       </c>
       <c r="O160" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>-29930</v>
+        <v>-79635</v>
       </c>
       <c r="Q160" t="n">
-        <v>2167</v>
+        <v>4778</v>
       </c>
       <c r="R160" t="n">
-        <v>-27764</v>
+        <v>-74857</v>
       </c>
       <c r="S160" t="n">
-        <v>1353</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="161">
@@ -7660,50 +7664,56 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H161" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J161" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-2.222</v>
+        <v>-1.701</v>
       </c>
       <c r="N161" t="n">
-        <v>-21055</v>
+        <v>-9977</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="P161" t="n">
-        <v>-26698</v>
+        <v>-29930</v>
       </c>
       <c r="Q161" t="n">
-        <v>2047</v>
+        <v>2167</v>
       </c>
       <c r="R161" t="n">
-        <v>-24651</v>
+        <v>-27764</v>
       </c>
       <c r="S161" t="n">
-        <v>1371</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="162">
@@ -7719,46 +7729,50 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>10/12~10/16</t>
+          <t>10/05~10/09</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>100</v>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="n">
-        <v>14</v>
-      </c>
-      <c r="L162" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>5</v>
+      </c>
       <c r="M162" t="n">
-        <v>11.734</v>
+        <v>-2.222</v>
       </c>
       <c r="N162" t="n">
-        <v>82725</v>
-      </c>
-      <c r="O162" t="inlineStr"/>
+        <v>-21055</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
       <c r="P162" t="n">
-        <v>79775</v>
+        <v>-26698</v>
       </c>
       <c r="Q162" t="n">
-        <v>1210</v>
+        <v>2047</v>
       </c>
       <c r="R162" t="n">
-        <v>80985</v>
+        <v>-24651</v>
       </c>
       <c r="S162" t="n">
-        <v>1352</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="163">
@@ -7774,175 +7788,175 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>10/12~10/16</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>100</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>14</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>11.734</v>
+      </c>
+      <c r="N163" t="n">
+        <v>82725</v>
+      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>79775</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>1210</v>
+      </c>
+      <c r="R163" t="n">
+        <v>80985</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
           <t>10/19~10/23</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>2</v>
-      </c>
-      <c r="E163" t="n">
+      <c r="D164" t="n">
+        <v>4</v>
+      </c>
+      <c r="E164" t="n">
         <v>50</v>
       </c>
-      <c r="F163" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G163" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H163" t="n">
+      <c r="F164" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J164" t="n">
         <v>4.83</v>
       </c>
-      <c r="I163" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J163" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="K163" t="n">
-        <v>16</v>
-      </c>
-      <c r="L163" t="n">
-        <v>5</v>
-      </c>
-      <c r="M163" t="n">
-        <v>-1.647</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-400</v>
-      </c>
-      <c r="O163" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="P163" t="n">
-        <v>7563</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>2450</v>
-      </c>
-      <c r="R163" t="n">
-        <v>10013</v>
-      </c>
-      <c r="S163" t="n">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="K164" t="n">
+        <v>11</v>
+      </c>
+      <c r="L164" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-0.794</v>
+      </c>
+      <c r="N164" t="n">
+        <v>-121</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P164" t="n">
+        <v>7930</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>3974</v>
+      </c>
+      <c r="R164" t="n">
+        <v>11904</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E164" s="2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I164" s="2" t="n">
+      <c r="D165" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I165" s="2" t="n">
         <v>11.73</v>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="J165" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K164" s="2" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="M164" s="2" t="n">
-        <v>-1.231</v>
-      </c>
-      <c r="N164" s="2" t="n">
-        <v>-8217</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P164" s="2" t="n">
-        <v>-156313</v>
-      </c>
-      <c r="Q164" s="2" t="n">
-        <v>18762</v>
-      </c>
-      <c r="R164" s="2" t="n">
-        <v>-137551</v>
-      </c>
-      <c r="S164" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>US_TR_ADD1</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="n">
-        <v>100</v>
-      </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="n">
-        <v>5</v>
-      </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="n">
-        <v>8.897</v>
-      </c>
-      <c r="N166" t="n">
-        <v>21615</v>
-      </c>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="n">
-        <v>21615</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>355</v>
-      </c>
-      <c r="R166" t="n">
-        <v>21970</v>
-      </c>
-      <c r="S166" t="n">
-        <v>1352</v>
-      </c>
+      <c r="K165" s="2" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>-1.108</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>-7419</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>-155946</v>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>20286</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>-135660</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7957,7 +7971,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10/12~10/16</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7968,325 +7982,329 @@
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>6.68</v>
+        <v>8.9</v>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>6.68</v>
+        <v>8.9</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="n">
-        <v>6.68</v>
+        <v>8.897</v>
       </c>
       <c r="N167" t="n">
-        <v>57221</v>
+        <v>21615</v>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="n">
-        <v>57221</v>
+        <v>21615</v>
       </c>
       <c r="Q167" t="n">
-        <v>1239</v>
+        <v>355</v>
       </c>
       <c r="R167" t="n">
-        <v>58460</v>
+        <v>21970</v>
       </c>
       <c r="S167" t="n">
         <v>1352</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>10/12~10/16</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>100</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="n">
+        <v>12</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="N168" t="n">
+        <v>57221</v>
+      </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
+        <v>57221</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>1239</v>
+      </c>
+      <c r="R168" t="n">
+        <v>58460</v>
+      </c>
+      <c r="S168" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>US_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10/19~10/23</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>6</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-3.832</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-8293</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>-8293</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>297</v>
+      </c>
+      <c r="R169" t="n">
+        <v>-7996</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n">
+      <c r="D170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>23514</v>
+      </c>
+      <c r="O170" s="2" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>70543</v>
+      </c>
+      <c r="Q170" s="2" t="n">
+        <v>1891</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>72434</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
         <v>2</v>
       </c>
-      <c r="E168" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="n">
-        <v>7.788</v>
-      </c>
-      <c r="N168" s="2" t="n">
-        <v>39418</v>
-      </c>
-      <c r="O168" s="2" t="inlineStr"/>
-      <c r="P168" s="2" t="n">
-        <v>78836</v>
-      </c>
-      <c r="Q168" s="2" t="n">
-        <v>1594</v>
-      </c>
-      <c r="R168" s="2" t="n">
-        <v>80430</v>
-      </c>
-      <c r="S168" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R172" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E170" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="n">
+      <c r="E173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="n">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="n">
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M170" t="n">
+      <c r="M173" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N170" t="n">
+      <c r="N173" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
+      <c r="O173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q170" t="n">
+      <c r="Q173" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R170" t="n">
+      <c r="R173" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S170" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M171" s="2" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N171" s="2" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" s="2" t="n">
-        <v>-54889</v>
-      </c>
-      <c r="Q171" s="2" t="n">
-        <v>1054</v>
-      </c>
-      <c r="R171" s="2" t="n">
-        <v>-53835</v>
-      </c>
-      <c r="S171" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>17</v>
-      </c>
-      <c r="E173" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F173" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G173" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H173" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I173" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J173" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L173" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M173" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N173" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O173" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P173" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R173" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S173" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>7</v>
-      </c>
-      <c r="E174" t="n">
-        <v>100</v>
-      </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N174" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q174" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R174" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S174" t="n">
-        <v>1383</v>
-      </c>
+      <c r="S173" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8301,241 +8319,304 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>17</v>
+      </c>
+      <c r="E175" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G175" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I175" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J175" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M175" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O175" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P175" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R175" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S175" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>7</v>
+      </c>
+      <c r="E176" t="n">
+        <v>100</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N176" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R176" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S176" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D177" t="n">
         <v>4</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E177" t="n">
         <v>50</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F177" t="n">
         <v>2.51</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G177" t="n">
         <v>11.43</v>
       </c>
-      <c r="H175" t="n">
+      <c r="H177" t="n">
         <v>2.87</v>
       </c>
-      <c r="I175" t="n">
+      <c r="I177" t="n">
         <v>12</v>
       </c>
-      <c r="J175" t="n">
+      <c r="J177" t="n">
         <v>4.94</v>
       </c>
-      <c r="K175" t="n">
+      <c r="K177" t="n">
         <v>14</v>
       </c>
-      <c r="L175" t="n">
+      <c r="L177" t="n">
         <v>14</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M177" t="n">
         <v>4.282</v>
       </c>
-      <c r="N175" t="n">
+      <c r="N177" t="n">
         <v>7910</v>
       </c>
-      <c r="O175" t="n">
+      <c r="O177" t="n">
         <v>2.51</v>
       </c>
-      <c r="P175" t="n">
+      <c r="P177" t="n">
         <v>-912</v>
       </c>
-      <c r="Q175" t="n">
+      <c r="Q177" t="n">
         <v>635</v>
       </c>
-      <c r="R175" t="n">
+      <c r="R177" t="n">
         <v>-278</v>
       </c>
-      <c r="S175" t="n">
+      <c r="S177" t="n">
         <v>1369</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D178" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E178" s="2" t="n">
         <v>64.3</v>
       </c>
-      <c r="F176" s="2" t="n">
+      <c r="F178" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="G176" s="2" t="n">
+      <c r="G178" s="2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H176" s="2" t="n">
+      <c r="H178" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I176" s="2" t="n">
+      <c r="I178" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J178" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K176" s="2" t="n">
+      <c r="K178" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L176" s="2" t="n">
+      <c r="L178" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M176" s="2" t="n">
+      <c r="M178" s="2" t="n">
         <v>3.779</v>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N178" s="2" t="n">
         <v>7875</v>
       </c>
-      <c r="O176" s="2" t="n">
+      <c r="O178" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P176" s="2" t="n">
+      <c r="P178" s="2" t="n">
         <v>220281</v>
       </c>
-      <c r="Q176" s="2" t="n">
+      <c r="Q178" s="2" t="n">
         <v>9734</v>
       </c>
-      <c r="R176" s="2" t="n">
+      <c r="R178" s="2" t="n">
         <v>230014</v>
       </c>
-      <c r="S176" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="S178" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="n">
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
         <v>0.54</v>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="n">
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="n">
         <v>0.54</v>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="n">
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="n">
         <v>12</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M180" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N178" t="n">
+      <c r="N180" t="n">
         <v>-1280</v>
       </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q178" t="n">
+      <c r="Q180" t="n">
         <v>208</v>
       </c>
-      <c r="R178" t="n">
+      <c r="R180" t="n">
         <v>-1072</v>
       </c>
-      <c r="S178" t="n">
+      <c r="S180" t="n">
         <v>1383</v>
       </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M179" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="N179" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="Q179" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="R179" s="2" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="S179" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -8549,34 +8630,50 @@
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="2" t="inlineStr"/>
-      <c r="F181" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="2" t="inlineStr"/>
-      <c r="N181" s="2" t="inlineStr"/>
-      <c r="O181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P181" s="2" t="n">
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="Q181" s="2" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="R181" s="2" t="n">
-        <v>0</v>
+        <v>-1072</v>
       </c>
       <c r="S181" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -8615,232 +8712,153 @@
       <c r="S183" s="2" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr"/>
+      <c r="P185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D185" t="n">
+      <c r="D187" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E187" t="n">
         <v>100</v>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="n">
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="n">
         <v>2.1</v>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="n">
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="n">
         <v>2.1</v>
       </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="n">
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="n">
         <v>52.73</v>
       </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="n">
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="n">
         <v>2.102</v>
       </c>
-      <c r="N185" t="n">
+      <c r="N187" t="n">
         <v>2341</v>
       </c>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="n">
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="n">
         <v>2341</v>
       </c>
-      <c r="Q185" t="n">
+      <c r="Q187" t="n">
         <v>34</v>
       </c>
-      <c r="R185" t="n">
+      <c r="R187" t="n">
         <v>2375</v>
       </c>
-      <c r="S185" t="n">
+      <c r="S187" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
+      <c r="D188" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E188" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="n">
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="2" t="n">
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="n">
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="n">
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N186" s="2" t="n">
+      <c r="N188" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O186" s="2" t="inlineStr"/>
-      <c r="P186" s="2" t="n">
+      <c r="O188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q186" s="2" t="n">
+      <c r="Q188" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R186" s="2" t="n">
+      <c r="R188" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S186" s="2" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" t="n">
-        <v>100</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="n">
-        <v>1</v>
-      </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="n">
-        <v>2.876</v>
-      </c>
-      <c r="N188" t="n">
-        <v>4316</v>
-      </c>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="n">
-        <v>13859</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>327</v>
-      </c>
-      <c r="R188" t="n">
-        <v>14186</v>
-      </c>
-      <c r="S188" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>업비트SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>6</v>
-      </c>
-      <c r="E189" t="n">
-        <v>50</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G189" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="H189" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I189" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="J189" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K189" t="n">
-        <v>1</v>
-      </c>
-      <c r="L189" t="n">
-        <v>1</v>
-      </c>
-      <c r="M189" t="n">
-        <v>2.895</v>
-      </c>
-      <c r="N189" t="n">
-        <v>2294</v>
-      </c>
-      <c r="O189" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P189" t="n">
-        <v>23105</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>1932</v>
-      </c>
-      <c r="R189" t="n">
-        <v>25037</v>
-      </c>
-      <c r="S189" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S188" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8855,56 +8873,46 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>25</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1.17</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H190" t="n">
-        <v>3.45</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="J190" t="n">
-        <v>5.27</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="n">
         <v>1</v>
       </c>
-      <c r="L190" t="n">
-        <v>3.17</v>
-      </c>
+      <c r="L190" t="inlineStr"/>
       <c r="M190" t="n">
-        <v>-1.847</v>
+        <v>2.876</v>
       </c>
       <c r="N190" t="n">
-        <v>-4637</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0.39</v>
-      </c>
+        <v>4316</v>
+      </c>
+      <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
-        <v>-60655</v>
+        <v>13859</v>
       </c>
       <c r="Q190" t="n">
-        <v>2747</v>
+        <v>327</v>
       </c>
       <c r="R190" t="n">
-        <v>-57908</v>
+        <v>14186</v>
       </c>
       <c r="S190" t="n">
-        <v>1371</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="191">
@@ -8920,53 +8928,53 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>10/12~10/16</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D191" t="n">
         <v>6</v>
       </c>
       <c r="E191" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="F191" t="n">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="G191" t="n">
-        <v>3.8</v>
+        <v>10.69</v>
       </c>
       <c r="H191" t="n">
-        <v>6.38</v>
+        <v>4.9</v>
       </c>
       <c r="I191" t="n">
-        <v>8.890000000000001</v>
+        <v>17.63</v>
       </c>
       <c r="J191" t="n">
-        <v>6.46</v>
+        <v>5.38</v>
       </c>
       <c r="K191" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L191" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.409</v>
+        <v>2.895</v>
       </c>
       <c r="N191" t="n">
-        <v>817</v>
+        <v>2294</v>
       </c>
       <c r="O191" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="P191" t="n">
-        <v>2913</v>
+        <v>23105</v>
       </c>
       <c r="Q191" t="n">
-        <v>1390</v>
+        <v>1932</v>
       </c>
       <c r="R191" t="n">
-        <v>4304</v>
+        <v>25037</v>
       </c>
       <c r="S191" t="n">
         <v>1352</v>
@@ -8985,399 +8993,437 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>8</v>
+      </c>
+      <c r="E192" t="n">
+        <v>25</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H192" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I192" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J192" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-1.847</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-4637</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P192" t="n">
+        <v>-60655</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>2747</v>
+      </c>
+      <c r="R192" t="n">
+        <v>-57908</v>
+      </c>
+      <c r="S192" t="n">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>10/12~10/16</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>6</v>
+      </c>
+      <c r="E193" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H193" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="J193" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="N193" t="n">
+        <v>817</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P193" t="n">
+        <v>2913</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>1390</v>
+      </c>
+      <c r="R193" t="n">
+        <v>4304</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>업비트SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
           <t>10/19~10/23</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="n">
-        <v>-2713</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>110</v>
-      </c>
-      <c r="R192" t="n">
-        <v>-2603</v>
-      </c>
-      <c r="S192" t="n">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="D194" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-2.651</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-5304</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>-8617</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>208</v>
+      </c>
+      <c r="R194" t="n">
+        <v>-8409</v>
+      </c>
+      <c r="S194" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-Top3</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E193" s="2" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="F193" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G193" s="2" t="n">
+      <c r="D195" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G195" s="2" t="n">
         <v>5.61</v>
       </c>
-      <c r="H193" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I193" s="2" t="n">
+      <c r="H195" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="I195" s="2" t="n">
         <v>17.63</v>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J195" s="2" t="n">
         <v>6.46</v>
       </c>
-      <c r="K193" s="2" t="n">
+      <c r="K195" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="L193" s="2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="M193" s="2" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="N193" s="2" t="n">
-        <v>-672</v>
-      </c>
-      <c r="O193" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P193" s="2" t="n">
-        <v>-23491</v>
-      </c>
-      <c r="Q193" s="2" t="n">
-        <v>6506</v>
-      </c>
-      <c r="R193" s="2" t="n">
-        <v>-16984</v>
-      </c>
-      <c r="S193" s="2" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="L195" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>-1075</v>
+      </c>
+      <c r="O195" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P195" s="2" t="n">
+        <v>-29395</v>
+      </c>
+      <c r="Q195" s="2" t="n">
+        <v>6604</v>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>-22790</v>
+      </c>
+      <c r="S195" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>09/21~09/25</t>
         </is>
       </c>
-      <c r="D195" t="n">
+      <c r="D197" t="n">
         <v>11</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E197" t="n">
         <v>36.4</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F197" t="n">
         <v>3.92</v>
       </c>
-      <c r="G195" t="n">
+      <c r="G197" t="n">
         <v>3.1</v>
       </c>
-      <c r="H195" t="n">
+      <c r="H197" t="n">
         <v>0.79</v>
       </c>
-      <c r="I195" t="n">
+      <c r="I197" t="n">
         <v>6.36</v>
       </c>
-      <c r="J195" t="n">
+      <c r="J197" t="n">
         <v>1.95</v>
       </c>
-      <c r="K195" t="n">
+      <c r="K197" t="n">
         <v>753.65</v>
       </c>
-      <c r="L195" t="n">
+      <c r="L197" t="n">
         <v>197.67</v>
       </c>
-      <c r="M195" t="n">
+      <c r="M197" t="n">
         <v>0.625</v>
       </c>
-      <c r="N195" t="n">
+      <c r="N197" t="n">
         <v>1249</v>
       </c>
-      <c r="O195" t="n">
+      <c r="O197" t="n">
         <v>2.24</v>
       </c>
-      <c r="P195" t="n">
+      <c r="P197" t="n">
         <v>13742</v>
       </c>
-      <c r="Q195" t="n">
+      <c r="Q197" t="n">
         <v>2208</v>
       </c>
-      <c r="R195" t="n">
+      <c r="R197" t="n">
         <v>15950</v>
       </c>
-      <c r="S195" t="n">
+      <c r="S197" t="n">
         <v>1353</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>09/28~10/02</t>
         </is>
       </c>
-      <c r="D196" t="n">
+      <c r="D198" t="n">
         <v>22</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E198" t="n">
         <v>27.3</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F198" t="n">
         <v>2.05</v>
       </c>
-      <c r="G196" t="n">
+      <c r="G198" t="n">
         <v>1.89</v>
       </c>
-      <c r="H196" t="n">
+      <c r="H198" t="n">
         <v>0.92</v>
       </c>
-      <c r="I196" t="n">
+      <c r="I198" t="n">
         <v>6.1</v>
       </c>
-      <c r="J196" t="n">
+      <c r="J198" t="n">
         <v>2.94</v>
       </c>
-      <c r="K196" t="n">
+      <c r="K198" t="n">
         <v>208.19</v>
       </c>
-      <c r="L196" t="n">
+      <c r="L198" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="M196" t="n">
+      <c r="M198" t="n">
         <v>-0.155</v>
       </c>
-      <c r="N196" t="n">
+      <c r="N198" t="n">
         <v>-311</v>
       </c>
-      <c r="O196" t="n">
+      <c r="O198" t="n">
         <v>0.77</v>
       </c>
-      <c r="P196" t="n">
+      <c r="P198" t="n">
         <v>-6837</v>
       </c>
-      <c r="Q196" t="n">
+      <c r="Q198" t="n">
         <v>4398</v>
       </c>
-      <c r="R196" t="n">
+      <c r="R198" t="n">
         <v>-2439</v>
       </c>
-      <c r="S196" t="n">
+      <c r="S198" t="n">
         <v>1352</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>업비트SCO-15분</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n">
+      <c r="D199" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E197" s="2" t="n">
+      <c r="E199" s="2" t="n">
         <v>30.3</v>
       </c>
-      <c r="F197" s="2" t="n">
+      <c r="F199" s="2" t="n">
         <v>2.69</v>
       </c>
-      <c r="G197" s="2" t="n">
+      <c r="G199" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="H197" s="2" t="n">
+      <c r="H199" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="I197" s="2" t="n">
+      <c r="I199" s="2" t="n">
         <v>6.36</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J199" s="2" t="n">
         <v>2.94</v>
       </c>
-      <c r="K197" s="2" t="n">
+      <c r="K199" s="2" t="n">
         <v>426.38</v>
       </c>
-      <c r="L197" s="2" t="n">
+      <c r="L199" s="2" t="n">
         <v>129.08</v>
       </c>
-      <c r="M197" s="2" t="n">
+      <c r="M199" s="2" t="n">
         <v>0.105</v>
       </c>
-      <c r="N197" s="2" t="n">
+      <c r="N199" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="O197" s="2" t="n">
+      <c r="O199" s="2" t="n">
         <v>1.17</v>
       </c>
-      <c r="P197" s="2" t="n">
+      <c r="P199" s="2" t="n">
         <v>6905</v>
       </c>
-      <c r="Q197" s="2" t="n">
+      <c r="Q199" s="2" t="n">
         <v>6606</v>
       </c>
-      <c r="R197" s="2" t="n">
+      <c r="R199" s="2" t="n">
         <v>13511</v>
       </c>
-      <c r="S197" s="2" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>09/21~09/25</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>61</v>
-      </c>
-      <c r="R199" t="n">
-        <v>973</v>
-      </c>
-      <c r="S199" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>바이낸스SCO-Top3</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>09/28~10/02</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>6</v>
-      </c>
-      <c r="E200" t="n">
-        <v>50</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="G200" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H200" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I200" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J200" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="K200" t="n">
-        <v>1</v>
-      </c>
-      <c r="L200" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M200" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="N200" t="n">
-        <v>1885</v>
-      </c>
-      <c r="O200" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P200" t="n">
-        <v>18124</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>1048</v>
-      </c>
-      <c r="R200" t="n">
-        <v>19173</v>
-      </c>
-      <c r="S200" t="n">
-        <v>1352</v>
-      </c>
+      <c r="S199" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9392,56 +9438,34 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>10/05~10/09</t>
+          <t>09/21~09/25</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>9</v>
-      </c>
-      <c r="E201" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G201" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="H201" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="I201" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="J201" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="L201" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M201" t="n">
-        <v>1.191</v>
-      </c>
-      <c r="N201" t="n">
-        <v>3288</v>
-      </c>
-      <c r="O201" t="n">
-        <v>1.73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
       <c r="P201" t="n">
-        <v>28879</v>
+        <v>912</v>
       </c>
       <c r="Q201" t="n">
-        <v>1694</v>
+        <v>61</v>
       </c>
       <c r="R201" t="n">
-        <v>30573</v>
+        <v>973</v>
       </c>
       <c r="S201" t="n">
-        <v>1371</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="202">
@@ -9457,360 +9481,366 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>10/12~10/16</t>
+          <t>09/28~10/02</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E202" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F202" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29</v>
+        <v>7.01</v>
       </c>
       <c r="H202" t="n">
-        <v>5.22</v>
+        <v>6.41</v>
       </c>
       <c r="I202" t="n">
-        <v>7.33</v>
+        <v>10.66</v>
       </c>
       <c r="J202" t="n">
-        <v>7.89</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L202" t="n">
         <v>0.67</v>
       </c>
       <c r="M202" t="n">
-        <v>-2.346</v>
+        <v>0.299</v>
       </c>
       <c r="N202" t="n">
-        <v>-6343</v>
+        <v>1885</v>
       </c>
       <c r="O202" t="n">
-        <v>0.4</v>
+        <v>1.28</v>
       </c>
       <c r="P202" t="n">
-        <v>-57769</v>
+        <v>18124</v>
       </c>
       <c r="Q202" t="n">
-        <v>1380</v>
+        <v>1048</v>
       </c>
       <c r="R202" t="n">
-        <v>-56389</v>
+        <v>19173</v>
       </c>
       <c r="S202" t="n">
         <v>1352</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>바이낸스SCO-Top3</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>10/05~10/09</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>9</v>
+      </c>
+      <c r="E203" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G203" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H203" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I203" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="J203" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="N203" t="n">
+        <v>3288</v>
+      </c>
+      <c r="O203" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P203" t="n">
+        <v>28879</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>1694</v>
+      </c>
+      <c r="R203" t="n">
+        <v>30573</v>
+      </c>
+      <c r="S203" t="n">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>10/12~10/16</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>8</v>
+      </c>
+      <c r="E204" t="n">
+        <v>25</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="H204" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="I204" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="J204" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M204" t="n">
+        <v>-2.346</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-6343</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P204" t="n">
+        <v>-57769</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>1380</v>
+      </c>
+      <c r="R204" t="n">
+        <v>-56389</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>바이낸스SCO-Top3</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n">
+      <c r="D205" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="E205" s="2" t="n">
         <v>47.8</v>
       </c>
-      <c r="F203" s="2" t="n">
+      <c r="F205" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="G203" s="2" t="n">
+      <c r="G205" s="2" t="n">
         <v>5.37</v>
       </c>
-      <c r="H203" s="2" t="n">
+      <c r="H205" s="2" t="n">
         <v>5.44</v>
       </c>
-      <c r="I203" s="2" t="n">
+      <c r="I205" s="2" t="n">
         <v>11.86</v>
       </c>
-      <c r="J203" s="2" t="n">
+      <c r="J205" s="2" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="K203" s="2" t="n">
+      <c r="K205" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L203" s="2" t="n">
+      <c r="L205" s="2" t="n">
         <v>0.83</v>
       </c>
-      <c r="M203" s="2" t="n">
+      <c r="M205" s="2" t="n">
         <v>-0.272</v>
       </c>
-      <c r="N203" s="2" t="n">
+      <c r="N205" s="2" t="n">
         <v>-428</v>
       </c>
-      <c r="O203" s="2" t="n">
+      <c r="O205" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="P203" s="2" t="n">
+      <c r="P205" s="2" t="n">
         <v>-9854</v>
       </c>
-      <c r="Q203" s="2" t="n">
+      <c r="Q205" s="2" t="n">
         <v>4183</v>
       </c>
-      <c r="R203" s="2" t="n">
+      <c r="R205" s="2" t="n">
         <v>-5670</v>
       </c>
-      <c r="S203" s="2" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="S205" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
         <is>
           <t>10/05~10/09</t>
         </is>
       </c>
-      <c r="D205" t="n">
+      <c r="D207" t="n">
         <v>2</v>
       </c>
-      <c r="E205" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="n">
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="n">
         <v>3.13</v>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="n">
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="n">
         <v>4.14</v>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="n">
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="n">
         <v>1</v>
       </c>
-      <c r="M205" t="n">
+      <c r="M207" t="n">
         <v>-3.133</v>
       </c>
-      <c r="N205" t="n">
+      <c r="N207" t="n">
         <v>-95612</v>
       </c>
-      <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" t="n">
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
         <v>-191223</v>
       </c>
-      <c r="Q205" t="n">
+      <c r="Q207" t="n">
         <v>6904</v>
       </c>
-      <c r="R205" t="n">
+      <c r="R207" t="n">
         <v>-184319</v>
       </c>
-      <c r="S205" t="n">
+      <c r="S207" t="n">
         <v>1371</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>업비트국면v6</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n">
+      <c r="D208" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="n">
+      <c r="E208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="n">
         <v>3.13</v>
       </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="n">
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="n">
         <v>4.14</v>
       </c>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="n">
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M206" s="2" t="n">
+      <c r="M208" s="2" t="n">
         <v>-3.133</v>
       </c>
-      <c r="N206" s="2" t="n">
+      <c r="N208" s="2" t="n">
         <v>-95612</v>
       </c>
-      <c r="O206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" s="2" t="n">
+      <c r="O208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" s="2" t="n">
         <v>-191223</v>
       </c>
-      <c r="Q206" s="2" t="n">
+      <c r="Q208" s="2" t="n">
         <v>6904</v>
       </c>
-      <c r="R206" s="2" t="n">
+      <c r="R208" s="2" t="n">
         <v>-184319</v>
       </c>
-      <c r="S206" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>2</v>
-      </c>
-      <c r="E208" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="n">
-        <v>1</v>
-      </c>
-      <c r="M208" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N208" t="n">
-        <v>-7586</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>-15172</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>485</v>
-      </c>
-      <c r="R208" t="n">
-        <v>-14686</v>
-      </c>
-      <c r="S208" t="n">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>4</v>
-      </c>
-      <c r="E209" t="n">
-        <v>25</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G209" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H209" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I209" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J209" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K209" t="n">
-        <v>1</v>
-      </c>
-      <c r="L209" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M209" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N209" t="n">
-        <v>-12569</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P209" t="n">
-        <v>-50275</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>5599</v>
-      </c>
-      <c r="R209" t="n">
-        <v>-44676</v>
-      </c>
-      <c r="S209" t="n">
-        <v>1340</v>
-      </c>
+      <c r="S208" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9825,7 +9855,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -9839,33 +9869,33 @@
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N210" t="n">
-        <v>-2262</v>
+        <v>-7586</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
       </c>
       <c r="P210" t="n">
-        <v>-4524</v>
+        <v>-15172</v>
       </c>
       <c r="Q210" t="n">
-        <v>2769</v>
+        <v>485</v>
       </c>
       <c r="R210" t="n">
-        <v>-1755</v>
+        <v>-14686</v>
       </c>
       <c r="S210" t="n">
         <v>1340</v>
@@ -9884,43 +9914,53 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E211" t="n">
-        <v>100</v>
-      </c>
-      <c r="F211" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G211" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H211" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I211" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J211" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K211" t="n">
-        <v>14</v>
-      </c>
-      <c r="L211" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M211" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N211" t="n">
-        <v>15322</v>
-      </c>
-      <c r="O211" t="inlineStr"/>
+        <v>-12569</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P211" t="n">
-        <v>45967</v>
+        <v>-50275</v>
       </c>
       <c r="Q211" t="n">
-        <v>4029</v>
+        <v>5599</v>
       </c>
       <c r="R211" t="n">
-        <v>49995</v>
+        <v>-44676</v>
       </c>
       <c r="S211" t="n">
         <v>1340</v>
@@ -9939,11 +9979,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -9953,36 +9993,36 @@
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M212" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N212" t="n">
-        <v>-28997</v>
+        <v>-2262</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
       </c>
       <c r="P212" t="n">
-        <v>-86990</v>
+        <v>-4524</v>
       </c>
       <c r="Q212" t="n">
-        <v>13787</v>
+        <v>2769</v>
       </c>
       <c r="R212" t="n">
-        <v>-73203</v>
+        <v>-1755</v>
       </c>
       <c r="S212" t="n">
-        <v>1411</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="213">
@@ -9998,50 +10038,46 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="n">
+        <v>14</v>
+      </c>
+      <c r="L213" t="inlineStr"/>
       <c r="M213" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N213" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
+        <v>15322</v>
+      </c>
+      <c r="O213" t="inlineStr"/>
       <c r="P213" t="n">
-        <v>-68185</v>
+        <v>45967</v>
       </c>
       <c r="Q213" t="n">
-        <v>5784</v>
+        <v>4029</v>
       </c>
       <c r="R213" t="n">
-        <v>-62401</v>
+        <v>49995</v>
       </c>
       <c r="S213" t="n">
-        <v>1383</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="214">
@@ -10057,7 +10093,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>09/07~09/11</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -10071,36 +10107,36 @@
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
-        <v>3.42</v>
+        <v>0.86</v>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="n">
-        <v>20</v>
+        <v>4.67</v>
       </c>
       <c r="M214" t="n">
-        <v>-3.417</v>
+        <v>-0.864</v>
       </c>
       <c r="N214" t="n">
-        <v>-120621</v>
+        <v>-28997</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
       </c>
       <c r="P214" t="n">
-        <v>-324235</v>
+        <v>-86990</v>
       </c>
       <c r="Q214" t="n">
-        <v>7584</v>
+        <v>13787</v>
       </c>
       <c r="R214" t="n">
-        <v>-316651</v>
+        <v>-73203</v>
       </c>
       <c r="S214" t="n">
-        <v>1338</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="215">
@@ -10116,224 +10152,228 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+    